--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD4D83B-931F-422B-91BA-E4DFE42A2C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BA09AC-1FEE-483B-8A4A-C13EFF566158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse V2" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="108">
   <si>
     <t>N</t>
   </si>
@@ -352,6 +352,18 @@
   </si>
   <si>
     <t>Gg</t>
+  </si>
+  <si>
+    <t>Unité exiobase</t>
+  </si>
+  <si>
+    <t>Unité affichage</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>Égalité</t>
   </si>
 </sst>
 </file>
@@ -725,15 +737,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE3858F0-9336-48E3-86F2-B1B2EA88DE16}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.15234375" customWidth="1"/>
-    <col min="2" max="2" width="6.921875" customWidth="1"/>
-    <col min="5" max="5" width="14.07421875" customWidth="1"/>
+    <col min="1" max="1" width="21.1796875" customWidth="1"/>
+    <col min="2" max="2" width="6.90625" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>94</v>
       </c>
@@ -765,7 +777,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -797,7 +809,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -829,7 +841,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>84</v>
       </c>
@@ -840,7 +852,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -872,12 +884,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -918,7 +930,7 @@
         <v>2764949.7572000008</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -959,12 +971,12 @@
         <v>2.1722746361223184E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -977,14 +989,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.15234375" customWidth="1"/>
-    <col min="2" max="2" width="13.07421875" customWidth="1"/>
-    <col min="5" max="5" width="14.07421875" customWidth="1"/>
+    <col min="1" max="1" width="21.1796875" customWidth="1"/>
+    <col min="2" max="2" width="13.08984375" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>94</v>
       </c>
@@ -1010,7 +1022,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1036,7 +1048,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>84</v>
       </c>
@@ -1044,7 +1056,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1070,14 +1082,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="B7">
         <f>((Population!C116/100)*B2)*1000</f>
@@ -1104,11 +1116,11 @@
         <v>14.465802328523662</v>
       </c>
       <c r="H7">
-        <f>(H2*Population!C115)/1000</f>
-        <v>2764.9497572000009</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+        <f>(H2*Population!C115)*0.000277778</f>
+        <v>768.04221365550188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1141,19 +1153,19 @@
         <v>2.1722746361223184E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="B12" t="s">
         <v>96</v>
@@ -1174,10 +1186,10 @@
         <v>103</v>
       </c>
       <c r="H12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>102</v>
       </c>
@@ -1200,10 +1212,14 @@
         <v>1000000</v>
       </c>
       <c r="H13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+        <f>1/0.000277778</f>
+        <v>3599.9971200023037</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>104</v>
+      </c>
       <c r="B14" t="s">
         <v>99</v>
       </c>
@@ -1234,13 +1250,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95CE491-5889-4A7E-A6ED-A3FC6F8FA184}">
   <dimension ref="A1:I121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.3828125" customWidth="1"/>
-    <col min="2" max="2" width="12.84375" customWidth="1"/>
+    <col min="1" max="1" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="48.45" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="48.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -1254,7 +1270,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -1268,7 +1284,7 @@
         <v>722828.87800000003</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -1282,7 +1298,7 @@
         <v>725449.93</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -1296,7 +1312,7 @@
         <v>727517.08100000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -1310,7 +1326,7 @@
         <v>727716.30099999998</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -1324,7 +1340,7 @@
         <v>728295.52300000004</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -1338,7 +1354,7 @@
         <v>729473.78</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -1352,7 +1368,7 @@
         <v>729287.41799999995</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -1366,7 +1382,7 @@
         <v>729452.23499999999</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -1380,7 +1396,7 @@
         <v>729398.01599999995</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -1394,7 +1410,7 @@
         <v>728330.19400000002</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -1408,7 +1424,7 @@
         <v>728105.16299999994</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -1422,7 +1438,7 @@
         <v>728223.255</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -1436,7 +1452,7 @@
         <v>728252.19</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -1450,7 +1466,7 @@
         <v>730000.83799999999</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -1464,7 +1480,7 @@
         <v>730751.91200000001</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -1478,7 +1494,7 @@
         <v>731740.46699999995</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -1492,7 +1508,7 @@
         <v>732352.56200000003</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -1506,7 +1522,7 @@
         <v>733015.57299999997</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -1520,7 +1536,7 @@
         <v>734777.08299999998</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -1534,7 +1550,7 @@
         <v>736321.8</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -1548,7 +1564,7 @@
         <v>737549.64</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -1562,7 +1578,7 @@
         <v>738740.995</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -1576,7 +1592,7 @@
         <v>739977.41500000004</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -1590,7 +1606,7 @@
         <v>740940.27500000002</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -1604,7 +1620,7 @@
         <v>742001.28700000001</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -1618,7 +1634,7 @@
         <v>743279.99399999995</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -1632,7 +1648,7 @@
         <v>745194.076</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -1646,7 +1662,7 @@
         <v>746812.14</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -1660,7 +1676,7 @@
         <v>748046.28399999999</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -1674,7 +1690,7 @@
         <v>749083.44900000002</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -1688,7 +1704,7 @@
         <v>749924.80500000005</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -1702,7 +1718,7 @@
         <v>749123.28399999999</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -1716,7 +1732,7 @@
         <v>748103.72499999998</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -1730,7 +1746,7 @@
         <v>745825.46</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -1744,7 +1760,7 @@
         <v>745380.28899999999</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>2025</v>
       </c>
@@ -1758,7 +1774,7 @@
         <v>744787.35800000001</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>2026</v>
       </c>
@@ -1772,7 +1788,7 @@
         <v>744010.30599999998</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>2027</v>
       </c>
@@ -1786,7 +1802,7 @@
         <v>742954.41700000002</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>2028</v>
       </c>
@@ -1800,7 +1816,7 @@
         <v>741789.71200000006</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>2029</v>
       </c>
@@ -1814,7 +1830,7 @@
         <v>740527.35400000005</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>2030</v>
       </c>
@@ -1828,7 +1844,7 @@
         <v>739157.09199999995</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>2031</v>
       </c>
@@ -1842,7 +1858,7 @@
         <v>737709.81599999999</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>2032</v>
       </c>
@@ -1856,7 +1872,7 @@
         <v>736143.12100000004</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>2033</v>
       </c>
@@ -1870,7 +1886,7 @@
         <v>734589.397</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>2034</v>
       </c>
@@ -1884,7 +1900,7 @@
         <v>733012.58799999999</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>2035</v>
       </c>
@@ -1898,7 +1914,7 @@
         <v>731408.71900000004</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>2036</v>
       </c>
@@ -1912,7 +1928,7 @@
         <v>729772.30099999998</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>2037</v>
       </c>
@@ -1926,7 +1942,7 @@
         <v>728095.92099999997</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>2038</v>
       </c>
@@ -1940,7 +1956,7 @@
         <v>726400.87600000005</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>2039</v>
       </c>
@@ -1954,7 +1970,7 @@
         <v>724703.647</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>2040</v>
       </c>
@@ -1968,7 +1984,7 @@
         <v>722958.26199999999</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>2041</v>
       </c>
@@ -1982,7 +1998,7 @@
         <v>721244.98499999999</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>2042</v>
       </c>
@@ -1996,7 +2012,7 @@
         <v>719536.97499999998</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>2043</v>
       </c>
@@ -2010,7 +2026,7 @@
         <v>717819.94799999997</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>2044</v>
       </c>
@@ -2024,7 +2040,7 @@
         <v>716032.201</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>2045</v>
       </c>
@@ -2038,7 +2054,7 @@
         <v>714211.69299999997</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>2046</v>
       </c>
@@ -2052,7 +2068,7 @@
         <v>712348.01199999999</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>2047</v>
       </c>
@@ -2066,7 +2082,7 @@
         <v>710440.74300000002</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>2048</v>
       </c>
@@ -2080,7 +2096,7 @@
         <v>708437.35199999996</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>2049</v>
       </c>
@@ -2094,7 +2110,7 @@
         <v>706353.86800000002</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>2050</v>
       </c>
@@ -2108,7 +2124,7 @@
         <v>704160.17799999996</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>2051</v>
       </c>
@@ -2122,7 +2138,7 @@
         <v>701895.34</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>2052</v>
       </c>
@@ -2136,7 +2152,7 @@
         <v>699538.17700000003</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>2053</v>
       </c>
@@ -2150,7 +2166,7 @@
         <v>697115.44700000004</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>2054</v>
       </c>
@@ -2164,7 +2180,7 @@
         <v>694513.78700000001</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>2055</v>
       </c>
@@ -2178,7 +2194,7 @@
         <v>691851.88199999998</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>2056</v>
       </c>
@@ -2192,7 +2208,7 @@
         <v>689074.61100000003</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>2057</v>
       </c>
@@ -2206,7 +2222,7 @@
         <v>686255.70799999998</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>2058</v>
       </c>
@@ -2220,7 +2236,7 @@
         <v>683407.30299999996</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>2059</v>
       </c>
@@ -2234,7 +2250,7 @@
         <v>680520.071</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>2060</v>
       </c>
@@ -2248,7 +2264,7 @@
         <v>677603.74899999995</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>2061</v>
       </c>
@@ -2262,7 +2278,7 @@
         <v>674715.93099999998</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>2062</v>
       </c>
@@ -2276,7 +2292,7 @@
         <v>671815.46400000004</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>2063</v>
       </c>
@@ -2290,7 +2306,7 @@
         <v>668937.91299999994</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>2064</v>
       </c>
@@ -2304,7 +2320,7 @@
         <v>666081.65899999999</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>2065</v>
       </c>
@@ -2318,7 +2334,7 @@
         <v>663254.68299999996</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>2066</v>
       </c>
@@ -2332,7 +2348,7 @@
         <v>660460.06999999995</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>2067</v>
       </c>
@@ -2346,7 +2362,7 @@
         <v>657736.19900000002</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>2068</v>
       </c>
@@ -2360,7 +2376,7 @@
         <v>655082.67299999995</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>2069</v>
       </c>
@@ -2374,7 +2390,7 @@
         <v>652466.40500000003</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>2070</v>
       </c>
@@ -2388,7 +2404,7 @@
         <v>649895.46600000001</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>2071</v>
       </c>
@@ -2402,7 +2418,7 @@
         <v>647385.17299999995</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>2072</v>
       </c>
@@ -2416,7 +2432,7 @@
         <v>644924.50300000003</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>2073</v>
       </c>
@@ -2430,7 +2446,7 @@
         <v>642548.04799999995</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>2074</v>
       </c>
@@ -2444,7 +2460,7 @@
         <v>640200.39800000004</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>2075</v>
       </c>
@@ -2458,7 +2474,7 @@
         <v>637905.63800000004</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>2076</v>
       </c>
@@ -2472,7 +2488,7 @@
         <v>635718.05700000003</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>2077</v>
       </c>
@@ -2486,7 +2502,7 @@
         <v>633586.69099999999</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>2078</v>
       </c>
@@ -2500,7 +2516,7 @@
         <v>631465.69099999999</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>2079</v>
       </c>
@@ -2514,7 +2530,7 @@
         <v>629415.12899999996</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>2080</v>
       </c>
@@ -2528,7 +2544,7 @@
         <v>627404.68799999997</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>2081</v>
       </c>
@@ -2542,7 +2558,7 @@
         <v>625461.88899999997</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>2082</v>
       </c>
@@ -2556,7 +2572,7 @@
         <v>623586.20299999998</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>2083</v>
       </c>
@@ -2570,7 +2586,7 @@
         <v>621727.15399999998</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>2084</v>
       </c>
@@ -2584,7 +2600,7 @@
         <v>619907.59900000005</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>2085</v>
       </c>
@@ -2598,7 +2614,7 @@
         <v>618109.28700000001</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>2086</v>
       </c>
@@ -2612,7 +2628,7 @@
         <v>616324.20200000005</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>2087</v>
       </c>
@@ -2626,7 +2642,7 @@
         <v>614569.38399999996</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>2088</v>
       </c>
@@ -2640,7 +2656,7 @@
         <v>612868.772</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>2089</v>
       </c>
@@ -2654,7 +2670,7 @@
         <v>611200.07799999998</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>2090</v>
       </c>
@@ -2668,7 +2684,7 @@
         <v>609526.97699999996</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>2091</v>
       </c>
@@ -2682,7 +2698,7 @@
         <v>607859.16</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>2092</v>
       </c>
@@ -2696,7 +2712,7 @@
         <v>606237.61699999997</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>2093</v>
       </c>
@@ -2710,7 +2726,7 @@
         <v>604606.87600000005</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>2094</v>
       </c>
@@ -2724,7 +2740,7 @@
         <v>603012.85499999998</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>2095</v>
       </c>
@@ -2738,7 +2754,7 @@
         <v>601427.07799999998</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>2096</v>
       </c>
@@ -2752,7 +2768,7 @@
         <v>599799.50300000003</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>2097</v>
       </c>
@@ -2766,7 +2782,7 @@
         <v>598134.46</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>2098</v>
       </c>
@@ -2780,7 +2796,7 @@
         <v>596471.93000000005</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>2099</v>
       </c>
@@ -2794,7 +2810,7 @@
         <v>594809.66299999994</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>2100</v>
       </c>
@@ -2808,7 +2824,7 @@
         <v>593112.88</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>77</v>
       </c>
@@ -2840,7 +2856,7 @@
         <v>9.639258714121274</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A115" s="11" t="s">
         <v>28</v>
       </c>
@@ -2872,7 +2888,7 @@
         <v>729634.64224242419</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
         <v>24</v>
       </c>
@@ -2904,7 +2920,7 @@
         <v>8.2811143358722195</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
         <v>29</v>
       </c>
@@ -2936,7 +2952,7 @@
         <v>676189.9753048782</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>24</v>
       </c>
@@ -2968,19 +2984,19 @@
         <v>7.0357584289374984</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="3"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="3"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>22</v>
       </c>
@@ -2996,13 +3012,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8683F5-D89E-4384-A263-C6122D6DA873}">
   <dimension ref="A1:AJ45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.69140625" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -3053,7 +3069,7 @@
       <c r="AI1" s="13"/>
       <c r="AJ1" s="13"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>30</v>
       </c>
@@ -3107,7 +3123,7 @@
       <c r="AI2" s="13"/>
       <c r="AJ2" s="13"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
         <v>31</v>
       </c>
@@ -3161,7 +3177,7 @@
       <c r="AI3" s="13"/>
       <c r="AJ3" s="13"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>32</v>
       </c>
@@ -3216,7 +3232,7 @@
       <c r="AI4" s="13"/>
       <c r="AJ4" s="13"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>33</v>
       </c>
@@ -3269,7 +3285,7 @@
       <c r="AI5" s="13"/>
       <c r="AJ5" s="13"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>34</v>
       </c>
@@ -3295,7 +3311,7 @@
         <v>24904675997.177227</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
         <v>35</v>
       </c>
@@ -3321,7 +3337,7 @@
         <v>25612762187.674767</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
         <v>36</v>
       </c>
@@ -3347,7 +3363,7 @@
         <v>26087721958.213924</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
         <v>37</v>
       </c>
@@ -3373,7 +3389,7 @@
         <v>26723818654.148617</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
         <v>38</v>
       </c>
@@ -3399,7 +3415,7 @@
         <v>27468476865.381031</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>39</v>
       </c>
@@ -3425,7 +3441,7 @@
         <v>28176082288.3083</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
         <v>40</v>
       </c>
@@ -3451,7 +3467,7 @@
         <v>29240167861.778976</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
         <v>41</v>
       </c>
@@ -3477,7 +3493,7 @@
         <v>29862791642.623837</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>42</v>
       </c>
@@ -3503,7 +3519,7 @@
         <v>30165942432.463612</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A15" s="13" t="s">
         <v>43</v>
       </c>
@@ -3529,7 +3545,7 @@
         <v>30462092599.50692</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
         <v>44</v>
       </c>
@@ -3555,7 +3571,7 @@
         <v>31221908220.131401</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
         <v>45</v>
       </c>
@@ -3581,7 +3597,7 @@
         <v>31813500020.819954</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
         <v>46</v>
       </c>
@@ -3607,7 +3623,7 @@
         <v>32916700218.346203</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
         <v>47</v>
       </c>
@@ -3633,7 +3649,7 @@
         <v>33919859610.622345</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="13" t="s">
         <v>48</v>
       </c>
@@ -3659,7 +3675,7 @@
         <v>34182103766.776295</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="13" t="s">
         <v>49</v>
       </c>
@@ -3685,7 +3701,7 @@
         <v>32714648377.874294</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="13" t="s">
         <v>50</v>
       </c>
@@ -3712,7 +3728,7 @@
       </c>
       <c r="J22" s="13"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="13" t="s">
         <v>51</v>
       </c>
@@ -3738,7 +3754,7 @@
         <v>34133681735.471703</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
         <v>52</v>
       </c>
@@ -3764,7 +3780,7 @@
         <v>33882036018.543774</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="13" t="s">
         <v>53</v>
       </c>
@@ -3790,7 +3806,7 @@
         <v>33878734646.466373</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="13" t="s">
         <v>54</v>
       </c>
@@ -3816,7 +3832,7 @@
         <v>34469485024.636459</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="13" t="s">
         <v>55</v>
       </c>
@@ -3842,7 +3858,7 @@
         <v>35298868327.366135</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="13" t="s">
         <v>56</v>
       </c>
@@ -3868,7 +3884,7 @@
         <v>36019907345.254646</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="13" t="s">
         <v>57</v>
       </c>
@@ -3894,7 +3910,7 @@
         <v>37119573491.364235</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="13" t="s">
         <v>58</v>
       </c>
@@ -3920,7 +3936,7 @@
         <v>37930710214.837662</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="13" t="s">
         <v>59</v>
       </c>
@@ -3946,7 +3962,7 @@
         <v>38699419341.686249</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="13" t="s">
         <v>60</v>
       </c>
@@ -3972,7 +3988,7 @@
         <v>36574113872.711426</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="13" t="s">
         <v>61</v>
       </c>
@@ -3998,7 +4014,7 @@
         <v>38931911154.245689</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="13" t="s">
         <v>62</v>
       </c>
@@ -4024,7 +4040,7 @@
         <v>40231131436.83564</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="13" t="s">
         <v>63</v>
       </c>
@@ -4050,7 +4066,7 @@
         <v>40177113825.347435</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="13" t="s">
         <v>64</v>
       </c>
@@ -4076,7 +4092,7 @@
         <v>40502412753.686844</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -4099,7 +4115,7 @@
         <v>43631.695837336869</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>73</v>
       </c>
@@ -4122,7 +4138,7 @@
         <v>0.1498424508861913</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="E40" s="11" t="s">
         <v>82</v>
       </c>
@@ -4139,7 +4155,7 @@
         <v>1.5668798264892982</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="E41" s="3" t="s">
         <v>83</v>
       </c>
@@ -4156,7 +4172,7 @@
         <v>5.9042950726820198E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="E42" s="3" t="s">
         <v>81</v>
       </c>
@@ -4173,7 +4189,7 @@
         <v>0.65838190592741441</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>67</v>
       </c>
@@ -4181,7 +4197,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -4189,7 +4205,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>74</v>
       </c>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87BA09AC-1FEE-483B-8A4A-C13EFF566158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641D283A-44E6-44BC-BF35-ED9203F7490B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641D283A-44E6-44BC-BF35-ED9203F7490B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3630FF22-4F24-491F-ABE5-3C8D591A44D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Synthèse V2" sheetId="4" r:id="rId1"/>
-    <sheet name="Synthèse" sheetId="1" r:id="rId2"/>
+    <sheet name="Synthèse" sheetId="1" r:id="rId1"/>
+    <sheet name="DLS" sheetId="5" r:id="rId2"/>
     <sheet name="Population" sheetId="2" r:id="rId3"/>
     <sheet name="Capacité" sheetId="3" r:id="rId4"/>
   </sheets>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="119">
   <si>
     <t>N</t>
   </si>
@@ -66,9 +66,6 @@
     <t>CO2</t>
   </si>
   <si>
-    <t>Km3</t>
-  </si>
-  <si>
     <t>M km2</t>
   </si>
   <si>
@@ -93,9 +90,6 @@
     <t>Budget Global annuel</t>
   </si>
   <si>
-    <t>Egalité</t>
-  </si>
-  <si>
     <t>Capacité</t>
   </si>
   <si>
@@ -300,30 +294,6 @@
     <t>Sols</t>
   </si>
   <si>
-    <t>Correspondances</t>
-  </si>
-  <si>
-    <t>water</t>
-  </si>
-  <si>
-    <t>land_use</t>
-  </si>
-  <si>
-    <t>biogeochemical</t>
-  </si>
-  <si>
-    <t>ghg_emissions</t>
-  </si>
-  <si>
-    <t>msa</t>
-  </si>
-  <si>
-    <t>energy</t>
-  </si>
-  <si>
-    <t>raw_materials</t>
-  </si>
-  <si>
     <t>Nom LP</t>
   </si>
   <si>
@@ -364,6 +334,69 @@
   </si>
   <si>
     <t>Égalité</t>
+  </si>
+  <si>
+    <t>kt</t>
+  </si>
+  <si>
+    <t>Budget annuel par habitant</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>GJ</t>
+  </si>
+  <si>
+    <t>m3</t>
+  </si>
+  <si>
+    <t>m2</t>
+  </si>
+  <si>
+    <t>Égalité (p. hab)</t>
+  </si>
+  <si>
+    <t>Égalité (p. hab) limite haute</t>
+  </si>
+  <si>
+    <t>Current system technology</t>
+  </si>
+  <si>
+    <t>Efficient scenario</t>
+  </si>
+  <si>
+    <t>1000m2/hab.</t>
+  </si>
+  <si>
+    <t>m3/hab./an</t>
+  </si>
+  <si>
+    <t>t/hab/an</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0921800925003027</t>
+  </si>
+  <si>
+    <t>1000km2</t>
+  </si>
+  <si>
+    <t>Égalité (limite haute)</t>
+  </si>
+  <si>
+    <t>Capacité (limite haute)</t>
+  </si>
+  <si>
+    <t>GJ/hab/an</t>
+  </si>
+  <si>
+    <t>https://linkinghub.elsevier.com/retrieve/pii/S0959378020307512</t>
+  </si>
+  <si>
+    <t>Current system technology (p.hab)</t>
+  </si>
+  <si>
+    <t>Efficient scenario (p.hab)</t>
   </si>
 </sst>
 </file>
@@ -373,7 +406,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#\ ###\ ###\ ##0;\-#\ ###\ ###\ ##0;0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,8 +434,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -415,8 +456,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -424,13 +471,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -454,8 +531,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Lien hypertexte" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{50672D9D-075A-40C6-BDA5-FA61CF826F7B}"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
@@ -735,251 +826,553 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE3858F0-9336-48E3-86F2-B1B2EA88DE16}">
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.1796875" customWidth="1"/>
-    <col min="2" max="2" width="6.90625" customWidth="1"/>
-    <col min="5" max="5" width="14.08984375" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="1" max="1" width="21.1328125" customWidth="1"/>
+    <col min="2" max="2" width="13.06640625" customWidth="1"/>
+    <col min="5" max="5" width="14.06640625" customWidth="1"/>
+    <col min="10" max="10" width="11.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <f>170/74</f>
+        <v>2.2972972972972974</v>
+      </c>
+      <c r="C2">
+        <f>(1.33*170+163.83)/74</f>
+        <v>5.2693243243243248</v>
+      </c>
+      <c r="D2">
+        <v>2800</v>
+      </c>
+      <c r="E2">
+        <v>10.6</v>
+      </c>
+      <c r="F2">
+        <v>28.5</v>
+      </c>
+      <c r="G2">
+        <v>1.87</v>
+      </c>
+      <c r="H2">
+        <v>39.6</v>
+      </c>
+      <c r="I2">
+        <v>25</v>
+      </c>
+      <c r="J2">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3">
+        <f>1055/74</f>
+        <v>14.256756756756756</v>
+      </c>
+      <c r="C3">
+        <f>(1.33*1055+163.83)/74</f>
+        <v>21.175405405405407</v>
+      </c>
+      <c r="E3">
+        <v>14.6</v>
+      </c>
+      <c r="F3">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="G3">
+        <v>17</v>
+      </c>
+      <c r="H3">
+        <v>49</v>
+      </c>
+      <c r="I3">
+        <v>50</v>
+      </c>
+      <c r="J3">
+        <v>26068</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="E4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="15" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="C3">
-        <v>5.3</v>
-      </c>
-      <c r="D3">
-        <v>2800</v>
-      </c>
-      <c r="E3">
-        <v>10.6</v>
-      </c>
-      <c r="F3">
-        <v>28.5</v>
-      </c>
-      <c r="G3">
-        <v>1.87</v>
-      </c>
-      <c r="H3">
-        <v>3724</v>
-      </c>
-      <c r="I3">
-        <v>25</v>
-      </c>
-      <c r="J3">
-        <v>41.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4">
-        <v>14.6</v>
-      </c>
-      <c r="I4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="I4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="J4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" t="s">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" s="19"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" s="19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>17</v>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7">
+        <f>((Population!C116/100)*B2)*1000</f>
+        <v>17.77125593184725</v>
+      </c>
+      <c r="C7">
+        <f>((Population!C116/100)*C2)*1000</f>
+        <v>40.762034267677642</v>
+      </c>
+      <c r="D7">
+        <f>(Population!C116/100)*D2</f>
+        <v>21.660024876933825</v>
+      </c>
+      <c r="E7">
+        <f>((Population!C116/100)*E2)*1000</f>
+        <v>81.998665605535194</v>
+      </c>
+      <c r="F7">
+        <f>((Population!C116/100)*F2)*1000</f>
+        <v>220.468110354505</v>
+      </c>
+      <c r="G7">
+        <f>((Population!C116/100)*G2)*1000</f>
+        <v>14.465802328523662</v>
+      </c>
+      <c r="H7">
+        <f>(H2*Population!C115)*0.000277778</f>
+        <v>738.21533157179306</v>
+      </c>
+      <c r="I7">
+        <f>((Population!C116/100)*I2)*1000</f>
+        <v>193.39307925833771</v>
+      </c>
+      <c r="J7">
+        <f>(Population!C116/100)*J2</f>
+        <v>28.807833086321985</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" s="19" t="s">
+        <v>113</v>
       </c>
       <c r="B8">
-        <f>(Population!C116/100)*B3</f>
-        <v>1.7792163291767069E-2</v>
+        <f>((Population!C116/100)*B3)*1000</f>
+        <v>110.28632357705203</v>
       </c>
       <c r="C8">
-        <f>(Population!C116/100)*C3</f>
-        <v>4.0999332802767595E-2</v>
+        <f>((Population!C116/100)*C3)*1000</f>
+        <v>163.8070742358</v>
       </c>
       <c r="D8">
         <f>(Population!C116/100)*D3</f>
-        <v>21.660024876933825</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <f>(Population!C116/100)*E3</f>
-        <v>8.199866560553519E-2</v>
+        <f>((Population!C116/100)*E3)*1000</f>
+        <v>112.94155828686922</v>
       </c>
       <c r="F8">
-        <f>(Population!C116/100)*F3</f>
-        <v>0.220468110354505</v>
+        <f>((Population!C116/100)*F3)*1000</f>
+        <v>291.6367635215733</v>
       </c>
       <c r="G8">
-        <f>(Population!C116/100)*G3</f>
-        <v>1.4465802328523661E-2</v>
+        <f>((Population!C116/100)*G3)*1000</f>
+        <v>131.50729389566965</v>
       </c>
       <c r="H8">
-        <f>(Population!C116/100)*H3</f>
-        <v>28.807833086321985</v>
+        <f>(H3*Population!C115)*0.000366668</f>
+        <v>1205.7551281814922</v>
       </c>
       <c r="I8">
-        <f>(Population!C116/100)*I3</f>
-        <v>0.19339307925833771</v>
+        <f>((Population!C116/100)*I3)*1000</f>
+        <v>386.78615851667541</v>
       </c>
       <c r="J8">
-        <f>J3*Population!C115</f>
-        <v>2764949.7572000008</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+        <f>(Population!C116/100)*J3</f>
+        <v>201.6548316042539</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" s="19"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="14">
+        <v>1000000000</v>
+      </c>
+      <c r="C11" s="14">
+        <v>1000000000</v>
+      </c>
+      <c r="D11" s="14">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="14">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="14">
+        <v>1000000</v>
+      </c>
+      <c r="G11" s="14">
+        <v>1000000</v>
+      </c>
+      <c r="H11">
+        <f>1/0.000277778</f>
+        <v>3599.9971200023037</v>
+      </c>
+      <c r="I11" s="14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="J12" s="15"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" s="19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B15">
+        <f>B2*1000000000/(Population!B115*1000)</f>
+        <v>0.26480616600193263</v>
+      </c>
+      <c r="C15">
+        <f>C2*1000000000/(Population!B115*1000)</f>
+        <v>0.60738746064196225</v>
+      </c>
+      <c r="D15">
+        <f>D2*1000000000/(Population!B115*1000)</f>
+        <v>322.75198585647314</v>
+      </c>
+      <c r="E15">
+        <f>E2*1000000000000/(Population!B115*1000)</f>
+        <v>1221.8468035995054</v>
+      </c>
+      <c r="F15">
+        <f>F2*1000000000/(Population!B115*1000)</f>
+        <v>3.2851541417533872</v>
+      </c>
+      <c r="G15">
+        <f>G2*1000000000/(Population!B115*1000)</f>
+        <v>0.21555221912557312</v>
+      </c>
+      <c r="H15">
+        <f>H2</f>
+        <v>39.6</v>
+      </c>
+      <c r="I15">
+        <f>I2*1000000000/(Population!B115*1000)</f>
+        <v>2.881714159432796</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16">
+        <f>B3*1000000000/(Population!B115*1000)</f>
+        <v>1.6433559125414052</v>
+      </c>
+      <c r="C16">
+        <f>C3*1000000000/(Population!B115*1000)</f>
+        <v>2.4408586235394609</v>
+      </c>
+      <c r="I16">
+        <f>I3*1000000000/(Population!B115*1000)</f>
+        <v>5.7634283188655919</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="J17" s="15"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A19" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19">
+        <f>(Capacité!G40/100)*B2</f>
+        <v>1.2112525850852601E-3</v>
+      </c>
+      <c r="C19">
+        <f>(Capacité!G40/100)*C2</f>
+        <v>2.7782571794252677E-3</v>
+      </c>
+      <c r="D19">
+        <f>(Capacité!G40/100)*D2</f>
+        <v>1.4763031507627404</v>
+      </c>
+      <c r="E19">
+        <f>(Capacité!G40/100)*E2</f>
+        <v>5.5888619278875173E-3</v>
+      </c>
+      <c r="F19">
+        <f>(Capacité!G40/100)*F2</f>
+        <v>1.5026657070263608E-2</v>
+      </c>
+      <c r="G19">
+        <f>(Capacité!G40/100)*G2</f>
+        <v>9.8595960425940164E-4</v>
+      </c>
+      <c r="H19">
+        <f>(Capacité!G40/100)*H2</f>
+        <v>2.0879144560787332E-2</v>
+      </c>
+      <c r="I19">
+        <f>((Capacité!G39/100)*I2)*1000</f>
+        <v>13.737674325397714</v>
+      </c>
+      <c r="J19">
+        <f>(Capacité!G40/100)*J2</f>
+        <v>1.9634831905144448</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A20" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20">
+        <f>(Capacité!G40/100)*B3</f>
+        <v>7.5168910427349956E-3</v>
+      </c>
+      <c r="C20">
+        <f>(Capacité!G40/100)*C3</f>
+        <v>1.1164756328099417E-2</v>
+      </c>
+      <c r="D20">
+        <f>(Capacité!G40/100)*D3</f>
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <f>(Capacité!G40/100)*E3</f>
+        <v>7.6978664289771466E-3</v>
+      </c>
+      <c r="F20">
+        <f>(Capacité!G40/100)*F3</f>
+        <v>1.9877367422769757E-2</v>
+      </c>
+      <c r="G20">
+        <f>(Capacité!G40/100)*G3</f>
+        <v>8.9632691296309235E-3</v>
+      </c>
+      <c r="H20">
+        <f>(Capacité!G40/100)*H3</f>
+        <v>2.5835305138347957E-2</v>
+      </c>
+      <c r="I20">
+        <f>((Capacité!G40/100)*I3)*1000</f>
+        <v>26.362556263620363</v>
+      </c>
+      <c r="J20">
+        <f>(Capacité!G40/100)*J3</f>
+        <v>13.744382333601115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A21" s="19"/>
+    </row>
+    <row r="22" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="15"/>
+    </row>
+    <row r="23" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B9">
-        <f>(Capacité!G40/100)*B3</f>
-        <v>1.2126775881265367E-3</v>
-      </c>
-      <c r="C9">
-        <f>(Capacité!G40/100)*C3</f>
-        <v>2.7944309639437587E-3</v>
-      </c>
-      <c r="D9">
-        <f>(Capacité!G40/100)*D3</f>
-        <v>1.4763031507627404</v>
-      </c>
-      <c r="E9">
-        <f>(Capacité!G40/100)*E3</f>
-        <v>5.5888619278875173E-3</v>
-      </c>
-      <c r="F9">
-        <f>(Capacité!G40/100)*F3</f>
-        <v>1.5026657070263608E-2</v>
-      </c>
-      <c r="G9">
-        <f>(Capacité!G40/100)*G3</f>
-        <v>9.8595960425940164E-4</v>
-      </c>
-      <c r="H9">
-        <f>(Capacité!G40/100)*H3</f>
-        <v>1.9634831905144448</v>
-      </c>
-      <c r="I9">
-        <f>(Capacité!G40/100)*I3</f>
-        <v>1.3181278131810182E-2</v>
-      </c>
-      <c r="J9">
-        <f>(Capacité!G40/100)*J3</f>
-        <v>2.1722746361223184E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A24" s="19"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A25" s="19"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A26" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -987,262 +1380,187 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1104A7-2272-4986-AE6B-8EA45794950A}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.1796875" customWidth="1"/>
-    <col min="2" max="2" width="13.08984375" customWidth="1"/>
-    <col min="5" max="5" width="14.08984375" customWidth="1"/>
+    <col min="1" max="1" width="27.796875" customWidth="1"/>
+    <col min="3" max="4" width="12.3984375" customWidth="1"/>
+    <col min="5" max="5" width="11.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="B2">
-        <v>2.2999999999999998</v>
+        <v>2.57</v>
       </c>
       <c r="C2">
-        <v>5.3</v>
+        <v>145.30000000000001</v>
       </c>
       <c r="D2">
-        <v>2800</v>
+        <v>4.53</v>
       </c>
       <c r="E2">
-        <v>10.6</v>
+        <v>3.95</v>
       </c>
       <c r="F2">
-        <v>28.5</v>
-      </c>
-      <c r="G2">
-        <v>1.87</v>
-      </c>
-      <c r="H2">
-        <v>41.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>118</v>
+      </c>
+      <c r="B3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C3">
+        <v>140.30000000000001</v>
+      </c>
+      <c r="D3">
+        <v>4.21</v>
       </c>
       <c r="E3">
-        <v>14.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>3.67</v>
+      </c>
+      <c r="F3">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7">
+        <f>(B2*Population!C115*0.000001)*1000</f>
+        <v>172.47380767000001</v>
+      </c>
+      <c r="C7">
+        <f>C2*Population!C115*1000*0.000000001</f>
+        <v>9.751145624300003</v>
+      </c>
+      <c r="D7">
+        <f>(D2*Population!C115*1000*0.000001)</f>
+        <v>304.01025243000004</v>
+      </c>
+      <c r="E7">
+        <f>(E2*Population!C115*0.000001)*1000</f>
+        <v>265.08620245000003</v>
+      </c>
+      <c r="F7">
+        <f>F2*Population!C115*0.000277778</f>
+        <v>484.68683386026811</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
         <v>107</v>
       </c>
-      <c r="B7">
-        <f>((Population!C116/100)*B2)*1000</f>
-        <v>17.792163291767068</v>
-      </c>
-      <c r="C7">
-        <f>((Population!C116/100)*C2)*1000</f>
-        <v>40.999332802767597</v>
-      </c>
-      <c r="D7">
-        <f>(Population!C116/100)*D2</f>
-        <v>21.660024876933825</v>
-      </c>
-      <c r="E7">
-        <f>((Population!C116/100)*E2)*1000</f>
-        <v>81.998665605535194</v>
-      </c>
-      <c r="F7">
-        <f>((Population!C116/100)*F2)*1000</f>
-        <v>220.468110354505</v>
-      </c>
-      <c r="G7">
-        <f>((Population!C116/100)*G2)*1000</f>
-        <v>14.465802328523662</v>
-      </c>
-      <c r="H7">
-        <f>(H2*Population!C115)*0.000277778</f>
-        <v>768.04221365550188</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
       <c r="B8">
-        <f>(Capacité!G40/100)*B2</f>
-        <v>1.2126775881265367E-3</v>
+        <f>(B3*Population!C115*0.000001)*1000</f>
+        <v>147.64294820000003</v>
       </c>
       <c r="C8">
-        <f>(Capacité!G40/100)*C2</f>
-        <v>2.7944309639437587E-3</v>
+        <f>(C3*Population!C115*0.000001)</f>
+        <v>9.415593469300001</v>
       </c>
       <c r="D8">
-        <f>(Capacité!G40/100)*D2</f>
-        <v>1.4763031507627404</v>
+        <f>(D3*Population!C115*0.000001)*1000</f>
+        <v>282.53491451000002</v>
       </c>
       <c r="E8">
-        <f>(Capacité!G40/100)*E2</f>
-        <v>5.5888619278875173E-3</v>
+        <f>(E3*Population!C115*0.000001)*1000</f>
+        <v>246.29528177</v>
       </c>
       <c r="F8">
-        <f>(Capacité!G40/100)*F2</f>
-        <v>1.5026657070263608E-2</v>
-      </c>
-      <c r="G8">
-        <f>(Capacité!G40/100)*G2</f>
-        <v>9.8595960425940164E-4</v>
-      </c>
-      <c r="H8">
-        <f>(Capacité!G40/100)*H2</f>
-        <v>2.1722746361223184E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <f>F3*Population!C115*0.000277778</f>
+        <v>285.21955992546549</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H12" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B13" s="14">
-        <v>1000000000</v>
-      </c>
-      <c r="C13" s="14">
-        <v>1000000000</v>
-      </c>
-      <c r="D13" s="14">
-        <v>1000</v>
-      </c>
-      <c r="E13" s="14">
-        <v>1000</v>
-      </c>
-      <c r="F13" s="14">
-        <v>1000000</v>
-      </c>
-      <c r="G13" s="14">
-        <v>1000000</v>
-      </c>
-      <c r="H13">
-        <f>1/0.000277778</f>
-        <v>3599.9971200023037</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>104</v>
-      </c>
-      <c r="B14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G14" t="s">
-        <v>99</v>
-      </c>
-      <c r="H14" t="s">
-        <v>98</v>
+      <c r="B11" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="22" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B11:E11"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F11" r:id="rId1" xr:uid="{F7B5DC7E-06B3-4D92-84C6-221AF8CD7354}"/>
+    <hyperlink ref="B11" r:id="rId2" xr:uid="{7753ABD6-E8C9-41B2-94EA-8111D4B50F91}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1250,27 +1568,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95CE491-5889-4A7E-A6ED-A3FC6F8FA184}">
   <dimension ref="A1:I121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.36328125" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" customWidth="1"/>
+    <col min="1" max="1" width="12.3984375" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="48.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="48.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -1284,7 +1602,7 @@
         <v>722828.87800000003</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -1298,7 +1616,7 @@
         <v>725449.93</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -1312,7 +1630,7 @@
         <v>727517.08100000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -1326,7 +1644,7 @@
         <v>727716.30099999998</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -1340,7 +1658,7 @@
         <v>728295.52300000004</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -1354,7 +1672,7 @@
         <v>729473.78</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -1368,7 +1686,7 @@
         <v>729287.41799999995</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -1382,7 +1700,7 @@
         <v>729452.23499999999</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -1396,7 +1714,7 @@
         <v>729398.01599999995</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -1410,7 +1728,7 @@
         <v>728330.19400000002</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -1424,7 +1742,7 @@
         <v>728105.16299999994</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -1438,7 +1756,7 @@
         <v>728223.255</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -1452,7 +1770,7 @@
         <v>728252.19</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -1466,7 +1784,7 @@
         <v>730000.83799999999</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -1480,7 +1798,7 @@
         <v>730751.91200000001</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -1494,7 +1812,7 @@
         <v>731740.46699999995</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -1508,7 +1826,7 @@
         <v>732352.56200000003</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -1522,7 +1840,7 @@
         <v>733015.57299999997</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -1536,7 +1854,7 @@
         <v>734777.08299999998</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -1550,7 +1868,7 @@
         <v>736321.8</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -1564,7 +1882,7 @@
         <v>737549.64</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -1578,7 +1896,7 @@
         <v>738740.995</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -1592,7 +1910,7 @@
         <v>739977.41500000004</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -1606,7 +1924,7 @@
         <v>740940.27500000002</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -1620,7 +1938,7 @@
         <v>742001.28700000001</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -1634,7 +1952,7 @@
         <v>743279.99399999995</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -1648,7 +1966,7 @@
         <v>745194.076</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -1662,7 +1980,7 @@
         <v>746812.14</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -1676,7 +1994,7 @@
         <v>748046.28399999999</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -1690,7 +2008,7 @@
         <v>749083.44900000002</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -1704,7 +2022,7 @@
         <v>749924.80500000005</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -1718,7 +2036,7 @@
         <v>749123.28399999999</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -1732,7 +2050,7 @@
         <v>748103.72499999998</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -1746,7 +2064,7 @@
         <v>745825.46</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -1760,7 +2078,7 @@
         <v>745380.28899999999</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>2025</v>
       </c>
@@ -1774,7 +2092,7 @@
         <v>744787.35800000001</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>2026</v>
       </c>
@@ -1788,7 +2106,7 @@
         <v>744010.30599999998</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>2027</v>
       </c>
@@ -1802,7 +2120,7 @@
         <v>742954.41700000002</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>2028</v>
       </c>
@@ -1816,7 +2134,7 @@
         <v>741789.71200000006</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>2029</v>
       </c>
@@ -1830,7 +2148,7 @@
         <v>740527.35400000005</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>2030</v>
       </c>
@@ -1844,7 +2162,7 @@
         <v>739157.09199999995</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>2031</v>
       </c>
@@ -1858,7 +2176,7 @@
         <v>737709.81599999999</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>2032</v>
       </c>
@@ -1872,7 +2190,7 @@
         <v>736143.12100000004</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>2033</v>
       </c>
@@ -1886,7 +2204,7 @@
         <v>734589.397</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>2034</v>
       </c>
@@ -1900,7 +2218,7 @@
         <v>733012.58799999999</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <v>2035</v>
       </c>
@@ -1914,7 +2232,7 @@
         <v>731408.71900000004</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
         <v>2036</v>
       </c>
@@ -1928,7 +2246,7 @@
         <v>729772.30099999998</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="1">
         <v>2037</v>
       </c>
@@ -1942,7 +2260,7 @@
         <v>728095.92099999997</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
         <v>2038</v>
       </c>
@@ -1956,7 +2274,7 @@
         <v>726400.87600000005</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="1">
         <v>2039</v>
       </c>
@@ -1970,7 +2288,7 @@
         <v>724703.647</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="1">
         <v>2040</v>
       </c>
@@ -1984,7 +2302,7 @@
         <v>722958.26199999999</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
         <v>2041</v>
       </c>
@@ -1998,7 +2316,7 @@
         <v>721244.98499999999</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="1">
         <v>2042</v>
       </c>
@@ -2012,7 +2330,7 @@
         <v>719536.97499999998</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="1">
         <v>2043</v>
       </c>
@@ -2026,7 +2344,7 @@
         <v>717819.94799999997</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
         <v>2044</v>
       </c>
@@ -2040,7 +2358,7 @@
         <v>716032.201</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="1">
         <v>2045</v>
       </c>
@@ -2054,7 +2372,7 @@
         <v>714211.69299999997</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="1">
         <v>2046</v>
       </c>
@@ -2068,7 +2386,7 @@
         <v>712348.01199999999</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="1">
         <v>2047</v>
       </c>
@@ -2082,7 +2400,7 @@
         <v>710440.74300000002</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="1">
         <v>2048</v>
       </c>
@@ -2096,7 +2414,7 @@
         <v>708437.35199999996</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="1">
         <v>2049</v>
       </c>
@@ -2110,7 +2428,7 @@
         <v>706353.86800000002</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
         <v>2050</v>
       </c>
@@ -2124,7 +2442,7 @@
         <v>704160.17799999996</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="1">
         <v>2051</v>
       </c>
@@ -2138,7 +2456,7 @@
         <v>701895.34</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="1">
         <v>2052</v>
       </c>
@@ -2152,7 +2470,7 @@
         <v>699538.17700000003</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="1">
         <v>2053</v>
       </c>
@@ -2166,7 +2484,7 @@
         <v>697115.44700000004</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="1">
         <v>2054</v>
       </c>
@@ -2180,7 +2498,7 @@
         <v>694513.78700000001</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="1">
         <v>2055</v>
       </c>
@@ -2194,7 +2512,7 @@
         <v>691851.88199999998</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
         <v>2056</v>
       </c>
@@ -2208,7 +2526,7 @@
         <v>689074.61100000003</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="1">
         <v>2057</v>
       </c>
@@ -2222,7 +2540,7 @@
         <v>686255.70799999998</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="1">
         <v>2058</v>
       </c>
@@ -2236,7 +2554,7 @@
         <v>683407.30299999996</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
         <v>2059</v>
       </c>
@@ -2250,7 +2568,7 @@
         <v>680520.071</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="1">
         <v>2060</v>
       </c>
@@ -2264,7 +2582,7 @@
         <v>677603.74899999995</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="1">
         <v>2061</v>
       </c>
@@ -2278,7 +2596,7 @@
         <v>674715.93099999998</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
         <v>2062</v>
       </c>
@@ -2292,7 +2610,7 @@
         <v>671815.46400000004</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="1">
         <v>2063</v>
       </c>
@@ -2306,7 +2624,7 @@
         <v>668937.91299999994</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="1">
         <v>2064</v>
       </c>
@@ -2320,7 +2638,7 @@
         <v>666081.65899999999</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="1">
         <v>2065</v>
       </c>
@@ -2334,7 +2652,7 @@
         <v>663254.68299999996</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="1">
         <v>2066</v>
       </c>
@@ -2348,7 +2666,7 @@
         <v>660460.06999999995</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="1">
         <v>2067</v>
       </c>
@@ -2362,7 +2680,7 @@
         <v>657736.19900000002</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="1">
         <v>2068</v>
       </c>
@@ -2376,7 +2694,7 @@
         <v>655082.67299999995</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="1">
         <v>2069</v>
       </c>
@@ -2390,7 +2708,7 @@
         <v>652466.40500000003</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="1">
         <v>2070</v>
       </c>
@@ -2404,7 +2722,7 @@
         <v>649895.46600000001</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="1">
         <v>2071</v>
       </c>
@@ -2418,7 +2736,7 @@
         <v>647385.17299999995</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="1">
         <v>2072</v>
       </c>
@@ -2432,7 +2750,7 @@
         <v>644924.50300000003</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="1">
         <v>2073</v>
       </c>
@@ -2446,7 +2764,7 @@
         <v>642548.04799999995</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="1">
         <v>2074</v>
       </c>
@@ -2460,7 +2778,7 @@
         <v>640200.39800000004</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="1">
         <v>2075</v>
       </c>
@@ -2474,7 +2792,7 @@
         <v>637905.63800000004</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="1">
         <v>2076</v>
       </c>
@@ -2488,7 +2806,7 @@
         <v>635718.05700000003</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="1">
         <v>2077</v>
       </c>
@@ -2502,7 +2820,7 @@
         <v>633586.69099999999</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="1">
         <v>2078</v>
       </c>
@@ -2516,7 +2834,7 @@
         <v>631465.69099999999</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="1">
         <v>2079</v>
       </c>
@@ -2530,7 +2848,7 @@
         <v>629415.12899999996</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="1">
         <v>2080</v>
       </c>
@@ -2544,7 +2862,7 @@
         <v>627404.68799999997</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="1">
         <v>2081</v>
       </c>
@@ -2558,7 +2876,7 @@
         <v>625461.88899999997</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="1">
         <v>2082</v>
       </c>
@@ -2572,7 +2890,7 @@
         <v>623586.20299999998</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="1">
         <v>2083</v>
       </c>
@@ -2586,7 +2904,7 @@
         <v>621727.15399999998</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="1">
         <v>2084</v>
       </c>
@@ -2600,7 +2918,7 @@
         <v>619907.59900000005</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" s="1">
         <v>2085</v>
       </c>
@@ -2614,7 +2932,7 @@
         <v>618109.28700000001</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" s="1">
         <v>2086</v>
       </c>
@@ -2628,7 +2946,7 @@
         <v>616324.20200000005</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" s="1">
         <v>2087</v>
       </c>
@@ -2642,7 +2960,7 @@
         <v>614569.38399999996</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" s="1">
         <v>2088</v>
       </c>
@@ -2656,7 +2974,7 @@
         <v>612868.772</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" s="1">
         <v>2089</v>
       </c>
@@ -2670,7 +2988,7 @@
         <v>611200.07799999998</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" s="1">
         <v>2090</v>
       </c>
@@ -2684,7 +3002,7 @@
         <v>609526.97699999996</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A103" s="1">
         <v>2091</v>
       </c>
@@ -2698,7 +3016,7 @@
         <v>607859.16</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A104" s="1">
         <v>2092</v>
       </c>
@@ -2712,7 +3030,7 @@
         <v>606237.61699999997</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" s="1">
         <v>2093</v>
       </c>
@@ -2726,7 +3044,7 @@
         <v>604606.87600000005</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A106" s="1">
         <v>2094</v>
       </c>
@@ -2740,7 +3058,7 @@
         <v>603012.85499999998</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A107" s="1">
         <v>2095</v>
       </c>
@@ -2754,7 +3072,7 @@
         <v>601427.07799999998</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A108" s="1">
         <v>2096</v>
       </c>
@@ -2768,7 +3086,7 @@
         <v>599799.50300000003</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" s="1">
         <v>2097</v>
       </c>
@@ -2782,7 +3100,7 @@
         <v>598134.46</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" s="1">
         <v>2098</v>
       </c>
@@ -2796,7 +3114,7 @@
         <v>596471.93000000005</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A111" s="1">
         <v>2099</v>
       </c>
@@ -2810,7 +3128,7 @@
         <v>594809.66299999994</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A112" s="1">
         <v>2100</v>
       </c>
@@ -2824,9 +3142,9 @@
         <v>593112.88</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B114">
         <f>B27*100/B27</f>
@@ -2841,7 +3159,7 @@
         <v>10.008512952112008</v>
       </c>
       <c r="F114" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G114">
         <f>B31*100/B31</f>
@@ -2856,9 +3174,9 @@
         <v>9.639258714121274</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A115" s="11" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B115" s="9">
         <f>AVERAGE(B27:B63)</f>
@@ -2873,7 +3191,7 @@
         <v>731385.82940540521</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G115" s="4">
         <f>AVERAGE(B31:B63)</f>
@@ -2888,9 +3206,9 @@
         <v>729634.64224242419</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A116" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B116" s="8">
         <f>B115/B115</f>
@@ -2905,7 +3223,7 @@
         <v>8.4305796024242223</v>
       </c>
       <c r="F116" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G116" s="5">
         <f>G115/G115</f>
@@ -2920,9 +3238,9 @@
         <v>8.2811143358722195</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A117" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B117" s="4">
         <f>AVERAGE(B29:B112)</f>
@@ -2937,7 +3255,7 @@
         <v>677886.14760714292</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G117" s="4">
         <f>AVERAGE(B31:B112)</f>
@@ -2952,9 +3270,9 @@
         <v>676189.9753048782</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B118" s="5">
         <f>B117/B117</f>
@@ -2969,7 +3287,7 @@
         <v>7.087913983422621</v>
       </c>
       <c r="F118" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G118" s="5">
         <f>G117/G117</f>
@@ -2984,24 +3302,24 @@
         <v>7.0357584289374984</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119" s="3"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120" s="3"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B121" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -3012,33 +3330,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8683F5-D89E-4384-A263-C6122D6DA873}">
   <dimension ref="A1:AJ45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7265625" customWidth="1"/>
+    <col min="3" max="3" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
@@ -3069,9 +3387,9 @@
       <c r="AI1" s="13"/>
       <c r="AJ1" s="13"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A2" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" s="13">
         <v>11257.436263054224</v>
@@ -3123,9 +3441,9 @@
       <c r="AI2" s="13"/>
       <c r="AJ2" s="13"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" s="13">
         <v>11166.5096464532</v>
@@ -3177,9 +3495,9 @@
       <c r="AI3" s="13"/>
       <c r="AJ3" s="13"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A4" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B4" s="13">
         <v>11132.379518801288</v>
@@ -3232,9 +3550,9 @@
       <c r="AI4" s="13"/>
       <c r="AJ4" s="13"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A5" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B5" s="13">
         <v>11125.655948461339</v>
@@ -3285,9 +3603,9 @@
       <c r="AI5" s="13"/>
       <c r="AJ5" s="13"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A6" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B6" s="13">
         <v>11251.216001515992</v>
@@ -3311,9 +3629,9 @@
         <v>24904675997.177227</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A7" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B7" s="13">
         <v>11429.359024753261</v>
@@ -3337,9 +3655,9 @@
         <v>25612762187.674767</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A8" s="13" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B8" s="13">
         <v>11679.153608780653</v>
@@ -3363,9 +3681,9 @@
         <v>26087721958.213924</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A9" s="13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B9" s="13">
         <v>11964.177719327863</v>
@@ -3389,9 +3707,9 @@
         <v>26723818654.148617</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A10" s="13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B10" s="13">
         <v>12088.101662261559</v>
@@ -3415,9 +3733,9 @@
         <v>27468476865.381031</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A11" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B11" s="13">
         <v>12351.548049120385</v>
@@ -3441,9 +3759,9 @@
         <v>28176082288.3083</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A12" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" s="13">
         <v>12769.83149176615</v>
@@ -3467,9 +3785,9 @@
         <v>29240167861.778976</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A13" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B13" s="13">
         <v>12904.861928294958</v>
@@ -3493,9 +3811,9 @@
         <v>29862791642.623837</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A14" s="13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" s="13">
         <v>13093.065120858157</v>
@@ -3519,9 +3837,9 @@
         <v>30165942432.463612</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A15" s="13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" s="13">
         <v>13402.991953645811</v>
@@ -3545,9 +3863,9 @@
         <v>30462092599.50692</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A16" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="13">
         <v>13914.811142290484</v>
@@ -3571,9 +3889,9 @@
         <v>31221908220.131401</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" s="13">
         <v>14370.885028756215</v>
@@ -3597,9 +3915,9 @@
         <v>31813500020.819954</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="13" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="13">
         <v>14927.548526144859</v>
@@ -3623,9 +3941,9 @@
         <v>32916700218.346203</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B19" s="13">
         <v>15510.865766860974</v>
@@ -3649,9 +3967,9 @@
         <v>33919859610.622345</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B20" s="13">
         <v>15747.72951097517</v>
@@ -3675,9 +3993,9 @@
         <v>34182103766.776295</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B21" s="13">
         <v>15452.501218625677</v>
@@ -3701,9 +4019,9 @@
         <v>32714648377.874294</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B22" s="13">
         <v>16047.989739120134</v>
@@ -3728,9 +4046,9 @@
       </c>
       <c r="J22" s="13"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B23" s="13">
         <v>16479.488794650872</v>
@@ -3754,9 +4072,9 @@
         <v>34133681735.471703</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B24" s="13">
         <v>16784.949179715102</v>
@@ -3780,9 +4098,9 @@
         <v>33882036018.543774</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B25" s="13">
         <v>17122.045527201219</v>
@@ -3806,9 +4124,9 @@
         <v>33878734646.466373</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B26" s="13">
         <v>17500.17482812225</v>
@@ -3832,9 +4150,9 @@
         <v>34469485024.636459</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B27" s="13">
         <v>17868.090856870793</v>
@@ -3858,9 +4176,9 @@
         <v>35298868327.366135</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B28" s="13">
         <v>18232.726915707946</v>
@@ -3884,9 +4202,9 @@
         <v>36019907345.254646</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B29" s="13">
         <v>18714.938943125886</v>
@@ -3910,9 +4228,9 @@
         <v>37119573491.364235</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B30" s="13">
         <v>19189.020223224863</v>
@@ -3936,9 +4254,9 @@
         <v>37930710214.837662</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B31" s="13">
         <v>19552.083514829628</v>
@@ -3962,9 +4280,9 @@
         <v>38699419341.686249</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B32" s="13">
         <v>18811.493553031505</v>
@@ -3988,9 +4306,9 @@
         <v>36574113872.711426</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B33" s="13">
         <v>19866.767918404636</v>
@@ -4014,9 +4332,9 @@
         <v>38931911154.245689</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B34" s="13">
         <v>20409.442097193965</v>
@@ -4040,9 +4358,9 @@
         <v>40231131436.83564</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B35" s="13">
         <v>20918.304708117044</v>
@@ -4066,9 +4384,9 @@
         <v>40177113825.347435</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B36" s="13">
         <v>21405.118104266388</v>
@@ -4092,15 +4410,15 @@
         <v>40502412753.686844</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B38">
         <v>50000</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F38">
         <f>SUM(F2:F36)/SUM(Population!B2:B36)</f>
@@ -4115,15 +4433,15 @@
         <v>43631.695837336869</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B39">
         <v>7500</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F39">
         <f>1-(F38-B39)/(B38-B39)</f>
@@ -4138,9 +4456,9 @@
         <v>0.1498424508861913</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="E40" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F40" s="10">
         <f>(Population!B115*Capacité!F39)*100/(Population!B115*Capacité!F39)</f>
@@ -4155,9 +4473,9 @@
         <v>1.5668798264892982</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E41" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F41">
         <f>1-(B27-B39)/(B38-B39)</f>
@@ -4172,9 +4490,9 @@
         <v>5.9042950726820198E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="E42" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F42">
         <f>(Population!B115*Capacité!F41)*100/(Population!B115*Capacité!F41)</f>
@@ -4189,28 +4507,28 @@
         <v>0.65838190592741441</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B44" t="s">
         <v>67</v>
       </c>
-      <c r="B43" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79962A65-2DA5-4677-830F-50BB9044D0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B37D5D-3804-449C-B357-4A21C28AF5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="1" r:id="rId1"/>
@@ -896,17 +896,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -914,11 +908,17 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1204,14 +1204,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.15234375" customWidth="1"/>
-    <col min="4" max="4" width="14.07421875" customWidth="1"/>
-    <col min="9" max="10" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1328125" customWidth="1"/>
+    <col min="4" max="4" width="14.06640625" customWidth="1"/>
+    <col min="9" max="10" width="11.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="18" t="s">
         <v>83</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="19" t="s">
         <v>15</v>
       </c>
@@ -1249,10 +1249,10 @@
         <v>5.2693243243243248</v>
       </c>
       <c r="C2">
-        <v>1100</v>
+        <v>2800</v>
       </c>
       <c r="D2">
-        <v>10.6</v>
+        <v>12.6</v>
       </c>
       <c r="E2">
         <v>28.5</v>
@@ -1270,7 +1270,7 @@
         <v>3724</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="19" t="s">
         <v>81</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>26068</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="16" t="s">
         <v>5</v>
       </c>
@@ -1329,10 +1329,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="19"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="37" t="s">
         <v>14</v>
       </c>
@@ -1345,7 +1345,7 @@
       <c r="H6" s="38"/>
       <c r="I6" s="38"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="37" t="s">
         <v>95</v>
       </c>
@@ -1355,11 +1355,11 @@
       </c>
       <c r="C7" s="38">
         <f>(Population!C116/100)*C2</f>
-        <v>8.5092954873668596</v>
+        <v>21.660024876933825</v>
       </c>
       <c r="D7" s="38">
         <f>((Population!C116/100)*D2)*1000</f>
-        <v>81.998665605535194</v>
+        <v>97.470111946202195</v>
       </c>
       <c r="E7" s="38">
         <f>((Population!C116/100)*E2)*1000</f>
@@ -1382,7 +1382,7 @@
         <v>28.807833086321985</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" s="37" t="s">
         <v>108</v>
       </c>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="J8" s="31"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" s="37"/>
       <c r="B9" s="38"/>
       <c r="C9" s="38"/>
@@ -1431,7 +1431,7 @@
       <c r="H9" s="38"/>
       <c r="I9" s="38"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="37" t="s">
         <v>93</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="19" t="s">
         <v>90</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="16" t="s">
         <v>92</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -1530,7 +1530,7 @@
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="34" t="s">
         <v>97</v>
       </c>
@@ -1543,7 +1543,7 @@
       <c r="H14" s="22"/>
       <c r="I14" s="22"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="34" t="s">
         <v>141</v>
       </c>
@@ -1553,11 +1553,11 @@
       </c>
       <c r="C15" s="22">
         <f>C2*1000000000/(Population!B115*1000)</f>
-        <v>126.79542301504301</v>
+        <v>322.75198585647314</v>
       </c>
       <c r="D15" s="22">
         <f>D2*1000000000000/(Population!B115*1000)</f>
-        <v>1221.8468035995054</v>
+        <v>1452.3839363541292</v>
       </c>
       <c r="E15" s="22">
         <f>E2*1000000000/(Population!B115*1000)</f>
@@ -1580,7 +1580,7 @@
         <v>0.42926014118910927</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="34" t="s">
         <v>142</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>3.0048209883237651</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" s="35" t="s">
         <v>5</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="19"/>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -1657,7 +1657,7 @@
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="19" t="s">
         <v>16</v>
       </c>
@@ -1667,11 +1667,11 @@
       </c>
       <c r="C19">
         <f>(Capacité!G40/100)*C2</f>
-        <v>0.57997623779964802</v>
+        <v>1.4763031507627404</v>
       </c>
       <c r="D19">
         <f>(Capacité!G40/100)*D2</f>
-        <v>5.5888619278875173E-3</v>
+        <v>6.643364178432332E-3</v>
       </c>
       <c r="E19">
         <f>(Capacité!G40/100)*E2</f>
@@ -1694,7 +1694,7 @@
         <v>1.9634831905144448</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="19" t="s">
         <v>109</v>
       </c>
@@ -1731,16 +1731,16 @@
         <v>13.744382333601115</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="19"/>
     </row>
-    <row r="22" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="19" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="15"/>
     </row>
-    <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="16" t="s">
         <v>116</v>
       </c>
@@ -1753,7 +1753,7 @@
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="19" t="s">
         <v>115</v>
       </c>
@@ -1763,11 +1763,11 @@
       </c>
       <c r="C24" s="31">
         <f>C2*Besoins!C5</f>
-        <v>6.0220953149447558</v>
+        <v>15.328969892586652</v>
       </c>
       <c r="D24" s="31">
         <f>D2*Besoins!D5*1000</f>
-        <v>122.5562751865215</v>
+        <v>145.68010069341233</v>
       </c>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -1781,7 +1781,7 @@
         <v>43.039686548122148</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" s="19" t="s">
         <v>121</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>301.27780583685501</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="19"/>
     </row>
   </sheetData>
@@ -1820,15 +1820,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1104A7-2272-4986-AE6B-8EA45794950A}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.765625" customWidth="1"/>
-    <col min="3" max="4" width="12.3828125" customWidth="1"/>
-    <col min="5" max="5" width="11.921875" customWidth="1"/>
-    <col min="7" max="7" width="14.84375" customWidth="1"/>
+    <col min="1" max="1" width="27.73046875" customWidth="1"/>
+    <col min="3" max="4" width="12.3984375" customWidth="1"/>
+    <col min="5" max="5" width="11.9296875" customWidth="1"/>
+    <col min="7" max="7" width="14.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="23" t="s">
         <v>83</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="22" t="s">
         <v>137</v>
       </c>
@@ -1877,7 +1877,7 @@
         <v>4.0776939000000005E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="22" t="s">
         <v>138</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>2.9475940000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="22" t="s">
         <v>170</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>3.5126439500000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="22" t="s">
         <v>5</v>
       </c>
@@ -1955,12 +1955,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>2.7340017428936065E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>1.9682472147114907E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="31" t="s">
         <v>117</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>2.3511244788025486E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="33" t="s">
         <v>102</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>29.823675351128617</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="33" t="s">
         <v>103</v>
       </c>
@@ -2122,7 +2122,7 @@
         <v>21.558284824403962</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="33" t="s">
         <v>171</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>25.690980087766288</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="33" t="s">
         <v>5</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -2188,17 +2188,17 @@
         <v>111</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G22" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G23" t="s">
         <v>134</v>
       </c>
@@ -2219,132 +2219,132 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE59BEB1-58EA-414F-91E0-ADFFF27E94F9}">
   <dimension ref="A2:U6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.07421875" style="31"/>
+    <col min="1" max="1" width="11.06640625" style="31"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" ht="15.9" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="50" t="s">
+    <row r="2" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="50" t="s">
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="51" t="s">
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="L2" s="51"/>
+      <c r="L2" s="49"/>
       <c r="M2" s="52" t="s">
         <v>146</v>
       </c>
-      <c r="N2" s="53" t="s">
+      <c r="N2" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="O2" s="50" t="s">
+      <c r="O2" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="51" t="s">
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="S2" s="51"/>
-      <c r="T2" s="48" t="s">
+      <c r="S2" s="49"/>
+      <c r="T2" s="53" t="s">
         <v>168</v>
       </c>
-      <c r="U2" s="49" t="s">
+      <c r="U2" s="51" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="17.149999999999999" x14ac:dyDescent="0.4">
-      <c r="B3" s="46" t="s">
+    <row r="3" spans="1:21" ht="17.649999999999999" x14ac:dyDescent="0.45">
+      <c r="B3" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D3" s="47" t="s">
         <v>152</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="E3" s="46" t="s">
         <v>153</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="G3" s="47" t="s">
+      <c r="G3" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="H3" s="46" t="s">
+      <c r="H3" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="I3" s="46" t="s">
+      <c r="I3" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="J3" s="46" t="s">
+      <c r="J3" s="47" t="s">
         <v>158</v>
       </c>
-      <c r="K3" s="47" t="s">
+      <c r="K3" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="L3" s="47" t="s">
+      <c r="L3" s="46" t="s">
         <v>160</v>
       </c>
       <c r="M3" s="52"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="46" t="s">
+      <c r="N3" s="50"/>
+      <c r="O3" s="47" t="s">
         <v>161</v>
       </c>
-      <c r="P3" s="46" t="s">
+      <c r="P3" s="47" t="s">
         <v>162</v>
       </c>
       <c r="Q3" s="39" t="s">
         <v>163</v>
       </c>
-      <c r="R3" s="47" t="s">
+      <c r="R3" s="46" t="s">
         <v>165</v>
       </c>
-      <c r="S3" s="47" t="s">
+      <c r="S3" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="T3" s="48"/>
-      <c r="U3" s="49"/>
-    </row>
-    <row r="4" spans="1:21" ht="37.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
+      <c r="T3" s="53"/>
+      <c r="U3" s="51"/>
+    </row>
+    <row r="4" spans="1:21" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
       <c r="M4" s="52"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
+      <c r="N4" s="50"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
       <c r="Q4" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="49"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="R4" s="46"/>
+      <c r="S4" s="46"/>
+      <c r="T4" s="53"/>
+      <c r="U4" s="51"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="31" t="s">
         <v>167</v>
       </c>
@@ -2410,7 +2410,7 @@
         <v>15.600000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A6" s="31" t="s">
         <v>13</v>
       </c>
@@ -2424,17 +2424,6 @@
     <mergeCell ref="U2:U4"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="R2:S2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:M4"/>
     <mergeCell ref="O3:O4"/>
@@ -2442,6 +2431,17 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T2:T4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -2451,13 +2451,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95CE491-5889-4A7E-A6ED-A3FC6F8FA184}">
   <dimension ref="A1:I121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.3828125" customWidth="1"/>
-    <col min="2" max="2" width="12.84375" customWidth="1"/>
+    <col min="1" max="1" width="12.3984375" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="48.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="48.7" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>722828.87800000003</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>725449.93</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>727517.08100000001</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>727716.30099999998</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>728295.52300000004</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>729473.78</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -2569,7 +2569,7 @@
         <v>729287.41799999995</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -2583,7 +2583,7 @@
         <v>729452.23499999999</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>729398.01599999995</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>728330.19400000002</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>728105.16299999994</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>728223.255</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>728252.19</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>730000.83799999999</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>730751.91200000001</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>731740.46699999995</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>732352.56200000003</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>733015.57299999997</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -2737,7 +2737,7 @@
         <v>734777.08299999998</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>736321.8</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>737549.64</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>738740.995</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>739977.41500000004</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>740940.27500000002</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -2821,7 +2821,7 @@
         <v>742001.28700000001</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -2835,7 +2835,7 @@
         <v>743279.99399999995</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>745194.076</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>746812.14</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>748046.28399999999</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>749083.44900000002</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>749924.80500000005</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>749123.28399999999</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>748103.72499999998</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>745825.46</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>745380.28899999999</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>2025</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>744787.35800000001</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>2026</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>744010.30599999998</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>2027</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>742954.41700000002</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>2028</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>741789.71200000006</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>2029</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>740527.35400000005</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>2030</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>739157.09199999995</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>2031</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>737709.81599999999</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>2032</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>736143.12100000004</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>2033</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>734589.397</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>2034</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>733012.58799999999</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <v>2035</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>731408.71900000004</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
         <v>2036</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>729772.30099999998</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="1">
         <v>2037</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>728095.92099999997</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
         <v>2038</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>726400.87600000005</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="1">
         <v>2039</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>724703.647</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="1">
         <v>2040</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>722958.26199999999</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
         <v>2041</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>721244.98499999999</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="1">
         <v>2042</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>719536.97499999998</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="1">
         <v>2043</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>717819.94799999997</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
         <v>2044</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>716032.201</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="1">
         <v>2045</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>714211.69299999997</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="1">
         <v>2046</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>712348.01199999999</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="1">
         <v>2047</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>710440.74300000002</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="1">
         <v>2048</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>708437.35199999996</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="1">
         <v>2049</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>706353.86800000002</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
         <v>2050</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>704160.17799999996</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="1">
         <v>2051</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>701895.34</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="1">
         <v>2052</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>699538.17700000003</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="1">
         <v>2053</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>697115.44700000004</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="1">
         <v>2054</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>694513.78700000001</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="1">
         <v>2055</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>691851.88199999998</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
         <v>2056</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>689074.61100000003</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="1">
         <v>2057</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>686255.70799999998</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="1">
         <v>2058</v>
       </c>
@@ -3437,7 +3437,7 @@
         <v>683407.30299999996</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
         <v>2059</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>680520.071</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="1">
         <v>2060</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>677603.74899999995</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="1">
         <v>2061</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>674715.93099999998</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
         <v>2062</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>671815.46400000004</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="1">
         <v>2063</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>668937.91299999994</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="1">
         <v>2064</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>666081.65899999999</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="1">
         <v>2065</v>
       </c>
@@ -3535,7 +3535,7 @@
         <v>663254.68299999996</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="1">
         <v>2066</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>660460.06999999995</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="1">
         <v>2067</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>657736.19900000002</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="1">
         <v>2068</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>655082.67299999995</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="1">
         <v>2069</v>
       </c>
@@ -3591,7 +3591,7 @@
         <v>652466.40500000003</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="1">
         <v>2070</v>
       </c>
@@ -3605,7 +3605,7 @@
         <v>649895.46600000001</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="1">
         <v>2071</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>647385.17299999995</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="1">
         <v>2072</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>644924.50300000003</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="1">
         <v>2073</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>642548.04799999995</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="1">
         <v>2074</v>
       </c>
@@ -3661,7 +3661,7 @@
         <v>640200.39800000004</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="1">
         <v>2075</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>637905.63800000004</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="1">
         <v>2076</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>635718.05700000003</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="1">
         <v>2077</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>633586.69099999999</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="1">
         <v>2078</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>631465.69099999999</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="1">
         <v>2079</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>629415.12899999996</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="1">
         <v>2080</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>627404.68799999997</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="1">
         <v>2081</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>625461.88899999997</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="1">
         <v>2082</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>623586.20299999998</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="1">
         <v>2083</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>621727.15399999998</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="1">
         <v>2084</v>
       </c>
@@ -3801,7 +3801,7 @@
         <v>619907.59900000005</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A97" s="1">
         <v>2085</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>618109.28700000001</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A98" s="1">
         <v>2086</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>616324.20200000005</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A99" s="1">
         <v>2087</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>614569.38399999996</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A100" s="1">
         <v>2088</v>
       </c>
@@ -3857,7 +3857,7 @@
         <v>612868.772</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A101" s="1">
         <v>2089</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>611200.07799999998</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A102" s="1">
         <v>2090</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>609526.97699999996</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A103" s="1">
         <v>2091</v>
       </c>
@@ -3899,7 +3899,7 @@
         <v>607859.16</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A104" s="1">
         <v>2092</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>606237.61699999997</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A105" s="1">
         <v>2093</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>604606.87600000005</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A106" s="1">
         <v>2094</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>603012.85499999998</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A107" s="1">
         <v>2095</v>
       </c>
@@ -3955,7 +3955,7 @@
         <v>601427.07799999998</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A108" s="1">
         <v>2096</v>
       </c>
@@ -3969,7 +3969,7 @@
         <v>599799.50300000003</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A109" s="1">
         <v>2097</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>598134.46</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A110" s="1">
         <v>2098</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>596471.93000000005</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A111" s="1">
         <v>2099</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>594809.66299999994</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A112" s="1">
         <v>2100</v>
       </c>
@@ -4024,8 +4024,12 @@
       <c r="D112" s="2">
         <v>593112.88</v>
       </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="E112">
+        <f>37*1000000/(C115*1000)</f>
+        <v>0.55133009054881488</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>74</v>
       </c>
@@ -4057,7 +4061,7 @@
         <v>9.639258714121274</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A115" s="11" t="s">
         <v>25</v>
       </c>
@@ -4089,7 +4093,7 @@
         <v>729634.64224242419</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A116" s="10" t="s">
         <v>21</v>
       </c>
@@ -4121,7 +4125,7 @@
         <v>8.2811143358722195</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A117" s="3" t="s">
         <v>26</v>
       </c>
@@ -4153,7 +4157,7 @@
         <v>676189.9753048782</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>21</v>
       </c>
@@ -4185,19 +4189,19 @@
         <v>7.0357584289374984</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A119" s="3"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A120" s="3"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>19</v>
       </c>
@@ -4216,13 +4220,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8683F5-D89E-4384-A263-C6122D6DA873}">
   <dimension ref="A1:AJ45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.69140625" customWidth="1"/>
+    <col min="3" max="3" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -4273,7 +4277,7 @@
       <c r="AI1" s="13"/>
       <c r="AJ1" s="13"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A2" s="13" t="s">
         <v>27</v>
       </c>
@@ -4327,7 +4331,7 @@
       <c r="AI2" s="13"/>
       <c r="AJ2" s="13"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" s="13" t="s">
         <v>28</v>
       </c>
@@ -4381,7 +4385,7 @@
       <c r="AI3" s="13"/>
       <c r="AJ3" s="13"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A4" s="13" t="s">
         <v>29</v>
       </c>
@@ -4436,7 +4440,7 @@
       <c r="AI4" s="13"/>
       <c r="AJ4" s="13"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A5" s="13" t="s">
         <v>30</v>
       </c>
@@ -4489,7 +4493,7 @@
       <c r="AI5" s="13"/>
       <c r="AJ5" s="13"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A6" s="13" t="s">
         <v>31</v>
       </c>
@@ -4515,7 +4519,7 @@
         <v>24904675997.177227</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A7" s="13" t="s">
         <v>32</v>
       </c>
@@ -4541,7 +4545,7 @@
         <v>25612762187.674767</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A8" s="13" t="s">
         <v>33</v>
       </c>
@@ -4567,7 +4571,7 @@
         <v>26087721958.213924</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A9" s="13" t="s">
         <v>34</v>
       </c>
@@ -4593,7 +4597,7 @@
         <v>26723818654.148617</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A10" s="13" t="s">
         <v>35</v>
       </c>
@@ -4619,7 +4623,7 @@
         <v>27468476865.381031</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A11" s="13" t="s">
         <v>36</v>
       </c>
@@ -4645,7 +4649,7 @@
         <v>28176082288.3083</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A12" s="13" t="s">
         <v>37</v>
       </c>
@@ -4671,7 +4675,7 @@
         <v>29240167861.778976</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A13" s="13" t="s">
         <v>38</v>
       </c>
@@ -4697,7 +4701,7 @@
         <v>29862791642.623837</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A14" s="13" t="s">
         <v>39</v>
       </c>
@@ -4723,7 +4727,7 @@
         <v>30165942432.463612</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A15" s="13" t="s">
         <v>40</v>
       </c>
@@ -4749,7 +4753,7 @@
         <v>30462092599.50692</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A16" s="13" t="s">
         <v>41</v>
       </c>
@@ -4775,7 +4779,7 @@
         <v>31221908220.131401</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="13" t="s">
         <v>42</v>
       </c>
@@ -4801,7 +4805,7 @@
         <v>31813500020.819954</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="13" t="s">
         <v>43</v>
       </c>
@@ -4827,7 +4831,7 @@
         <v>32916700218.346203</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="13" t="s">
         <v>44</v>
       </c>
@@ -4853,7 +4857,7 @@
         <v>33919859610.622345</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" s="13" t="s">
         <v>45</v>
       </c>
@@ -4879,7 +4883,7 @@
         <v>34182103766.776295</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" s="13" t="s">
         <v>46</v>
       </c>
@@ -4905,7 +4909,7 @@
         <v>32714648377.874294</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="13" t="s">
         <v>47</v>
       </c>
@@ -4932,7 +4936,7 @@
       </c>
       <c r="J22" s="13"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="13" t="s">
         <v>48</v>
       </c>
@@ -4958,7 +4962,7 @@
         <v>34133681735.471703</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
         <v>49</v>
       </c>
@@ -4984,7 +4988,7 @@
         <v>33882036018.543774</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="13" t="s">
         <v>50</v>
       </c>
@@ -5010,7 +5014,7 @@
         <v>33878734646.466373</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="13" t="s">
         <v>51</v>
       </c>
@@ -5036,7 +5040,7 @@
         <v>34469485024.636459</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="13" t="s">
         <v>52</v>
       </c>
@@ -5062,7 +5066,7 @@
         <v>35298868327.366135</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="13" t="s">
         <v>53</v>
       </c>
@@ -5088,7 +5092,7 @@
         <v>36019907345.254646</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="13" t="s">
         <v>54</v>
       </c>
@@ -5114,7 +5118,7 @@
         <v>37119573491.364235</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="13" t="s">
         <v>55</v>
       </c>
@@ -5140,7 +5144,7 @@
         <v>37930710214.837662</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="13" t="s">
         <v>56</v>
       </c>
@@ -5166,7 +5170,7 @@
         <v>38699419341.686249</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="13" t="s">
         <v>57</v>
       </c>
@@ -5192,7 +5196,7 @@
         <v>36574113872.711426</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="13" t="s">
         <v>58</v>
       </c>
@@ -5218,7 +5222,7 @@
         <v>38931911154.245689</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="13" t="s">
         <v>59</v>
       </c>
@@ -5244,7 +5248,7 @@
         <v>40231131436.83564</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" s="13" t="s">
         <v>60</v>
       </c>
@@ -5270,7 +5274,7 @@
         <v>40177113825.347435</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="13" t="s">
         <v>61</v>
       </c>
@@ -5296,7 +5300,7 @@
         <v>40502412753.686844</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>69</v>
       </c>
@@ -5319,7 +5323,7 @@
         <v>43631.695837336869</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>70</v>
       </c>
@@ -5342,7 +5346,7 @@
         <v>0.1498424508861913</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="E40" s="11" t="s">
         <v>79</v>
       </c>
@@ -5359,7 +5363,7 @@
         <v>1.5668798264892982</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E41" s="3" t="s">
         <v>80</v>
       </c>
@@ -5376,7 +5380,7 @@
         <v>5.9042950726820198E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="E42" s="3" t="s">
         <v>78</v>
       </c>
@@ -5393,7 +5397,7 @@
         <v>0.65838190592741441</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>64</v>
       </c>
@@ -5401,7 +5405,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -5409,7 +5413,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>71</v>
       </c>
@@ -5429,13 +5433,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC11EFA9-274E-476D-8BFE-D8769B6BF052}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="28.69140625" customWidth="1"/>
-    <col min="2" max="2" width="11.61328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B1" s="31" t="s">
         <v>2</v>
       </c>
@@ -5455,7 +5459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="31" t="s">
         <v>120</v>
       </c>
@@ -5484,7 +5488,7 @@
         <v>1.1537633897179685E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="31" t="s">
         <v>119</v>
       </c>
@@ -5513,7 +5517,7 @@
         <v>1.1584810603112349E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -5542,7 +5546,7 @@
         <v>1.1557380920548374E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>130</v>
       </c>
@@ -5550,7 +5554,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>122</v>
       </c>
@@ -5572,7 +5576,7 @@
         <v>0.74445404791547987</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>123</v>
       </c>
@@ -5590,7 +5594,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>124</v>
       </c>
@@ -5601,7 +5605,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>125</v>
       </c>
@@ -5612,7 +5616,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -5623,7 +5627,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>127</v>
       </c>
@@ -5642,114 +5646,114 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE07EBE8-6449-4730-9E28-CE2F7AF6313A}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.07421875" customWidth="1"/>
+    <col min="1" max="1" width="13.06640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2">
         <f>170/74</f>
         <v>2.2972972972972974</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3">
         <f>1055/74</f>
         <v>14.256756756756756</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" s="38"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" s="38">
         <f>((Population!C116/100)*A2)*1000</f>
         <v>17.77125593184725</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" s="38">
         <f>((Population!C116/100)*A3)*1000</f>
         <v>110.28632357705203</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" s="38"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" s="38" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" s="14">
         <v>1000000000</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="15" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" s="20"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" s="22"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" s="22">
         <f>A2*1000000000/(Population!B115*1000)</f>
         <v>0.26480616600193263</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" s="22">
         <f>A3*1000000000/(Population!B115*1000)</f>
         <v>1.6433559125414052</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" s="36" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="20"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19">
         <f>(Capacité!G40/100)*A2</f>
         <v>1.2112525850852601E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20">
         <f>(Capacité!G40/100)*A3</f>
         <v>7.5168910427349956E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="15"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24">
         <f>A2*Besoins!B5*1000</f>
         <v>14.650416625630157</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" s="31">
         <f>A3*Besoins!B5*1000</f>
         <v>90.918762000234196</v>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B37D5D-3804-449C-B357-4A21C28AF5B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C70F14F-3361-4CDE-8AB9-8F520D3CBC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="8002" windowWidth="14595" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Synthèse" sheetId="1" r:id="rId1"/>
-    <sheet name="DLS" sheetId="5" r:id="rId2"/>
-    <sheet name="DLE" sheetId="7" r:id="rId3"/>
-    <sheet name="Population" sheetId="2" r:id="rId4"/>
-    <sheet name="Capacité" sheetId="3" r:id="rId5"/>
-    <sheet name="Besoins" sheetId="6" r:id="rId6"/>
-    <sheet name="Feuil1" sheetId="8" r:id="rId7"/>
+    <sheet name="Synthèse" sheetId="9" r:id="rId1"/>
+    <sheet name="Synthèse v2" sheetId="1" r:id="rId2"/>
+    <sheet name="DLS" sheetId="5" r:id="rId3"/>
+    <sheet name="DLE" sheetId="7" r:id="rId4"/>
+    <sheet name="Population" sheetId="2" r:id="rId5"/>
+    <sheet name="Capacité" sheetId="3" r:id="rId6"/>
+    <sheet name="Besoins" sheetId="6" r:id="rId7"/>
+    <sheet name="Feuil1" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="206">
   <si>
     <t>N</t>
   </si>
@@ -109,18 +110,6 @@
   </si>
   <si>
     <t>Part mondiale</t>
-  </si>
-  <si>
-    <t>Population Europe</t>
-  </si>
-  <si>
-    <t>Population Monde  (au 1er janvier)</t>
-  </si>
-  <si>
-    <t>Population France</t>
-  </si>
-  <si>
-    <t>Moyenne 2015-2051</t>
   </si>
   <si>
     <t>Moyenne 2015-2100</t>
@@ -636,6 +625,114 @@
   <si>
     <t>1e6 MSA-loss.ha</t>
   </si>
+  <si>
+    <t>Part 2011</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>USD 2017 (USD/hab/an)</t>
+  </si>
+  <si>
+    <t>Monde</t>
+  </si>
+  <si>
+    <t>Ratio Fr/Monde</t>
+  </si>
+  <si>
+    <t>moyenne 2015-2050</t>
+  </si>
+  <si>
+    <t>SSP1</t>
+  </si>
+  <si>
+    <t>SSP2</t>
+  </si>
+  <si>
+    <t>SSP3</t>
+  </si>
+  <si>
+    <t>SSP4</t>
+  </si>
+  <si>
+    <t>SSP5</t>
+  </si>
+  <si>
+    <t>Moyenne</t>
+  </si>
+  <si>
+    <t>Mt RME</t>
+  </si>
+  <si>
+    <t>MtCO2eq</t>
+  </si>
+  <si>
+    <t>GHG</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Land</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Materials</t>
+  </si>
+  <si>
+    <t>Biodiversity</t>
+  </si>
+  <si>
+    <t>Gm3</t>
+  </si>
+  <si>
+    <t>Europe</t>
+  </si>
+  <si>
+    <t>Moyenne 2015-2050</t>
+  </si>
+  <si>
+    <t>GtCO2eq</t>
+  </si>
+  <si>
+    <t>Conversion (p.hab)</t>
+  </si>
+  <si>
+    <t>Unité affichage (p.hab)</t>
+  </si>
+  <si>
+    <t>tCO2eq</t>
+  </si>
+  <si>
+    <t>medium variant, 1st july</t>
+  </si>
+  <si>
+    <t>GHG emissions</t>
+  </si>
+  <si>
+    <t>Cropland use</t>
+  </si>
+  <si>
+    <t>N surplus</t>
+  </si>
+  <si>
+    <t>P surplus</t>
+  </si>
+  <si>
+    <t>Final Energy use</t>
+  </si>
+  <si>
+    <t>Raw material consumption</t>
+  </si>
+  <si>
+    <t>Biodiversity loss</t>
+  </si>
+  <si>
+    <t>Blue water consumption</t>
+  </si>
 </sst>
 </file>
 
@@ -644,7 +741,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#\ ###\ ###\ ##0;\-#\ ###\ ###\ ##0;0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -714,8 +811,33 @@
       <name val="Calibri Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -782,8 +904,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E5496"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -820,14 +960,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -890,6 +1046,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="13" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -920,11 +1086,22 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Lien hypertexte" xfId="3" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{50672D9D-075A-40C6-BDA5-FA61CF826F7B}"/>
+    <cellStyle name="Normal 3" xfId="4" xr:uid="{AC874C84-457E-4D34-A0FE-462462C06730}"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1202,27 +1379,689 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C32444-97C3-4A7C-A91C-82059EB528AD}">
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.1328125" customWidth="1"/>
-    <col min="4" max="4" width="14.06640625" customWidth="1"/>
-    <col min="9" max="10" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.15234375" style="31" customWidth="1"/>
+    <col min="2" max="3" width="9.23046875" style="31"/>
+    <col min="4" max="4" width="14.07421875" style="31" customWidth="1"/>
+    <col min="5" max="8" width="9.23046875" style="31"/>
+    <col min="9" max="10" width="11.84375" style="31" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.23046875" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="31">
+        <f>(1.33*170+163.83)/74</f>
+        <v>5.2693243243243248</v>
+      </c>
+      <c r="C2" s="31">
+        <v>2800</v>
+      </c>
+      <c r="D2" s="31">
+        <v>12.6</v>
+      </c>
+      <c r="E2" s="31">
+        <v>57</v>
+      </c>
+      <c r="F2" s="31">
+        <v>4.5</v>
+      </c>
+      <c r="G2" s="31">
+        <v>39.6</v>
+      </c>
+      <c r="H2" s="31">
+        <v>25</v>
+      </c>
+      <c r="I2" s="31">
+        <v>3724</v>
+      </c>
+      <c r="K2" s="31">
+        <f>(0.258-K3)/K3</f>
+        <v>1.2845755630300952</v>
+      </c>
+      <c r="L2" s="31">
+        <f>0.258/K3</f>
+        <v>2.2845755630300952</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A3" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="31">
+        <f>(1.33*1055+163.83)/74</f>
+        <v>21.175405405405407</v>
+      </c>
+      <c r="C3" s="31">
+        <v>4500</v>
+      </c>
+      <c r="D3" s="31">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="F3" s="31">
+        <v>9</v>
+      </c>
+      <c r="G3" s="31">
+        <v>49</v>
+      </c>
+      <c r="H3" s="31">
+        <v>50</v>
+      </c>
+      <c r="K3" s="31">
+        <f>Population!C113*Synthèse!D2/100</f>
+        <v>0.11293126135771475</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A6" s="19"/>
+      <c r="K6" s="31">
+        <f>269/100 -1</f>
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A7" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A8" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="38">
+        <f>((Population!C116/100)*B2)*1000</f>
+        <v>40.756329332322622</v>
+      </c>
+      <c r="C8" s="38">
+        <f>(Population!C116/100)*C2</f>
+        <v>21.656993403065282</v>
+      </c>
+      <c r="D8" s="38">
+        <f>((Population!C116/100)*D2)*1000</f>
+        <v>97.456470313793773</v>
+      </c>
+      <c r="E8" s="38">
+        <f>((Population!C116/100)*E2)*1000</f>
+        <v>440.87450856240042</v>
+      </c>
+      <c r="F8" s="38">
+        <f>((Population!C116/100)*F2)*1000</f>
+        <v>34.805882254926345</v>
+      </c>
+      <c r="G8" s="38">
+        <f>(G2*Population!C115)*0.000277778</f>
+        <v>738.39512671562909</v>
+      </c>
+      <c r="H8" s="38">
+        <f>((Population!C116/100)*H2)*1000</f>
+        <v>193.36601252736861</v>
+      </c>
+      <c r="I8" s="38">
+        <f>(Population!C116/100)*I2</f>
+        <v>28.803801226076825</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A9" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="38">
+        <f>((Population!C116/100)*B3)*1000</f>
+        <v>163.78414827574923</v>
+      </c>
+      <c r="C9" s="38">
+        <f>(Population!C116/100)*C3</f>
+        <v>34.805882254926345</v>
+      </c>
+      <c r="D9" s="38">
+        <f>((Population!C116/100)*D3)*1000</f>
+        <v>126.84810421795379</v>
+      </c>
+      <c r="E9" s="38">
+        <f>((Population!C116/100)*E3)*1000</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="38">
+        <f>((Population!C116/100)*F3)*1000</f>
+        <v>69.611764509852691</v>
+      </c>
+      <c r="G9" s="38">
+        <f>(G3*Population!C115)*0.000366668</f>
+        <v>1206.0487944160323</v>
+      </c>
+      <c r="H9" s="38">
+        <f>((Population!C116/100)*H3)*1000</f>
+        <v>386.73202505473722</v>
+      </c>
+      <c r="I9" s="38">
+        <f>(Population!C116/100)*I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A10" s="37"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="I11" s="38" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A12" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="32">
+        <v>1</v>
+      </c>
+      <c r="C12" s="32">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="32">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="F12" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="G12" s="31">
+        <f>1/0.000277778</f>
+        <v>3599.9971200023037</v>
+      </c>
+      <c r="H12" s="32">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="32">
+        <v>10000000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A15" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A16" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="22">
+        <f>B2*1000000000/(Population!B115*1000)</f>
+        <v>0.60715457766544023</v>
+      </c>
+      <c r="C16" s="22">
+        <f>C2*1000000000/(Population!B115*1000)</f>
+        <v>322.62823709968256</v>
+      </c>
+      <c r="D16" s="22">
+        <f>D2*1000000000000/(Population!B115*1000)</f>
+        <v>1451.8270669485714</v>
+      </c>
+      <c r="E16" s="22">
+        <f>E2*1000000000/(Population!B115*1000)</f>
+        <v>6.5677891123863947</v>
+      </c>
+      <c r="F16" s="22">
+        <f>F2*1000000000/(Population!B115*1000)</f>
+        <v>0.51850966676734689</v>
+      </c>
+      <c r="G16" s="22">
+        <f>G2</f>
+        <v>39.6</v>
+      </c>
+      <c r="H16" s="22">
+        <f>H2*1000000000/(Population!B115*1000)</f>
+        <v>2.8806092598185939</v>
+      </c>
+      <c r="I16" s="22">
+        <f>I2*1000000/(Population!B115*1000)</f>
+        <v>0.42909555534257776</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="22">
+        <f>B3*1000000000/(Population!B115*1000)</f>
+        <v>2.4399227556489409</v>
+      </c>
+      <c r="C17" s="22">
+        <f>C3*1000000000/(Population!B115*1000)</f>
+        <v>518.50966676734697</v>
+      </c>
+      <c r="D17" s="22">
+        <f>D3*1000000000000/(Population!B115*1000)</f>
+        <v>1889.6796744409976</v>
+      </c>
+      <c r="E17" s="22">
+        <f>E3*1000000000/(Population!B115*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="22">
+        <f>F3*1000000000/(Population!B115*1000)</f>
+        <v>1.0370193335346938</v>
+      </c>
+      <c r="G17" s="22">
+        <f>G3</f>
+        <v>49</v>
+      </c>
+      <c r="H17" s="22">
+        <f>H3*1000000000/(Population!B115*1000)</f>
+        <v>5.7612185196371879</v>
+      </c>
+      <c r="I17" s="22">
+        <f>I3*1000000/(Population!B115*1000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="36" t="s">
         <v>83</v>
       </c>
+      <c r="F18" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18" s="36" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B19" s="59">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C19" s="59">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="D19" s="59">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E19" s="59">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F19" s="59">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="G19" s="59">
+        <v>1E-3</v>
+      </c>
+      <c r="H19" s="59">
+        <v>1E-3</v>
+      </c>
+      <c r="I19" s="59">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="31">
+        <f>(Capacité!G43/100)*B2</f>
+        <v>2.7787518571914371E-3</v>
+      </c>
+      <c r="C21" s="31">
+        <f>(Capacité!G43/100)*C2</f>
+        <v>1.4765660113611818</v>
+      </c>
+      <c r="D21" s="31">
+        <f>(Capacité!G43/100)*D2</f>
+        <v>6.6445470511253182E-3</v>
+      </c>
+      <c r="E21" s="31">
+        <f>(Capacité!G43/100)*E2</f>
+        <v>3.0058665231281204E-2</v>
+      </c>
+      <c r="F21" s="31">
+        <f>(Capacité!G43/100)*F2</f>
+        <v>2.3730525182590425E-3</v>
+      </c>
+      <c r="G21" s="31">
+        <f>(Capacité!G43/100)*G2</f>
+        <v>2.0882862160679572E-2</v>
+      </c>
+      <c r="H21" s="31">
+        <f>((Capacité!G42/100)*H2)*1000</f>
+        <v>13.743345116682876</v>
+      </c>
+      <c r="I21" s="31">
+        <f>(Capacité!G43/100)*I2</f>
+        <v>1.963832795110372</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="31">
+        <f>(Capacité!G43/100)*B3</f>
+        <v>1.1166744249434098E-2</v>
+      </c>
+      <c r="C22" s="31">
+        <f>(Capacité!G43/100)*C3</f>
+        <v>2.3730525182590423</v>
+      </c>
+      <c r="D22" s="31">
+        <f>(Capacité!G43/100)*D3</f>
+        <v>8.6484580665440649E-3</v>
+      </c>
+      <c r="E22" s="31">
+        <f>(Capacité!G43/100)*E3</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="31">
+        <f>(Capacité!G43/100)*F3</f>
+        <v>4.746105036518085E-3</v>
+      </c>
+      <c r="G22" s="31">
+        <f>(Capacité!G43/100)*G3</f>
+        <v>2.5839905198820682E-2</v>
+      </c>
+      <c r="H22" s="31">
+        <f>((Capacité!G43/100)*H3)*1000</f>
+        <v>26.367250202878246</v>
+      </c>
+      <c r="I22" s="31">
+        <f>(Capacité!G43/100)*I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23" s="19"/>
+    </row>
+    <row r="24" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="15"/>
+    </row>
+    <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="31">
+        <f>B2*Besoins!B5*1000</f>
+        <v>33.599043710798185</v>
+      </c>
+      <c r="C26" s="31">
+        <f>C2*Besoins!C5</f>
+        <v>15.326824494696991</v>
+      </c>
+      <c r="D26" s="31">
+        <f>D2*Besoins!D5*1000</f>
+        <v>145.65971173167631</v>
+      </c>
+      <c r="H26" s="31">
+        <f>H2*Besoins!E5*1000</f>
+        <v>183.26764541723307</v>
+      </c>
+      <c r="I26" s="31">
+        <f>I2*Besoins!G5</f>
+        <v>43.033662839201128</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A27" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" s="31">
+        <f>B3*Besoins!B5*1000</f>
+        <v>135.02174624662513</v>
+      </c>
+      <c r="C27" s="31">
+        <f>C3*Besoins!C5</f>
+        <v>24.632396509334448</v>
+      </c>
+      <c r="D27" s="31">
+        <f>D3*Besoins!D5*1000</f>
+        <v>189.58883114281673</v>
+      </c>
+      <c r="H27" s="31">
+        <f>H3*Besoins!E5*1000</f>
+        <v>366.53529083446614</v>
+      </c>
+      <c r="I27" s="31">
+        <f>I3*Besoins!G5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A28" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="21.15234375" customWidth="1"/>
+    <col min="4" max="4" width="14.07421875" customWidth="1"/>
+    <col min="9" max="10" width="11.84375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="18" t="s">
+        <v>79</v>
+      </c>
       <c r="B1" s="17" t="s">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>3</v>
+        <v>185</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="E1" s="17" t="s">
         <v>0</v>
@@ -1231,16 +2070,16 @@
         <v>1</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>12</v>
+        <v>187</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>11</v>
+        <v>188</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="19" t="s">
         <v>15</v>
       </c>
@@ -1269,10 +2108,18 @@
       <c r="I2">
         <v>3724</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K2">
+        <f>(0.258-K3)/K3</f>
+        <v>1.2845755630300952</v>
+      </c>
+      <c r="L2">
+        <f>0.258/K3</f>
+        <v>2.2845755630300952</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B3">
         <f>(1.33*1055+163.83)/74</f>
@@ -1282,7 +2129,7 @@
         <v>4500</v>
       </c>
       <c r="D3">
-        <v>14.6</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="E3">
         <v>37.700000000000003</v>
@@ -1299,8 +2146,12 @@
       <c r="I3">
         <v>26068</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="K3">
+        <f>Population!C113*'Synthèse v2'!D2/100</f>
+        <v>0.11293126135771475</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="16" t="s">
         <v>5</v>
       </c>
@@ -1308,7 +2159,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>8</v>
@@ -1329,10 +2180,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="19"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K5">
+        <f>269/100 -1</f>
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="37" t="s">
         <v>14</v>
       </c>
@@ -1345,82 +2200,82 @@
       <c r="H6" s="38"/>
       <c r="I6" s="38"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="37" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B7" s="38">
         <f>((Population!C116/100)*B2)*1000</f>
-        <v>40.762034267677642</v>
+        <v>40.756329332322622</v>
       </c>
       <c r="C7" s="38">
         <f>(Population!C116/100)*C2</f>
-        <v>21.660024876933825</v>
+        <v>21.656993403065282</v>
       </c>
       <c r="D7" s="38">
         <f>((Population!C116/100)*D2)*1000</f>
-        <v>97.470111946202195</v>
+        <v>97.456470313793773</v>
       </c>
       <c r="E7" s="38">
         <f>((Population!C116/100)*E2)*1000</f>
-        <v>220.468110354505</v>
+        <v>220.43725428120021</v>
       </c>
       <c r="F7" s="38">
         <f>((Population!C116/100)*F2)*1000</f>
-        <v>14.465802328523662</v>
+        <v>14.463777737047172</v>
       </c>
       <c r="G7" s="38">
         <f>(G2*Population!C115)*0.000277778</f>
-        <v>738.21533157179306</v>
+        <v>738.39512671562909</v>
       </c>
       <c r="H7" s="38">
         <f>((Population!C116/100)*H2)*1000</f>
-        <v>193.39307925833771</v>
+        <v>193.36601252736861</v>
       </c>
       <c r="I7" s="38">
         <f>(Population!C116/100)*I2</f>
-        <v>28.807833086321985</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+        <v>28.803801226076825</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="37" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B8" s="38">
         <f>((Population!C116/100)*B3)*1000</f>
-        <v>163.8070742358</v>
+        <v>163.78414827574923</v>
       </c>
       <c r="C8" s="38">
         <f>(Population!C116/100)*C3</f>
-        <v>34.810754266500787</v>
+        <v>34.805882254926345</v>
       </c>
       <c r="D8" s="38">
         <f>((Population!C116/100)*D3)*1000</f>
-        <v>112.94155828686922</v>
+        <v>126.84810421795379</v>
       </c>
       <c r="E8" s="38">
         <f>((Population!C116/100)*E3)*1000</f>
-        <v>291.6367635215733</v>
+        <v>291.59594689127186</v>
       </c>
       <c r="F8" s="38">
         <f>((Population!C116/100)*F3)*1000</f>
-        <v>131.50729389566965</v>
+        <v>131.48888851861065</v>
       </c>
       <c r="G8" s="38">
         <f>(G3*Population!C115)*0.000366668</f>
-        <v>1205.7551281814922</v>
+        <v>1206.0487944160323</v>
       </c>
       <c r="H8" s="38">
         <f>((Population!C116/100)*H3)*1000</f>
-        <v>386.78615851667541</v>
+        <v>386.73202505473722</v>
       </c>
       <c r="I8" s="38">
         <f>(Population!C116/100)*I3</f>
-        <v>201.6548316042539</v>
+        <v>201.62660858253778</v>
       </c>
       <c r="J8" s="31"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="37"/>
       <c r="B9" s="38"/>
       <c r="C9" s="38"/>
@@ -1431,41 +2286,41 @@
       <c r="H9" s="38"/>
       <c r="I9" s="38"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="37" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>85</v>
+        <v>182</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B11" s="14">
-        <v>1000000000</v>
+        <v>1</v>
       </c>
       <c r="C11" s="14">
         <v>1000</v>
@@ -1490,36 +2345,36 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>96</v>
-      </c>
       <c r="I12" s="15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -1530,9 +2385,9 @@
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="34" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -1543,29 +2398,29 @@
       <c r="H14" s="22"/>
       <c r="I14" s="22"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="34" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B15" s="22">
         <f>B2*1000000000/(Population!B115*1000)</f>
-        <v>0.60738746064196225</v>
+        <v>0.60715457766544023</v>
       </c>
       <c r="C15" s="22">
         <f>C2*1000000000/(Population!B115*1000)</f>
-        <v>322.75198585647314</v>
+        <v>322.62823709968256</v>
       </c>
       <c r="D15" s="22">
         <f>D2*1000000000000/(Population!B115*1000)</f>
-        <v>1452.3839363541292</v>
+        <v>1451.8270669485714</v>
       </c>
       <c r="E15" s="22">
         <f>E2*1000000000/(Population!B115*1000)</f>
-        <v>3.2851541417533872</v>
+        <v>3.2838945561931974</v>
       </c>
       <c r="F15" s="22">
         <f>F2*1000000000/(Population!B115*1000)</f>
-        <v>0.21555221912557312</v>
+        <v>0.21546957263443084</v>
       </c>
       <c r="G15" s="22">
         <f>G2</f>
@@ -1573,36 +2428,36 @@
       </c>
       <c r="H15" s="22">
         <f>H2*1000000000/(Population!B115*1000)</f>
-        <v>2.881714159432796</v>
+        <v>2.8806092598185939</v>
       </c>
       <c r="I15" s="22">
         <f>I2*1000000/(Population!B115*1000)</f>
-        <v>0.42926014118910927</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+        <v>0.42909555534257776</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="34" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B16" s="22">
         <f>B3*1000000000/(Population!B115*1000)</f>
-        <v>2.4408586235394609</v>
+        <v>2.4399227556489409</v>
       </c>
       <c r="C16" s="22">
         <f>C3*1000000000/(Population!B115*1000)</f>
-        <v>518.70854869790321</v>
+        <v>518.50966676734697</v>
       </c>
       <c r="D16" s="22">
         <f>D3*1000000000000/(Population!B115*1000)</f>
-        <v>1682.9210691087528</v>
+        <v>1889.6796744409976</v>
       </c>
       <c r="E16" s="22">
         <f>E3*1000000000/(Population!B115*1000)</f>
-        <v>4.3456249524246564</v>
+        <v>4.3439587638064401</v>
       </c>
       <c r="F16" s="22">
         <f>F3*1000000000/(Population!B115*1000)</f>
-        <v>1.9595656284143013</v>
+        <v>1.958814296676644</v>
       </c>
       <c r="G16" s="22">
         <f>G3</f>
@@ -1610,43 +2465,43 @@
       </c>
       <c r="H16" s="22">
         <f>H3*1000000000/(Population!B115*1000)</f>
-        <v>5.7634283188655919</v>
+        <v>5.7612185196371879</v>
       </c>
       <c r="I16" s="22">
         <f>I3*1000000/(Population!B115*1000)</f>
-        <v>3.0048209883237651</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>3.0036688873980446</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="35" t="s">
         <v>5</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F17" s="36" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G17" s="36" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="H17" s="36" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I17" s="36" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="19"/>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -1657,92 +2512,92 @@
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
         <v>16</v>
       </c>
       <c r="B19">
-        <f>(Capacité!G40/100)*B2</f>
-        <v>2.7782571794252677E-3</v>
+        <f>(Capacité!G43/100)*B2</f>
+        <v>2.7787518571914371E-3</v>
       </c>
       <c r="C19">
-        <f>(Capacité!G40/100)*C2</f>
-        <v>1.4763031507627404</v>
+        <f>(Capacité!G43/100)*C2</f>
+        <v>1.4765660113611818</v>
       </c>
       <c r="D19">
-        <f>(Capacité!G40/100)*D2</f>
-        <v>6.643364178432332E-3</v>
+        <f>(Capacité!G43/100)*D2</f>
+        <v>6.6445470511253182E-3</v>
       </c>
       <c r="E19">
-        <f>(Capacité!G40/100)*E2</f>
-        <v>1.5026657070263608E-2</v>
+        <f>(Capacité!G43/100)*E2</f>
+        <v>1.5029332615640602E-2</v>
       </c>
       <c r="F19">
-        <f>(Capacité!G40/100)*F2</f>
-        <v>9.8595960425940164E-4</v>
+        <f>(Capacité!G43/100)*F2</f>
+        <v>9.8613515758764645E-4</v>
       </c>
       <c r="G19">
-        <f>(Capacité!G40/100)*G2</f>
-        <v>2.0879144560787332E-2</v>
+        <f>(Capacité!G43/100)*G2</f>
+        <v>2.0882862160679572E-2</v>
       </c>
       <c r="H19">
-        <f>((Capacité!G39/100)*H2)*1000</f>
-        <v>13.737674325397714</v>
+        <f>((Capacité!G42/100)*H2)*1000</f>
+        <v>13.743345116682876</v>
       </c>
       <c r="I19">
-        <f>(Capacité!G40/100)*I2</f>
-        <v>1.9634831905144448</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+        <f>(Capacité!G43/100)*I2</f>
+        <v>1.963832795110372</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B20">
-        <f>(Capacité!G40/100)*B3</f>
-        <v>1.1164756328099417E-2</v>
+        <f>(Capacité!G43/100)*B3</f>
+        <v>1.1166744249434098E-2</v>
       </c>
       <c r="C20">
-        <f>(Capacité!G40/100)*C3</f>
-        <v>2.3726300637258331</v>
+        <f>(Capacité!G43/100)*C3</f>
+        <v>2.3730525182590423</v>
       </c>
       <c r="D20">
-        <f>(Capacité!G40/100)*D3</f>
-        <v>7.6978664289771466E-3</v>
+        <f>(Capacité!G43/100)*D3</f>
+        <v>8.6484580665440649E-3</v>
       </c>
       <c r="E20">
-        <f>(Capacité!G40/100)*E3</f>
-        <v>1.9877367422769757E-2</v>
+        <f>(Capacité!G43/100)*E3</f>
+        <v>1.9880906652970199E-2</v>
       </c>
       <c r="F20">
-        <f>(Capacité!G40/100)*F3</f>
-        <v>8.9632691296309235E-3</v>
+        <f>(Capacité!G43/100)*F3</f>
+        <v>8.9648650689786048E-3</v>
       </c>
       <c r="G20">
-        <f>(Capacité!G40/100)*G3</f>
-        <v>2.5835305138347957E-2</v>
+        <f>(Capacité!G43/100)*G3</f>
+        <v>2.5839905198820682E-2</v>
       </c>
       <c r="H20">
-        <f>((Capacité!G40/100)*H3)*1000</f>
-        <v>26.362556263620363</v>
+        <f>((Capacité!G43/100)*H3)*1000</f>
+        <v>26.367250202878246</v>
       </c>
       <c r="I20">
-        <f>(Capacité!G40/100)*I3</f>
-        <v>13.744382333601115</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+        <f>(Capacité!G43/100)*I3</f>
+        <v>13.746829565772604</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" s="19"/>
     </row>
-    <row r="22" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="19" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="15"/>
     </row>
-    <row r="23" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="16" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -1753,63 +2608,63 @@
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B24" s="31">
         <f>B2*Besoins!B5*1000</f>
-        <v>33.603746793129218</v>
+        <v>33.599043710798185</v>
       </c>
       <c r="C24" s="31">
         <f>C2*Besoins!C5</f>
-        <v>15.328969892586652</v>
+        <v>15.326824494696991</v>
       </c>
       <c r="D24" s="31">
         <f>D2*Besoins!D5*1000</f>
-        <v>145.68010069341233</v>
+        <v>145.65971173167631</v>
       </c>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
       <c r="G24" s="31"/>
       <c r="H24" s="31">
         <f>H2*Besoins!E5*1000</f>
-        <v>183.29329861237841</v>
+        <v>183.26764541723307</v>
       </c>
       <c r="I24" s="31">
         <f>I2*Besoins!G5</f>
-        <v>43.039686548122148</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+        <v>43.033662839201128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B25" s="31">
         <f>B3*Besoins!B5*1000</f>
-        <v>135.04064614135262</v>
+        <v>135.02174624662513</v>
       </c>
       <c r="C25" s="31">
         <f>C3*Besoins!C5</f>
-        <v>24.635844470228548</v>
+        <v>24.632396509334448</v>
       </c>
       <c r="D25" s="31">
         <f>D3*Besoins!D5*1000</f>
-        <v>168.80392620030318</v>
+        <v>189.58883114281673</v>
       </c>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
       <c r="G25" s="31"/>
       <c r="H25" s="31">
         <f>H3*Besoins!E5*1000</f>
-        <v>366.58659722475682</v>
+        <v>366.53529083446614</v>
       </c>
       <c r="I25" s="31">
         <f>I3*Besoins!G5</f>
-        <v>301.27780583685501</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+        <v>301.23563987440787</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="19"/>
     </row>
   </sheetData>
@@ -1817,20 +2672,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1104A7-2272-4986-AE6B-8EA45794950A}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="27.73046875" customWidth="1"/>
-    <col min="3" max="4" width="12.3984375" customWidth="1"/>
-    <col min="5" max="5" width="11.9296875" customWidth="1"/>
-    <col min="7" max="7" width="14.86328125" customWidth="1"/>
+    <col min="1" max="1" width="27.69140625" customWidth="1"/>
+    <col min="3" max="4" width="12.3828125" customWidth="1"/>
+    <col min="5" max="5" width="11.921875" customWidth="1"/>
+    <col min="7" max="7" width="14.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="23" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>2</v>
@@ -1839,7 +2694,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>11</v>
@@ -1851,9 +2706,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B2" s="22">
         <v>2.57</v>
@@ -1877,9 +2732,9 @@
         <v>4.0776939000000005E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B3" s="22">
         <v>2.2000000000000002</v>
@@ -1903,9 +2758,9 @@
         <v>2.9475940000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B4" s="22">
         <f>(DLS!B2+DLS!B3)/2</f>
@@ -1932,37 +2787,37 @@
         <v>3.5126439500000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D5" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="E5" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="F5" s="22" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
         <v>110</v>
       </c>
-      <c r="G5" s="22" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B8" s="26">
         <v>3.9404604370967649</v>
@@ -1986,9 +2841,9 @@
         <v>2.7340017428936065E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B9" s="27">
         <v>1.8456474232498501</v>
@@ -2012,9 +2867,9 @@
         <v>1.9682472147114907E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="31" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B10">
         <f>(DLS!B8+DLS!B9)/2</f>
@@ -2041,166 +2896,166 @@
         <v>2.3511244788025486E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G11" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="E11" t="s">
-        <v>105</v>
-      </c>
-      <c r="F11" t="s">
-        <v>110</v>
-      </c>
-      <c r="G11" s="31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="33" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B13" s="33">
         <f>(B2*Population!C115*0.000001)*1000</f>
-        <v>172.47380767000001</v>
+        <v>172.51581432</v>
       </c>
       <c r="C13" s="33">
         <f>C2*Population!C115*1000*0.000000001</f>
-        <v>9.751145624300003</v>
+        <v>9.7535205528000031</v>
       </c>
       <c r="D13" s="33">
         <f>(D2*Population!C115*1000*0.000000001)</f>
-        <v>304.01025243000009</v>
+        <v>304.08429528000011</v>
       </c>
       <c r="E13" s="33">
         <f>(E2*Population!C115*0.000001)*1000</f>
-        <v>265.08620245000003</v>
+        <v>265.15076520000008</v>
       </c>
       <c r="F13" s="33">
         <f>F2*Population!C115*0.000277778</f>
-        <v>494.19049726929296</v>
+        <v>494.3108592392208</v>
       </c>
       <c r="G13" s="33">
         <f>(G2*Population!D115*1000)*0.000001</f>
-        <v>29.823675351128617</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+        <v>17.921343875225901</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B14" s="33">
         <f>(B3*Population!C115*0.000001)*1000</f>
-        <v>147.64294820000003</v>
+        <v>147.67890720000005</v>
       </c>
       <c r="C14" s="33">
         <f>(C3*Population!C115*0.000001)</f>
-        <v>9.415593469300001</v>
+        <v>9.4178866728000017</v>
       </c>
       <c r="D14" s="33">
         <f>(D3*Population!C115*0.000000001)*1000</f>
-        <v>282.53491451000008</v>
+        <v>282.60372696000007</v>
       </c>
       <c r="E14" s="33">
         <f>(E3*Population!C115*0.000001)*1000</f>
-        <v>246.29528177</v>
+        <v>246.35526792000005</v>
       </c>
       <c r="F14" s="33">
         <f>F3*Population!C115*0.000277778</f>
-        <v>290.81210031616087</v>
+        <v>290.88292870615692</v>
       </c>
       <c r="G14" s="33">
         <f>(G3*Population!D115*1000)*0.000001</f>
-        <v>21.558284824403962</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.45">
+        <v>12.954588297702438</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A15" s="33" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B15" s="33">
         <f>(B4*Population!C115*0.000001)*1000</f>
-        <v>160.05837793500001</v>
+        <v>160.09736076000002</v>
       </c>
       <c r="C15" s="33">
         <f>(C4*Population!C115*0.000001)</f>
-        <v>9.583369546800002</v>
+        <v>9.5857036128000015</v>
       </c>
       <c r="D15" s="33">
         <f>(D4*Population!C115*0.000000001)*1000</f>
-        <v>293.27258347000009</v>
+        <v>293.34401112000006</v>
       </c>
       <c r="E15" s="33">
         <f>(E4*Population!C115*0.000001)*1000</f>
-        <v>255.69074211000003</v>
+        <v>255.75301656000005</v>
       </c>
       <c r="F15" s="33">
         <f>F4*Population!C115*0.000277778</f>
-        <v>392.50129879272691</v>
+        <v>392.59689397268886</v>
       </c>
       <c r="G15" s="33">
         <f>(G4*Population!D115*1000)*0.000001</f>
-        <v>25.690980087766288</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+        <v>15.43796608646417</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="33" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G16" s="33" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="45"/>
+      <c r="B18" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
       <c r="F18" s="21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="G21" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="G22" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="G23" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2216,137 +3071,137 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE59BEB1-58EA-414F-91E0-ADFFF27E94F9}">
   <dimension ref="A2:U6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.06640625" style="31"/>
+    <col min="1" max="1" width="11.07421875" style="31"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" ht="15.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49" t="s">
+    <row r="2" spans="1:21" ht="16.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="52" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="52" t="s">
+        <v>140</v>
+      </c>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="L2" s="53"/>
+      <c r="M2" s="56" t="s">
+        <v>142</v>
+      </c>
+      <c r="N2" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="48" t="s">
+      <c r="O2" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49" t="s">
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="L2" s="49"/>
-      <c r="M2" s="52" t="s">
+      <c r="S2" s="53"/>
+      <c r="T2" s="57" t="s">
+        <v>164</v>
+      </c>
+      <c r="U2" s="55" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="B3" s="51" t="s">
         <v>146</v>
       </c>
-      <c r="N2" s="50" t="s">
+      <c r="C3" s="51" t="s">
         <v>147</v>
       </c>
-      <c r="O2" s="48" t="s">
+      <c r="D3" s="51" t="s">
         <v>148</v>
       </c>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="S2" s="49"/>
-      <c r="T2" s="53" t="s">
-        <v>168</v>
-      </c>
-      <c r="U2" s="51" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="17.649999999999999" x14ac:dyDescent="0.45">
-      <c r="B3" s="47" t="s">
+      <c r="F3" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="G3" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="H3" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="E3" s="46" t="s">
+      <c r="I3" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="F3" s="46" t="s">
+      <c r="J3" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="G3" s="46" t="s">
+      <c r="K3" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="H3" s="47" t="s">
+      <c r="L3" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="I3" s="47" t="s">
+      <c r="M3" s="56"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="J3" s="47" t="s">
+      <c r="P3" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="K3" s="46" t="s">
+      <c r="Q3" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="L3" s="46" t="s">
+      <c r="R3" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="S3" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="T3" s="57"/>
+      <c r="U3" s="55"/>
+    </row>
+    <row r="4" spans="1:21" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="39" t="s">
         <v>160</v>
       </c>
-      <c r="M3" s="52"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="47" t="s">
-        <v>161</v>
-      </c>
-      <c r="P3" s="47" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q3" s="39" t="s">
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="57"/>
+      <c r="U4" s="55"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="A5" s="31" t="s">
         <v>163</v>
-      </c>
-      <c r="R3" s="46" t="s">
-        <v>165</v>
-      </c>
-      <c r="S3" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="T3" s="53"/>
-      <c r="U3" s="51"/>
-    </row>
-    <row r="4" spans="1:21" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="47"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="46"/>
-      <c r="L4" s="46"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="R4" s="46"/>
-      <c r="S4" s="46"/>
-      <c r="T4" s="53"/>
-      <c r="U4" s="51"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A5" s="31" t="s">
-        <v>167</v>
       </c>
       <c r="B5" s="40">
         <v>2.7</v>
@@ -2410,7 +3265,7 @@
         <v>15.600000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A6" s="31" t="s">
         <v>13</v>
       </c>
@@ -2448,1590 +3303,1602 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95CE491-5889-4A7E-A6ED-A3FC6F8FA184}">
-  <dimension ref="A1:I121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I122"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" customWidth="1"/>
-    <col min="2" max="2" width="12.86328125" customWidth="1"/>
+    <col min="1" max="1" width="12.3828125" customWidth="1"/>
+    <col min="2" max="2" width="12.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="48.7" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B1" s="61" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1" s="61" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
       <c r="B2" s="2">
-        <v>5280969.5199999996</v>
+        <v>5327803.1100000003</v>
       </c>
       <c r="C2" s="2">
-        <v>56847.224000000002</v>
+        <v>56990.237999999998</v>
       </c>
       <c r="D2" s="2">
-        <v>722828.87800000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+        <v>419997.47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
       <c r="B3" s="2">
-        <v>5374636.7000000002</v>
+        <v>5418735.8909999998</v>
       </c>
       <c r="C3" s="2">
-        <v>57133.252999999997</v>
+        <v>57271.565000000002</v>
       </c>
       <c r="D3" s="2">
-        <v>725449.93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+        <v>421419.174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
       <c r="B4" s="2">
-        <v>5462835.0829999996</v>
+        <v>5505989.8159999996</v>
       </c>
       <c r="C4" s="2">
-        <v>57409.877</v>
+        <v>57554.87</v>
       </c>
       <c r="D4" s="2">
-        <v>727517.08100000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+        <v>422863.59999999992</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
       <c r="B5" s="2">
-        <v>5549144.5489999996</v>
+        <v>5591544.7970000003</v>
       </c>
       <c r="C5" s="2">
-        <v>57699.862999999998</v>
+        <v>57801.266000000003</v>
       </c>
       <c r="D5" s="2">
-        <v>727716.30099999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+        <v>424104.70499999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
       <c r="B6" s="2">
-        <v>5633945.0449999999</v>
+        <v>5675551.2549999999</v>
       </c>
       <c r="C6" s="2">
-        <v>57902.67</v>
+        <v>57999.866000000002</v>
       </c>
       <c r="D6" s="2">
-        <v>728295.52300000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+        <v>425188.98800000019</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
       <c r="B7" s="2">
-        <v>5717157.466</v>
+        <v>5758878.9819999998</v>
       </c>
       <c r="C7" s="2">
-        <v>58097.063000000002</v>
+        <v>58192.203000000001</v>
       </c>
       <c r="D7" s="2">
-        <v>729473.78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+        <v>425847.82800000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
       <c r="B8" s="2">
-        <v>5800600.4979999997</v>
+        <v>5842055.7340000002</v>
       </c>
       <c r="C8" s="2">
-        <v>58287.343000000001</v>
+        <v>58380.641000000003</v>
       </c>
       <c r="D8" s="2">
-        <v>729287.41799999995</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+        <v>426181.87299999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
       <c r="B9" s="2">
-        <v>5883510.9689999996</v>
+        <v>5924787.8159999996</v>
       </c>
       <c r="C9" s="2">
-        <v>58473.94</v>
+        <v>58568.66</v>
       </c>
       <c r="D9" s="2">
-        <v>729452.23499999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+        <v>426651.66799999989</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
       <c r="B10" s="2">
-        <v>5966064.6639999999</v>
+        <v>6007066.6900000004</v>
       </c>
       <c r="C10" s="2">
-        <v>58663.38</v>
+        <v>58778.815999999999</v>
       </c>
       <c r="D10" s="2">
-        <v>729398.01599999995</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+        <v>426655.42999999993</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
       <c r="B11" s="2">
-        <v>6048068.7149999999</v>
+        <v>6089006.3389999997</v>
       </c>
       <c r="C11" s="2">
-        <v>58894.252</v>
+        <v>59084.21</v>
       </c>
       <c r="D11" s="2">
-        <v>728330.19400000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+        <v>426830.63099999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
       <c r="B12" s="2">
-        <v>6129943.9639999997</v>
+        <v>6171702.9929999998</v>
       </c>
       <c r="C12" s="2">
-        <v>59274.167999999998</v>
+        <v>59483.716999999997</v>
       </c>
       <c r="D12" s="2">
-        <v>728105.16299999994</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+        <v>427627.31800000009</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
       <c r="B13" s="2">
-        <v>6213462.023</v>
+        <v>6254936.4589999998</v>
       </c>
       <c r="C13" s="2">
-        <v>59693.264999999999</v>
+        <v>59905.127999999997</v>
       </c>
       <c r="D13" s="2">
-        <v>728223.255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+        <v>428578.28599999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
       <c r="B14" s="2">
-        <v>6296410.8959999997</v>
+        <v>6337730.3420000002</v>
       </c>
       <c r="C14" s="2">
-        <v>60116.99</v>
+        <v>60327.248</v>
       </c>
       <c r="D14" s="2">
-        <v>728252.19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+        <v>429890.46400000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
       <c r="B15" s="2">
-        <v>6379049.7879999997</v>
+        <v>6420361.6339999996</v>
       </c>
       <c r="C15" s="2">
-        <v>60537.506000000001</v>
+        <v>60741.125999999997</v>
       </c>
       <c r="D15" s="2">
-        <v>730000.83799999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+        <v>431461.80999999994</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
       <c r="B16" s="2">
-        <v>6461673.4790000003</v>
+        <v>6503377.7719999999</v>
       </c>
       <c r="C16" s="2">
-        <v>60944.745000000003</v>
+        <v>61175.247000000003</v>
       </c>
       <c r="D16" s="2">
-        <v>730751.91200000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+        <v>433058.58899999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
       <c r="B17" s="2">
-        <v>6545082.0650000004</v>
+        <v>6586970.1320000002</v>
       </c>
       <c r="C17" s="2">
-        <v>61405.748</v>
+        <v>61625.031999999999</v>
       </c>
       <c r="D17" s="2">
-        <v>731740.46699999995</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+        <v>434557.12100000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
       <c r="B18" s="2">
-        <v>6628858.1979999999</v>
+        <v>6671452.0149999997</v>
       </c>
       <c r="C18" s="2">
-        <v>61844.315999999999</v>
+        <v>62049.838000000003</v>
       </c>
       <c r="D18" s="2">
-        <v>732352.56200000003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+        <v>435683.11500000011</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
       <c r="B19" s="2">
-        <v>6714045.8329999996</v>
+        <v>6757308.7810000004</v>
       </c>
       <c r="C19" s="2">
-        <v>62255.358999999997</v>
+        <v>62432.438999999998</v>
       </c>
       <c r="D19" s="2">
-        <v>733015.57299999997</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+        <v>436994.47300000006</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
       <c r="B20" s="2">
-        <v>6800571.7300000004</v>
+        <v>6844457.6619999995</v>
       </c>
       <c r="C20" s="2">
-        <v>62609.519</v>
+        <v>62780.19</v>
       </c>
       <c r="D20" s="2">
-        <v>734777.08299999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+        <v>438548.18900000007</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
       <c r="B21" s="2">
-        <v>6888343.5939999996</v>
+        <v>6932766.4160000002</v>
       </c>
       <c r="C21" s="2">
-        <v>62950.860999999997</v>
+        <v>63106.463000000003</v>
       </c>
       <c r="D21" s="2">
-        <v>736321.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+        <v>439690.78899999993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
       <c r="B22" s="2">
-        <v>6977189.2369999997</v>
+        <v>7021732.148</v>
       </c>
       <c r="C22" s="2">
-        <v>63262.065000000002</v>
+        <v>63417.362999999998</v>
       </c>
       <c r="D22" s="2">
-        <v>737549.64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+        <v>440608.95100000006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
       <c r="B23" s="2">
-        <v>7066275.0590000004</v>
+        <v>7110923.7649999997</v>
       </c>
       <c r="C23" s="2">
-        <v>63572.66</v>
+        <v>63733.777000000002</v>
       </c>
       <c r="D23" s="2">
-        <v>738740.995</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+        <v>441440.62800000008</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
       <c r="B24" s="2">
-        <v>7155572.4720000001</v>
+        <v>7201202.4850000003</v>
       </c>
       <c r="C24" s="2">
-        <v>63894.894</v>
+        <v>64058.464999999997</v>
       </c>
       <c r="D24" s="2">
-        <v>739977.41500000004</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+        <v>441999.21399999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
       <c r="B25" s="2">
-        <v>7246832.4970000004</v>
+        <v>7291793.585</v>
       </c>
       <c r="C25" s="2">
-        <v>64222.036999999997</v>
+        <v>64387.733999999997</v>
       </c>
       <c r="D25" s="2">
-        <v>740940.27500000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+        <v>442399.391</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
       <c r="B26" s="2">
-        <v>7336754.6730000004</v>
+        <v>7381616.2439999999</v>
       </c>
       <c r="C26" s="2">
-        <v>64553.430999999997</v>
+        <v>64692.493000000002</v>
       </c>
       <c r="D26" s="2">
-        <v>742001.28700000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+        <v>442964.72000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
       <c r="B27" s="2">
-        <v>7426477.8150000004</v>
+        <v>7470491.8720000004</v>
       </c>
       <c r="C27" s="2">
-        <v>64831.553999999996</v>
+        <v>64916.336000000003</v>
       </c>
       <c r="D27" s="2">
-        <v>743279.99399999995</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+        <v>443910.90800000017</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
       <c r="B28" s="2">
-        <v>7514505.9280000003</v>
+        <v>7558554.5259999996</v>
       </c>
       <c r="C28" s="2">
-        <v>65001.118000000002</v>
+        <v>65086.855000000003</v>
       </c>
       <c r="D28" s="2">
-        <v>745194.076</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+        <v>444911.48800000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
       <c r="B29" s="2">
-        <v>7602603.1229999997</v>
+        <v>7645617.9539999999</v>
       </c>
       <c r="C29" s="2">
-        <v>65172.593000000001</v>
+        <v>65284.775999999998</v>
       </c>
       <c r="D29" s="2">
-        <v>746812.14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+        <v>445696.74599999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
       <c r="B30" s="2">
-        <v>7688632.7850000001</v>
+        <v>7729902.7810000004</v>
       </c>
       <c r="C30" s="2">
-        <v>65396.959000000003</v>
+        <v>65519.542999999998</v>
       </c>
       <c r="D30" s="2">
-        <v>748046.28399999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+        <v>446503.6480000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
       <c r="B31" s="2">
-        <v>7771172.7759999996</v>
+        <v>7811293.6979999999</v>
       </c>
       <c r="C31" s="2">
-        <v>65642.126000000004</v>
+        <v>65729.459000000003</v>
       </c>
       <c r="D31" s="2">
-        <v>749083.44900000002</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+        <v>447369.19099999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
       <c r="B32" s="2">
-        <v>7851414.6210000003</v>
+        <v>7887001.2920000004</v>
       </c>
       <c r="C32" s="2">
-        <v>65816.792000000001</v>
+        <v>65905.277000000002</v>
       </c>
       <c r="D32" s="2">
-        <v>749924.80500000005</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+        <v>447777.53599999996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
       <c r="B33" s="2">
-        <v>7922587.9630000005</v>
+        <v>7954448.3909999998</v>
       </c>
       <c r="C33" s="2">
-        <v>65993.763000000006</v>
+        <v>66083.547999999995</v>
       </c>
       <c r="D33" s="2">
-        <v>749123.28399999999</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+        <v>447705.902</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
       <c r="B34" s="2">
-        <v>7986308.8200000003</v>
+        <v>8021407.1919999998</v>
       </c>
       <c r="C34" s="2">
-        <v>66173.331999999995</v>
+        <v>66277.409</v>
       </c>
       <c r="D34" s="2">
-        <v>748103.72499999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+        <v>449113.45499999996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
       <c r="B35" s="2">
-        <v>8056505.5640000002</v>
+        <v>8091734.9299999997</v>
       </c>
       <c r="C35" s="2">
-        <v>66381.485000000001</v>
+        <v>66438.822</v>
       </c>
       <c r="D35" s="2">
-        <v>745825.46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+        <v>450657.52199999994</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
       <c r="B36" s="2">
-        <v>8126964.2960000001</v>
+        <v>8161972.5719999997</v>
       </c>
       <c r="C36" s="2">
-        <v>66496.159</v>
+        <v>66548.53</v>
       </c>
       <c r="D36" s="2">
-        <v>745380.28899999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+        <v>450259.53600000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" s="1">
         <v>2025</v>
       </c>
       <c r="B37" s="2">
-        <v>8196980.8490000004</v>
+        <v>8231613.0700000003</v>
       </c>
       <c r="C37" s="2">
-        <v>66600.902000000002</v>
+        <v>66650.804000000004</v>
       </c>
       <c r="D37" s="2">
-        <v>744787.35800000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+        <v>448992.58499999996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" s="1">
         <v>2026</v>
       </c>
       <c r="B38" s="2">
-        <v>8266245.2910000002</v>
+        <v>8300678.3949999996</v>
       </c>
       <c r="C38" s="2">
-        <v>66700.706999999995</v>
+        <v>66746.400999999998</v>
       </c>
       <c r="D38" s="2">
-        <v>744010.30599999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+        <v>447890.473</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39" s="1">
         <v>2027</v>
       </c>
       <c r="B39" s="2">
-        <v>8335111.5</v>
+        <v>8369094.3439999996</v>
       </c>
       <c r="C39" s="2">
-        <v>66792.093999999997</v>
+        <v>66838.260999999999</v>
       </c>
       <c r="D39" s="2">
-        <v>742954.41700000002</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+        <v>447205.74899999995</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40" s="1">
         <v>2028</v>
       </c>
       <c r="B40" s="2">
-        <v>8403077.1889999993</v>
+        <v>8436618.8859999999</v>
       </c>
       <c r="C40" s="2">
-        <v>66884.429000000004</v>
+        <v>66928.635999999999</v>
       </c>
       <c r="D40" s="2">
-        <v>741789.71200000006</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+        <v>446459.31699999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41" s="1">
         <v>2029</v>
       </c>
       <c r="B41" s="2">
-        <v>8470160.5840000007</v>
+        <v>8503285.3230000008</v>
       </c>
       <c r="C41" s="2">
-        <v>66972.842999999993</v>
+        <v>67018.328999999998</v>
       </c>
       <c r="D41" s="2">
-        <v>740527.35400000005</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+        <v>445651.23500000004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42" s="1">
         <v>2030</v>
       </c>
       <c r="B42" s="2">
-        <v>8536410.0620000008</v>
+        <v>8569124.9110000003</v>
       </c>
       <c r="C42" s="2">
-        <v>67063.815000000002</v>
+        <v>67107.691000000006</v>
       </c>
       <c r="D42" s="2">
-        <v>739157.09199999995</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+        <v>444782.38100000005</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43" s="1">
         <v>2031</v>
       </c>
       <c r="B43" s="2">
-        <v>8601839.7599999998</v>
+        <v>8634119.3330000006</v>
       </c>
       <c r="C43" s="2">
-        <v>67151.566999999995</v>
+        <v>67194.854999999996</v>
       </c>
       <c r="D43" s="2">
-        <v>737709.81599999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+        <v>443853.3349999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44" s="1">
         <v>2032</v>
       </c>
       <c r="B44" s="2">
-        <v>8666398.9069999997</v>
+        <v>8698229.8120000008</v>
       </c>
       <c r="C44" s="2">
-        <v>67238.142999999996</v>
+        <v>67281.98</v>
       </c>
       <c r="D44" s="2">
-        <v>736143.12100000004</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+        <v>442896.55800000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A45" s="1">
         <v>2033</v>
       </c>
       <c r="B45" s="2">
-        <v>8730060.7170000002</v>
+        <v>8761449.0810000002</v>
       </c>
       <c r="C45" s="2">
-        <v>67325.816000000006</v>
+        <v>67369.322</v>
       </c>
       <c r="D45" s="2">
-        <v>734589.397</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+        <v>441929.64600000007</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A46" s="1">
         <v>2034</v>
       </c>
       <c r="B46" s="2">
-        <v>8792837.4450000003</v>
+        <v>8823784.909</v>
       </c>
       <c r="C46" s="2">
-        <v>67412.827000000005</v>
+        <v>67458.149000000005</v>
       </c>
       <c r="D46" s="2">
-        <v>733012.58799999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+        <v>440942.37400000007</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A47" s="1">
         <v>2035</v>
       </c>
       <c r="B47" s="2">
-        <v>8854732.3719999995</v>
+        <v>8885210.1809999999</v>
       </c>
       <c r="C47" s="2">
-        <v>67503.471999999994</v>
+        <v>67547.945999999996</v>
       </c>
       <c r="D47" s="2">
-        <v>731408.71900000004</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+        <v>439928.23599999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A48" s="1">
         <v>2036</v>
       </c>
       <c r="B48" s="2">
-        <v>8915687.9900000002</v>
+        <v>8945686.6140000001</v>
       </c>
       <c r="C48" s="2">
-        <v>67592.418999999994</v>
+        <v>67635.315000000002</v>
       </c>
       <c r="D48" s="2">
-        <v>729772.30099999998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+        <v>438876.35599999991</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A49" s="1">
         <v>2037</v>
       </c>
       <c r="B49" s="2">
-        <v>8975685.2390000001</v>
+        <v>9005152.6239999998</v>
       </c>
       <c r="C49" s="2">
-        <v>67678.212</v>
+        <v>67721.11</v>
       </c>
       <c r="D49" s="2">
-        <v>728095.92099999997</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+        <v>437800.28700000013</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A50" s="1">
         <v>2038</v>
       </c>
       <c r="B50" s="2">
-        <v>9034620.0089999996</v>
+        <v>9063572.9260000009</v>
       </c>
       <c r="C50" s="2">
-        <v>67764.008000000002</v>
+        <v>67801.926999999996</v>
       </c>
       <c r="D50" s="2">
-        <v>726400.87600000005</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+        <v>436704.79599999997</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A51" s="1">
         <v>2039</v>
       </c>
       <c r="B51" s="2">
-        <v>9092525.8430000003</v>
+        <v>9120928.3800000008</v>
       </c>
       <c r="C51" s="2">
-        <v>67839.845000000001</v>
+        <v>67873.403000000006</v>
       </c>
       <c r="D51" s="2">
-        <v>724703.647</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+        <v>435575.79399999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A52" s="1">
         <v>2040</v>
       </c>
       <c r="B52" s="2">
-        <v>9149330.9169999994</v>
+        <v>9177190.2029999997</v>
       </c>
       <c r="C52" s="2">
-        <v>67906.960999999996</v>
+        <v>67938.903999999995</v>
       </c>
       <c r="D52" s="2">
-        <v>722958.26199999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+        <v>434422.40100000007</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A53" s="1">
         <v>2041</v>
       </c>
       <c r="B53" s="2">
-        <v>9205049.4879999999</v>
+        <v>9232281.5749999993</v>
       </c>
       <c r="C53" s="2">
-        <v>67970.846999999994</v>
+        <v>68002.574999999997</v>
       </c>
       <c r="D53" s="2">
-        <v>721244.98499999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+        <v>433267.647</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A54" s="1">
         <v>2042</v>
       </c>
       <c r="B54" s="2">
-        <v>9259513.6620000005</v>
+        <v>9286110.3709999993</v>
       </c>
       <c r="C54" s="2">
-        <v>68034.303</v>
+        <v>68063.86</v>
       </c>
       <c r="D54" s="2">
-        <v>719536.97499999998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+        <v>432096.70899999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A55" s="1">
         <v>2043</v>
       </c>
       <c r="B55" s="2">
-        <v>9312707.0789999999</v>
+        <v>9338661.3139999993</v>
       </c>
       <c r="C55" s="2">
-        <v>68093.417000000001</v>
+        <v>68115.785999999993</v>
       </c>
       <c r="D55" s="2">
-        <v>717819.94799999997</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+        <v>430874.26299999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A56" s="1">
         <v>2044</v>
       </c>
       <c r="B56" s="2">
-        <v>9364615.5490000006</v>
+        <v>9389873.693</v>
       </c>
       <c r="C56" s="2">
-        <v>68138.154999999999</v>
+        <v>68157.082999999999</v>
       </c>
       <c r="D56" s="2">
-        <v>716032.201</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+        <v>429598.62099999987</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A57" s="1">
         <v>2045</v>
       </c>
       <c r="B57" s="2">
-        <v>9415131.8379999995</v>
+        <v>9439639.6679999996</v>
       </c>
       <c r="C57" s="2">
-        <v>68176.009999999995</v>
+        <v>68190.955000000002</v>
       </c>
       <c r="D57" s="2">
-        <v>714211.69299999997</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+        <v>428280.46499999997</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A58" s="1">
         <v>2046</v>
       </c>
       <c r="B58" s="2">
-        <v>9464147.4979999997</v>
+        <v>9487889.6040000003</v>
       </c>
       <c r="C58" s="2">
-        <v>68205.899000000005</v>
+        <v>68214.672999999995</v>
       </c>
       <c r="D58" s="2">
-        <v>712348.01199999999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+        <v>426921.04200000002</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A59" s="1">
         <v>2047</v>
       </c>
       <c r="B59" s="2">
-        <v>9511631.7100000009</v>
+        <v>9534545.977</v>
       </c>
       <c r="C59" s="2">
-        <v>68223.445999999996</v>
+        <v>68229.077000000005</v>
       </c>
       <c r="D59" s="2">
-        <v>710440.74300000002</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+        <v>425511.16099999996</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A60" s="1">
         <v>2048</v>
       </c>
       <c r="B60" s="2">
-        <v>9557460.2449999992</v>
+        <v>9579536.0429999996</v>
       </c>
       <c r="C60" s="2">
-        <v>68234.707999999999</v>
+        <v>68235.289000000004</v>
       </c>
       <c r="D60" s="2">
-        <v>708437.35199999996</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+        <v>424046.07800000015</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A61" s="1">
         <v>2049</v>
       </c>
       <c r="B61" s="2">
-        <v>9601611.841</v>
+        <v>9622824.0289999992</v>
       </c>
       <c r="C61" s="2">
-        <v>68235.870999999999</v>
+        <v>68231.375</v>
       </c>
       <c r="D61" s="2">
-        <v>706353.86800000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+        <v>422524.55599999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A62" s="1">
         <v>2050</v>
       </c>
       <c r="B62" s="2">
-        <v>9644036.216</v>
+        <v>9664378.5869999994</v>
       </c>
       <c r="C62" s="2">
-        <v>68226.879000000001</v>
+        <v>68219.675000000003</v>
       </c>
       <c r="D62" s="2">
-        <v>704160.17799999996</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+        <v>420955.34100000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A63" s="1">
         <v>2051</v>
       </c>
       <c r="B63" s="2">
-        <v>9684720.9580000006</v>
+        <v>9704192.3039999995</v>
       </c>
       <c r="C63" s="2">
-        <v>68212.471000000005</v>
+        <v>68200.254000000001</v>
       </c>
       <c r="D63" s="2">
-        <v>701895.34</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+        <v>419346.89500000008</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A64" s="1">
         <v>2052</v>
       </c>
       <c r="B64" s="2">
-        <v>9723663.6490000002</v>
+        <v>9742264.5150000006</v>
       </c>
       <c r="C64" s="2">
-        <v>68188.038</v>
+        <v>68175.77</v>
       </c>
       <c r="D64" s="2">
-        <v>699538.17700000003</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+        <v>417691.14999999997</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A65" s="1">
         <v>2053</v>
       </c>
       <c r="B65" s="2">
-        <v>9760865.3809999991</v>
+        <v>9778614.6140000001</v>
       </c>
       <c r="C65" s="2">
-        <v>68163.502999999997</v>
+        <v>68146.932000000001</v>
       </c>
       <c r="D65" s="2">
-        <v>697115.44700000004</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+        <v>415966.71600000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A66" s="1">
         <v>2054</v>
       </c>
       <c r="B66" s="2">
-        <v>9796363.8469999991</v>
+        <v>9813251.659</v>
       </c>
       <c r="C66" s="2">
-        <v>68130.36</v>
+        <v>68111.014999999999</v>
       </c>
       <c r="D66" s="2">
-        <v>694513.78700000001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+        <v>414174.85799999995</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A67" s="1">
         <v>2055</v>
       </c>
       <c r="B67" s="2">
-        <v>9830139.4710000008</v>
+        <v>9846237.5700000003</v>
       </c>
       <c r="C67" s="2">
-        <v>68091.668999999994</v>
+        <v>68067.630999999994</v>
       </c>
       <c r="D67" s="2">
-        <v>691851.88199999998</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+        <v>412334.533</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A68" s="1">
         <v>2056</v>
       </c>
       <c r="B68" s="2">
-        <v>9862335.6699999999</v>
+        <v>9877680.3920000009</v>
       </c>
       <c r="C68" s="2">
-        <v>68043.592999999993</v>
+        <v>68022.156000000003</v>
       </c>
       <c r="D68" s="2">
-        <v>689074.61100000003</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+        <v>410448.42000000004</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A69" s="1">
         <v>2057</v>
       </c>
       <c r="B69" s="2">
-        <v>9893025.1140000001</v>
+        <v>9907637.193</v>
       </c>
       <c r="C69" s="2">
-        <v>68000.72</v>
+        <v>67978.668999999994</v>
       </c>
       <c r="D69" s="2">
-        <v>686255.70799999998</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+        <v>408533.27399999992</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A70" s="1">
         <v>2058</v>
       </c>
       <c r="B70" s="2">
-        <v>9922249.2719999999</v>
+        <v>9936164.3790000007</v>
       </c>
       <c r="C70" s="2">
-        <v>67956.618000000002</v>
+        <v>67935.849000000002</v>
       </c>
       <c r="D70" s="2">
-        <v>683407.30299999996</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+        <v>406603.29399999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A71" s="1">
         <v>2059</v>
       </c>
       <c r="B71" s="2">
-        <v>9950079.4859999996</v>
+        <v>9963337.0820000004</v>
       </c>
       <c r="C71" s="2">
-        <v>67915.081000000006</v>
+        <v>67892.952000000005</v>
       </c>
       <c r="D71" s="2">
-        <v>680520.071</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+        <v>404661.71100000007</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A72" s="1">
         <v>2060</v>
       </c>
       <c r="B72" s="2">
-        <v>9976594.6789999995</v>
+        <v>9989232.2919999994</v>
       </c>
       <c r="C72" s="2">
-        <v>67870.823000000004</v>
+        <v>67850.294999999998</v>
       </c>
       <c r="D72" s="2">
-        <v>677603.74899999995</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+        <v>402712.63299999991</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A73" s="1">
         <v>2061</v>
       </c>
       <c r="B73" s="2">
-        <v>10001869.904999999</v>
+        <v>10013916.213</v>
       </c>
       <c r="C73" s="2">
-        <v>67829.766000000003</v>
+        <v>67810.557000000001</v>
       </c>
       <c r="D73" s="2">
-        <v>674715.93099999998</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+        <v>400766.93200000015</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A74" s="1">
         <v>2062</v>
       </c>
       <c r="B74" s="2">
-        <v>10025962.521</v>
+        <v>10037466.6</v>
       </c>
       <c r="C74" s="2">
-        <v>67791.349000000002</v>
+        <v>67772.615999999995</v>
       </c>
       <c r="D74" s="2">
-        <v>671815.46400000004</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+        <v>398823.46799999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A75" s="1">
         <v>2063</v>
       </c>
       <c r="B75" s="2">
-        <v>10048970.677999999</v>
+        <v>10059950.035</v>
       </c>
       <c r="C75" s="2">
-        <v>67753.883000000002</v>
+        <v>67739.664000000004</v>
       </c>
       <c r="D75" s="2">
-        <v>668937.91299999994</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+        <v>396899.60199999996</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A76" s="1">
         <v>2064</v>
       </c>
       <c r="B76" s="2">
-        <v>10070929.392000001</v>
+        <v>10081402.737</v>
       </c>
       <c r="C76" s="2">
-        <v>67725.445000000007</v>
+        <v>67713.646999999997</v>
       </c>
       <c r="D76" s="2">
-        <v>666081.65899999999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+        <v>395004.61700000003</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A77" s="1">
         <v>2065</v>
       </c>
       <c r="B77" s="2">
-        <v>10091876.081</v>
+        <v>10101849.561000001</v>
       </c>
       <c r="C77" s="2">
-        <v>67701.849000000002</v>
+        <v>67691.804000000004</v>
       </c>
       <c r="D77" s="2">
-        <v>663254.68299999996</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+        <v>393131.79000000004</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A78" s="1">
         <v>2066</v>
       </c>
       <c r="B78" s="2">
-        <v>10111823.040999999</v>
+        <v>10121317.107000001</v>
       </c>
       <c r="C78" s="2">
-        <v>67681.759999999995</v>
+        <v>67677.298999999999</v>
       </c>
       <c r="D78" s="2">
-        <v>660460.06999999995</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+        <v>391291.73300000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A79" s="1">
         <v>2067</v>
       </c>
       <c r="B79" s="2">
-        <v>10130811.174000001</v>
+        <v>10139808.361</v>
       </c>
       <c r="C79" s="2">
-        <v>67672.839000000007</v>
+        <v>67669.051999999996</v>
       </c>
       <c r="D79" s="2">
-        <v>657736.19900000002</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+        <v>389489.04200000002</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A80" s="1">
         <v>2068</v>
       </c>
       <c r="B80" s="2">
-        <v>10148805.547</v>
+        <v>10157301.941</v>
       </c>
       <c r="C80" s="2">
-        <v>67665.263999999996</v>
+        <v>67664.28</v>
       </c>
       <c r="D80" s="2">
-        <v>655082.67299999995</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+        <v>387721.924</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A81" s="1">
         <v>2069</v>
       </c>
       <c r="B81" s="2">
-        <v>10165798.334000001</v>
+        <v>10173782.135</v>
       </c>
       <c r="C81" s="2">
-        <v>67663.296000000002</v>
+        <v>67668.108999999997</v>
       </c>
       <c r="D81" s="2">
-        <v>652466.40500000003</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+        <v>385994.04200000007</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A82" s="1">
         <v>2070</v>
       </c>
       <c r="B82" s="2">
-        <v>10181765.935000001</v>
+        <v>10189241.959000001</v>
       </c>
       <c r="C82" s="2">
-        <v>67672.922000000006</v>
+        <v>67678.904999999999</v>
       </c>
       <c r="D82" s="2">
-        <v>649895.46600000001</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+        <v>384310.26799999998</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A83" s="1">
         <v>2071</v>
       </c>
       <c r="B83" s="2">
-        <v>10196717.982999999</v>
+        <v>10203681.568</v>
       </c>
       <c r="C83" s="2">
-        <v>67684.888000000006</v>
+        <v>67698.398000000001</v>
       </c>
       <c r="D83" s="2">
-        <v>647385.17299999995</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+        <v>382670.826</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A84" s="1">
         <v>2072</v>
       </c>
       <c r="B84" s="2">
-        <v>10210645.153999999</v>
+        <v>10217055.169</v>
       </c>
       <c r="C84" s="2">
-        <v>67711.907000000007</v>
+        <v>67724.513999999996</v>
       </c>
       <c r="D84" s="2">
-        <v>644924.50300000003</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+        <v>381068.141</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A85" s="1">
         <v>2073</v>
       </c>
       <c r="B85" s="2">
-        <v>10223465.184</v>
+        <v>10229327.823999999</v>
       </c>
       <c r="C85" s="2">
-        <v>67737.119999999995</v>
+        <v>67752.34</v>
       </c>
       <c r="D85" s="2">
-        <v>642548.04799999995</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+        <v>379495.90099999995</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A86" s="1">
         <v>2074</v>
       </c>
       <c r="B86" s="2">
-        <v>10235190.464</v>
+        <v>10240485.056</v>
       </c>
       <c r="C86" s="2">
-        <v>67767.558999999994</v>
+        <v>67784.584000000003</v>
       </c>
       <c r="D86" s="2">
-        <v>640200.39800000004</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+        <v>377958.35600000003</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A87" s="1">
         <v>2075</v>
       </c>
       <c r="B87" s="2">
-        <v>10245779.647</v>
+        <v>10250496.432</v>
       </c>
       <c r="C87" s="2">
-        <v>67801.61</v>
+        <v>67822.260999999999</v>
       </c>
       <c r="D87" s="2">
-        <v>637905.63800000004</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+        <v>376480.08500000008</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A88" s="1">
         <v>2076</v>
       </c>
       <c r="B88" s="2">
-        <v>10255213.216</v>
+        <v>10259351.432</v>
       </c>
       <c r="C88" s="2">
-        <v>67842.911999999997</v>
+        <v>67863.936000000002</v>
       </c>
       <c r="D88" s="2">
-        <v>635718.05700000003</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+        <v>375047.78200000006</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A89" s="1">
         <v>2077</v>
       </c>
       <c r="B89" s="2">
-        <v>10263489.648</v>
+        <v>10267045.023</v>
       </c>
       <c r="C89" s="2">
-        <v>67884.960000000006</v>
+        <v>67905.317999999999</v>
       </c>
       <c r="D89" s="2">
-        <v>633586.69099999999</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+        <v>373634.73</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A90" s="1">
         <v>2078</v>
       </c>
       <c r="B90" s="2">
-        <v>10270600.397</v>
+        <v>10273556.322000001</v>
       </c>
       <c r="C90" s="2">
-        <v>67925.676000000007</v>
+        <v>67945.203999999998</v>
       </c>
       <c r="D90" s="2">
-        <v>631465.69099999999</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+        <v>372260.67599999998</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A91" s="1">
         <v>2079</v>
       </c>
       <c r="B91" s="2">
-        <v>10276512.248</v>
+        <v>10278887.472999999</v>
       </c>
       <c r="C91" s="2">
-        <v>67964.732000000004</v>
+        <v>67984.811000000002</v>
       </c>
       <c r="D91" s="2">
-        <v>629415.12899999996</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+        <v>370924.19000000006</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A92" s="1">
         <v>2080</v>
       </c>
       <c r="B92" s="2">
-        <v>10281262.698000001</v>
+        <v>10283078.028999999</v>
       </c>
       <c r="C92" s="2">
-        <v>68004.89</v>
+        <v>68024.937000000005</v>
       </c>
       <c r="D92" s="2">
-        <v>627404.68799999997</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+        <v>369621.90600000002</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A93" s="1">
         <v>2081</v>
       </c>
       <c r="B93" s="2">
-        <v>10284893.358999999</v>
+        <v>10286161.734999999</v>
       </c>
       <c r="C93" s="2">
-        <v>68044.983999999997</v>
+        <v>68066.815000000002</v>
       </c>
       <c r="D93" s="2">
-        <v>625461.88899999997</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+        <v>368361.90900000004</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A94" s="1">
         <v>2082</v>
       </c>
       <c r="B94" s="2">
-        <v>10287430.111</v>
+        <v>10288205.050000001</v>
       </c>
       <c r="C94" s="2">
-        <v>68088.646999999997</v>
+        <v>68108.438999999998</v>
       </c>
       <c r="D94" s="2">
-        <v>623586.20299999998</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+        <v>367136.15699999989</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A95" s="1">
         <v>2083</v>
       </c>
       <c r="B95" s="2">
-        <v>10288979.989</v>
+        <v>10289247.323000001</v>
       </c>
       <c r="C95" s="2">
-        <v>68128.232000000004</v>
+        <v>68153.316999999995</v>
       </c>
       <c r="D95" s="2">
-        <v>621727.15399999998</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+        <v>365939.98800000007</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A96" s="1">
         <v>2084</v>
       </c>
       <c r="B96" s="2">
-        <v>10289514.658</v>
+        <v>10289315.244000001</v>
       </c>
       <c r="C96" s="2">
-        <v>68178.400999999998</v>
+        <v>68198.942999999999</v>
       </c>
       <c r="D96" s="2">
-        <v>619907.59900000005</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+        <v>364768.47600000014</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A97" s="1">
         <v>2085</v>
       </c>
       <c r="B97" s="2">
-        <v>10289115.83</v>
+        <v>10288456.598999999</v>
       </c>
       <c r="C97" s="2">
-        <v>68219.483999999997</v>
+        <v>68237.653999999995</v>
       </c>
       <c r="D97" s="2">
-        <v>618109.28700000001</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+        <v>363612.08199999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A98" s="1">
         <v>2086</v>
       </c>
       <c r="B98" s="2">
-        <v>10287797.368000001</v>
+        <v>10286708.359999999</v>
       </c>
       <c r="C98" s="2">
-        <v>68255.823000000004</v>
+        <v>68276.452000000005</v>
       </c>
       <c r="D98" s="2">
-        <v>616324.20200000005</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+        <v>362474.72799999989</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A99" s="1">
         <v>2087</v>
       </c>
       <c r="B99" s="2">
-        <v>10285619.351</v>
+        <v>10284111.374</v>
       </c>
       <c r="C99" s="2">
-        <v>68297.081999999995</v>
+        <v>68316.292000000001</v>
       </c>
       <c r="D99" s="2">
-        <v>614569.38399999996</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+        <v>361363.54499999998</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A100" s="1">
         <v>2088</v>
       </c>
       <c r="B100" s="2">
-        <v>10282603.396</v>
+        <v>10280704.572000001</v>
       </c>
       <c r="C100" s="2">
-        <v>68335.501000000004</v>
+        <v>68354.444000000003</v>
       </c>
       <c r="D100" s="2">
-        <v>612868.772</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+        <v>360281.40500000003</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A101" s="1">
         <v>2089</v>
       </c>
       <c r="B101" s="2">
-        <v>10278805.749</v>
+        <v>10276518.279999999</v>
       </c>
       <c r="C101" s="2">
-        <v>68373.388000000006</v>
+        <v>68389.692999999999</v>
       </c>
       <c r="D101" s="2">
-        <v>611200.07799999998</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+        <v>359214.11100000003</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A102" s="1">
         <v>2090</v>
       </c>
       <c r="B102" s="2">
-        <v>10274230.810000001</v>
+        <v>10271565.07</v>
       </c>
       <c r="C102" s="2">
-        <v>68405.998999999996</v>
+        <v>68421.883000000002</v>
       </c>
       <c r="D102" s="2">
-        <v>609526.97699999996</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+        <v>358149.47100000002</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A103" s="1">
         <v>2091</v>
       </c>
       <c r="B103" s="2">
-        <v>10268899.331</v>
+        <v>10265861.714</v>
       </c>
       <c r="C103" s="2">
-        <v>68437.766000000003</v>
+        <v>68451.044999999998</v>
       </c>
       <c r="D103" s="2">
-        <v>607859.16</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+        <v>357104.93199999997</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A104" s="1">
         <v>2092</v>
       </c>
       <c r="B104" s="2">
-        <v>10262824.096000001</v>
+        <v>10259408.375</v>
       </c>
       <c r="C104" s="2">
-        <v>68464.323999999993</v>
+        <v>68475.278000000006</v>
       </c>
       <c r="D104" s="2">
-        <v>606237.61699999997</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+        <v>356085.554</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A105" s="1">
         <v>2093</v>
       </c>
       <c r="B105" s="2">
-        <v>10255992.654999999</v>
+        <v>10252184.759</v>
       </c>
       <c r="C105" s="2">
-        <v>68486.232000000004</v>
+        <v>68498.701000000001</v>
       </c>
       <c r="D105" s="2">
-        <v>604606.87600000005</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+        <v>355083.0670000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A106" s="1">
         <v>2094</v>
       </c>
       <c r="B106" s="2">
-        <v>10248376.862</v>
+        <v>10244185.836999999</v>
       </c>
       <c r="C106" s="2">
-        <v>68511.168999999994</v>
+        <v>68518.865000000005</v>
       </c>
       <c r="D106" s="2">
-        <v>603012.85499999998</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+        <v>354087.00400000002</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A107" s="1">
         <v>2095</v>
       </c>
       <c r="B107" s="2">
-        <v>10239994.812000001</v>
+        <v>10235403.601</v>
       </c>
       <c r="C107" s="2">
-        <v>68526.562000000005</v>
+        <v>68529.646999999997</v>
       </c>
       <c r="D107" s="2">
-        <v>601427.07799999998</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+        <v>353078.46800000005</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A108" s="1">
         <v>2096</v>
       </c>
       <c r="B108" s="2">
-        <v>10230812.389</v>
+        <v>10225850.874</v>
       </c>
       <c r="C108" s="2">
-        <v>68532.732000000004</v>
+        <v>68529.527000000002</v>
       </c>
       <c r="D108" s="2">
-        <v>599799.50300000003</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+        <v>352052.02500000008</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A109" s="1">
         <v>2097</v>
       </c>
       <c r="B109" s="2">
-        <v>10220889.357999999</v>
+        <v>10215549.310000001</v>
       </c>
       <c r="C109" s="2">
-        <v>68526.320999999996</v>
+        <v>68523.856</v>
       </c>
       <c r="D109" s="2">
-        <v>598134.46</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+        <v>351009.62299999996</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A110" s="1">
         <v>2098</v>
       </c>
       <c r="B110" s="2">
-        <v>10210209.263</v>
+        <v>10204489.862</v>
       </c>
       <c r="C110" s="2">
-        <v>68521.392000000007</v>
+        <v>68516.588000000003</v>
       </c>
       <c r="D110" s="2">
-        <v>596471.93000000005</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+        <v>349970.60700000002</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A111" s="1">
         <v>2099</v>
       </c>
       <c r="B111" s="2">
-        <v>10198770.460999999</v>
+        <v>10192689.066</v>
       </c>
       <c r="C111" s="2">
-        <v>68511.785000000003</v>
+        <v>68503.747000000003</v>
       </c>
       <c r="D111" s="2">
-        <v>594809.66299999994</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+        <v>348929.72599999985</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A112" s="1">
         <v>2100</v>
       </c>
       <c r="B112" s="2">
-        <v>10186607.67</v>
+        <v>10180160.751</v>
       </c>
       <c r="C112" s="2">
-        <v>68495.709000000003</v>
+        <v>68484.558000000005</v>
       </c>
       <c r="D112" s="2">
-        <v>593112.88</v>
-      </c>
-      <c r="E112">
-        <f>37*1000000/(C115*1000)</f>
-        <v>0.55133009054881488</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
+        <v>347864.81900000002</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>170</v>
+      </c>
+      <c r="B113" s="2">
+        <v>100</v>
+      </c>
+      <c r="C113" s="31">
+        <f>C23*100/B23</f>
+        <v>0.89627985204535521</v>
+      </c>
+      <c r="D113" s="31">
+        <f>D23*100/B23</f>
+        <v>6.2079223823601231</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B114">
         <f>B27*100/B27</f>
@@ -4039,61 +4906,61 @@
       </c>
       <c r="C114">
         <f>C27*100/B27</f>
-        <v>0.87297849148694984</v>
+        <v>0.86897003721149357</v>
       </c>
       <c r="D114">
         <f>D27*100/B27</f>
-        <v>10.008512952112008</v>
+        <v>5.9421911649996391</v>
       </c>
       <c r="F114" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G114">
         <f>B31*100/B31</f>
-        <v>99.999999999999986</v>
+        <v>100</v>
       </c>
       <c r="H114">
         <f>C31*100/B31</f>
-        <v>0.84468751232407302</v>
+        <v>0.8414670033061149</v>
       </c>
       <c r="I114">
         <f>D31*100/B31</f>
-        <v>9.639258714121274</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+        <v>5.7272099641387726</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A115" s="11" t="s">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="B115" s="9">
-        <f>AVERAGE(B27:B63)</f>
-        <v>8675392.0121351369</v>
+        <f>AVERAGE(B27:B62)</f>
+        <v>8678719.5850277767</v>
       </c>
       <c r="C115" s="9">
-        <f>AVERAGE(C27:C63)</f>
-        <v>67110.431000000011</v>
+        <f>AVERAGE(C27:C62)</f>
+        <v>67126.776000000013</v>
       </c>
       <c r="D115" s="9">
-        <f>AVERAGE(D27:D63)</f>
-        <v>731385.82940540521</v>
+        <f>AVERAGE(D27:D62)</f>
+        <v>439497.03716666671</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G115" s="4">
         <f>AVERAGE(B31:B63)</f>
-        <v>8810826.8120606076</v>
+        <v>8840410.0070303045</v>
       </c>
       <c r="H115" s="4">
         <f t="shared" ref="H115:I115" si="0">AVERAGE(C31:C63)</f>
-        <v>67354.052212121213</v>
+        <v>67392.626666666692</v>
       </c>
       <c r="I115" s="4">
         <f t="shared" si="0"/>
-        <v>729634.64224242419</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
+        <v>438188.4073636363</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A116" s="10" t="s">
         <v>21</v>
       </c>
@@ -4103,11 +4970,11 @@
       </c>
       <c r="C116" s="7">
         <f>C115*100/B115</f>
-        <v>0.77357231703335083</v>
+        <v>0.77346405010947439</v>
       </c>
       <c r="D116" s="7">
         <f>D115*100/B115</f>
-        <v>8.4305796024242223</v>
+        <v>5.0640769397005476</v>
       </c>
       <c r="F116" t="s">
         <v>21</v>
@@ -4118,46 +4985,46 @@
       </c>
       <c r="H116" s="6">
         <f>H115*100/G115</f>
-        <v>0.76444644354970559</v>
+        <v>0.76232467287233219</v>
       </c>
       <c r="I116" s="6">
         <f>I115*100/G115</f>
-        <v>8.2811143358722195</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+        <v>4.9566525423048082</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A117" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B117" s="4">
         <f>AVERAGE(B29:B112)</f>
-        <v>9563972.5480952356</v>
+        <v>9579276.7785238083</v>
       </c>
       <c r="C117" s="4">
         <f t="shared" ref="C117:D117" si="1">AVERAGE(C29:C112)</f>
-        <v>67719.521904761874</v>
+        <v>67739.169619047636</v>
       </c>
       <c r="D117" s="4">
         <f t="shared" si="1"/>
-        <v>677886.14760714292</v>
+        <v>403389.38254761917</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G117" s="4">
         <f>AVERAGE(B31:B112)</f>
-        <v>9610761.6845365837</v>
+        <v>9625411.3251341451</v>
       </c>
       <c r="H117" s="4">
         <f t="shared" ref="H117:I117" si="2">AVERAGE(C31:C112)</f>
-        <v>67778.905951219494</v>
+        <v>67796.169865853692</v>
       </c>
       <c r="I117" s="4">
         <f t="shared" si="2"/>
-        <v>676189.9753048782</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
+        <v>402347.65536585363</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
         <v>21</v>
       </c>
@@ -4167,11 +5034,11 @@
       </c>
       <c r="C118" s="6">
         <f>C117*100/B117</f>
-        <v>0.70806896992033841</v>
+        <v>0.70714283745214446</v>
       </c>
       <c r="D118" s="6">
         <f>D117*100/B117</f>
-        <v>7.087913983422621</v>
+        <v>4.2110630256763759</v>
       </c>
       <c r="F118" t="s">
         <v>21</v>
@@ -4182,31 +5049,36 @@
       </c>
       <c r="H118" s="6">
         <f>H117*100/G117</f>
-        <v>0.70523969042197399</v>
+        <v>0.70434569054542562</v>
       </c>
       <c r="I118" s="6">
         <f>I117*100/G117</f>
-        <v>7.0357584289374984</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
+        <v>4.1800567453697495</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A119" s="3"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A120" s="3"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>19</v>
       </c>
       <c r="B121" s="21" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B122" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -4217,38 +5089,38 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8683F5-D89E-4384-A263-C6122D6DA873}">
-  <dimension ref="A1:AJ45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AK48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.69140625" customWidth="1"/>
+    <col min="9" max="9" width="10.69140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>18</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
         <v>63</v>
       </c>
-      <c r="D1" t="s">
-        <v>67</v>
-      </c>
       <c r="F1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
       <c r="L1" s="13"/>
@@ -4276,10 +5148,11 @@
       <c r="AH1" s="13"/>
       <c r="AI1" s="13"/>
       <c r="AJ1" s="13"/>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.45">
+      <c r="AK1" s="13"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B2" s="13">
         <v>11257.436263054224</v>
@@ -4292,17 +5165,16 @@
       </c>
       <c r="F2">
         <f>B2*Population!B2</f>
-        <v>59450177778.532051</v>
+        <v>59977403932.927078</v>
       </c>
       <c r="G2">
         <f>C2*Population!C2</f>
-        <v>2197479792.4133053</v>
+        <v>2203008125.248558</v>
       </c>
       <c r="H2">
         <f>D2*Population!D2</f>
-        <v>24157333333.131027</v>
-      </c>
-      <c r="I2" s="13"/>
+        <v>14036543351.636398</v>
+      </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
@@ -4330,10 +5202,11 @@
       <c r="AH2" s="13"/>
       <c r="AI2" s="13"/>
       <c r="AJ2" s="13"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
+      <c r="AK2" s="13"/>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B3" s="13">
         <v>11166.5096464532</v>
@@ -4346,17 +5219,16 @@
       </c>
       <c r="F3">
         <f>B3*Population!B3</f>
-        <v>60015932556.731392</v>
+        <v>60508366598.43367</v>
       </c>
       <c r="G3">
         <f>C3*Population!C3</f>
-        <v>2224651877.2797241</v>
+        <v>2230037463.3315167</v>
       </c>
       <c r="H3">
         <f>D3*Population!D3</f>
-        <v>24361404436.744926</v>
-      </c>
-      <c r="I3" s="13"/>
+        <v>14151718141.613138</v>
+      </c>
       <c r="J3" s="13"/>
       <c r="K3" s="13"/>
       <c r="L3" s="13"/>
@@ -4384,10 +5256,11 @@
       <c r="AH3" s="13"/>
       <c r="AI3" s="13"/>
       <c r="AJ3" s="13"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
+      <c r="AK3" s="13"/>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B4" s="13">
         <v>11132.379518801288</v>
@@ -4401,17 +5274,16 @@
       <c r="E4" s="13"/>
       <c r="F4">
         <f>B4*Population!B4</f>
-        <v>60814353392.578331</v>
+        <v>61294768258.366867</v>
       </c>
       <c r="G4">
         <f>C4*Population!C4</f>
-        <v>2258039781.8426242</v>
+        <v>2263742632.6271453</v>
       </c>
       <c r="H4">
         <f>D4*Population!D4</f>
-        <v>24502622732.112122</v>
-      </c>
-      <c r="I4" s="13"/>
+        <v>14241957376.039623</v>
+      </c>
       <c r="J4" s="13"/>
       <c r="K4" s="13"/>
       <c r="L4" s="13"/>
@@ -4439,10 +5311,11 @@
       <c r="AH4" s="13"/>
       <c r="AI4" s="13"/>
       <c r="AJ4" s="13"/>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
+      <c r="AK4" s="13"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B5" s="13">
         <v>11125.655948461339</v>
@@ -4455,17 +5328,16 @@
       </c>
       <c r="F5">
         <f>B5*Population!B5</f>
-        <v>61737873060.453659</v>
+        <v>62209603631.8311</v>
       </c>
       <c r="G5">
         <f>C5*Population!C5</f>
-        <v>2251484091.1171813</v>
+        <v>2255440898.4546885</v>
       </c>
       <c r="H5">
         <f>D5*Population!D5</f>
-        <v>24289920209.391624</v>
-      </c>
-      <c r="J5" s="13"/>
+        <v>14155886615.047218</v>
+      </c>
       <c r="K5" s="13"/>
       <c r="L5" s="13"/>
       <c r="M5" s="13"/>
@@ -4492,10 +5364,11 @@
       <c r="AH5" s="13"/>
       <c r="AI5" s="13"/>
       <c r="AJ5" s="13"/>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
+      <c r="AK5" s="13"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B6" s="13">
         <v>11251.216001515992</v>
@@ -4508,20 +5381,20 @@
       </c>
       <c r="F6">
         <f>B6*Population!B6</f>
-        <v>63388732641.965729</v>
+        <v>63856853097.680168</v>
       </c>
       <c r="G6">
         <f>C6*Population!C6</f>
-        <v>2304606686.9015002</v>
+        <v>2308475222.6968288</v>
       </c>
       <c r="H6">
         <f>D6*Population!D6</f>
-        <v>24904675997.177227</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
+        <v>14539693914.48213</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B7" s="13">
         <v>11429.359024753261</v>
@@ -4534,20 +5407,20 @@
       </c>
       <c r="F7">
         <f>B7*Population!B7</f>
-        <v>65343445279.962585</v>
+        <v>65820295465.383568</v>
       </c>
       <c r="G7">
         <f>C7*Population!C7</f>
-        <v>2357039498.9511337</v>
+        <v>2360899396.9623327</v>
       </c>
       <c r="H7">
         <f>D7*Population!D7</f>
-        <v>25612762187.674767</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.45">
+        <v>14952064687.920418</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B8" s="13">
         <v>11679.153608780653</v>
@@ -4560,20 +5433,20 @@
       </c>
       <c r="F8">
         <f>B8*Population!B8</f>
-        <v>67746104239.311546</v>
+        <v>68230266308.44381</v>
       </c>
       <c r="G8">
         <f>C8*Population!C8</f>
-        <v>2389241293.9235272</v>
+        <v>2393065647.9387803</v>
       </c>
       <c r="H8">
         <f>D8*Population!D8</f>
-        <v>26087721958.213924</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.45">
+        <v>15245174854.3053</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B9" s="13">
         <v>11964.177719327863</v>
@@ -4586,20 +5459,20 @@
       </c>
       <c r="F9">
         <f>B9*Population!B9</f>
-        <v>70391370846.730881</v>
+        <v>70885214379.932388</v>
       </c>
       <c r="G9">
         <f>C9*Population!C9</f>
-        <v>2448709269.176506</v>
+        <v>2452675852.2727776</v>
       </c>
       <c r="H9">
         <f>D9*Population!D9</f>
-        <v>26723818654.148617</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.45">
+        <v>15630580395.880232</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B10" s="13">
         <v>12088.101662261559</v>
@@ -4612,20 +5485,20 @@
       </c>
       <c r="F10">
         <f>B10*Population!B10</f>
-        <v>72118396182.05835</v>
+        <v>72614032840.705048</v>
       </c>
       <c r="G10">
         <f>C10*Population!C10</f>
-        <v>2532060625.7380643</v>
+        <v>2537043136.9808993</v>
       </c>
       <c r="H10">
         <f>D10*Population!D10</f>
-        <v>27468476865.381031</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.45">
+        <v>16067461867.683767</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B11" s="13">
         <v>12351.548049120385</v>
@@ -4638,20 +5511,20 @@
       </c>
       <c r="F11">
         <f>B11*Population!B11</f>
-        <v>74703011337.704285</v>
+        <v>75208654367.557098</v>
       </c>
       <c r="G11">
         <f>C11*Population!C11</f>
-        <v>2614912785.9868221</v>
+        <v>2623346946.9810138</v>
       </c>
       <c r="H11">
         <f>D11*Population!D11</f>
-        <v>28176082288.3083</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.45">
+        <v>16512311423.171005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B12" s="13">
         <v>12769.83149176615</v>
@@ -4664,20 +5537,20 @@
       </c>
       <c r="F12">
         <f>B12*Population!B12</f>
-        <v>78278351474.249023</v>
+        <v>78811607237.838806</v>
       </c>
       <c r="G12">
         <f>C12*Population!C12</f>
-        <v>2722016731.4508624</v>
+        <v>2731639740.9894996</v>
       </c>
       <c r="H12">
         <f>D12*Population!D12</f>
-        <v>29240167861.778976</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.45">
+        <v>17173198592.745512</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13">
         <v>12904.861928294958</v>
@@ -4690,20 +5563,20 @@
       </c>
       <c r="F13">
         <f>B13*Population!B13</f>
-        <v>80183869503.519272</v>
+        <v>80719091373.653183</v>
       </c>
       <c r="G13">
         <f>C13*Population!C13</f>
-        <v>2773042906.8022509</v>
+        <v>2782884975.071826</v>
       </c>
       <c r="H13">
         <f>D13*Population!D13</f>
-        <v>29862791642.623837</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.45">
+        <v>17575027945.751125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B14" s="13">
         <v>13093.065120858157</v>
@@ -4716,20 +5589,20 @@
       </c>
       <c r="F14">
         <f>B14*Population!B14</f>
-        <v>82439317889.00885</v>
+        <v>82980316086.244644</v>
       </c>
       <c r="G14">
         <f>C14*Population!C14</f>
-        <v>2802099919.6978536</v>
+        <v>2811900209.5146894</v>
       </c>
       <c r="H14">
         <f>D14*Population!D14</f>
-        <v>30165942432.463612</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.45">
+        <v>17807088213.890675</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B15" s="13">
         <v>13402.991953645811</v>
@@ -4742,20 +5615,20 @@
       </c>
       <c r="F15">
         <f>B15*Population!B15</f>
-        <v>85498352980.470016</v>
+        <v>86052055319.99826</v>
       </c>
       <c r="G15">
         <f>C15*Population!C15</f>
-        <v>2828976728.2645211</v>
+        <v>2838492089.5582156</v>
       </c>
       <c r="H15">
         <f>D15*Population!D15</f>
-        <v>30462092599.50692</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.45">
+        <v>18004403454.357212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B16" s="13">
         <v>13914.811142290484</v>
@@ -4768,20 +5641,20 @@
       </c>
       <c r="F16">
         <f>B16*Population!B16</f>
-        <v>89912966123.432114</v>
+        <v>90493273484.349854</v>
       </c>
       <c r="G16">
         <f>C16*Population!C16</f>
-        <v>2908310128.4557562</v>
+        <v>2919309785.624382</v>
       </c>
       <c r="H16">
         <f>D16*Population!D16</f>
-        <v>31221908220.131401</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+        <v>18502743951.352955</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B17" s="13">
         <v>14370.885028756215</v>
@@ -4794,20 +5667,20 @@
       </c>
       <c r="F17">
         <f>B17*Population!B17</f>
-        <v>94058621859.889313</v>
+        <v>94660590454.823151</v>
       </c>
       <c r="G17">
         <f>C17*Population!C17</f>
-        <v>2963285740.6685023</v>
+        <v>2973867830.6441307</v>
       </c>
       <c r="H17">
         <f>D17*Population!D17</f>
-        <v>31813500020.819954</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+        <v>18893014123.791737</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B18" s="13">
         <v>14927.548526144859</v>
@@ -4820,20 +5693,20 @@
       </c>
       <c r="F18">
         <f>B18*Population!B18</f>
-        <v>98952602423.578171</v>
+        <v>99588423693.759399</v>
       </c>
       <c r="G18">
         <f>C18*Population!C18</f>
-        <v>3044178054.197875</v>
+        <v>3054294514.408299</v>
       </c>
       <c r="H18">
         <f>D18*Population!D18</f>
-        <v>32916700218.346203</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+        <v>19582440522.206104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="13" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B19" s="13">
         <v>15510.865766860974</v>
@@ -4846,20 +5719,20 @@
       </c>
       <c r="F19">
         <f>B19*Population!B19</f>
-        <v>104140663668.21527</v>
+        <v>104811709447.32196</v>
       </c>
       <c r="G19">
         <f>C19*Population!C19</f>
-        <v>3122590833.8613753</v>
+        <v>3131472774.2074294</v>
       </c>
       <c r="H19">
         <f>D19*Population!D19</f>
-        <v>33919859610.622345</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+        <v>20221659294.512562</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B20" s="13">
         <v>15747.72951097517</v>
@@ -4872,20 +5745,20 @@
       </c>
       <c r="F20">
         <f>B20*Population!B20</f>
-        <v>107093564124.02448</v>
+        <v>107784667910.49751</v>
       </c>
       <c r="G20">
         <f>C20*Population!C20</f>
-        <v>3134751986.9433608</v>
+        <v>3143297193.2459941</v>
       </c>
       <c r="H20">
         <f>D20*Population!D20</f>
-        <v>34182103766.776295</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+        <v>20401425207.663731</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B21" s="13">
         <v>15452.501218625677</v>
@@ -4898,20 +5771,20 @@
       </c>
       <c r="F21">
         <f>B21*Population!B21</f>
-        <v>106442137780.59737</v>
+        <v>107128581491.68716</v>
       </c>
       <c r="G21">
         <f>C21*Population!C21</f>
-        <v>3047134272.6924968</v>
+        <v>3054666182.1782069</v>
       </c>
       <c r="H21">
         <f>D21*Population!D21</f>
-        <v>32714648377.874294</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+        <v>19535384606.465698</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B22" s="13">
         <v>16047.989739120134</v>
@@ -4924,21 +5797,21 @@
       </c>
       <c r="F22">
         <f>B22*Population!B22</f>
-        <v>111969861283.27544</v>
+        <v>112684685461.95398</v>
       </c>
       <c r="G22">
         <f>C22*Population!C22</f>
-        <v>3108092009.6560588</v>
+        <v>3115721866.0781589</v>
       </c>
       <c r="H22">
         <f>D22*Population!D22</f>
-        <v>33374409148.164501</v>
-      </c>
-      <c r="J22" s="13"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+        <v>19937727045.758663</v>
+      </c>
+      <c r="K22" s="13"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B23" s="13">
         <v>16479.488794650872</v>
@@ -4951,20 +5824,20 @@
       </c>
       <c r="F23">
         <f>B23*Population!B23</f>
-        <v>116448600654.71143</v>
+        <v>117184388504.93408</v>
       </c>
       <c r="G23">
         <f>C23*Population!C23</f>
-        <v>3184080094.8225183</v>
+        <v>3192149749.8068705</v>
       </c>
       <c r="H23">
         <f>D23*Population!D23</f>
-        <v>34133681735.471703</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+        <v>20396856277.427464</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B24" s="13">
         <v>16784.949179715102</v>
@@ -4977,20 +5850,20 @@
       </c>
       <c r="F24">
         <f>B24*Population!B24</f>
-        <v>120105920294.28836</v>
+        <v>120871817743.56311</v>
       </c>
       <c r="G24">
         <f>C24*Population!C24</f>
-        <v>3190631588.120542</v>
+        <v>3198799608.5495367</v>
       </c>
       <c r="H24">
         <f>D24*Population!D24</f>
-        <v>33882036018.543774</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+        <v>20238230228.845612</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="13" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B25" s="13">
         <v>17122.045527201219</v>
@@ -5003,20 +5876,20 @@
       </c>
       <c r="F25">
         <f>B25*Population!B25</f>
-        <v>124080595941.6353</v>
+        <v>124850421737.32379</v>
       </c>
       <c r="G25">
         <f>C25*Population!C25</f>
-        <v>3215374569.8962469</v>
+        <v>3223670443.7893171</v>
       </c>
       <c r="H25">
         <f>D25*Population!D25</f>
-        <v>33878734646.466373</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+        <v>20228258715.518364</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="13" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B26" s="13">
         <v>17500.17482812225</v>
@@ -5029,20 +5902,20 @@
       </c>
       <c r="F26">
         <f>B26*Population!B26</f>
-        <v>128394489448.54289</v>
+        <v>129179574784.1071</v>
       </c>
       <c r="G26">
         <f>C26*Population!C26</f>
-        <v>3248752626.016736</v>
+        <v>3255751139.1969132</v>
       </c>
       <c r="H26">
         <f>D26*Population!D26</f>
-        <v>34469485024.636459</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+        <v>20577815766.621822</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="13" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B27" s="13">
         <v>17868.090856870793</v>
@@ -5055,20 +5928,20 @@
       </c>
       <c r="F27">
         <f>B27*Population!B27</f>
-        <v>132696980344.95529</v>
+        <v>133483427514.41078</v>
       </c>
       <c r="G27">
         <f>C27*Population!C27</f>
-        <v>3285850867.3195839</v>
+        <v>3290147864.5538802</v>
       </c>
       <c r="H27">
         <f>D27*Population!D27</f>
-        <v>35298868327.366135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+        <v>21081628480.603973</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B28" s="13">
         <v>18232.726915707946</v>
@@ -5081,20 +5954,20 @@
       </c>
       <c r="F28">
         <f>B28*Population!B28</f>
-        <v>137009934491.69252</v>
+        <v>137813060550.04633</v>
       </c>
       <c r="G28">
         <f>C28*Population!C28</f>
-        <v>3314021894.5552607</v>
+        <v>3318393116.2190709</v>
       </c>
       <c r="H28">
         <f>D28*Population!D28</f>
-        <v>36019907345.254646</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+        <v>21505364965.621891</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B29" s="13">
         <v>18714.938943125886</v>
@@ -5107,20 +5980,20 @@
       </c>
       <c r="F29">
         <f>B29*Population!B29</f>
-        <v>142282253255.76318</v>
+        <v>143087273191.57706</v>
       </c>
       <c r="G29">
         <f>C29*Population!C29</f>
-        <v>3382168620.8821168</v>
+        <v>3387990421.1961908</v>
       </c>
       <c r="H29">
         <f>D29*Population!D29</f>
-        <v>37119573491.364235</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+        <v>22152924720.812515</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B30" s="13">
         <v>19189.020223224863</v>
@@ -5133,20 +6006,20 @@
       </c>
       <c r="F30">
         <f>B30*Population!B30</f>
-        <v>147537330000.3147</v>
+        <v>148329260788.17111</v>
       </c>
       <c r="G30">
         <f>C30*Population!C30</f>
-        <v>3437326529.174746</v>
+        <v>3443769661.1138372</v>
       </c>
       <c r="H30">
         <f>D30*Population!D30</f>
-        <v>37930710214.837662</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+        <v>22640578323.033131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B31" s="13">
         <v>19552.083514829628</v>
@@ -5159,20 +6032,20 @@
       </c>
       <c r="F31">
         <f>B31*Population!B31</f>
-        <v>151942619124.5224</v>
+        <v>152727066742.15836</v>
       </c>
       <c r="G31">
         <f>C31*Population!C31</f>
-        <v>3508476774.2787137</v>
+        <v>3513144596.9224849</v>
       </c>
       <c r="H31">
         <f>D31*Population!D31</f>
-        <v>38699419341.686249</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+        <v>23112148514.524086</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B32" s="13">
         <v>18811.493553031505</v>
@@ -5185,20 +6058,20 @@
       </c>
       <c r="F32">
         <f>B32*Population!B32</f>
-        <v>147696835525.1188</v>
+        <v>148366273957.20917</v>
       </c>
       <c r="G32">
         <f>C32*Population!C32</f>
-        <v>3245513774.264863</v>
+        <v>3249877087.601615</v>
       </c>
       <c r="H32">
         <f>D32*Population!D32</f>
-        <v>36574113872.711426</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+        <v>21838278294.189957</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B33" s="13">
         <v>19866.767918404636</v>
@@ -5211,20 +6084,20 @@
       </c>
       <c r="F33">
         <f>B33*Population!B33</f>
-        <v>157396216374.06714</v>
+        <v>158029180102.92416</v>
       </c>
       <c r="G33">
         <f>C33*Population!C33</f>
-        <v>3465816591.7571898</v>
+        <v>3470531860.7242112</v>
       </c>
       <c r="H33">
         <f>D33*Population!D33</f>
-        <v>38931911154.245689</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+        <v>23267260238.964119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" s="13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B34" s="13">
         <v>20409.442097193965</v>
@@ -5237,20 +6110,20 @@
       </c>
       <c r="F34">
         <f>B34*Population!B34</f>
-        <v>162996107432.09946</v>
+        <v>163712445623.13922</v>
       </c>
       <c r="G34">
         <f>C34*Population!C34</f>
-        <v>3551775096.365675</v>
+        <v>3557361305.8783598</v>
       </c>
       <c r="H34">
         <f>D34*Population!D34</f>
-        <v>40231131436.83564</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+        <v>24152188840.065418</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B35" s="13">
         <v>20918.304708117044</v>
@@ -5263,20 +6136,20 @@
       </c>
       <c r="F35">
         <f>B35*Population!B35</f>
-        <v>168528438270.39236</v>
+        <v>169265376883.05414</v>
       </c>
       <c r="G35">
         <f>C35*Population!C35</f>
-        <v>3604297109.3329239</v>
+        <v>3607410320.5447221</v>
       </c>
       <c r="H35">
         <f>D35*Population!D35</f>
-        <v>40177113825.347435</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+        <v>24276616351.55632</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A36" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B36" s="13">
         <v>21405.118104266388</v>
@@ -5289,157 +6162,303 @@
       </c>
       <c r="F36">
         <f>B36*Population!B36</f>
-        <v>173958630585.03613</v>
+        <v>174707986867.4429</v>
       </c>
       <c r="G36">
         <f>C36*Population!C36</f>
-        <v>3643946175.5877328</v>
+        <v>3646816072.2559252</v>
       </c>
       <c r="H36">
         <f>D36*Population!D36</f>
-        <v>40502412753.686844</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
+        <v>24466165583.505955</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="31" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="E38">
+        <v>2015</v>
+      </c>
+      <c r="F38">
+        <f>B27</f>
+        <v>17868.090856870793</v>
+      </c>
+      <c r="G38" s="31">
+        <f t="shared" ref="G38:H38" si="0">C27</f>
+        <v>50682.895358633301</v>
+      </c>
+      <c r="H38" s="31">
+        <f t="shared" si="0"/>
+        <v>47490.67459411014</v>
+      </c>
+      <c r="K38" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="31" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="E39" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="F39" s="31">
+        <v>1</v>
+      </c>
+      <c r="G39" s="31">
+        <f>G38/F38</f>
+        <v>2.8365031141054602</v>
+      </c>
+      <c r="H39" s="31">
+        <f>H38/F38</f>
+        <v>2.6578482824228877</v>
+      </c>
+      <c r="K39" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="L39" s="58"/>
+      <c r="M39" s="58"/>
+    </row>
+    <row r="40" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40">
+        <v>50000</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F40">
+        <f>SUM(F2:F36)/SUM(Population!B2:B36)</f>
+        <v>15732.164711604171</v>
+      </c>
+      <c r="G40">
+        <f>SUM(G2:G36)/SUM(Population!C2:C36)</f>
+        <v>47663.631330163909</v>
+      </c>
+      <c r="H40">
+        <f>SUM(H2:H36)/SUM(Population!D2:D36)</f>
+        <v>43700.966271954145</v>
+      </c>
+      <c r="J40" s="31"/>
+      <c r="K40" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="L40" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="M40" s="44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="31" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="E41" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F41" s="31">
+        <v>1</v>
+      </c>
+      <c r="G41" s="31">
+        <f>G40/F40</f>
+        <v>3.0296931289440945</v>
+      </c>
+      <c r="H41" s="31">
+        <f>H40/F40</f>
+        <v>2.7778101153314241</v>
+      </c>
+      <c r="J41" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="K41" s="45">
+        <v>55077.287499999999</v>
+      </c>
+      <c r="L41" s="45">
+        <v>23235.55</v>
+      </c>
+      <c r="M41" s="46">
+        <v>2.3703888007815599</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42">
+        <v>7500</v>
+      </c>
+      <c r="E42" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B38">
-        <v>50000</v>
-      </c>
-      <c r="E38" s="3" t="s">
+      <c r="F42">
+        <f>1-(F40-B42)/(B40-B42)</f>
+        <v>0.80630200678578423</v>
+      </c>
+      <c r="G42">
+        <f>1-(G40-B42)/(B40-B42)</f>
+        <v>5.4973380466731503E-2</v>
+      </c>
+      <c r="H42">
+        <f>1-(H40-B42)/(B40-B42)</f>
+        <v>0.14821255830696134</v>
+      </c>
+      <c r="J42" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="K42" s="45">
+        <v>53985.9</v>
+      </c>
+      <c r="L42" s="45">
+        <v>22052.862499999999</v>
+      </c>
+      <c r="M42" s="46">
+        <v>2.4480223372362699</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="E43" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F43" s="10">
+        <f>(Population!B115*Capacité!F42)*100/(Population!B115*Capacité!F42)</f>
+        <v>100</v>
+      </c>
+      <c r="G43" s="10">
+        <f>(Population!C115*Capacité!G42)*100/(Population!B115*Capacité!F42)</f>
+        <v>5.2734500405756501E-2</v>
+      </c>
+      <c r="H43" s="10">
+        <f>(Population!D115*Capacité!H42)*100/(Population!B115*Capacité!F42)</f>
+        <v>0.93086683696635297</v>
+      </c>
+      <c r="I43" s="10"/>
+      <c r="J43" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="K43" s="45">
+        <v>52102.45</v>
+      </c>
+      <c r="L43" s="45">
+        <v>20638.025000000001</v>
+      </c>
+      <c r="M43" s="46">
+        <v>2.5245850802099499</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="E44" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F44">
+        <f>1-(B27-B42)/(B40-B42)</f>
+        <v>0.75604492101480492</v>
+      </c>
+      <c r="G44">
+        <f>MAX(1-(C27-B42)/(B40-B42),0)</f>
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <f>MAX(1-(D27-B42)/(B40-B42),0)</f>
+        <v>5.9042950726820198E-2</v>
+      </c>
+      <c r="J44" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="K44" s="45">
+        <v>55263.5</v>
+      </c>
+      <c r="L44" s="45">
+        <v>21733.662499999999</v>
+      </c>
+      <c r="M44" s="46">
+        <v>2.5427605678518299</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="E45" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="F45">
+        <f>(Population!B115*Capacité!F44)*100/(Population!B115*Capacité!F44)</f>
+        <v>100</v>
+      </c>
+      <c r="G45">
+        <f>(Population!C115*Capacité!G44)*100/(Population!B115*Capacité!F44)</f>
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <f>(Population!D115*Capacité!H44)*100/(Population!B115*Capacité!F44)</f>
+        <v>0.39547656087185179</v>
+      </c>
+      <c r="J45" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="K45" s="45">
+        <v>56918.724999999999</v>
+      </c>
+      <c r="L45" s="45">
+        <v>24625.825000000001</v>
+      </c>
+      <c r="M45" s="46">
+        <v>2.31134286871607</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s">
+        <v>61</v>
+      </c>
+      <c r="J46" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="K46" s="31"/>
+      <c r="L46" s="31"/>
+      <c r="M46" s="47">
+        <f>AVERAGE(M41:M45)</f>
+        <v>2.4394199309591356</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>67</v>
+      </c>
+      <c r="B48" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="F38">
-        <f>SUM(F2:F36)/SUM(Population!B2:B36)</f>
-        <v>15735.40978182493</v>
-      </c>
-      <c r="G38">
-        <f>SUM(G2:G36)/SUM(Population!C2:C36)</f>
-        <v>47664.595364682391</v>
-      </c>
-      <c r="H38">
-        <f>SUM(H2:H36)/SUM(Population!D2:D36)</f>
-        <v>43631.695837336869</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>70</v>
-      </c>
-      <c r="B39">
-        <v>7500</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="F39">
-        <f>1-(F38-B39)/(B38-B39)</f>
-        <v>0.80622565219235454</v>
-      </c>
-      <c r="G39">
-        <f>1-(G38-B39)/(B38-B39)</f>
-        <v>5.4950697301590856E-2</v>
-      </c>
-      <c r="H39">
-        <f>1-(H38-B39)/(B38-B39)</f>
-        <v>0.1498424508861913</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="E40" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F40" s="10">
-        <f>(Population!B115*Capacité!F39)*100/(Population!B115*Capacité!F39)</f>
-        <v>100</v>
-      </c>
-      <c r="G40" s="10">
-        <f>(Population!C115*Capacité!G39)*100/(Population!B115*Capacité!F39)</f>
-        <v>5.2725112527240728E-2</v>
-      </c>
-      <c r="H40" s="10">
-        <f>(Population!D115*Capacité!H39)*100/(Population!B115*Capacité!F39)</f>
-        <v>1.5668798264892982</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="E41" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F41">
-        <f>1-(B27-B39)/(B38-B39)</f>
-        <v>0.75604492101480492</v>
-      </c>
-      <c r="G41">
-        <f>MAX(1-(C27-B39)/(B38-B39),0)</f>
-        <v>0</v>
-      </c>
-      <c r="H41">
-        <f>MAX(1-(D27-B39)/(B38-B39),0)</f>
-        <v>5.9042950726820198E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="E42" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F42">
-        <f>(Population!B115*Capacité!F41)*100/(Population!B115*Capacité!F41)</f>
-        <v>100</v>
-      </c>
-      <c r="G42">
-        <f>(Population!C115*Capacité!G41)*100/(Population!B115*Capacité!F41)</f>
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <f>(Population!D115*Capacité!H41)*100/(Population!B115*Capacité!F41)</f>
-        <v>0.65838190592741441</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>64</v>
-      </c>
-      <c r="B43" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>19</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>71</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>72</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="K39:M39"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B44" r:id="rId1" xr:uid="{95CBC694-0581-4D50-9574-5F9F43EFE88E}"/>
-    <hyperlink ref="B45" r:id="rId2" xr:uid="{F1AC7F8B-6E35-450D-9416-466DBBC662CB}"/>
+    <hyperlink ref="B47" r:id="rId1" xr:uid="{95CBC694-0581-4D50-9574-5F9F43EFE88E}"/>
+    <hyperlink ref="B48" r:id="rId2" xr:uid="{F1AC7F8B-6E35-450D-9416-466DBBC662CB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC11EFA9-274E-476D-8BFE-D8769B6BF052}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.69140625" customWidth="1"/>
+    <col min="2" max="2" width="11.61328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B1" s="31" t="s">
         <v>2</v>
       </c>
@@ -5447,7 +6466,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E1" s="31" t="s">
         <v>11</v>
@@ -5459,110 +6478,110 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="31" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B2">
         <f>(Population!C115*DLS!B2)/(Population!B115*DLS!B8)</f>
-        <v>5.0453008893561703E-3</v>
+        <v>5.0445947637680474E-3</v>
       </c>
       <c r="C2" s="31">
         <f>(Population!C115*DLS!C2)/(Population!B115*DLS!C8)</f>
-        <v>5.4712861762416078E-3</v>
+        <v>5.470520430995939E-3</v>
       </c>
       <c r="D2" s="31">
         <f>(Population!C115*DLS!D2)/(Population!B115*DLS!D8)</f>
-        <v>1.1540161342524667E-2</v>
+        <v>1.1538546215222302E-2</v>
       </c>
       <c r="E2" s="31">
         <f>(Population!C115*DLS!E2)/(Population!B115*DLS!E8)</f>
-        <v>6.3658555255869491E-3</v>
+        <v>6.3649645790258835E-3</v>
       </c>
       <c r="F2" s="31">
-        <f>(Population!D115*DLS!F2)/(Population!C115*DLS!F8)</f>
-        <v>11.111934715799952</v>
+        <f>(Population!C115*DLS!F2)/(Population!B115*DLS!F8)</f>
+        <v>7.8863001187632689E-3</v>
       </c>
       <c r="G2" s="31">
         <f>(Population!C115*DLS!G2)/(Population!B115*DLS!G8)</f>
-        <v>1.1537633897179685E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+        <v>1.1536019123611196E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="31" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B3" s="31">
         <f>(Population!C115*DLS!B3)/(Population!B115*DLS!B9)</f>
-        <v>9.2209328609291312E-3</v>
+        <v>9.2196423260765513E-3</v>
       </c>
       <c r="C3" s="31">
         <f>(Population!C115*DLS!C3)/(Population!B115*DLS!C9)</f>
-        <v>5.478101591125246E-3</v>
+        <v>5.4773348920140012E-3</v>
       </c>
       <c r="D3" s="31">
         <f>(Population!C115*DLS!D3)/(Population!B115*DLS!D9)</f>
-        <v>1.1585409246018084E-2</v>
+        <v>1.1583787785951202E-2</v>
       </c>
       <c r="E3" s="31">
         <f>(Population!C115*DLS!E3)/(Population!B115*DLS!E9)</f>
-        <v>8.7627150482219827E-3</v>
+        <v>8.7614886441971934E-3</v>
       </c>
       <c r="F3" s="31">
-        <f>(Population!D115*DLS!F3)/(Population!C115*DLS!F9)</f>
-        <v>11.111934715799952</v>
+        <f>(Population!C115*DLS!F3)/(Population!B115*DLS!F9)</f>
+        <v>7.8863001187632689E-3</v>
       </c>
       <c r="G3" s="31">
         <f>(Population!C115*DLS!G3)/(Population!B115*DLS!G9)</f>
-        <v>1.1584810603112349E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+        <v>1.1583189226829783E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B5">
         <f>(Population!C115*DLS!B4)/(Population!B115*DLS!B10)</f>
-        <v>6.3772401782154799E-3</v>
+        <v>6.3763476382916566E-3</v>
       </c>
       <c r="C5" s="31">
         <f>(Population!C115*DLS!C4)/(Population!B115*DLS!C10)</f>
-        <v>5.4746321044952329E-3</v>
+        <v>5.4738658909632108E-3</v>
       </c>
       <c r="D5" s="31">
         <f>(Population!C115*DLS!D4)/(Population!B115*DLS!D10)</f>
-        <v>1.1561912753445425E-2</v>
+        <v>1.1560294581879071E-2</v>
       </c>
       <c r="E5" s="31">
         <f>(Population!C115*DLS!E4)/(Population!B115*DLS!E10)</f>
-        <v>7.3317319444951368E-3</v>
+        <v>7.3307058166893228E-3</v>
       </c>
       <c r="F5" s="31">
-        <f>(Population!D115*DLS!F4)/(Population!C115*DLS!F10)</f>
-        <v>11.111934715799952</v>
+        <f>(Population!C115*DLS!F4)/(Population!B115*DLS!F10)</f>
+        <v>7.8863001187632689E-3</v>
       </c>
       <c r="G5" s="31">
         <f>(Population!C115*DLS!G4)/(Population!B115*DLS!G10)</f>
-        <v>1.1557380920548374E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+        <v>1.1555763383244126E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D8" s="31">
         <v>3494.0786014333898</v>
       </c>
       <c r="E8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F8">
         <f>1-F9</f>
@@ -5576,15 +6595,15 @@
         <v>0.74445404791547987</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D9" s="31">
         <v>201.308612543306</v>
       </c>
       <c r="E9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F9">
         <f>SUM(D9:D12)/SUM(D8:D13)</f>
@@ -5594,48 +6613,48 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D10">
         <v>520</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D11">
         <v>40</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D12">
         <v>40</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D13">
         <v>211</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -5643,120 +6662,120 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE07EBE8-6449-4730-9E28-CE2F7AF6313A}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.06640625" customWidth="1"/>
+    <col min="1" max="1" width="13.07421875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2">
         <f>170/74</f>
         <v>2.2972972972972974</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3">
         <f>1055/74</f>
         <v>14.256756756756756</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" s="38"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" s="38">
         <f>((Population!C116/100)*A2)*1000</f>
-        <v>17.77125593184725</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+        <v>17.76876871873117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" s="38">
         <f>((Population!C116/100)*A3)*1000</f>
-        <v>110.28632357705203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+        <v>110.27088822506695</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" s="38"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" s="38" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" s="14">
         <v>1000000000</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" s="20"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" s="22"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" s="22">
         <f>A2*1000000000/(Population!B115*1000)</f>
-        <v>0.26480616600193263</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+        <v>0.264704634686033</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" s="22">
         <f>A3*1000000000/(Population!B115*1000)</f>
-        <v>1.6433559125414052</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>1.6427258211397928</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="36" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" s="20"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19">
-        <f>(Capacité!G40/100)*A2</f>
-        <v>1.2112525850852601E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+        <f>(Capacité!G43/100)*A2</f>
+        <v>1.2114682525646763E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20">
-        <f>(Capacité!G40/100)*A3</f>
-        <v>7.5168910427349956E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <f>(Capacité!G43/100)*A3</f>
+        <v>7.5182294497396079E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="15"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24">
         <f>A2*Besoins!B5*1000</f>
-        <v>14.650416625630157</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+        <v>14.648366196075427</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" s="31">
         <f>A3*Besoins!B5*1000</f>
-        <v>90.918762000234196</v>
+        <v>90.906037275644564</v>
       </c>
     </row>
   </sheetData>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C70F14F-3361-4CDE-8AB9-8F520D3CBC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C827263-2CED-4E99-B68C-80376596CF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="8002" windowWidth="14595" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="9" r:id="rId1"/>
     <sheet name="Synthèse v2" sheetId="1" r:id="rId2"/>
-    <sheet name="DLS" sheetId="5" r:id="rId3"/>
-    <sheet name="DLE" sheetId="7" r:id="rId4"/>
-    <sheet name="Population" sheetId="2" r:id="rId5"/>
-    <sheet name="Capacité" sheetId="3" r:id="rId6"/>
-    <sheet name="Besoins" sheetId="6" r:id="rId7"/>
-    <sheet name="Feuil1" sheetId="8" r:id="rId8"/>
+    <sheet name="DLS v2" sheetId="10" r:id="rId3"/>
+    <sheet name="DLS" sheetId="5" r:id="rId4"/>
+    <sheet name="DLE" sheetId="7" r:id="rId5"/>
+    <sheet name="Population" sheetId="2" r:id="rId6"/>
+    <sheet name="Capacité" sheetId="3" r:id="rId7"/>
+    <sheet name="Besoins" sheetId="6" r:id="rId8"/>
+    <sheet name="Feuil1" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="206">
   <si>
     <t>N</t>
   </si>
@@ -722,9 +723,6 @@
     <t>P surplus</t>
   </si>
   <si>
-    <t>Final Energy use</t>
-  </si>
-  <si>
     <t>Raw material consumption</t>
   </si>
   <si>
@@ -732,6 +730,9 @@
   </si>
   <si>
     <t>Blue water consumption</t>
+  </si>
+  <si>
+    <t>Final energy use</t>
   </si>
 </sst>
 </file>
@@ -983,7 +984,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1021,9 +1022,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1056,6 +1054,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1088,13 +1093,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="14" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1383,12 +1381,12 @@
   <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.15234375" style="31" customWidth="1"/>
-    <col min="2" max="3" width="9.23046875" style="31"/>
-    <col min="4" max="4" width="14.07421875" style="31" customWidth="1"/>
-    <col min="5" max="8" width="9.23046875" style="31"/>
-    <col min="9" max="10" width="11.84375" style="31" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.23046875" style="31"/>
+    <col min="1" max="1" width="21.15234375" style="28" customWidth="1"/>
+    <col min="2" max="3" width="9.23046875" style="28"/>
+    <col min="4" max="4" width="14.07421875" style="28" customWidth="1"/>
+    <col min="5" max="8" width="9.23046875" style="28"/>
+    <col min="9" max="10" width="11.84375" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.23046875" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
@@ -1399,7 +1397,7 @@
         <v>198</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D1" s="17" t="s">
         <v>199</v>
@@ -1411,49 +1409,49 @@
         <v>201</v>
       </c>
       <c r="G1" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H1" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="I1" s="18" t="s">
         <v>203</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="31">
+      <c r="B2" s="28">
         <f>(1.33*170+163.83)/74</f>
         <v>5.2693243243243248</v>
       </c>
-      <c r="C2" s="31">
+      <c r="C2" s="28">
         <v>2800</v>
       </c>
-      <c r="D2" s="31">
+      <c r="D2" s="28">
         <v>12.6</v>
       </c>
-      <c r="E2" s="31">
+      <c r="E2" s="28">
         <v>57</v>
       </c>
-      <c r="F2" s="31">
+      <c r="F2" s="28">
         <v>4.5</v>
       </c>
-      <c r="G2" s="31">
+      <c r="G2" s="28">
         <v>39.6</v>
       </c>
-      <c r="H2" s="31">
+      <c r="H2" s="28">
         <v>25</v>
       </c>
-      <c r="I2" s="31">
+      <c r="I2" s="28">
         <v>3724</v>
       </c>
-      <c r="K2" s="31">
+      <c r="K2" s="28">
         <f>(0.258-K3)/K3</f>
         <v>1.2845755630300952</v>
       </c>
-      <c r="L2" s="31">
+      <c r="L2" s="28">
         <f>0.258/K3</f>
         <v>2.2845755630300952</v>
       </c>
@@ -1462,26 +1460,26 @@
       <c r="A3" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="28">
         <f>(1.33*1055+163.83)/74</f>
         <v>21.175405405405407</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="28">
         <v>4500</v>
       </c>
-      <c r="D3" s="31">
+      <c r="D3" s="28">
         <v>16.399999999999999</v>
       </c>
-      <c r="F3" s="31">
+      <c r="F3" s="28">
         <v>9</v>
       </c>
-      <c r="G3" s="31">
+      <c r="G3" s="28">
         <v>49</v>
       </c>
-      <c r="H3" s="31">
+      <c r="H3" s="28">
         <v>50</v>
       </c>
-      <c r="K3" s="31">
+      <c r="K3" s="28">
         <f>Population!C113*Synthèse!D2/100</f>
         <v>0.11293126135771475</v>
       </c>
@@ -1528,135 +1526,135 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="19"/>
-      <c r="K6" s="31">
+      <c r="K6" s="28">
         <f>269/100 -1</f>
         <v>1.69</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="35">
         <f>((Population!C116/100)*B2)*1000</f>
         <v>40.756329332322622</v>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="35">
         <f>(Population!C116/100)*C2</f>
         <v>21.656993403065282</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="35">
         <f>((Population!C116/100)*D2)*1000</f>
         <v>97.456470313793773</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="35">
         <f>((Population!C116/100)*E2)*1000</f>
         <v>440.87450856240042</v>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="35">
         <f>((Population!C116/100)*F2)*1000</f>
         <v>34.805882254926345</v>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="35">
         <f>(G2*Population!C115)*0.000277778</f>
         <v>738.39512671562909</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="35">
         <f>((Population!C116/100)*H2)*1000</f>
         <v>193.36601252736861</v>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="35">
         <f>(Population!C116/100)*I2</f>
         <v>28.803801226076825</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="35">
         <f>((Population!C116/100)*B3)*1000</f>
         <v>163.78414827574923</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="35">
         <f>(Population!C116/100)*C3</f>
         <v>34.805882254926345</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="35">
         <f>((Population!C116/100)*D3)*1000</f>
         <v>126.84810421795379</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="35">
         <f>((Population!C116/100)*E3)*1000</f>
         <v>0</v>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="35">
         <f>((Population!C116/100)*F3)*1000</f>
         <v>69.611764509852691</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="35">
         <f>(G3*Population!C115)*0.000366668</f>
         <v>1206.0487944160323</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="35">
         <f>((Population!C116/100)*H3)*1000</f>
         <v>386.73202505473722</v>
       </c>
-      <c r="I9" s="38">
+      <c r="I9" s="35">
         <f>(Population!C116/100)*I3</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A10" s="37"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="F11" s="38" t="s">
+      <c r="F11" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="H11" s="38" t="s">
+      <c r="H11" s="35" t="s">
         <v>182</v>
       </c>
-      <c r="I11" s="38" t="s">
+      <c r="I11" s="35" t="s">
         <v>169</v>
       </c>
     </row>
@@ -1664,29 +1662,29 @@
       <c r="A12" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="B12" s="32">
+      <c r="B12" s="29">
         <v>1</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="29">
         <v>1000</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="29">
         <v>1000</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="29">
         <v>1E-3</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="29">
         <v>1E-3</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="28">
         <f>1/0.000277778</f>
         <v>3599.9971200023037</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="29">
         <v>1000</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="29">
         <v>10000000000</v>
       </c>
     </row>
@@ -1731,7 +1729,7 @@
       <c r="I14" s="20"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="31" t="s">
         <v>93</v>
       </c>
       <c r="B15" s="22"/>
@@ -1744,7 +1742,7 @@
       <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="31" t="s">
         <v>137</v>
       </c>
       <c r="B16" s="22">
@@ -1781,7 +1779,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="31" t="s">
         <v>138</v>
       </c>
       <c r="B17" s="22">
@@ -1818,31 +1816,31 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="33" t="s">
         <v>196</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F18" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="36" t="s">
+      <c r="G18" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="H18" s="36" t="s">
+      <c r="H18" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="I18" s="36" t="s">
+      <c r="I18" s="33" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1850,28 +1848,28 @@
       <c r="A19" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="B19" s="59">
+      <c r="B19" s="45">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="C19" s="59">
+      <c r="C19" s="45">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="D19" s="59">
+      <c r="D19" s="45">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="E19" s="59">
+      <c r="E19" s="45">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="F19" s="59">
+      <c r="F19" s="45">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="G19" s="59">
+      <c r="G19" s="45">
         <v>1E-3</v>
       </c>
-      <c r="H19" s="59">
+      <c r="H19" s="45">
         <v>1E-3</v>
       </c>
-      <c r="I19" s="59">
+      <c r="I19" s="45">
         <v>10000</v>
       </c>
     </row>
@@ -1890,35 +1888,35 @@
       <c r="A21" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="28">
         <f>(Capacité!G43/100)*B2</f>
         <v>2.7787518571914371E-3</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="28">
         <f>(Capacité!G43/100)*C2</f>
         <v>1.4765660113611818</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="28">
         <f>(Capacité!G43/100)*D2</f>
         <v>6.6445470511253182E-3</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="28">
         <f>(Capacité!G43/100)*E2</f>
         <v>3.0058665231281204E-2</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="28">
         <f>(Capacité!G43/100)*F2</f>
         <v>2.3730525182590425E-3</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="28">
         <f>(Capacité!G43/100)*G2</f>
         <v>2.0882862160679572E-2</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="28">
         <f>((Capacité!G42/100)*H2)*1000</f>
         <v>13.743345116682876</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="28">
         <f>(Capacité!G43/100)*I2</f>
         <v>1.963832795110372</v>
       </c>
@@ -1927,35 +1925,35 @@
       <c r="A22" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="28">
         <f>(Capacité!G43/100)*B3</f>
         <v>1.1166744249434098E-2</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="28">
         <f>(Capacité!G43/100)*C3</f>
         <v>2.3730525182590423</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="28">
         <f>(Capacité!G43/100)*D3</f>
         <v>8.6484580665440649E-3</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="28">
         <f>(Capacité!G43/100)*E3</f>
         <v>0</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="28">
         <f>(Capacité!G43/100)*F3</f>
         <v>4.746105036518085E-3</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="28">
         <f>(Capacité!G43/100)*G3</f>
         <v>2.5839905198820682E-2</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="28">
         <f>((Capacité!G43/100)*H3)*1000</f>
         <v>26.367250202878246</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="28">
         <f>(Capacité!G43/100)*I3</f>
         <v>0</v>
       </c>
@@ -1986,50 +1984,50 @@
       <c r="A26" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="31">
+      <c r="B26" s="28">
         <f>B2*Besoins!B5*1000</f>
         <v>33.599043710798185</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="28" t="e">
         <f>C2*Besoins!C5</f>
-        <v>15.326824494696991</v>
-      </c>
-      <c r="D26" s="31">
+        <v>#REF!</v>
+      </c>
+      <c r="D26" s="28" t="e">
         <f>D2*Besoins!D5*1000</f>
-        <v>145.65971173167631</v>
-      </c>
-      <c r="H26" s="31">
+        <v>#REF!</v>
+      </c>
+      <c r="H26" s="28">
         <f>H2*Besoins!E5*1000</f>
         <v>183.26764541723307</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="28" t="e">
         <f>I2*Besoins!G5</f>
-        <v>43.033662839201128</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="28">
         <f>B3*Besoins!B5*1000</f>
         <v>135.02174624662513</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="28" t="e">
         <f>C3*Besoins!C5</f>
-        <v>24.632396509334448</v>
-      </c>
-      <c r="D27" s="31">
+        <v>#REF!</v>
+      </c>
+      <c r="D27" s="28" t="e">
         <f>D3*Besoins!D5*1000</f>
-        <v>189.58883114281673</v>
-      </c>
-      <c r="H27" s="31">
+        <v>#REF!</v>
+      </c>
+      <c r="H27" s="28">
         <f>H3*Besoins!E5*1000</f>
         <v>366.53529083446614</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="28" t="e">
         <f>I3*Besoins!G5</f>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.4">
@@ -2188,130 +2186,130 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="35">
         <f>((Population!C116/100)*B2)*1000</f>
         <v>40.756329332322622</v>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="35">
         <f>(Population!C116/100)*C2</f>
         <v>21.656993403065282</v>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="35">
         <f>((Population!C116/100)*D2)*1000</f>
         <v>97.456470313793773</v>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="35">
         <f>((Population!C116/100)*E2)*1000</f>
         <v>220.43725428120021</v>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="35">
         <f>((Population!C116/100)*F2)*1000</f>
         <v>14.463777737047172</v>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="35">
         <f>(G2*Population!C115)*0.000277778</f>
         <v>738.39512671562909</v>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="35">
         <f>((Population!C116/100)*H2)*1000</f>
         <v>193.36601252736861</v>
       </c>
-      <c r="I7" s="38">
+      <c r="I7" s="35">
         <f>(Population!C116/100)*I2</f>
         <v>28.803801226076825</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="35">
         <f>((Population!C116/100)*B3)*1000</f>
         <v>163.78414827574923</v>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="35">
         <f>(Population!C116/100)*C3</f>
         <v>34.805882254926345</v>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="35">
         <f>((Population!C116/100)*D3)*1000</f>
         <v>126.84810421795379</v>
       </c>
-      <c r="E8" s="38">
+      <c r="E8" s="35">
         <f>((Population!C116/100)*E3)*1000</f>
         <v>291.59594689127186</v>
       </c>
-      <c r="F8" s="38">
+      <c r="F8" s="35">
         <f>((Population!C116/100)*F3)*1000</f>
         <v>131.48888851861065</v>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="35">
         <f>(G3*Population!C115)*0.000366668</f>
         <v>1206.0487944160323</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="35">
         <f>((Population!C116/100)*H3)*1000</f>
         <v>386.73202505473722</v>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="35">
         <f>(Population!C116/100)*I3</f>
         <v>201.62660858253778</v>
       </c>
-      <c r="J8" s="31"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A9" s="37"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="H10" s="38" t="s">
+      <c r="H10" s="35" t="s">
         <v>182</v>
       </c>
-      <c r="I10" s="38" t="s">
+      <c r="I10" s="35" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2341,7 +2339,7 @@
       <c r="H11" s="14">
         <v>1000</v>
       </c>
-      <c r="I11" s="32">
+      <c r="I11" s="29">
         <v>10000000000</v>
       </c>
     </row>
@@ -2386,7 +2384,7 @@
       <c r="I13" s="20"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="31" t="s">
         <v>93</v>
       </c>
       <c r="B14" s="22"/>
@@ -2399,7 +2397,7 @@
       <c r="I14" s="22"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="31" t="s">
         <v>137</v>
       </c>
       <c r="B15" s="22">
@@ -2436,7 +2434,7 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="31" t="s">
         <v>138</v>
       </c>
       <c r="B16" s="22">
@@ -2473,31 +2471,31 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="36" t="s">
+      <c r="E17" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="36" t="s">
+      <c r="G17" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="H17" s="36" t="s">
+      <c r="H17" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="I17" s="36" t="s">
+      <c r="I17" s="33" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2612,56 +2610,56 @@
       <c r="A24" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="28">
         <f>B2*Besoins!B5*1000</f>
         <v>33.599043710798185</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="28" t="e">
         <f>C2*Besoins!C5</f>
-        <v>15.326824494696991</v>
-      </c>
-      <c r="D24" s="31">
+        <v>#REF!</v>
+      </c>
+      <c r="D24" s="28" t="e">
         <f>D2*Besoins!D5*1000</f>
-        <v>145.65971173167631</v>
-      </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31">
+        <v>#REF!</v>
+      </c>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28">
         <f>H2*Besoins!E5*1000</f>
         <v>183.26764541723307</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="28" t="e">
         <f>I2*Besoins!G5</f>
-        <v>43.033662839201128</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="28">
         <f>B3*Besoins!B5*1000</f>
         <v>135.02174624662513</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="28" t="e">
         <f>C3*Besoins!C5</f>
-        <v>24.632396509334448</v>
-      </c>
-      <c r="D25" s="31">
+        <v>#REF!</v>
+      </c>
+      <c r="D25" s="28" t="e">
         <f>D3*Besoins!D5*1000</f>
-        <v>189.58883114281673</v>
-      </c>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31">
+        <v>#REF!</v>
+      </c>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28">
         <f>H3*Besoins!E5*1000</f>
         <v>366.53529083446614</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="28" t="e">
         <f>I3*Besoins!G5</f>
-        <v>301.23563987440787</v>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
@@ -2673,14 +2671,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1104A7-2272-4986-AE6B-8EA45794950A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0A75E4-DA25-4A08-8974-1A31A91FD529}">
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="27.69140625" customWidth="1"/>
-    <col min="3" max="4" width="12.3828125" customWidth="1"/>
-    <col min="5" max="5" width="11.921875" customWidth="1"/>
-    <col min="7" max="7" width="14.84375" customWidth="1"/>
+    <col min="1" max="1" width="27.69140625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="11.07421875" style="28"/>
+    <col min="3" max="4" width="12.3828125" style="28" customWidth="1"/>
+    <col min="5" max="5" width="11.921875" style="28" customWidth="1"/>
+    <col min="6" max="6" width="11.07421875" style="28"/>
+    <col min="7" max="7" width="14.84375" style="28" customWidth="1"/>
+    <col min="8" max="16384" width="11.07421875" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.4">
@@ -2758,32 +2759,32 @@
         <v>2.9475940000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
         <v>166</v>
       </c>
       <c r="B4" s="22">
-        <f>(DLS!B2+DLS!B3)/2</f>
+        <f>('DLS v2'!B2+'DLS v2'!B3)/2</f>
         <v>2.3849999999999998</v>
       </c>
       <c r="C4" s="22">
-        <f>(DLS!C2+DLS!C3)/2</f>
+        <f>('DLS v2'!C2+'DLS v2'!C3)/2</f>
         <v>142.80000000000001</v>
       </c>
       <c r="D4" s="22">
-        <f>(DLS!D2+DLS!D3)/2</f>
+        <f>('DLS v2'!D2+'DLS v2'!D3)/2</f>
         <v>4370</v>
       </c>
       <c r="E4" s="22">
-        <f>(DLS!E2+DLS!E3)/2</f>
+        <f>('DLS v2'!E2+'DLS v2'!E3)/2</f>
         <v>3.81</v>
       </c>
       <c r="F4" s="22">
-        <f>(DLS!F2+DLS!F3)/2</f>
+        <f>('DLS v2'!F2+'DLS v2'!F3)/2</f>
         <v>21.054901960784314</v>
       </c>
       <c r="G4" s="22">
-        <f>(DLS!G2+DLS!G3)/2</f>
+        <f>('DLS v2'!G2+'DLS v2'!G3)/2</f>
         <v>3.5126439500000002E-2</v>
       </c>
     </row>
@@ -2811,226 +2812,226 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+      <c r="A7" s="28" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+      <c r="A8" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="28">
         <v>3.9404604370967649</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="28">
         <v>205.43626131827909</v>
       </c>
       <c r="D8" s="28">
         <f>3036.5975761951</f>
         <v>3036.5975761950999</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="28">
         <v>4.8</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="28">
         <f>26</f>
         <v>26</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="28">
         <f>(B8*0.27+D8*0.9)*0.00001</f>
         <v>2.7340017428936065E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
+      <c r="A9" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <v>1.8456474232498501</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="28">
         <v>198.12008644674611</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <f>2811.06984272459</f>
         <v>2811.0698427245902</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="28">
         <v>3.239875298796179</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="28">
         <f>15.3</f>
         <v>15.3</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="28">
         <f>(B9*0.27+D9*0.7)*0.00001</f>
         <v>1.9682472147114907E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="B10">
-        <f>(DLS!B8+DLS!B9)/2</f>
+      <c r="B10" s="28">
+        <f>('DLS v2'!B8+'DLS v2'!B9)/2</f>
         <v>2.8930539301733074</v>
       </c>
-      <c r="C10" s="31">
-        <f>(DLS!C8+DLS!C9)/2</f>
+      <c r="C10" s="28">
+        <f>('DLS v2'!C8+'DLS v2'!C9)/2</f>
         <v>201.77817388251259</v>
       </c>
-      <c r="D10" s="31">
-        <f>(DLS!D8+DLS!D9)/2</f>
+      <c r="D10" s="28">
+        <f>('DLS v2'!D8+'DLS v2'!D9)/2</f>
         <v>2923.8337094598451</v>
       </c>
-      <c r="E10" s="31">
-        <f>(DLS!E8+DLS!E9)/2</f>
+      <c r="E10" s="28">
+        <f>('DLS v2'!E8+'DLS v2'!E9)/2</f>
         <v>4.0199376493980896</v>
       </c>
-      <c r="F10" s="31">
-        <f>(DLS!F8+DLS!F9)/2</f>
+      <c r="F10" s="28">
+        <f>('DLS v2'!F8+'DLS v2'!F9)/2</f>
         <v>20.65</v>
       </c>
-      <c r="G10" s="31">
-        <f>(DLS!G8+DLS!G9)/2</f>
+      <c r="G10" s="28">
+        <f>('DLS v2'!G8+'DLS v2'!G9)/2</f>
         <v>2.3511244788025486E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
+      <c r="A11" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="28" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="30">
         <f>(B2*Population!C115*0.000001)*1000</f>
         <v>172.51581432</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="30">
         <f>C2*Population!C115*1000*0.000000001</f>
         <v>9.7535205528000031</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="30">
         <f>(D2*Population!C115*1000*0.000000001)</f>
         <v>304.08429528000011</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="30">
         <f>(E2*Population!C115*0.000001)*1000</f>
         <v>265.15076520000008</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="30">
         <f>F2*Population!C115*0.000277778</f>
         <v>494.3108592392208</v>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="30">
         <f>(G2*Population!D115*1000)*0.000001</f>
         <v>17.921343875225901</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="30">
         <f>(B3*Population!C115*0.000001)*1000</f>
         <v>147.67890720000005</v>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="30">
         <f>(C3*Population!C115*0.000001)</f>
         <v>9.4178866728000017</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="30">
         <f>(D3*Population!C115*0.000000001)*1000</f>
         <v>282.60372696000007</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="30">
         <f>(E3*Population!C115*0.000001)*1000</f>
         <v>246.35526792000005</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="30">
         <f>F3*Population!C115*0.000277778</f>
         <v>290.88292870615692</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="30">
         <f>(G3*Population!D115*1000)*0.000001</f>
         <v>12.954588297702438</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="31" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="33" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="30">
         <f>(B4*Population!C115*0.000001)*1000</f>
         <v>160.09736076000002</v>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="30">
         <f>(C4*Population!C115*0.000001)</f>
         <v>9.5857036128000015</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="30">
         <f>(D4*Population!C115*0.000000001)*1000</f>
         <v>293.34401112000006</v>
       </c>
-      <c r="E15" s="33">
+      <c r="E15" s="30">
         <f>(E4*Population!C115*0.000001)*1000</f>
         <v>255.75301656000005</v>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="30">
         <f>F4*Population!C115*0.000277778</f>
         <v>392.59689397268886</v>
       </c>
-      <c r="G15" s="33">
+      <c r="G15" s="30">
         <f>(G4*Population!D115*1000)*0.000001</f>
         <v>15.43796608646417</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="33" t="s">
+      <c r="E16" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="F16" s="33" t="s">
+      <c r="F16" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="30" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
+      <c r="A18" s="28" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="48" t="s">
@@ -3044,17 +3045,17 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="G21" t="s">
+      <c r="G21" s="28" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="G22" t="s">
+      <c r="G22" s="28" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="G23" t="s">
+      <c r="G23" s="28" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3063,7 +3064,247 @@
     <mergeCell ref="B18:E18"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F18" r:id="rId1" xr:uid="{F7B5DC7E-06B3-4D92-84C6-221AF8CD7354}"/>
+    <hyperlink ref="F18" r:id="rId1" xr:uid="{FE1DF694-6272-4B23-A77B-2E2C32319CE3}"/>
+    <hyperlink ref="B18" r:id="rId2" xr:uid="{690E7B6F-16A8-495D-9B9E-E651E414B818}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1104A7-2272-4986-AE6B-8EA45794950A}">
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="27.69140625" customWidth="1"/>
+    <col min="3" max="3" width="11.921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="22">
+        <v>2.57</v>
+      </c>
+      <c r="C2" s="22">
+        <v>3.95</v>
+      </c>
+      <c r="D2" s="22">
+        <f>D3*(D8/D9)</f>
+        <v>26.509803921568629</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="22">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C3" s="22">
+        <v>3.67</v>
+      </c>
+      <c r="D3" s="22">
+        <f>DLE!U5</f>
+        <v>15.600000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" s="22">
+        <f>(DLS!B2+DLS!B3)/2</f>
+        <v>2.3849999999999998</v>
+      </c>
+      <c r="C4" s="22">
+        <f>(DLS!C2+DLS!C3)/2</f>
+        <v>3.81</v>
+      </c>
+      <c r="D4" s="22">
+        <f>(DLS!D2+DLS!D3)/2</f>
+        <v>21.054901960784314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="26">
+        <v>3.9404604370967649</v>
+      </c>
+      <c r="C8" s="24">
+        <v>4.8</v>
+      </c>
+      <c r="D8">
+        <f>26</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="27">
+        <v>1.8456474232498501</v>
+      </c>
+      <c r="C9" s="25">
+        <v>3.239875298796179</v>
+      </c>
+      <c r="D9">
+        <f>15.3</f>
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10">
+        <f>(DLS!B8+DLS!B9)/2</f>
+        <v>2.8930539301733074</v>
+      </c>
+      <c r="C10" s="28">
+        <f>(DLS!C8+DLS!C9)/2</f>
+        <v>4.0199376493980896</v>
+      </c>
+      <c r="D10" s="28">
+        <f>(DLS!D8+DLS!D9)/2</f>
+        <v>20.65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="30">
+        <f>(B2*Population!C115*0.000001)*1000</f>
+        <v>172.51581432</v>
+      </c>
+      <c r="C13" s="30">
+        <f>(C2*Population!C115*0.000001)*1000</f>
+        <v>265.15076520000008</v>
+      </c>
+      <c r="D13" s="30">
+        <f>D2*Population!C115*0.000277778</f>
+        <v>494.3108592392208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" s="30">
+        <f>(B3*Population!C115*0.000001)*1000</f>
+        <v>147.67890720000005</v>
+      </c>
+      <c r="C14" s="30">
+        <f>(C3*Population!C115*0.000001)*1000</f>
+        <v>246.35526792000005</v>
+      </c>
+      <c r="D14" s="30">
+        <f>D3*Population!C115*0.000277778</f>
+        <v>290.88292870615692</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="B15" s="30">
+        <f>(B4*Population!C115*0.000001)*1000</f>
+        <v>160.09736076000002</v>
+      </c>
+      <c r="C15" s="30">
+        <f>(C4*Population!C115*0.000001)*1000</f>
+        <v>255.75301656000005</v>
+      </c>
+      <c r="D15" s="30">
+        <f>D4*Population!C115*0.000277778</f>
+        <v>392.59689397268886</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="49"/>
+      <c r="D18" s="21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B18:C18"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D18" r:id="rId1" xr:uid="{F7B5DC7E-06B3-4D92-84C6-221AF8CD7354}"/>
     <hyperlink ref="B18" r:id="rId2" xr:uid="{7753ABD6-E8C9-41B2-94EA-8111D4B50F91}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3071,12 +3312,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE59BEB1-58EA-414F-91E0-ADFFF27E94F9}">
   <dimension ref="A2:U6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.07421875" style="31"/>
+    <col min="1" max="1" width="11.07421875" style="28"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
@@ -3163,7 +3404,7 @@
       <c r="P3" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="Q3" s="39" t="s">
+      <c r="Q3" s="36" t="s">
         <v>159</v>
       </c>
       <c r="R3" s="50" t="s">
@@ -3191,7 +3432,7 @@
       <c r="N4" s="54"/>
       <c r="O4" s="51"/>
       <c r="P4" s="51"/>
-      <c r="Q4" s="39" t="s">
+      <c r="Q4" s="36" t="s">
         <v>160</v>
       </c>
       <c r="R4" s="50"/>
@@ -3200,73 +3441,73 @@
       <c r="U4" s="55"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="40">
+      <c r="B5" s="37">
         <v>2.7</v>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="38">
         <v>0.3</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="38">
         <v>0.2</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="39">
         <v>0.8</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="39">
         <v>0.7</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="39">
         <v>0</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="38">
         <v>0.2</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="38">
         <v>1.3</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="38">
         <v>0.2</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="39">
         <v>0.3</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="39">
         <v>0.3</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="38">
         <v>1.4</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="39">
         <v>0.4</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="38">
         <v>0</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="38">
         <v>0.1</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="38">
         <v>0.4</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="39">
         <v>2.2999999999999998</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="39">
         <v>0.7</v>
       </c>
-      <c r="T5" s="41">
+      <c r="T5" s="38">
         <v>3.3</v>
       </c>
-      <c r="U5" s="43">
+      <c r="U5" s="40">
         <f>SUM(B5:T5)</f>
         <v>15.600000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="28" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3303,7 +3544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95CE491-5889-4A7E-A6ED-A3FC6F8FA184}">
   <dimension ref="A1:I122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -3313,16 +3554,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="47" t="s">
         <v>191</v>
       </c>
     </row>
@@ -4887,11 +5128,11 @@
       <c r="B113" s="2">
         <v>100</v>
       </c>
-      <c r="C113" s="31">
+      <c r="C113" s="28">
         <f>C23*100/B23</f>
         <v>0.89627985204535521</v>
       </c>
-      <c r="D113" s="31">
+      <c r="D113" s="28">
         <f>D23*100/B23</f>
         <v>6.2079223823601231</v>
       </c>
@@ -5089,14 +5330,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8683F5-D89E-4384-A263-C6122D6DA873}">
   <dimension ref="A1:AK48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="11.84375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.69140625" customWidth="1"/>
-    <col min="9" max="9" width="10.69140625" style="31"/>
+    <col min="9" max="9" width="10.69140625" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.4">
@@ -6173,7 +6414,7 @@
         <v>24466165583.505955</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="31" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A37" s="13"/>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
@@ -6187,11 +6428,11 @@
         <f>B27</f>
         <v>17868.090856870793</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="28">
         <f t="shared" ref="G38:H38" si="0">C27</f>
         <v>50682.895358633301</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="28">
         <f t="shared" si="0"/>
         <v>47490.67459411014</v>
       </c>
@@ -6199,18 +6440,18 @@
         <v>175</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="31" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="E39" s="31" t="s">
+    <row r="39" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="E39" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="28">
         <v>1</v>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="28">
         <f>G38/F38</f>
         <v>2.8365031141054602</v>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="28">
         <f>H38/F38</f>
         <v>2.6578482824228877</v>
       </c>
@@ -6242,42 +6483,42 @@
         <f>SUM(H2:H36)/SUM(Population!D2:D36)</f>
         <v>43700.966271954145</v>
       </c>
-      <c r="J40" s="31"/>
-      <c r="K40" s="44" t="s">
+      <c r="J40" s="28"/>
+      <c r="K40" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="L40" s="44" t="s">
+      <c r="L40" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="M40" s="44" t="s">
+      <c r="M40" s="41" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="31" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.4">
       <c r="E41" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="28">
         <v>1</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="28">
         <f>G40/F40</f>
         <v>3.0296931289440945</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="28">
         <f>H40/F40</f>
         <v>2.7778101153314241</v>
       </c>
-      <c r="J41" s="31" t="s">
+      <c r="J41" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="K41" s="45">
+      <c r="K41" s="42">
         <v>55077.287499999999</v>
       </c>
-      <c r="L41" s="45">
+      <c r="L41" s="42">
         <v>23235.55</v>
       </c>
-      <c r="M41" s="46">
+      <c r="M41" s="43">
         <v>2.3703888007815599</v>
       </c>
     </row>
@@ -6303,16 +6544,16 @@
         <f>1-(H40-B42)/(B40-B42)</f>
         <v>0.14821255830696134</v>
       </c>
-      <c r="J42" s="31" t="s">
+      <c r="J42" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="K42" s="45">
+      <c r="K42" s="42">
         <v>53985.9</v>
       </c>
-      <c r="L42" s="45">
+      <c r="L42" s="42">
         <v>22052.862499999999</v>
       </c>
-      <c r="M42" s="46">
+      <c r="M42" s="43">
         <v>2.4480223372362699</v>
       </c>
     </row>
@@ -6333,16 +6574,16 @@
         <v>0.93086683696635297</v>
       </c>
       <c r="I43" s="10"/>
-      <c r="J43" s="31" t="s">
+      <c r="J43" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="K43" s="45">
+      <c r="K43" s="42">
         <v>52102.45</v>
       </c>
-      <c r="L43" s="45">
+      <c r="L43" s="42">
         <v>20638.025000000001</v>
       </c>
-      <c r="M43" s="46">
+      <c r="M43" s="43">
         <v>2.5245850802099499</v>
       </c>
     </row>
@@ -6362,16 +6603,16 @@
         <f>MAX(1-(D27-B42)/(B40-B42),0)</f>
         <v>5.9042950726820198E-2</v>
       </c>
-      <c r="J44" s="31" t="s">
+      <c r="J44" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="K44" s="45">
+      <c r="K44" s="42">
         <v>55263.5</v>
       </c>
-      <c r="L44" s="45">
+      <c r="L44" s="42">
         <v>21733.662499999999</v>
       </c>
-      <c r="M44" s="46">
+      <c r="M44" s="43">
         <v>2.5427605678518299</v>
       </c>
     </row>
@@ -6391,16 +6632,16 @@
         <f>(Population!D115*Capacité!H44)*100/(Population!B115*Capacité!F44)</f>
         <v>0.39547656087185179</v>
       </c>
-      <c r="J45" s="31" t="s">
+      <c r="J45" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="K45" s="45">
+      <c r="K45" s="42">
         <v>56918.724999999999</v>
       </c>
-      <c r="L45" s="45">
+      <c r="L45" s="42">
         <v>24625.825000000001</v>
       </c>
-      <c r="M45" s="46">
+      <c r="M45" s="43">
         <v>2.31134286871607</v>
       </c>
     </row>
@@ -6411,12 +6652,12 @@
       <c r="B46" t="s">
         <v>61</v>
       </c>
-      <c r="J46" s="31" t="s">
+      <c r="J46" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="K46" s="31"/>
-      <c r="L46" s="31"/>
-      <c r="M46" s="47">
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="44">
         <f>AVERAGE(M41:M45)</f>
         <v>2.4394199309591356</v>
       </c>
@@ -6449,7 +6690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC11EFA9-274E-476D-8BFE-D8769B6BF052}">
   <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -6458,82 +6699,82 @@
     <col min="2" max="2" width="11.61328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="31" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="31" t="s">
+    <row r="1" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="28" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="28" t="s">
         <v>116</v>
       </c>
       <c r="B2">
         <f>(Population!C115*DLS!B2)/(Population!B115*DLS!B8)</f>
         <v>5.0445947637680474E-3</v>
       </c>
-      <c r="C2" s="31">
+      <c r="C2" s="28" t="e">
+        <f>(Population!C115*DLS!#REF!)/(Population!B115*DLS!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D2" s="28" t="e">
+        <f>(Population!C115*DLS!#REF!)/(Population!B115*DLS!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E2" s="28">
         <f>(Population!C115*DLS!C2)/(Population!B115*DLS!C8)</f>
-        <v>5.470520430995939E-3</v>
-      </c>
-      <c r="D2" s="31">
+        <v>6.3649645790258835E-3</v>
+      </c>
+      <c r="F2" s="28">
         <f>(Population!C115*DLS!D2)/(Population!B115*DLS!D8)</f>
-        <v>1.1538546215222302E-2</v>
-      </c>
-      <c r="E2" s="31">
-        <f>(Population!C115*DLS!E2)/(Population!B115*DLS!E8)</f>
-        <v>6.3649645790258835E-3</v>
-      </c>
-      <c r="F2" s="31">
-        <f>(Population!C115*DLS!F2)/(Population!B115*DLS!F8)</f>
         <v>7.8863001187632689E-3</v>
       </c>
-      <c r="G2" s="31">
-        <f>(Population!C115*DLS!G2)/(Population!B115*DLS!G8)</f>
-        <v>1.1536019123611196E-2</v>
+      <c r="G2" s="28" t="e">
+        <f>(Population!C115*DLS!#REF!)/(Population!B115*DLS!#REF!)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="28">
         <f>(Population!C115*DLS!B3)/(Population!B115*DLS!B9)</f>
         <v>9.2196423260765513E-3</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="28" t="e">
+        <f>(Population!C115*DLS!#REF!)/(Population!B115*DLS!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D3" s="28" t="e">
+        <f>(Population!C115*DLS!#REF!)/(Population!B115*DLS!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E3" s="28">
         <f>(Population!C115*DLS!C3)/(Population!B115*DLS!C9)</f>
-        <v>5.4773348920140012E-3</v>
-      </c>
-      <c r="D3" s="31">
+        <v>8.7614886441971934E-3</v>
+      </c>
+      <c r="F3" s="28">
         <f>(Population!C115*DLS!D3)/(Population!B115*DLS!D9)</f>
-        <v>1.1583787785951202E-2</v>
-      </c>
-      <c r="E3" s="31">
-        <f>(Population!C115*DLS!E3)/(Population!B115*DLS!E9)</f>
-        <v>8.7614886441971934E-3</v>
-      </c>
-      <c r="F3" s="31">
-        <f>(Population!C115*DLS!F3)/(Population!B115*DLS!F9)</f>
         <v>7.8863001187632689E-3</v>
       </c>
-      <c r="G3" s="31">
-        <f>(Population!C115*DLS!G3)/(Population!B115*DLS!G9)</f>
-        <v>1.1583189226829783E-2</v>
+      <c r="G3" s="28" t="e">
+        <f>(Population!C115*DLS!#REF!)/(Population!B115*DLS!#REF!)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -6544,25 +6785,25 @@
         <f>(Population!C115*DLS!B4)/(Population!B115*DLS!B10)</f>
         <v>6.3763476382916566E-3</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="28" t="e">
+        <f>(Population!C115*DLS!#REF!)/(Population!B115*DLS!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D5" s="28" t="e">
+        <f>(Population!C115*DLS!#REF!)/(Population!B115*DLS!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E5" s="28">
         <f>(Population!C115*DLS!C4)/(Population!B115*DLS!C10)</f>
-        <v>5.4738658909632108E-3</v>
-      </c>
-      <c r="D5" s="31">
+        <v>7.3307058166893228E-3</v>
+      </c>
+      <c r="F5" s="28">
         <f>(Population!C115*DLS!D4)/(Population!B115*DLS!D10)</f>
-        <v>1.1560294581879071E-2</v>
-      </c>
-      <c r="E5" s="31">
-        <f>(Population!C115*DLS!E4)/(Population!B115*DLS!E10)</f>
-        <v>7.3307058166893228E-3</v>
-      </c>
-      <c r="F5" s="31">
-        <f>(Population!C115*DLS!F4)/(Population!B115*DLS!F10)</f>
         <v>7.8863001187632689E-3</v>
       </c>
-      <c r="G5" s="31">
-        <f>(Population!C115*DLS!G4)/(Population!B115*DLS!G10)</f>
-        <v>1.1555763383244126E-2</v>
+      <c r="G5" s="28" t="e">
+        <f>(Population!C115*DLS!#REF!)/(Population!B115*DLS!#REF!)</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
@@ -6577,7 +6818,7 @@
       <c r="A8" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="28">
         <v>3494.0786014333898</v>
       </c>
       <c r="E8" t="s">
@@ -6599,7 +6840,7 @@
       <c r="A9" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="28">
         <v>201.308612543306</v>
       </c>
       <c r="E9" t="s">
@@ -6620,7 +6861,7 @@
       <c r="D10">
         <v>520</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="28" t="s">
         <v>125</v>
       </c>
     </row>
@@ -6631,7 +6872,7 @@
       <c r="D11">
         <v>40</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="28" t="s">
         <v>125</v>
       </c>
     </row>
@@ -6642,7 +6883,7 @@
       <c r="D12">
         <v>40</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="28" t="s">
         <v>125</v>
       </c>
     </row>
@@ -6662,7 +6903,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE07EBE8-6449-4730-9E28-CE2F7AF6313A}">
   <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
@@ -6693,25 +6934,25 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A6" s="38"/>
+      <c r="A6" s="35"/>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A7" s="38">
+      <c r="A7" s="35">
         <f>((Population!C116/100)*A2)*1000</f>
         <v>17.76876871873117</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A8" s="38">
+      <c r="A8" s="35">
         <f>((Population!C116/100)*A3)*1000</f>
         <v>110.27088822506695</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A9" s="38"/>
+      <c r="A9" s="35"/>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="35" t="s">
         <v>81</v>
       </c>
     </row>
@@ -6744,7 +6985,7 @@
       </c>
     </row>
     <row r="17" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="33" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6773,7 +7014,7 @@
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A25" s="31">
+      <c r="A25" s="28">
         <f>A3*Besoins!B5*1000</f>
         <v>90.906037275644564</v>
       </c>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C827263-2CED-4E99-B68C-80376596CF9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA0CC84-27DB-4816-B6D3-8CB0BF16E22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="9" r:id="rId1"/>
@@ -1067,23 +1067,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
@@ -1427,7 +1427,7 @@
         <v>5.2693243243243248</v>
       </c>
       <c r="C2" s="28">
-        <v>2800</v>
+        <v>1100</v>
       </c>
       <c r="D2" s="28">
         <v>12.6</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="C8" s="35">
         <f>(Population!C116/100)*C2</f>
-        <v>21.656993403065282</v>
+        <v>8.5081045512042177</v>
       </c>
       <c r="D8" s="35">
         <f>((Population!C116/100)*D2)*1000</f>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C16" s="22">
         <f>C2*1000000000/(Population!B115*1000)</f>
-        <v>322.62823709968256</v>
+        <v>126.74680743201814</v>
       </c>
       <c r="D16" s="22">
         <f>D2*1000000000000/(Population!B115*1000)</f>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C21" s="28">
         <f>(Capacité!G43/100)*C2</f>
-        <v>1.4765660113611818</v>
+        <v>0.58007950446332146</v>
       </c>
       <c r="D21" s="28">
         <f>(Capacité!G43/100)*D2</f>
@@ -3321,44 +3321,44 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="53" t="s">
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="55" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="52" t="s">
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53" t="s">
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="L2" s="53"/>
+      <c r="L2" s="55"/>
       <c r="M2" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="O2" s="52" t="s">
+      <c r="O2" s="54" t="s">
         <v>144</v>
       </c>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="53" t="s">
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="S2" s="53"/>
+      <c r="S2" s="55"/>
       <c r="T2" s="57" t="s">
         <v>164</v>
       </c>
-      <c r="U2" s="55" t="s">
+      <c r="U2" s="53" t="s">
         <v>165</v>
       </c>
     </row>
@@ -3372,13 +3372,13 @@
       <c r="D3" s="51" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="52" t="s">
         <v>151</v>
       </c>
       <c r="H3" s="51" t="s">
@@ -3390,14 +3390,14 @@
       <c r="J3" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="K3" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="L3" s="50" t="s">
+      <c r="L3" s="52" t="s">
         <v>156</v>
       </c>
       <c r="M3" s="56"/>
-      <c r="N3" s="54"/>
+      <c r="N3" s="50"/>
       <c r="O3" s="51" t="s">
         <v>157</v>
       </c>
@@ -3407,38 +3407,38 @@
       <c r="Q3" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="R3" s="50" t="s">
+      <c r="R3" s="52" t="s">
         <v>161</v>
       </c>
-      <c r="S3" s="50" t="s">
+      <c r="S3" s="52" t="s">
         <v>162</v>
       </c>
       <c r="T3" s="57"/>
-      <c r="U3" s="55"/>
+      <c r="U3" s="53"/>
     </row>
     <row r="4" spans="1:21" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
       <c r="D4" s="51"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
       <c r="H4" s="51"/>
       <c r="I4" s="51"/>
       <c r="J4" s="51"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
       <c r="M4" s="56"/>
-      <c r="N4" s="54"/>
+      <c r="N4" s="50"/>
       <c r="O4" s="51"/>
       <c r="P4" s="51"/>
       <c r="Q4" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
       <c r="T4" s="57"/>
-      <c r="U4" s="55"/>
+      <c r="U4" s="53"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A5" s="28" t="s">
@@ -3513,6 +3513,17 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
@@ -3527,17 +3538,6 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T2:T4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA0CC84-27DB-4816-B6D3-8CB0BF16E22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7737401D-8D08-4C39-A7E4-6571C26341A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="9017" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="9" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="209">
   <si>
     <t>N</t>
   </si>
@@ -239,18 +239,12 @@
     <t>UE</t>
   </si>
   <si>
-    <t>Mean 1990-2024</t>
-  </si>
-  <si>
     <t>Borne Max</t>
   </si>
   <si>
     <t>Borne Min</t>
   </si>
   <si>
-    <t>Source bornes</t>
-  </si>
-  <si>
     <t>https://data.europa.eu/doi/10.2800/890673</t>
   </si>
   <si>
@@ -261,9 +255,6 @@
   </si>
   <si>
     <t>Part 2019</t>
-  </si>
-  <si>
-    <t>Moyenne 2019-2051</t>
   </si>
   <si>
     <t>Moyenne 2019-2100</t>
@@ -733,6 +724,24 @@
   </si>
   <si>
     <t>Final energy use</t>
+  </si>
+  <si>
+    <t>Moyenne 2019-2050</t>
+  </si>
+  <si>
+    <t>Moyenne 1990-2024</t>
+  </si>
+  <si>
+    <t>GDP PPP</t>
+  </si>
+  <si>
+    <t>Bornes</t>
+  </si>
+  <si>
+    <t>Projections SSP</t>
+  </si>
+  <si>
+    <t>https://ssp.apps.ece.iiasa.ac.at/basic-drivers?type=line-chart&amp;variables=299&amp;regions=251,76&amp;runs=7,8,9,10,11,12&amp;dataHash=1f0c69e4b47fc1&amp;open=true</t>
   </si>
 </sst>
 </file>
@@ -1067,23 +1076,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
@@ -1379,46 +1388,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C32444-97C3-4A7C-A91C-82059EB528AD}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.15234375" style="28" customWidth="1"/>
-    <col min="2" max="3" width="9.23046875" style="28"/>
-    <col min="4" max="4" width="14.07421875" style="28" customWidth="1"/>
-    <col min="5" max="8" width="9.23046875" style="28"/>
-    <col min="9" max="10" width="11.84375" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.23046875" style="28"/>
+    <col min="1" max="1" width="21.1328125" style="28" customWidth="1"/>
+    <col min="2" max="3" width="9.19921875" style="28"/>
+    <col min="4" max="4" width="14.06640625" style="28" customWidth="1"/>
+    <col min="5" max="8" width="9.19921875" style="28"/>
+    <col min="9" max="10" width="11.86328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.19921875" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B1" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="C1" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="D1" s="17" t="s">
+      <c r="G1" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="I1" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="F1" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="19" t="s">
         <v>15</v>
       </c>
@@ -1456,9 +1465,9 @@
         <v>2.2845755630300952</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B3" s="28">
         <f>(1.33*1055+163.83)/74</f>
@@ -1484,15 +1493,15 @@
         <v>0.11293126135771475</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="16" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>8</v>
@@ -1513,7 +1522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="19"/>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -1524,14 +1533,14 @@
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="19"/>
       <c r="K6" s="28">
         <f>269/100 -1</f>
         <v>1.69</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="34" t="s">
         <v>14</v>
       </c>
@@ -1544,9 +1553,9 @@
       <c r="H7" s="35"/>
       <c r="I7" s="35"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="34" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B8" s="35">
         <f>((Population!C116/100)*B2)*1000</f>
@@ -1581,9 +1590,9 @@
         <v>28.803801226076825</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="34" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B9" s="35">
         <f>((Population!C116/100)*B3)*1000</f>
@@ -1618,7 +1627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="34"/>
       <c r="B10" s="35"/>
       <c r="C10" s="35"/>
@@ -1629,38 +1638,38 @@
       <c r="H10" s="35"/>
       <c r="I10" s="35"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="34" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E11" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="F11" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="35" t="s">
-        <v>90</v>
-      </c>
       <c r="H11" s="35" t="s">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="I11" s="35" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B12" s="29">
         <v>1</v>
@@ -1685,21 +1694,21 @@
         <v>1000</v>
       </c>
       <c r="I12" s="29">
-        <v>10000000000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>9</v>
@@ -1708,16 +1717,16 @@
         <v>9</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -1728,9 +1737,9 @@
       <c r="H14" s="20"/>
       <c r="I14" s="20"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="31" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B15" s="22"/>
       <c r="C15" s="22"/>
@@ -1741,9 +1750,9 @@
       <c r="H15" s="22"/>
       <c r="I15" s="22"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="31" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B16" s="22">
         <f>B2*1000000000/(Population!B115*1000)</f>
@@ -1778,9 +1787,9 @@
         <v>0.42909555534257776</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="31" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B17" s="22">
         <f>B3*1000000000/(Population!B115*1000)</f>
@@ -1815,38 +1824,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A18" s="32" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H18" s="33" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I18" s="33" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="19" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B19" s="45">
         <v>9.9999999999999995E-7</v>
@@ -1870,10 +1879,10 @@
         <v>1E-3</v>
       </c>
       <c r="I19" s="45">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="19"/>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
@@ -1884,7 +1893,7 @@
       <c r="H20" s="20"/>
       <c r="I20" s="20"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="19" t="s">
         <v>16</v>
       </c>
@@ -1921,9 +1930,9 @@
         <v>1.963832795110372</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B22" s="28">
         <f>(Capacité!G43/100)*B3</f>
@@ -1958,18 +1967,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" s="19"/>
     </row>
-    <row r="24" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A24" s="19" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="15"/>
     </row>
-    <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A25" s="16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -1980,9 +1989,9 @@
       <c r="H25" s="15"/>
       <c r="I25" s="15"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B26" s="28">
         <f>B2*Besoins!B5*1000</f>
@@ -2005,9 +2014,9 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" s="19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B27" s="28">
         <f>B3*Besoins!B5*1000</f>
@@ -2030,7 +2039,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" s="19"/>
     </row>
   </sheetData>
@@ -2041,25 +2050,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.15234375" customWidth="1"/>
-    <col min="4" max="4" width="14.07421875" customWidth="1"/>
-    <col min="9" max="10" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1328125" customWidth="1"/>
+    <col min="4" max="4" width="14.06640625" customWidth="1"/>
+    <col min="9" max="10" width="11.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E1" s="17" t="s">
         <v>0</v>
@@ -2068,16 +2077,16 @@
         <v>1</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="19" t="s">
         <v>15</v>
       </c>
@@ -2115,9 +2124,9 @@
         <v>2.2845755630300952</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B3">
         <f>(1.33*1055+163.83)/74</f>
@@ -2149,7 +2158,7 @@
         <v>0.11293126135771475</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="16" t="s">
         <v>5</v>
       </c>
@@ -2157,7 +2166,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>8</v>
@@ -2178,14 +2187,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="19"/>
       <c r="K5">
         <f>269/100 -1</f>
         <v>1.69</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="34" t="s">
         <v>14</v>
       </c>
@@ -2198,9 +2207,9 @@
       <c r="H6" s="35"/>
       <c r="I6" s="35"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="34" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B7" s="35">
         <f>((Population!C116/100)*B2)*1000</f>
@@ -2235,9 +2244,9 @@
         <v>28.803801226076825</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="34" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B8" s="35">
         <f>((Population!C116/100)*B3)*1000</f>
@@ -2273,7 +2282,7 @@
       </c>
       <c r="J8" s="28"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="34"/>
       <c r="B9" s="35"/>
       <c r="C9" s="35"/>
@@ -2284,38 +2293,38 @@
       <c r="H9" s="35"/>
       <c r="I9" s="35"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="34" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E10" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="35" t="s">
-        <v>90</v>
-      </c>
       <c r="H10" s="35" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I10" s="35" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B11" s="14">
         <v>1</v>
@@ -2343,36 +2352,36 @@
         <v>10000000000</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B12" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>84</v>
-      </c>
       <c r="E12" s="15" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -2383,9 +2392,9 @@
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="31" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -2396,9 +2405,9 @@
       <c r="H14" s="22"/>
       <c r="I14" s="22"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="31" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B15" s="22">
         <f>B2*1000000000/(Population!B115*1000)</f>
@@ -2433,9 +2442,9 @@
         <v>0.42909555534257776</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="31" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B16" s="22">
         <f>B3*1000000000/(Population!B115*1000)</f>
@@ -2470,36 +2479,36 @@
         <v>3.0036688873980446</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" s="32" t="s">
         <v>5</v>
       </c>
       <c r="B17" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>97</v>
-      </c>
       <c r="E17" s="33" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G17" s="33" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="H17" s="33" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I17" s="33" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="19"/>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -2510,7 +2519,7 @@
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="19" t="s">
         <v>16</v>
       </c>
@@ -2547,9 +2556,9 @@
         <v>1.963832795110372</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B20">
         <f>(Capacité!G43/100)*B3</f>
@@ -2584,18 +2593,18 @@
         <v>13.746829565772604</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="19"/>
     </row>
-    <row r="22" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="19" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="15"/>
     </row>
-    <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -2606,9 +2615,9 @@
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B24" s="28">
         <f>B2*Besoins!B5*1000</f>
@@ -2634,9 +2643,9 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" s="19" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B25" s="28">
         <f>B3*Besoins!B5*1000</f>
@@ -2662,7 +2671,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="19"/>
     </row>
   </sheetData>
@@ -2673,20 +2682,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0A75E4-DA25-4A08-8974-1A31A91FD529}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.69140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="11.07421875" style="28"/>
-    <col min="3" max="4" width="12.3828125" style="28" customWidth="1"/>
-    <col min="5" max="5" width="11.921875" style="28" customWidth="1"/>
-    <col min="6" max="6" width="11.07421875" style="28"/>
-    <col min="7" max="7" width="14.84375" style="28" customWidth="1"/>
-    <col min="8" max="16384" width="11.07421875" style="28"/>
+    <col min="1" max="1" width="27.6640625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="11.06640625" style="28"/>
+    <col min="3" max="4" width="12.3984375" style="28" customWidth="1"/>
+    <col min="5" max="5" width="11.9296875" style="28" customWidth="1"/>
+    <col min="6" max="6" width="11.06640625" style="28"/>
+    <col min="7" max="7" width="14.86328125" style="28" customWidth="1"/>
+    <col min="8" max="16384" width="11.06640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>2</v>
@@ -2695,7 +2704,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E1" s="23" t="s">
         <v>11</v>
@@ -2707,9 +2716,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B2" s="22">
         <v>2.57</v>
@@ -2733,9 +2742,9 @@
         <v>4.0776939000000005E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="22" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B3" s="22">
         <v>2.2000000000000002</v>
@@ -2759,9 +2768,9 @@
         <v>2.9475940000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="22" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B4" s="22">
         <f>('DLS v2'!B2+'DLS v2'!B3)/2</f>
@@ -2788,37 +2797,37 @@
         <v>3.5126439500000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="22" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="28" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="28" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B8" s="28">
         <v>3.9404604370967649</v>
@@ -2842,9 +2851,9 @@
         <v>2.7340017428936065E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="28" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B9" s="28">
         <v>1.8456474232498501</v>
@@ -2868,9 +2877,9 @@
         <v>1.9682472147114907E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="28" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B10" s="28">
         <f>('DLS v2'!B8+'DLS v2'!B9)/2</f>
@@ -2897,32 +2906,32 @@
         <v>2.3511244788025486E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="28" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="30" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B13" s="30">
         <f>(B2*Population!C115*0.000001)*1000</f>
@@ -2949,9 +2958,9 @@
         <v>17.921343875225901</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="30" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B14" s="30">
         <f>(B3*Population!C115*0.000001)*1000</f>
@@ -2978,9 +2987,9 @@
         <v>12.954588297702438</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="30" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B15" s="30">
         <f>(B4*Population!C115*0.000001)*1000</f>
@@ -3007,56 +3016,56 @@
         <v>15.43796608646417</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="30" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G16" s="30" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="28" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C18" s="49"/>
       <c r="D18" s="49"/>
       <c r="E18" s="49"/>
       <c r="F18" s="21" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G21" s="28" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G22" s="28" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G23" s="28" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3075,29 +3084,29 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1104A7-2272-4986-AE6B-8EA45794950A}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.69140625" customWidth="1"/>
-    <col min="3" max="3" width="11.921875" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C1" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="23" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B2" s="22">
         <v>2.57</v>
@@ -3110,9 +3119,9 @@
         <v>26.509803921568629</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="22" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B3" s="22">
         <v>2.2000000000000002</v>
@@ -3125,9 +3134,9 @@
         <v>15.600000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="22" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B4" s="22">
         <f>(DLS!B2+DLS!B3)/2</f>
@@ -3142,28 +3151,28 @@
         <v>21.054901960784314</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="22" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B8" s="26">
         <v>3.9404604370967649</v>
@@ -3176,9 +3185,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B9" s="27">
         <v>1.8456474232498501</v>
@@ -3191,9 +3200,9 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="28" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B10">
         <f>(DLS!B8+DLS!B9)/2</f>
@@ -3208,23 +3217,23 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="30" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B13" s="30">
         <f>(B2*Population!C115*0.000001)*1000</f>
@@ -3239,9 +3248,9 @@
         <v>494.3108592392208</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="30" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B14" s="30">
         <f>(B3*Population!C115*0.000001)*1000</f>
@@ -3256,9 +3265,9 @@
         <v>290.88292870615692</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="30" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B15" s="30">
         <f>(B4*Population!C115*0.000001)*1000</f>
@@ -3273,30 +3282,30 @@
         <v>392.59689397268886</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="30" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C18" s="49"/>
       <c r="D18" s="21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3315,134 +3324,134 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE59BEB1-58EA-414F-91E0-ADFFF27E94F9}">
   <dimension ref="A2:U6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.07421875" style="28"/>
+    <col min="1" max="1" width="11.06640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" ht="16.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="55" t="s">
+    <row r="2" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="L2" s="53"/>
+      <c r="M2" s="56" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="54" t="s">
+      <c r="N2" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="55" t="s">
+      <c r="O2" s="52" t="s">
         <v>141</v>
       </c>
-      <c r="L2" s="55"/>
-      <c r="M2" s="56" t="s">
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="53" t="s">
         <v>142</v>
       </c>
-      <c r="N2" s="50" t="s">
+      <c r="S2" s="53"/>
+      <c r="T2" s="57" t="s">
+        <v>161</v>
+      </c>
+      <c r="U2" s="55" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="17.649999999999999" x14ac:dyDescent="0.45">
+      <c r="B3" s="51" t="s">
         <v>143</v>
       </c>
-      <c r="O2" s="54" t="s">
+      <c r="C3" s="51" t="s">
         <v>144</v>
       </c>
-      <c r="P2" s="54"/>
-      <c r="Q2" s="54"/>
-      <c r="R2" s="55" t="s">
+      <c r="D3" s="51" t="s">
         <v>145</v>
       </c>
-      <c r="S2" s="55"/>
-      <c r="T2" s="57" t="s">
-        <v>164</v>
-      </c>
-      <c r="U2" s="53" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="17.149999999999999" x14ac:dyDescent="0.4">
-      <c r="B3" s="51" t="s">
+      <c r="E3" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="F3" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="G3" s="50" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="H3" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="I3" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="G3" s="52" t="s">
+      <c r="J3" s="51" t="s">
         <v>151</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="K3" s="50" t="s">
         <v>152</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="L3" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="M3" s="56"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="K3" s="52" t="s">
+      <c r="P3" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="L3" s="52" t="s">
+      <c r="Q3" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="M3" s="56"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="P3" s="51" t="s">
+      <c r="R3" s="50" t="s">
         <v>158</v>
       </c>
-      <c r="Q3" s="36" t="s">
+      <c r="S3" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="R3" s="52" t="s">
-        <v>161</v>
-      </c>
-      <c r="S3" s="52" t="s">
-        <v>162</v>
-      </c>
       <c r="T3" s="57"/>
-      <c r="U3" s="53"/>
-    </row>
-    <row r="4" spans="1:21" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="U3" s="55"/>
+    </row>
+    <row r="4" spans="1:21" ht="38" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
       <c r="D4" s="51"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
       <c r="H4" s="51"/>
       <c r="I4" s="51"/>
       <c r="J4" s="51"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
       <c r="M4" s="56"/>
-      <c r="N4" s="50"/>
+      <c r="N4" s="54"/>
       <c r="O4" s="51"/>
       <c r="P4" s="51"/>
       <c r="Q4" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="57"/>
+      <c r="U4" s="55"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A5" s="28" t="s">
         <v>160</v>
-      </c>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="57"/>
-      <c r="U4" s="53"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A5" s="28" t="s">
-        <v>163</v>
       </c>
       <c r="B5" s="37">
         <v>2.7</v>
@@ -3506,24 +3515,13 @@
         <v>15.600000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A6" s="28" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
@@ -3538,6 +3536,17 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T2:T4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -3546,28 +3555,28 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95CE491-5889-4A7E-A6ED-A3FC6F8FA184}">
-  <dimension ref="A1:I122"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:H127"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.3828125" customWidth="1"/>
-    <col min="2" max="2" width="12.84375" customWidth="1"/>
+    <col min="1" max="1" width="12.3984375" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="46" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="47" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C1" s="47" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D1" s="47" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -3581,7 +3590,7 @@
         <v>419997.47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -3595,7 +3604,7 @@
         <v>421419.174</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -3609,7 +3618,7 @@
         <v>422863.59999999992</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -3623,7 +3632,7 @@
         <v>424104.70499999996</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -3637,7 +3646,7 @@
         <v>425188.98800000019</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -3651,7 +3660,7 @@
         <v>425847.82800000004</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -3665,7 +3674,7 @@
         <v>426181.87299999996</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -3679,7 +3688,7 @@
         <v>426651.66799999989</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -3693,7 +3702,7 @@
         <v>426655.42999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -3707,7 +3716,7 @@
         <v>426830.63099999999</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -3721,7 +3730,7 @@
         <v>427627.31800000009</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -3735,7 +3744,7 @@
         <v>428578.28599999996</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -3749,7 +3758,7 @@
         <v>429890.46400000004</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -3763,7 +3772,7 @@
         <v>431461.80999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -3777,7 +3786,7 @@
         <v>433058.58899999998</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -3791,7 +3800,7 @@
         <v>434557.12100000004</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -3805,7 +3814,7 @@
         <v>435683.11500000011</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -3819,7 +3828,7 @@
         <v>436994.47300000006</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -3833,7 +3842,7 @@
         <v>438548.18900000007</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -3847,7 +3856,7 @@
         <v>439690.78899999993</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -3861,7 +3870,7 @@
         <v>440608.95100000006</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -3875,7 +3884,7 @@
         <v>441440.62800000008</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -3889,7 +3898,7 @@
         <v>441999.21399999998</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -3903,7 +3912,7 @@
         <v>442399.391</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -3917,7 +3926,7 @@
         <v>442964.72000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -3931,7 +3940,7 @@
         <v>443910.90800000017</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -3945,7 +3954,7 @@
         <v>444911.48800000001</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -3959,7 +3968,7 @@
         <v>445696.74599999998</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -3973,7 +3982,7 @@
         <v>446503.6480000001</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -3987,7 +3996,7 @@
         <v>447369.19099999999</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -4001,7 +4010,7 @@
         <v>447777.53599999996</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -4015,7 +4024,7 @@
         <v>447705.902</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -4029,7 +4038,7 @@
         <v>449113.45499999996</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -4043,7 +4052,7 @@
         <v>450657.52199999994</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -4057,7 +4066,7 @@
         <v>450259.53600000002</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>2025</v>
       </c>
@@ -4071,7 +4080,7 @@
         <v>448992.58499999996</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>2026</v>
       </c>
@@ -4085,7 +4094,7 @@
         <v>447890.473</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>2027</v>
       </c>
@@ -4099,7 +4108,7 @@
         <v>447205.74899999995</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>2028</v>
       </c>
@@ -4113,7 +4122,7 @@
         <v>446459.31699999998</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>2029</v>
       </c>
@@ -4127,7 +4136,7 @@
         <v>445651.23500000004</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>2030</v>
       </c>
@@ -4141,7 +4150,7 @@
         <v>444782.38100000005</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>2031</v>
       </c>
@@ -4155,7 +4164,7 @@
         <v>443853.3349999999</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>2032</v>
       </c>
@@ -4169,7 +4178,7 @@
         <v>442896.55800000002</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>2033</v>
       </c>
@@ -4183,7 +4192,7 @@
         <v>441929.64600000007</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>2034</v>
       </c>
@@ -4197,7 +4206,7 @@
         <v>440942.37400000007</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <v>2035</v>
       </c>
@@ -4211,7 +4220,7 @@
         <v>439928.23599999998</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
         <v>2036</v>
       </c>
@@ -4225,7 +4234,7 @@
         <v>438876.35599999991</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="1">
         <v>2037</v>
       </c>
@@ -4239,7 +4248,7 @@
         <v>437800.28700000013</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
         <v>2038</v>
       </c>
@@ -4253,7 +4262,7 @@
         <v>436704.79599999997</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="1">
         <v>2039</v>
       </c>
@@ -4267,7 +4276,7 @@
         <v>435575.79399999999</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="1">
         <v>2040</v>
       </c>
@@ -4281,7 +4290,7 @@
         <v>434422.40100000007</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
         <v>2041</v>
       </c>
@@ -4295,7 +4304,7 @@
         <v>433267.647</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="1">
         <v>2042</v>
       </c>
@@ -4309,7 +4318,7 @@
         <v>432096.70899999997</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="1">
         <v>2043</v>
       </c>
@@ -4323,7 +4332,7 @@
         <v>430874.26299999998</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
         <v>2044</v>
       </c>
@@ -4337,7 +4346,7 @@
         <v>429598.62099999987</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="1">
         <v>2045</v>
       </c>
@@ -4351,7 +4360,7 @@
         <v>428280.46499999997</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="1">
         <v>2046</v>
       </c>
@@ -4365,7 +4374,7 @@
         <v>426921.04200000002</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="1">
         <v>2047</v>
       </c>
@@ -4379,7 +4388,7 @@
         <v>425511.16099999996</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="1">
         <v>2048</v>
       </c>
@@ -4393,7 +4402,7 @@
         <v>424046.07800000015</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="1">
         <v>2049</v>
       </c>
@@ -4407,7 +4416,7 @@
         <v>422524.55599999998</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
         <v>2050</v>
       </c>
@@ -4421,7 +4430,7 @@
         <v>420955.34100000001</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="1">
         <v>2051</v>
       </c>
@@ -4435,7 +4444,7 @@
         <v>419346.89500000008</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="1">
         <v>2052</v>
       </c>
@@ -4449,7 +4458,7 @@
         <v>417691.14999999997</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="1">
         <v>2053</v>
       </c>
@@ -4463,7 +4472,7 @@
         <v>415966.71600000001</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="1">
         <v>2054</v>
       </c>
@@ -4477,7 +4486,7 @@
         <v>414174.85799999995</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="1">
         <v>2055</v>
       </c>
@@ -4491,7 +4500,7 @@
         <v>412334.533</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
         <v>2056</v>
       </c>
@@ -4505,7 +4514,7 @@
         <v>410448.42000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="1">
         <v>2057</v>
       </c>
@@ -4519,7 +4528,7 @@
         <v>408533.27399999992</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="1">
         <v>2058</v>
       </c>
@@ -4533,7 +4542,7 @@
         <v>406603.29399999999</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
         <v>2059</v>
       </c>
@@ -4547,7 +4556,7 @@
         <v>404661.71100000007</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="1">
         <v>2060</v>
       </c>
@@ -4561,7 +4570,7 @@
         <v>402712.63299999991</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="1">
         <v>2061</v>
       </c>
@@ -4575,7 +4584,7 @@
         <v>400766.93200000015</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
         <v>2062</v>
       </c>
@@ -4589,7 +4598,7 @@
         <v>398823.46799999999</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="1">
         <v>2063</v>
       </c>
@@ -4603,7 +4612,7 @@
         <v>396899.60199999996</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="1">
         <v>2064</v>
       </c>
@@ -4617,7 +4626,7 @@
         <v>395004.61700000003</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="1">
         <v>2065</v>
       </c>
@@ -4631,7 +4640,7 @@
         <v>393131.79000000004</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="1">
         <v>2066</v>
       </c>
@@ -4645,7 +4654,7 @@
         <v>391291.73300000001</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="1">
         <v>2067</v>
       </c>
@@ -4659,7 +4668,7 @@
         <v>389489.04200000002</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="1">
         <v>2068</v>
       </c>
@@ -4673,7 +4682,7 @@
         <v>387721.924</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="1">
         <v>2069</v>
       </c>
@@ -4687,7 +4696,7 @@
         <v>385994.04200000007</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="1">
         <v>2070</v>
       </c>
@@ -4701,7 +4710,7 @@
         <v>384310.26799999998</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="1">
         <v>2071</v>
       </c>
@@ -4715,7 +4724,7 @@
         <v>382670.826</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="1">
         <v>2072</v>
       </c>
@@ -4729,7 +4738,7 @@
         <v>381068.141</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="1">
         <v>2073</v>
       </c>
@@ -4743,7 +4752,7 @@
         <v>379495.90099999995</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="1">
         <v>2074</v>
       </c>
@@ -4757,7 +4766,7 @@
         <v>377958.35600000003</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="1">
         <v>2075</v>
       </c>
@@ -4771,7 +4780,7 @@
         <v>376480.08500000008</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="1">
         <v>2076</v>
       </c>
@@ -4785,7 +4794,7 @@
         <v>375047.78200000006</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="1">
         <v>2077</v>
       </c>
@@ -4799,7 +4808,7 @@
         <v>373634.73</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="1">
         <v>2078</v>
       </c>
@@ -4813,7 +4822,7 @@
         <v>372260.67599999998</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="1">
         <v>2079</v>
       </c>
@@ -4827,7 +4836,7 @@
         <v>370924.19000000006</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="1">
         <v>2080</v>
       </c>
@@ -4841,7 +4850,7 @@
         <v>369621.90600000002</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="1">
         <v>2081</v>
       </c>
@@ -4855,7 +4864,7 @@
         <v>368361.90900000004</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="1">
         <v>2082</v>
       </c>
@@ -4869,7 +4878,7 @@
         <v>367136.15699999989</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="1">
         <v>2083</v>
       </c>
@@ -4883,7 +4892,7 @@
         <v>365939.98800000007</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="1">
         <v>2084</v>
       </c>
@@ -4897,7 +4906,7 @@
         <v>364768.47600000014</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" s="1">
         <v>2085</v>
       </c>
@@ -4911,7 +4920,7 @@
         <v>363612.08199999999</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" s="1">
         <v>2086</v>
       </c>
@@ -4925,7 +4934,7 @@
         <v>362474.72799999989</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" s="1">
         <v>2087</v>
       </c>
@@ -4939,7 +4948,7 @@
         <v>361363.54499999998</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" s="1">
         <v>2088</v>
       </c>
@@ -4953,7 +4962,7 @@
         <v>360281.40500000003</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" s="1">
         <v>2089</v>
       </c>
@@ -4967,7 +4976,7 @@
         <v>359214.11100000003</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" s="1">
         <v>2090</v>
       </c>
@@ -4981,7 +4990,7 @@
         <v>358149.47100000002</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A103" s="1">
         <v>2091</v>
       </c>
@@ -4995,7 +5004,7 @@
         <v>357104.93199999997</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A104" s="1">
         <v>2092</v>
       </c>
@@ -5009,7 +5018,7 @@
         <v>356085.554</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" s="1">
         <v>2093</v>
       </c>
@@ -5023,7 +5032,7 @@
         <v>355083.0670000001</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A106" s="1">
         <v>2094</v>
       </c>
@@ -5037,7 +5046,7 @@
         <v>354087.00400000002</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A107" s="1">
         <v>2095</v>
       </c>
@@ -5051,7 +5060,7 @@
         <v>353078.46800000005</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A108" s="1">
         <v>2096</v>
       </c>
@@ -5065,7 +5074,7 @@
         <v>352052.02500000008</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" s="1">
         <v>2097</v>
       </c>
@@ -5079,7 +5088,7 @@
         <v>351009.62299999996</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" s="1">
         <v>2098</v>
       </c>
@@ -5093,7 +5102,7 @@
         <v>349970.60700000002</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A111" s="1">
         <v>2099</v>
       </c>
@@ -5107,7 +5116,7 @@
         <v>348929.72599999985</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A112" s="1">
         <v>2100</v>
       </c>
@@ -5121,9 +5130,9 @@
         <v>347864.81900000002</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B113" s="2">
         <v>100</v>
@@ -5137,9 +5146,9 @@
         <v>6.2079223823601231</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B114">
         <f>B27*100/B27</f>
@@ -5153,25 +5162,10 @@
         <f>D27*100/B27</f>
         <v>5.9421911649996391</v>
       </c>
-      <c r="F114" t="s">
-        <v>71</v>
-      </c>
-      <c r="G114">
-        <f>B31*100/B31</f>
-        <v>100</v>
-      </c>
-      <c r="H114">
-        <f>C31*100/B31</f>
-        <v>0.8414670033061149</v>
-      </c>
-      <c r="I114">
-        <f>D31*100/B31</f>
-        <v>5.7272099641387726</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="29.15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="115" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A115" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B115" s="9">
         <f>AVERAGE(B27:B62)</f>
@@ -5185,23 +5179,8 @@
         <f>AVERAGE(D27:D62)</f>
         <v>439497.03716666671</v>
       </c>
-      <c r="F115" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G115" s="4">
-        <f>AVERAGE(B31:B63)</f>
-        <v>8840410.0070303045</v>
-      </c>
-      <c r="H115" s="4">
-        <f t="shared" ref="H115:I115" si="0">AVERAGE(C31:C63)</f>
-        <v>67392.626666666692</v>
-      </c>
-      <c r="I115" s="4">
-        <f t="shared" si="0"/>
-        <v>438188.4073636363</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" s="10" t="s">
         <v>21</v>
       </c>
@@ -5217,23 +5196,8 @@
         <f>D115*100/B115</f>
         <v>5.0640769397005476</v>
       </c>
-      <c r="F116" t="s">
-        <v>21</v>
-      </c>
-      <c r="G116" s="5">
-        <f>G115/G115</f>
-        <v>1</v>
-      </c>
-      <c r="H116" s="6">
-        <f>H115*100/G115</f>
-        <v>0.76232467287233219</v>
-      </c>
-      <c r="I116" s="6">
-        <f>I115*100/G115</f>
-        <v>4.9566525423048082</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" ht="29.15" x14ac:dyDescent="0.4">
+    </row>
+    <row r="117" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A117" s="3" t="s">
         <v>22</v>
       </c>
@@ -5242,30 +5206,15 @@
         <v>9579276.7785238083</v>
       </c>
       <c r="C117" s="4">
-        <f t="shared" ref="C117:D117" si="1">AVERAGE(C29:C112)</f>
+        <f t="shared" ref="C117:D117" si="0">AVERAGE(C29:C112)</f>
         <v>67739.169619047636</v>
       </c>
       <c r="D117" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>403389.38254761917</v>
       </c>
-      <c r="F117" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G117" s="4">
-        <f>AVERAGE(B31:B112)</f>
-        <v>9625411.3251341451</v>
-      </c>
-      <c r="H117" s="4">
-        <f t="shared" ref="H117:I117" si="2">AVERAGE(C31:C112)</f>
-        <v>67796.169865853692</v>
-      </c>
-      <c r="I117" s="4">
-        <f t="shared" si="2"/>
-        <v>402347.65536585363</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.4">
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>21</v>
       </c>
@@ -5281,50 +5230,116 @@
         <f>D117*100/B117</f>
         <v>4.2110630256763759</v>
       </c>
-      <c r="F118" t="s">
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>69</v>
+      </c>
+      <c r="B119">
+        <f>B31*100/B31</f>
+        <v>100</v>
+      </c>
+      <c r="C119">
+        <f>C31*100/B31</f>
+        <v>0.8414670033061149</v>
+      </c>
+      <c r="D119">
+        <f>D31*100/B31</f>
+        <v>5.7272099641387726</v>
+      </c>
+      <c r="E119" s="3"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+    </row>
+    <row r="120" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A120" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B120" s="4">
+        <f>AVERAGE(B31:B62)</f>
+        <v>8813416.810250001</v>
+      </c>
+      <c r="C120" s="4">
+        <f>AVERAGE(C31:C62)</f>
+        <v>67367.388312500014</v>
+      </c>
+      <c r="D120" s="4">
+        <f>AVERAGE(D31:D62)</f>
+        <v>438777.20462499995</v>
+      </c>
+      <c r="E120" s="3"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="4"/>
+      <c r="H120" s="4"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
         <v>21</v>
       </c>
-      <c r="G118" s="5">
-        <f>G117/G117</f>
+      <c r="B121" s="5">
+        <f>B120/B120</f>
         <v>1</v>
       </c>
-      <c r="H118" s="6">
-        <f>H117*100/G117</f>
+      <c r="C121" s="6">
+        <f>C120*100/B120</f>
+        <v>0.76437311161945465</v>
+      </c>
+      <c r="D121" s="6">
+        <f>D120*100/B120</f>
+        <v>4.9785141684743905</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A122" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B122" s="4">
+        <f>AVERAGE(B31:B112)</f>
+        <v>9625411.3251341451</v>
+      </c>
+      <c r="C122" s="4">
+        <f>AVERAGE(C31:C112)</f>
+        <v>67796.169865853692</v>
+      </c>
+      <c r="D122" s="4">
+        <f>AVERAGE(D31:D112)</f>
+        <v>402347.65536585363</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>21</v>
+      </c>
+      <c r="B123" s="5">
+        <f>B122/B122</f>
+        <v>1</v>
+      </c>
+      <c r="C123" s="6">
+        <f>C122*100/B122</f>
         <v>0.70434569054542562</v>
       </c>
-      <c r="I118" s="6">
-        <f>I117*100/G117</f>
+      <c r="D123" s="6">
+        <f>D122*100/B122</f>
         <v>4.1800567453697495</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A119" s="3"/>
-      <c r="B119" s="4"/>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A120" s="3"/>
-      <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A121" t="s">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A126" t="s">
         <v>19</v>
       </c>
-      <c r="B121" s="21" t="s">
+      <c r="B126" s="21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B122" t="s">
-        <v>197</v>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B127" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B121" r:id="rId1" xr:uid="{263EB9F2-B14E-4059-B29E-0D771DC8E530}"/>
+    <hyperlink ref="B126" r:id="rId1" xr:uid="{263EB9F2-B14E-4059-B29E-0D771DC8E530}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5332,15 +5347,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8683F5-D89E-4384-A263-C6122D6DA873}">
-  <dimension ref="A1:AK48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AK49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.69140625" customWidth="1"/>
-    <col min="9" max="9" width="10.69140625" style="28"/>
+    <col min="3" max="3" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -5391,7 +5406,7 @@
       <c r="AJ1" s="13"/>
       <c r="AK1" s="13"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A2" s="13" t="s">
         <v>23</v>
       </c>
@@ -5445,7 +5460,7 @@
       <c r="AJ2" s="13"/>
       <c r="AK2" s="13"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A3" s="13" t="s">
         <v>24</v>
       </c>
@@ -5499,7 +5514,7 @@
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A4" s="13" t="s">
         <v>25</v>
       </c>
@@ -5554,7 +5569,7 @@
       <c r="AJ4" s="13"/>
       <c r="AK4" s="13"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A5" s="13" t="s">
         <v>26</v>
       </c>
@@ -5607,7 +5622,7 @@
       <c r="AJ5" s="13"/>
       <c r="AK5" s="13"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A6" s="13" t="s">
         <v>27</v>
       </c>
@@ -5633,7 +5648,7 @@
         <v>14539693914.48213</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A7" s="13" t="s">
         <v>28</v>
       </c>
@@ -5659,7 +5674,7 @@
         <v>14952064687.920418</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A8" s="13" t="s">
         <v>29</v>
       </c>
@@ -5685,7 +5700,7 @@
         <v>15245174854.3053</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A9" s="13" t="s">
         <v>30</v>
       </c>
@@ -5711,7 +5726,7 @@
         <v>15630580395.880232</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A10" s="13" t="s">
         <v>31</v>
       </c>
@@ -5737,7 +5752,7 @@
         <v>16067461867.683767</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A11" s="13" t="s">
         <v>32</v>
       </c>
@@ -5763,7 +5778,7 @@
         <v>16512311423.171005</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A12" s="13" t="s">
         <v>33</v>
       </c>
@@ -5789,7 +5804,7 @@
         <v>17173198592.745512</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A13" s="13" t="s">
         <v>34</v>
       </c>
@@ -5815,7 +5830,7 @@
         <v>17575027945.751125</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A14" s="13" t="s">
         <v>35</v>
       </c>
@@ -5841,7 +5856,7 @@
         <v>17807088213.890675</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A15" s="13" t="s">
         <v>36</v>
       </c>
@@ -5867,7 +5882,7 @@
         <v>18004403454.357212</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A16" s="13" t="s">
         <v>37</v>
       </c>
@@ -5893,7 +5908,7 @@
         <v>18502743951.352955</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" s="13" t="s">
         <v>38</v>
       </c>
@@ -5919,7 +5934,7 @@
         <v>18893014123.791737</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" s="13" t="s">
         <v>39</v>
       </c>
@@ -5945,7 +5960,7 @@
         <v>19582440522.206104</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" s="13" t="s">
         <v>40</v>
       </c>
@@ -5971,7 +5986,7 @@
         <v>20221659294.512562</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" s="13" t="s">
         <v>41</v>
       </c>
@@ -5997,7 +6012,7 @@
         <v>20401425207.663731</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" s="13" t="s">
         <v>42</v>
       </c>
@@ -6023,7 +6038,7 @@
         <v>19535384606.465698</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" s="13" t="s">
         <v>43</v>
       </c>
@@ -6050,7 +6065,7 @@
       </c>
       <c r="K22" s="13"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" s="13" t="s">
         <v>44</v>
       </c>
@@ -6076,7 +6091,7 @@
         <v>20396856277.427464</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
         <v>45</v>
       </c>
@@ -6102,7 +6117,7 @@
         <v>20238230228.845612</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" s="13" t="s">
         <v>46</v>
       </c>
@@ -6128,7 +6143,7 @@
         <v>20228258715.518364</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" s="13" t="s">
         <v>47</v>
       </c>
@@ -6154,7 +6169,7 @@
         <v>20577815766.621822</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" s="13" t="s">
         <v>48</v>
       </c>
@@ -6180,7 +6195,7 @@
         <v>21081628480.603973</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" s="13" t="s">
         <v>49</v>
       </c>
@@ -6206,7 +6221,7 @@
         <v>21505364965.621891</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" s="13" t="s">
         <v>50</v>
       </c>
@@ -6232,7 +6247,7 @@
         <v>22152924720.812515</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" s="13" t="s">
         <v>51</v>
       </c>
@@ -6258,7 +6273,7 @@
         <v>22640578323.033131</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" s="13" t="s">
         <v>52</v>
       </c>
@@ -6284,7 +6299,7 @@
         <v>23112148514.524086</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" s="13" t="s">
         <v>53</v>
       </c>
@@ -6310,7 +6325,7 @@
         <v>21838278294.189957</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33" s="13" t="s">
         <v>54</v>
       </c>
@@ -6336,7 +6351,7 @@
         <v>23267260238.964119</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A34" s="13" t="s">
         <v>55</v>
       </c>
@@ -6362,7 +6377,7 @@
         <v>24152188840.065418</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A35" s="13" t="s">
         <v>56</v>
       </c>
@@ -6388,7 +6403,7 @@
         <v>24276616351.55632</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A36" s="13" t="s">
         <v>57</v>
       </c>
@@ -6414,13 +6429,13 @@
         <v>24466165583.505955</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A37" s="13"/>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
       <c r="E38">
         <v>2015</v>
       </c>
@@ -6437,12 +6452,12 @@
         <v>47490.67459411014</v>
       </c>
       <c r="K38" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.4">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.45">
       <c r="E39" s="28" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F39" s="28">
         <v>1</v>
@@ -6456,20 +6471,20 @@
         <v>2.6578482824228877</v>
       </c>
       <c r="K39" s="58" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L39" s="58"/>
       <c r="M39" s="58"/>
     </row>
-    <row r="40" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B40">
         <v>50000</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>64</v>
+        <v>204</v>
       </c>
       <c r="F40">
         <f>SUM(F2:F36)/SUM(Population!B2:B36)</f>
@@ -6485,18 +6500,18 @@
       </c>
       <c r="J40" s="28"/>
       <c r="K40" s="41" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="L40" s="41" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="M40" s="41" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.4">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.45">
       <c r="E41" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F41" s="28">
         <v>1</v>
@@ -6510,7 +6525,7 @@
         <v>2.7778101153314241</v>
       </c>
       <c r="J41" s="28" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="K41" s="42">
         <v>55077.287499999999</v>
@@ -6522,15 +6537,15 @@
         <v>2.3703888007815599</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B42">
         <v>7500</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F42">
         <f>1-(F40-B42)/(B40-B42)</f>
@@ -6545,7 +6560,7 @@
         <v>0.14821255830696134</v>
       </c>
       <c r="J42" s="28" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K42" s="42">
         <v>53985.9</v>
@@ -6557,9 +6572,9 @@
         <v>2.4480223372362699</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="E43" s="11" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F43" s="10">
         <f>(Population!B115*Capacité!F42)*100/(Population!B115*Capacité!F42)</f>
@@ -6575,7 +6590,7 @@
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="28" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K43" s="42">
         <v>52102.45</v>
@@ -6587,9 +6602,9 @@
         <v>2.5245850802099499</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
       <c r="E44" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F44">
         <f>1-(B27-B42)/(B40-B42)</f>
@@ -6604,7 +6619,7 @@
         <v>5.9042950726820198E-2</v>
       </c>
       <c r="J44" s="28" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K44" s="42">
         <v>55263.5</v>
@@ -6616,9 +6631,9 @@
         <v>2.5427605678518299</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="E45" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F45">
         <f>(Population!B115*Capacité!F44)*100/(Population!B115*Capacité!F44)</f>
@@ -6633,7 +6648,7 @@
         <v>0.39547656087185179</v>
       </c>
       <c r="J45" s="28" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="K45" s="42">
         <v>56918.724999999999</v>
@@ -6645,7 +6660,7 @@
         <v>2.31134286871607</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -6653,7 +6668,7 @@
         <v>61</v>
       </c>
       <c r="J46" s="28" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K46" s="28"/>
       <c r="L46" s="28"/>
@@ -6662,20 +6677,28 @@
         <v>2.4394199309591356</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>205</v>
       </c>
       <c r="B47" s="21" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>67</v>
+        <v>206</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>207</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -6685,6 +6708,7 @@
   <hyperlinks>
     <hyperlink ref="B47" r:id="rId1" xr:uid="{95CBC694-0581-4D50-9574-5F9F43EFE88E}"/>
     <hyperlink ref="B48" r:id="rId2" xr:uid="{F1AC7F8B-6E35-450D-9416-466DBBC662CB}"/>
+    <hyperlink ref="B49" r:id="rId3" xr:uid="{BAB34978-CC8B-43E8-A180-17771B8ADC74}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6693,13 +6717,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC11EFA9-274E-476D-8BFE-D8769B6BF052}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="28.69140625" customWidth="1"/>
-    <col min="2" max="2" width="11.61328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B1" s="28" t="s">
         <v>2</v>
       </c>
@@ -6707,7 +6731,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E1" s="28" t="s">
         <v>11</v>
@@ -6719,9 +6743,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="28" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B2">
         <f>(Population!C115*DLS!B2)/(Population!B115*DLS!B8)</f>
@@ -6748,9 +6772,9 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="28" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B3" s="28">
         <f>(Population!C115*DLS!B3)/(Population!B115*DLS!B9)</f>
@@ -6777,9 +6801,9 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B5">
         <f>(Population!C115*DLS!B4)/(Population!B115*DLS!B10)</f>
@@ -6806,23 +6830,23 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D8" s="28">
         <v>3494.0786014333898</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F8">
         <f>1-F9</f>
@@ -6836,15 +6860,15 @@
         <v>0.74445404791547987</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D9" s="28">
         <v>201.308612543306</v>
       </c>
       <c r="E9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F9">
         <f>SUM(D9:D12)/SUM(D8:D13)</f>
@@ -6854,48 +6878,48 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D10">
         <v>520</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D11">
         <v>40</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D12">
         <v>40</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D13">
         <v>211</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -6906,114 +6930,114 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE07EBE8-6449-4730-9E28-CE2F7AF6313A}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.07421875" customWidth="1"/>
+    <col min="1" max="1" width="13.06640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2">
         <f>170/74</f>
         <v>2.2972972972972974</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3">
         <f>1055/74</f>
         <v>14.256756756756756</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" s="35"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" s="35">
         <f>((Population!C116/100)*A2)*1000</f>
         <v>17.76876871873117</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" s="35">
         <f>((Population!C116/100)*A3)*1000</f>
         <v>110.27088822506695</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" s="35"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" s="35" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" s="14">
         <v>1000000000</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" s="20"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" s="22"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" s="22">
         <f>A2*1000000000/(Population!B115*1000)</f>
         <v>0.264704634686033</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" s="22">
         <f>A3*1000000000/(Population!B115*1000)</f>
         <v>1.6427258211397928</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" s="33" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="20"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19">
         <f>(Capacité!G43/100)*A2</f>
         <v>1.2114682525646763E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20">
         <f>(Capacité!G43/100)*A3</f>
         <v>7.5182294497396079E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="15"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24">
         <f>A2*Besoins!B5*1000</f>
         <v>14.648366196075427</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" s="28">
         <f>A3*Besoins!B5*1000</f>
         <v>90.906037275644564</v>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7737401D-8D08-4C39-A7E4-6571C26341A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E523B3-C8E5-496D-8FDD-55429AA89D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="212">
   <si>
     <t>N</t>
   </si>
@@ -690,9 +690,6 @@
     <t>GtCO2eq</t>
   </si>
   <si>
-    <t>Conversion (p.hab)</t>
-  </si>
-  <si>
     <t>Unité affichage (p.hab)</t>
   </si>
   <si>
@@ -742,6 +739,18 @@
   </si>
   <si>
     <t>https://ssp.apps.ece.iiasa.ac.at/basic-drivers?type=line-chart&amp;variables=299&amp;regions=251,76&amp;runs=7,8,9,10,11,12&amp;dataHash=1f0c69e4b47fc1&amp;open=true</t>
+  </si>
+  <si>
+    <t>Conversion exiobase</t>
+  </si>
+  <si>
+    <t>Conversion exiobase (p.hab)</t>
+  </si>
+  <si>
+    <t>Conversion budget</t>
+  </si>
+  <si>
+    <t>Conversion budget (p.hab)</t>
   </si>
 </sst>
 </file>
@@ -993,7 +1002,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1070,29 +1079,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
@@ -1387,7 +1399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C32444-97C3-4A7C-A91C-82059EB528AD}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.1328125" style="28" customWidth="1"/>
@@ -1403,28 +1415,28 @@
         <v>76</v>
       </c>
       <c r="B1" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="E1" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="G1" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="F1" s="17" t="s">
+      <c r="H1" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="G1" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="H1" s="17" t="s">
+      <c r="I1" s="18" t="s">
         <v>199</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
@@ -1439,10 +1451,10 @@
         <v>1100</v>
       </c>
       <c r="D2" s="28">
-        <v>12.6</v>
+        <v>10.6</v>
       </c>
       <c r="E2" s="28">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="F2" s="28">
         <v>4.5</v>
@@ -1458,11 +1470,11 @@
       </c>
       <c r="K2" s="28">
         <f>(0.258-K3)/K3</f>
-        <v>1.2845755630300952</v>
+        <v>1.7156275560546412</v>
       </c>
       <c r="L2" s="28">
         <f>0.258/K3</f>
-        <v>2.2845755630300952</v>
+        <v>2.7156275560546415</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
@@ -1477,7 +1489,10 @@
         <v>4500</v>
       </c>
       <c r="D3" s="28">
-        <v>16.399999999999999</v>
+        <v>14.6</v>
+      </c>
+      <c r="E3" s="28">
+        <v>57</v>
       </c>
       <c r="F3" s="28">
         <v>9</v>
@@ -1490,7 +1505,7 @@
       </c>
       <c r="K3" s="28">
         <f>Population!C113*Synthèse!D2/100</f>
-        <v>0.11293126135771475</v>
+        <v>9.5005664316807653E-2</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -1534,60 +1549,86 @@
       <c r="I5" s="20"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" s="19"/>
-      <c r="K6" s="28">
+      <c r="A6" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A7" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" s="29">
+        <v>1E-3</v>
+      </c>
+      <c r="C7" s="28">
+        <v>1</v>
+      </c>
+      <c r="D7" s="29">
+        <v>1E-3</v>
+      </c>
+      <c r="E7" s="29">
+        <v>1E-3</v>
+      </c>
+      <c r="F7" s="29">
+        <v>1E-3</v>
+      </c>
+      <c r="G7" s="28">
+        <v>2.7777800000000001E-4</v>
+      </c>
+      <c r="H7" s="29">
+        <v>1E-3</v>
+      </c>
+      <c r="I7" s="29">
+        <v>1</v>
+      </c>
+      <c r="K7" s="28">
         <f>269/100 -1</f>
         <v>1.69</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="35"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="35">
-        <f>((Population!C116/100)*B2)*1000</f>
-        <v>40.756329332322622</v>
+      <c r="B8" s="48">
+        <f>((Population!C123/100)*B2)/B7</f>
+        <v>37.114258799240247</v>
       </c>
       <c r="C8" s="35">
-        <f>(Population!C116/100)*C2</f>
-        <v>8.5081045512042177</v>
+        <f>(Population!C123/100)*C2</f>
+        <v>7.7478025959996817</v>
       </c>
       <c r="D8" s="35">
-        <f>((Population!C116/100)*D2)*1000</f>
-        <v>97.456470313793773</v>
+        <f>((Population!C123/100)*D2)*1000</f>
+        <v>74.660643197815105</v>
       </c>
       <c r="E8" s="35">
-        <f>((Population!C116/100)*E2)*1000</f>
-        <v>440.87450856240042</v>
+        <f>((Population!C123/100)*E2)*1000</f>
+        <v>302.86864693453305</v>
       </c>
       <c r="F8" s="35">
-        <f>((Population!C116/100)*F2)*1000</f>
-        <v>34.805882254926345</v>
+        <f>((Population!C123/100)*F2)*1000</f>
+        <v>31.695556074544147</v>
       </c>
       <c r="G8" s="35">
         <f>(G2*Population!C115)*0.000277778</f>
         <v>738.39512671562909</v>
       </c>
       <c r="H8" s="35">
-        <f>((Population!C116/100)*H2)*1000</f>
-        <v>193.36601252736861</v>
+        <f>((Population!C123/100)*H2)*1000</f>
+        <v>176.08642263635642</v>
       </c>
       <c r="I8" s="35">
-        <f>(Population!C116/100)*I2</f>
-        <v>28.803801226076825</v>
+        <f>(Population!C123/100)*I2</f>
+        <v>26.22983351591165</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
@@ -1595,35 +1636,35 @@
         <v>101</v>
       </c>
       <c r="B9" s="35">
-        <f>((Population!C116/100)*B3)*1000</f>
-        <v>163.78414827574923</v>
+        <f>((Population!C123/100)*B3)*1000</f>
+        <v>149.14805542849609</v>
       </c>
       <c r="C9" s="35">
-        <f>(Population!C116/100)*C3</f>
-        <v>34.805882254926345</v>
+        <f>(Population!C123/100)*C3</f>
+        <v>31.69555607454415</v>
       </c>
       <c r="D9" s="35">
-        <f>((Population!C116/100)*D3)*1000</f>
-        <v>126.84810421795379</v>
+        <f>((Population!C123/100)*D3)*1000</f>
+        <v>102.83447081963213</v>
       </c>
       <c r="E9" s="35">
-        <f>((Population!C116/100)*E3)*1000</f>
-        <v>0</v>
+        <f>((Population!C123/100)*E3)*1000</f>
+        <v>401.47704361089257</v>
       </c>
       <c r="F9" s="35">
-        <f>((Population!C116/100)*F3)*1000</f>
-        <v>69.611764509852691</v>
+        <f>((Population!C123/100)*F3)*1000</f>
+        <v>63.391112149088293</v>
       </c>
       <c r="G9" s="35">
         <f>(G3*Population!C115)*0.000366668</f>
         <v>1206.0487944160323</v>
       </c>
       <c r="H9" s="35">
-        <f>((Population!C116/100)*H3)*1000</f>
-        <v>386.73202505473722</v>
+        <f>((Population!C123/100)*H3)*1000</f>
+        <v>352.17284527271283</v>
       </c>
       <c r="I9" s="35">
-        <f>(Population!C116/100)*I3</f>
+        <f>(Population!C123/100)*I3</f>
         <v>0</v>
       </c>
     </row>
@@ -1669,7 +1710,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" s="19" t="s">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="B12" s="29">
         <v>1</v>
@@ -1751,299 +1792,329 @@
       <c r="I15" s="22"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="49" t="s">
+        <v>211</v>
+      </c>
+      <c r="B16" s="50">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="C16" s="50">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="D16" s="50">
+        <v>9.9999999999999998E-13</v>
+      </c>
+      <c r="E16" s="50">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F16" s="50">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="G16" s="50">
+        <v>1</v>
+      </c>
+      <c r="H16" s="50">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="I16" s="50">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A17" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="B16" s="22">
-        <f>B2*1000000000/(Population!B115*1000)</f>
-        <v>0.60715457766544023</v>
-      </c>
-      <c r="C16" s="22">
-        <f>C2*1000000000/(Population!B115*1000)</f>
-        <v>126.74680743201814</v>
-      </c>
-      <c r="D16" s="22">
-        <f>D2*1000000000000/(Population!B115*1000)</f>
-        <v>1451.8270669485714</v>
-      </c>
-      <c r="E16" s="22">
-        <f>E2*1000000000/(Population!B115*1000)</f>
-        <v>6.5677891123863947</v>
-      </c>
-      <c r="F16" s="22">
-        <f>F2*1000000000/(Population!B115*1000)</f>
-        <v>0.51850966676734689</v>
-      </c>
-      <c r="G16" s="22">
+      <c r="B17" s="22">
+        <f>B2*1000000000/(Population!B122*1000)</f>
+        <v>0.54743887261886837</v>
+      </c>
+      <c r="C17" s="22">
+        <f>C2*1000000000/(Population!B122*1000)</f>
+        <v>114.28083048540991</v>
+      </c>
+      <c r="D17" s="22">
+        <f>D2*1000000000000/(Population!B122*1000)</f>
+        <v>1101.2516392230409</v>
+      </c>
+      <c r="E17" s="22">
+        <f>E2*1000000000/(Population!B122*1000)</f>
+        <v>4.4673415553387503</v>
+      </c>
+      <c r="F17" s="22">
+        <f>F2*1000000000/(Population!B122*1000)</f>
+        <v>0.46751248834940412</v>
+      </c>
+      <c r="G17" s="22">
         <f>G2</f>
         <v>39.6</v>
       </c>
-      <c r="H16" s="22">
-        <f>H2*1000000000/(Population!B115*1000)</f>
-        <v>2.8806092598185939</v>
-      </c>
-      <c r="I16" s="22">
-        <f>I2*1000000/(Population!B115*1000)</f>
-        <v>0.42909555534257776</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A17" s="31" t="s">
+      <c r="H17" s="22">
+        <f>H2*1000000000/(Population!B122*1000)</f>
+        <v>2.5972916019411341</v>
+      </c>
+      <c r="I17" s="22">
+        <f>I2*1000000/(Population!B122*1000)</f>
+        <v>0.38689255702515135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A18" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="B17" s="22">
-        <f>B3*1000000000/(Population!B115*1000)</f>
-        <v>2.4399227556489409</v>
-      </c>
-      <c r="C17" s="22">
-        <f>C3*1000000000/(Population!B115*1000)</f>
-        <v>518.50966676734697</v>
-      </c>
-      <c r="D17" s="22">
-        <f>D3*1000000000000/(Population!B115*1000)</f>
-        <v>1889.6796744409976</v>
-      </c>
-      <c r="E17" s="22">
-        <f>E3*1000000000/(Population!B115*1000)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="22">
-        <f>F3*1000000000/(Population!B115*1000)</f>
-        <v>1.0370193335346938</v>
-      </c>
-      <c r="G17" s="22">
+      <c r="B18" s="22">
+        <f>B3*1000000000/(Population!B122*1000)</f>
+        <v>2.1999481050863343</v>
+      </c>
+      <c r="C18" s="22">
+        <f>C3*1000000000/(Population!B122*1000)</f>
+        <v>467.51248834940412</v>
+      </c>
+      <c r="D18" s="22">
+        <f>D3*1000000000000/(Population!B122*1000)</f>
+        <v>1516.8182955336224</v>
+      </c>
+      <c r="E18" s="22">
+        <f>E3*1000000000/(Population!B122*1000)</f>
+        <v>5.9218248524257859</v>
+      </c>
+      <c r="F18" s="22">
+        <f>F3*1000000000/(Population!B122*1000)</f>
+        <v>0.93502497669880824</v>
+      </c>
+      <c r="G18" s="22">
         <f>G3</f>
         <v>49</v>
       </c>
-      <c r="H17" s="22">
-        <f>H3*1000000000/(Population!B115*1000)</f>
-        <v>5.7612185196371879</v>
-      </c>
-      <c r="I17" s="22">
-        <f>I3*1000000/(Population!B115*1000)</f>
+      <c r="H18" s="22">
+        <f>H3*1000000000/(Population!B122*1000)</f>
+        <v>5.1945832038822681</v>
+      </c>
+      <c r="I18" s="22">
+        <f>I3*1000000/(Population!B122*1000)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="32" t="s">
+    <row r="19" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="B19" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="B18" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="C18" s="33" t="s">
+      <c r="C19" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D19" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="33" t="s">
+      <c r="E19" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="33" t="s">
+      <c r="F19" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G19" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="H18" s="33" t="s">
+      <c r="H19" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="I18" s="33" t="s">
+      <c r="I19" s="33" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A19" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19" s="45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A20" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B20" s="45">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="C19" s="45">
+      <c r="C20" s="45">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="D19" s="45">
+      <c r="D20" s="45">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E20" s="45">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="F19" s="45">
+      <c r="F20" s="45">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="G19" s="45">
+      <c r="G20" s="45">
         <v>1E-3</v>
       </c>
-      <c r="H19" s="45">
+      <c r="H20" s="45">
         <v>1E-3</v>
       </c>
-      <c r="I19" s="45">
+      <c r="I20" s="45">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" s="19"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-    </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="28">
-        <f>(Capacité!G43/100)*B2</f>
-        <v>2.7787518571914371E-3</v>
-      </c>
-      <c r="C21" s="28">
-        <f>(Capacité!G43/100)*C2</f>
-        <v>0.58007950446332146</v>
-      </c>
-      <c r="D21" s="28">
-        <f>(Capacité!G43/100)*D2</f>
-        <v>6.6445470511253182E-3</v>
-      </c>
-      <c r="E21" s="28">
-        <f>(Capacité!G43/100)*E2</f>
-        <v>3.0058665231281204E-2</v>
-      </c>
-      <c r="F21" s="28">
-        <f>(Capacité!G43/100)*F2</f>
-        <v>2.3730525182590425E-3</v>
-      </c>
-      <c r="G21" s="28">
-        <f>(Capacité!G43/100)*G2</f>
-        <v>2.0882862160679572E-2</v>
-      </c>
-      <c r="H21" s="28">
-        <f>((Capacité!G42/100)*H2)*1000</f>
-        <v>13.743345116682876</v>
-      </c>
-      <c r="I21" s="28">
-        <f>(Capacité!G43/100)*I2</f>
-        <v>1.963832795110372</v>
-      </c>
+      <c r="A21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="28">
+        <f>(Capacité!C43/100)*B2</f>
+        <v>2.7787518571914371E-3</v>
+      </c>
+      <c r="C22" s="28">
+        <f>(Capacité!C43/100)*C2</f>
+        <v>0.58007950446332146</v>
+      </c>
+      <c r="D22" s="28">
+        <f>(Capacité!C43/100)*D2</f>
+        <v>5.5898570430101885E-3</v>
+      </c>
+      <c r="E22" s="28">
+        <f>(Capacité!C43/100)*E2</f>
+        <v>2.2675835174475294E-2</v>
+      </c>
+      <c r="F22" s="28">
+        <f>(Capacité!C43/100)*F2</f>
+        <v>2.3730525182590425E-3</v>
+      </c>
+      <c r="G22" s="28">
+        <f>(Capacité!C43/100)*G2</f>
+        <v>2.0882862160679572E-2</v>
+      </c>
+      <c r="H22" s="28">
+        <f>((Capacité!C42/100)*H2)*1000</f>
+        <v>13.743345116682876</v>
+      </c>
+      <c r="I22" s="28">
+        <f>(Capacité!C43/100)*I2</f>
+        <v>1.963832795110372</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A23" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B22" s="28">
-        <f>(Capacité!G43/100)*B3</f>
+      <c r="B23" s="28">
+        <f>(Capacité!C43/100)*B3</f>
         <v>1.1166744249434098E-2</v>
       </c>
-      <c r="C22" s="28">
-        <f>(Capacité!G43/100)*C3</f>
+      <c r="C23" s="28">
+        <f>(Capacité!C43/100)*C3</f>
         <v>2.3730525182590423</v>
       </c>
-      <c r="D22" s="28">
-        <f>(Capacité!G43/100)*D3</f>
-        <v>8.6484580665440649E-3</v>
-      </c>
-      <c r="E22" s="28">
-        <f>(Capacité!G43/100)*E3</f>
+      <c r="D23" s="28">
+        <f>(Capacité!C43/100)*D3</f>
+        <v>7.6992370592404488E-3</v>
+      </c>
+      <c r="E23" s="28">
+        <f>(Capacité!C43/100)*E3</f>
+        <v>3.0058665231281204E-2</v>
+      </c>
+      <c r="F23" s="28">
+        <f>(Capacité!C43/100)*F3</f>
+        <v>4.746105036518085E-3</v>
+      </c>
+      <c r="G23" s="28">
+        <f>(Capacité!C43/100)*G3</f>
+        <v>2.5839905198820682E-2</v>
+      </c>
+      <c r="H23" s="28">
+        <f>((Capacité!C43/100)*H3)*1000</f>
+        <v>26.367250202878246</v>
+      </c>
+      <c r="I23" s="28">
+        <f>(Capacité!C43/100)*I3</f>
         <v>0</v>
       </c>
-      <c r="F22" s="28">
-        <f>(Capacité!G43/100)*F3</f>
-        <v>4.746105036518085E-3</v>
-      </c>
-      <c r="G22" s="28">
-        <f>(Capacité!G43/100)*G3</f>
-        <v>2.5839905198820682E-2</v>
-      </c>
-      <c r="H22" s="28">
-        <f>((Capacité!G43/100)*H3)*1000</f>
-        <v>26.367250202878246</v>
-      </c>
-      <c r="I22" s="28">
-        <f>(Capacité!G43/100)*I3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A23" s="19"/>
-    </row>
-    <row r="24" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A24" s="19" t="s">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A24" s="19"/>
+    </row>
+    <row r="25" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="15"/>
-    </row>
-    <row r="25" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="16" t="s">
+      <c r="D25" s="15"/>
+    </row>
+    <row r="26" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A26" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A26" s="19" t="s">
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A27" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="28">
+      <c r="B27" s="28">
         <f>B2*Besoins!B5*1000</f>
         <v>33.599043710798185</v>
       </c>
-      <c r="C26" s="28" t="e">
+      <c r="C27" s="28" t="e">
         <f>C2*Besoins!C5</f>
         <v>#REF!</v>
       </c>
-      <c r="D26" s="28" t="e">
+      <c r="D27" s="28" t="e">
         <f>D2*Besoins!D5*1000</f>
         <v>#REF!</v>
       </c>
-      <c r="H26" s="28">
+      <c r="H27" s="28">
         <f>H2*Besoins!E5*1000</f>
         <v>183.26764541723307</v>
       </c>
-      <c r="I26" s="28" t="e">
+      <c r="I27" s="28" t="e">
         <f>I2*Besoins!G5</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A27" s="19" t="s">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A28" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B28" s="28">
         <f>B3*Besoins!B5*1000</f>
         <v>135.02174624662513</v>
       </c>
-      <c r="C27" s="28" t="e">
+      <c r="C28" s="28" t="e">
         <f>C3*Besoins!C5</f>
         <v>#REF!</v>
       </c>
-      <c r="D27" s="28" t="e">
+      <c r="D28" s="28" t="e">
         <f>D3*Besoins!D5*1000</f>
         <v>#REF!</v>
       </c>
-      <c r="H27" s="28">
+      <c r="H28" s="28">
         <f>H3*Besoins!E5*1000</f>
         <v>366.53529083446614</v>
       </c>
-      <c r="I27" s="28" t="e">
+      <c r="I28" s="28" t="e">
         <f>I3*Besoins!G5</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A28" s="19"/>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A29" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2524,35 +2595,35 @@
         <v>16</v>
       </c>
       <c r="B19">
-        <f>(Capacité!G43/100)*B2</f>
+        <f>(Capacité!C43/100)*B2</f>
         <v>2.7787518571914371E-3</v>
       </c>
       <c r="C19">
-        <f>(Capacité!G43/100)*C2</f>
+        <f>(Capacité!C43/100)*C2</f>
         <v>1.4765660113611818</v>
       </c>
       <c r="D19">
-        <f>(Capacité!G43/100)*D2</f>
+        <f>(Capacité!C43/100)*D2</f>
         <v>6.6445470511253182E-3</v>
       </c>
       <c r="E19">
-        <f>(Capacité!G43/100)*E2</f>
+        <f>(Capacité!C43/100)*E2</f>
         <v>1.5029332615640602E-2</v>
       </c>
       <c r="F19">
-        <f>(Capacité!G43/100)*F2</f>
+        <f>(Capacité!C43/100)*F2</f>
         <v>9.8613515758764645E-4</v>
       </c>
       <c r="G19">
-        <f>(Capacité!G43/100)*G2</f>
+        <f>(Capacité!C43/100)*G2</f>
         <v>2.0882862160679572E-2</v>
       </c>
       <c r="H19">
-        <f>((Capacité!G42/100)*H2)*1000</f>
+        <f>((Capacité!C42/100)*H2)*1000</f>
         <v>13.743345116682876</v>
       </c>
       <c r="I19">
-        <f>(Capacité!G43/100)*I2</f>
+        <f>(Capacité!C43/100)*I2</f>
         <v>1.963832795110372</v>
       </c>
     </row>
@@ -2561,35 +2632,35 @@
         <v>102</v>
       </c>
       <c r="B20">
-        <f>(Capacité!G43/100)*B3</f>
+        <f>(Capacité!C43/100)*B3</f>
         <v>1.1166744249434098E-2</v>
       </c>
       <c r="C20">
-        <f>(Capacité!G43/100)*C3</f>
+        <f>(Capacité!C43/100)*C3</f>
         <v>2.3730525182590423</v>
       </c>
       <c r="D20">
-        <f>(Capacité!G43/100)*D3</f>
+        <f>(Capacité!C43/100)*D3</f>
         <v>8.6484580665440649E-3</v>
       </c>
       <c r="E20">
-        <f>(Capacité!G43/100)*E3</f>
+        <f>(Capacité!C43/100)*E3</f>
         <v>1.9880906652970199E-2</v>
       </c>
       <c r="F20">
-        <f>(Capacité!G43/100)*F3</f>
+        <f>(Capacité!C43/100)*F3</f>
         <v>8.9648650689786048E-3</v>
       </c>
       <c r="G20">
-        <f>(Capacité!G43/100)*G3</f>
+        <f>(Capacité!C43/100)*G3</f>
         <v>2.5839905198820682E-2</v>
       </c>
       <c r="H20">
-        <f>((Capacité!G43/100)*H3)*1000</f>
+        <f>((Capacité!C43/100)*H3)*1000</f>
         <v>26.367250202878246</v>
       </c>
       <c r="I20">
-        <f>(Capacité!G43/100)*I3</f>
+        <f>(Capacité!C43/100)*I3</f>
         <v>13.746829565772604</v>
       </c>
     </row>
@@ -3043,12 +3114,12 @@
       <c r="A18" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
       <c r="F18" s="21" t="s">
         <v>104</v>
       </c>
@@ -3095,13 +3166,13 @@
         <v>76</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
@@ -3300,10 +3371,10 @@
       <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="49"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="21" t="s">
         <v>104</v>
       </c>
@@ -3330,124 +3401,124 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="53" t="s">
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="52" t="s">
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="53" t="s">
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="58" t="s">
         <v>138</v>
       </c>
-      <c r="L2" s="53"/>
-      <c r="M2" s="56" t="s">
+      <c r="L2" s="58"/>
+      <c r="M2" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="O2" s="52" t="s">
+      <c r="O2" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="53" t="s">
+      <c r="P2" s="57"/>
+      <c r="Q2" s="57"/>
+      <c r="R2" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="S2" s="53"/>
-      <c r="T2" s="57" t="s">
+      <c r="S2" s="58"/>
+      <c r="T2" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="U2" s="55" t="s">
+      <c r="U2" s="56" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="17.649999999999999" x14ac:dyDescent="0.45">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="54" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="54" t="s">
         <v>149</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="54" t="s">
         <v>151</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="K3" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="L3" s="50" t="s">
+      <c r="L3" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="M3" s="56"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="51" t="s">
+      <c r="M3" s="59"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="P3" s="51" t="s">
+      <c r="P3" s="54" t="s">
         <v>155</v>
       </c>
       <c r="Q3" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="R3" s="50" t="s">
+      <c r="R3" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="S3" s="50" t="s">
+      <c r="S3" s="55" t="s">
         <v>159</v>
       </c>
-      <c r="T3" s="57"/>
-      <c r="U3" s="55"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="56"/>
     </row>
     <row r="4" spans="1:21" ht="38" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="51"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="59"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
       <c r="Q4" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="57"/>
-      <c r="U4" s="55"/>
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="60"/>
+      <c r="U4" s="56"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
@@ -3522,6 +3593,17 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
@@ -3536,17 +3618,6 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T2:T4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -5254,7 +5325,7 @@
     </row>
     <row r="120" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A120" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B120" s="4">
         <f>AVERAGE(B31:B62)</f>
@@ -5334,7 +5405,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B127" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -5347,7 +5418,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8683F5-D89E-4384-A263-C6122D6DA873}">
-  <dimension ref="A1:AK49"/>
+  <dimension ref="A1:AK53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="11.86328125" bestFit="1" customWidth="1"/>
@@ -6436,19 +6507,19 @@
       <c r="D37" s="13"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="E38">
+      <c r="A38">
         <v>2015</v>
       </c>
-      <c r="F38">
+      <c r="B38">
         <f>B27</f>
         <v>17868.090856870793</v>
       </c>
-      <c r="G38" s="28">
-        <f t="shared" ref="G38:H38" si="0">C27</f>
+      <c r="C38" s="28">
+        <f>C27</f>
         <v>50682.895358633301</v>
       </c>
-      <c r="H38" s="28">
-        <f t="shared" si="0"/>
+      <c r="D38" s="28">
+        <f>D27</f>
         <v>47490.67459411014</v>
       </c>
       <c r="K38" t="s">
@@ -6456,45 +6527,39 @@
       </c>
     </row>
     <row r="39" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="E39" s="28" t="s">
+      <c r="A39" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="F39" s="28">
+      <c r="B39" s="28">
         <v>1</v>
       </c>
-      <c r="G39" s="28">
-        <f>G38/F38</f>
+      <c r="C39" s="28">
+        <f>C38/B38</f>
         <v>2.8365031141054602</v>
       </c>
-      <c r="H39" s="28">
-        <f>H38/F38</f>
+      <c r="D39" s="28">
+        <f>D38/B38</f>
         <v>2.6578482824228877</v>
       </c>
-      <c r="K39" s="58" t="s">
+      <c r="K39" s="61" t="s">
         <v>169</v>
       </c>
-      <c r="L39" s="58"/>
-      <c r="M39" s="58"/>
+      <c r="L39" s="61"/>
+      <c r="M39" s="61"/>
     </row>
     <row r="40" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>64</v>
+      <c r="A40" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="B40">
-        <v>50000</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F40">
         <f>SUM(F2:F36)/SUM(Population!B2:B36)</f>
         <v>15732.164711604171</v>
       </c>
-      <c r="G40">
+      <c r="C40">
         <f>SUM(G2:G36)/SUM(Population!C2:C36)</f>
         <v>47663.631330163909</v>
       </c>
-      <c r="H40">
+      <c r="D40">
         <f>SUM(H2:H36)/SUM(Population!D2:D36)</f>
         <v>43700.966271954145</v>
       </c>
@@ -6510,18 +6575,18 @@
       </c>
     </row>
     <row r="41" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="E41" s="3" t="s">
+      <c r="A41" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="F41" s="28">
+      <c r="B41" s="28">
         <v>1</v>
       </c>
-      <c r="G41" s="28">
-        <f>G40/F40</f>
+      <c r="C41" s="28">
+        <f>C40/B40</f>
         <v>3.0296931289440945</v>
       </c>
-      <c r="H41" s="28">
-        <f>H40/F40</f>
+      <c r="D41" s="28">
+        <f>D40/B40</f>
         <v>2.7778101153314241</v>
       </c>
       <c r="J41" s="28" t="s">
@@ -6538,25 +6603,19 @@
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>65</v>
+      <c r="A42" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="B42">
-        <v>7500</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F42">
-        <f>1-(F40-B42)/(B40-B42)</f>
+        <f>1-(B40-B53)/(B51-B53)</f>
         <v>0.80630200678578423</v>
       </c>
-      <c r="G42">
-        <f>1-(G40-B42)/(B40-B42)</f>
+      <c r="C42">
+        <f>1-(C40-B53)/(B51-B53)</f>
         <v>5.4973380466731503E-2</v>
       </c>
-      <c r="H42">
-        <f>1-(H40-B42)/(B40-B42)</f>
+      <c r="D42">
+        <f>1-(D40-B53)/(B51-B53)</f>
         <v>0.14821255830696134</v>
       </c>
       <c r="J42" s="28" t="s">
@@ -6573,19 +6632,19 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="E43" s="11" t="s">
+      <c r="A43" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F43" s="10">
-        <f>(Population!B115*Capacité!F42)*100/(Population!B115*Capacité!F42)</f>
+      <c r="B43" s="10">
+        <f>(Population!B115*Capacité!B42)*100/(Population!B115*Capacité!B42)</f>
         <v>100</v>
       </c>
-      <c r="G43" s="10">
-        <f>(Population!C115*Capacité!G42)*100/(Population!B115*Capacité!F42)</f>
+      <c r="C43" s="10">
+        <f>(Population!C115*Capacité!C42)*100/(Population!B115*Capacité!B42)</f>
         <v>5.2734500405756501E-2</v>
       </c>
-      <c r="H43" s="10">
-        <f>(Population!D115*Capacité!H42)*100/(Population!B115*Capacité!F42)</f>
+      <c r="D43" s="10">
+        <f>(Population!D115*Capacité!D42)*100/(Population!B115*Capacité!B42)</f>
         <v>0.93086683696635297</v>
       </c>
       <c r="I43" s="10"/>
@@ -6602,20 +6661,20 @@
         <v>2.5245850802099499</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="E44" s="3" t="s">
+    <row r="44" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A44" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F44">
-        <f>1-(B27-B42)/(B40-B42)</f>
+      <c r="B44">
+        <f>1-(B27-B53)/(B51-B53)</f>
         <v>0.75604492101480492</v>
       </c>
-      <c r="G44">
-        <f>MAX(1-(C27-B42)/(B40-B42),0)</f>
+      <c r="C44">
+        <f>MAX(1-(C27-B53)/(B51-B53),0)</f>
         <v>0</v>
       </c>
-      <c r="H44">
-        <f>MAX(1-(D27-B42)/(B40-B42),0)</f>
+      <c r="D44">
+        <f>MAX(1-(D27-B53)/(B51-B53),0)</f>
         <v>5.9042950726820198E-2</v>
       </c>
       <c r="J44" s="28" t="s">
@@ -6632,19 +6691,19 @@
       </c>
     </row>
     <row r="45" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="E45" s="3" t="s">
+      <c r="A45" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F45">
-        <f>(Population!B115*Capacité!F44)*100/(Population!B115*Capacité!F44)</f>
+      <c r="B45">
+        <f>(Population!B115*Capacité!B44)*100/(Population!B115*Capacité!B44)</f>
         <v>100</v>
       </c>
-      <c r="G45">
-        <f>(Population!C115*Capacité!G44)*100/(Population!B115*Capacité!F44)</f>
+      <c r="C45">
+        <f>(Population!C115*Capacité!C44)*100/(Population!B115*Capacité!B44)</f>
         <v>0</v>
       </c>
-      <c r="H45">
-        <f>(Population!D115*Capacité!H44)*100/(Population!B115*Capacité!F44)</f>
+      <c r="D45">
+        <f>(Population!D115*Capacité!D44)*100/(Population!B115*Capacité!B44)</f>
         <v>0.39547656087185179</v>
       </c>
       <c r="J45" s="28" t="s">
@@ -6679,7 +6738,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B47" s="21" t="s">
         <v>62</v>
@@ -6687,7 +6746,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B48" s="21" t="s">
         <v>66</v>
@@ -6695,10 +6754,30 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
+        <v>206</v>
+      </c>
+      <c r="B49" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="B49" s="21" t="s">
-        <v>208</v>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52" s="28"/>
+      <c r="B52" s="28"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>65</v>
+      </c>
+      <c r="B53">
+        <v>7500</v>
       </c>
     </row>
   </sheetData>
@@ -7018,13 +7097,13 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19">
-        <f>(Capacité!G43/100)*A2</f>
+        <f>(Capacité!C43/100)*A2</f>
         <v>1.2114682525646763E-3</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20">
-        <f>(Capacité!G43/100)*A3</f>
+        <f>(Capacité!C43/100)*A3</f>
         <v>7.5182294497396079E-3</v>
       </c>
     </row>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\PlaneFR\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E523B3-C8E5-496D-8FDD-55429AA89D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DF5D48-A77C-4FFD-9F11-909CC74F3E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="8002" windowWidth="14595" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="9" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="229">
   <si>
     <t>N</t>
   </si>
@@ -690,9 +690,6 @@
     <t>GtCO2eq</t>
   </si>
   <si>
-    <t>Unité affichage (p.hab)</t>
-  </si>
-  <si>
     <t>tCO2eq</t>
   </si>
   <si>
@@ -741,16 +738,70 @@
     <t>https://ssp.apps.ece.iiasa.ac.at/basic-drivers?type=line-chart&amp;variables=299&amp;regions=251,76&amp;runs=7,8,9,10,11,12&amp;dataHash=1f0c69e4b47fc1&amp;open=true</t>
   </si>
   <si>
-    <t>Conversion exiobase</t>
-  </si>
-  <si>
-    <t>Conversion exiobase (p.hab)</t>
-  </si>
-  <si>
-    <t>Conversion budget</t>
-  </si>
-  <si>
-    <t>Conversion budget (p.hab)</t>
+    <t>PDF.m2.yr</t>
+  </si>
+  <si>
+    <t>1e9 PDF.m2.yr</t>
+  </si>
+  <si>
+    <t>1e12 PDF.m2.yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PDF.m2.yr</t>
+  </si>
+  <si>
+    <t>Lower safe bound</t>
+  </si>
+  <si>
+    <t>Upper safe bound</t>
+  </si>
+  <si>
+    <t>Safe limit</t>
+  </si>
+  <si>
+    <t>Equality (Lower bound)</t>
+  </si>
+  <si>
+    <t>Equality (Upper bound)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equality </t>
+  </si>
+  <si>
+    <t>PB name</t>
+  </si>
+  <si>
+    <t>Figures unit</t>
+  </si>
+  <si>
+    <t>Unit budget</t>
+  </si>
+  <si>
+    <t>Equality (Lower bound) (p. cap)</t>
+  </si>
+  <si>
+    <t>Equality (p.cap)</t>
+  </si>
+  <si>
+    <t>Equality (Upper bound) (p.cap)</t>
+  </si>
+  <si>
+    <t>Figures unit (p.cap)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit Exiobase </t>
+  </si>
+  <si>
+    <t>Unit conversion budget</t>
+  </si>
+  <si>
+    <t>Unit conversion Exiobase</t>
+  </si>
+  <si>
+    <t>Unit conversion budget  (p. cap)</t>
+  </si>
+  <si>
+    <t>Unit conversion Exiobase  (p.cap)</t>
   </si>
 </sst>
 </file>
@@ -842,21 +893,21 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -941,6 +992,30 @@
         <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -1002,7 +1077,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1080,8 +1155,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1114,6 +1190,39 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="14" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="11" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1399,121 +1508,828 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C32444-97C3-4A7C-A91C-82059EB528AD}">
-  <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.1328125" style="28" customWidth="1"/>
-    <col min="2" max="3" width="9.19921875" style="28"/>
-    <col min="4" max="4" width="14.06640625" style="28" customWidth="1"/>
-    <col min="5" max="8" width="9.19921875" style="28"/>
-    <col min="9" max="10" width="11.86328125" style="28" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.19921875" style="28"/>
+    <col min="1" max="1" width="27" style="28" customWidth="1"/>
+    <col min="2" max="2" width="14.15234375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="11.69140625" style="28" customWidth="1"/>
+    <col min="4" max="4" width="14.07421875" style="28" customWidth="1"/>
+    <col min="5" max="7" width="9.23046875" style="28"/>
+    <col min="8" max="8" width="11.921875" style="28" customWidth="1"/>
+    <col min="9" max="9" width="13.921875" style="28" customWidth="1"/>
+    <col min="10" max="16384" width="9.23046875" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" s="3" customFormat="1" ht="31.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="79" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="80" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" s="80" t="s">
+        <v>199</v>
+      </c>
+      <c r="D1" s="80" t="s">
+        <v>194</v>
+      </c>
+      <c r="E1" s="80" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1" s="80" t="s">
+        <v>196</v>
+      </c>
+      <c r="G1" s="80" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1" s="80" t="s">
+        <v>197</v>
+      </c>
+      <c r="I1" s="81" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A2" s="72" t="s">
+        <v>211</v>
+      </c>
+      <c r="B2" s="73">
+        <f>(1.33*10+163.83)/74</f>
+        <v>2.3936486486486488</v>
+      </c>
+      <c r="C2" s="73">
+        <v>1100</v>
+      </c>
+      <c r="D2" s="73">
+        <v>10.6</v>
+      </c>
+      <c r="E2" s="73">
+        <v>34</v>
+      </c>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A3" s="74" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="75">
+        <f>(1.33*130+163.83)/74</f>
+        <v>4.5504054054054057</v>
+      </c>
+      <c r="C3" s="75">
+        <v>2800</v>
+      </c>
+      <c r="D3" s="75">
+        <v>12.6</v>
+      </c>
+      <c r="E3" s="75">
+        <v>57</v>
+      </c>
+      <c r="F3" s="75">
+        <v>4.5</v>
+      </c>
+      <c r="G3" s="75">
+        <v>39.6</v>
+      </c>
+      <c r="H3" s="75">
+        <v>25</v>
+      </c>
+      <c r="I3" s="76">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A4" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="75">
+        <f>(1.33*1050+163.83)/74</f>
+        <v>21.085540540540539</v>
+      </c>
+      <c r="C4" s="75">
+        <v>4500</v>
+      </c>
+      <c r="D4" s="75">
+        <v>14.6</v>
+      </c>
+      <c r="E4" s="75">
+        <v>74</v>
+      </c>
+      <c r="F4" s="75">
+        <v>9</v>
+      </c>
+      <c r="G4" s="75">
+        <v>49</v>
+      </c>
+      <c r="H4" s="75">
+        <v>50</v>
+      </c>
+      <c r="I4" s="75"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="77" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="78" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="78" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="78" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="78" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A7" s="63" t="s">
+        <v>225</v>
+      </c>
+      <c r="B7" s="64">
+        <v>1E-3</v>
+      </c>
+      <c r="C7" s="65">
+        <v>1</v>
+      </c>
+      <c r="D7" s="64">
+        <v>1E-3</v>
+      </c>
+      <c r="E7" s="64">
+        <v>1E-3</v>
+      </c>
+      <c r="F7" s="64">
+        <v>1E-3</v>
+      </c>
+      <c r="G7" s="65">
+        <v>2.7777800000000001E-4</v>
+      </c>
+      <c r="H7" s="64">
+        <v>1E-3</v>
+      </c>
+      <c r="I7" s="64">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A8" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="35">
+        <f>((Population!C121/100)*B2)*1000</f>
+        <v>18.296406656912701</v>
+      </c>
+      <c r="C8" s="35">
+        <f>(Population!C121/100)*C2</f>
+        <v>8.4081042278140004</v>
+      </c>
+      <c r="D8" s="35">
+        <f>((Population!C121/100)*D2)*1000</f>
+        <v>81.02354983166218</v>
+      </c>
+      <c r="E8" s="35">
+        <f>((Population!C121/100)*E2)*1000</f>
+        <v>259.88685795061457</v>
+      </c>
+      <c r="F8" s="35">
+        <f>((Population!C121/100)*F2)*1000</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="35">
+        <f>(G2*Population!C113)*0.000366668</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="35">
+        <f>((Population!C121/100)*H2)*1000</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="35">
+        <f>(Population!C121/100)*I2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A9" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="B9" s="48">
+        <f>((Population!C123/100)*B3)/B7</f>
+        <v>32.050584375319076</v>
+      </c>
+      <c r="C9" s="35">
+        <f>(Population!C123/100)*C3</f>
+        <v>19.721679335271915</v>
+      </c>
+      <c r="D9" s="35">
+        <f>((Population!C123/100)*D3)*1000</f>
+        <v>88.747557008723618</v>
+      </c>
+      <c r="E9" s="35">
+        <f>((Population!C123/100)*E3)*1000</f>
+        <v>401.47704361089257</v>
+      </c>
+      <c r="F9" s="35">
+        <f>((Population!C123/100)*F3)*1000</f>
+        <v>31.695556074544147</v>
+      </c>
+      <c r="G9" s="35">
+        <f>(G3*Population!C115)*0.000277778</f>
+        <v>738.39512671562909</v>
+      </c>
+      <c r="H9" s="35">
+        <f>((Population!C123/100)*H3)*1000</f>
+        <v>176.08642263635642</v>
+      </c>
+      <c r="I9" s="50">
+        <f>(Population!C123/100)*I3*1000</f>
+        <v>45.782469885452663</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A10" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="35">
+        <f>((Population!C123/100)*B4)*1000</f>
+        <v>148.51509612550592</v>
+      </c>
+      <c r="C10" s="35">
+        <f>(Population!C123/100)*C4</f>
+        <v>31.69555607454415</v>
+      </c>
+      <c r="D10" s="35">
+        <f>((Population!C123/100)*D4)*1000</f>
+        <v>102.83447081963213</v>
+      </c>
+      <c r="E10" s="35">
+        <f>((Population!C123/100)*E4)*1000</f>
+        <v>521.21581100361493</v>
+      </c>
+      <c r="F10" s="35">
+        <f>((Population!C123/100)*F4)*1000</f>
+        <v>63.391112149088293</v>
+      </c>
+      <c r="G10" s="35">
+        <f>(G4*Population!C115)*0.000366668</f>
+        <v>1206.0487944160323</v>
+      </c>
+      <c r="H10" s="35">
+        <f>((Population!C123/100)*H4)*1000</f>
+        <v>352.17284527271283</v>
+      </c>
+      <c r="I10" s="35">
+        <f>(Population!C123/100)*I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A11" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="35" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A12" s="63" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" s="64">
+        <v>1</v>
+      </c>
+      <c r="C12" s="64">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="64">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="64">
+        <v>1E-3</v>
+      </c>
+      <c r="F12" s="64">
+        <v>1E-3</v>
+      </c>
+      <c r="G12" s="65">
+        <f>1/0.000277778</f>
+        <v>3599.9971200023037</v>
+      </c>
+      <c r="H12" s="64">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="64">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="71" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="69"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+    </row>
+    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="67" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" s="68" t="s">
+        <v>180</v>
+      </c>
+      <c r="C14" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="68" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" s="68" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16" s="63" t="s">
+        <v>227</v>
+      </c>
+      <c r="B16" s="64">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="C16" s="64">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="D16" s="64">
+        <v>9.9999999999999998E-13</v>
+      </c>
+      <c r="E16" s="64">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F16" s="64">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="G16" s="64">
+        <v>1</v>
+      </c>
+      <c r="H16" s="64">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="I16" s="64">
+        <v>9.9999999999999998E-13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A17" s="31" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" s="22">
+        <f>B2*1000000000/(Population!B120*1000)</f>
+        <v>0.27159144973886129</v>
+      </c>
+      <c r="C17" s="22">
+        <f>C2*1000000000/(Population!B120*1000)</f>
+        <v>124.80971043156613</v>
+      </c>
+      <c r="D17" s="22">
+        <f>D2*1000000000000/(Population!B120*1000)</f>
+        <v>1202.711755067819</v>
+      </c>
+      <c r="E17" s="22">
+        <f>E2*1000000000/(Population!B120*1000)</f>
+        <v>3.8577546860665897</v>
+      </c>
+      <c r="F17" s="22">
+        <f>F2*1000000000/(Population!B120*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="22">
+        <f>G2</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="22">
+        <f>H2*1000000000/(Population!B120*1000)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="22">
+        <f>I2*1000000/(Population!B120*1000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="B18" s="22">
+        <f>B3*1000000000/(Population!B122*1000)</f>
+        <v>0.47274918979548014</v>
+      </c>
+      <c r="C18" s="22">
+        <f>C3*1000000000/(Population!B122*1000)</f>
+        <v>290.89665941740702</v>
+      </c>
+      <c r="D18" s="22">
+        <f>D3*1000000000000/(Population!B122*1000)</f>
+        <v>1309.0349673783317</v>
+      </c>
+      <c r="E18" s="22">
+        <f>E3*1000000000/(Population!B122*1000)</f>
+        <v>5.9218248524257859</v>
+      </c>
+      <c r="F18" s="22">
+        <f>F3*1000000000/(Population!B122*1000)</f>
+        <v>0.46751248834940412</v>
+      </c>
+      <c r="G18" s="22">
+        <f>G3</f>
+        <v>39.6</v>
+      </c>
+      <c r="H18" s="22">
+        <f>H3*1000000000/(Population!B122*1000)</f>
+        <v>2.5972916019411341</v>
+      </c>
+      <c r="I18" s="51">
+        <f>I3/(Population!B122*1000)*1000000000000</f>
+        <v>675.29581650469493</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A19" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="B19" s="22">
+        <f>B4*1000000000/(Population!B122*1000)</f>
+        <v>2.1906118947334106</v>
+      </c>
+      <c r="C19" s="22">
+        <f>C4*1000000000/(Population!B122*1000)</f>
+        <v>467.51248834940412</v>
+      </c>
+      <c r="D19" s="22">
+        <f>D4*1000000000000/(Population!B122*1000)</f>
+        <v>1516.8182955336224</v>
+      </c>
+      <c r="E19" s="22">
+        <f>E4*1000000000/(Population!B122*1000)</f>
+        <v>7.6879831417457574</v>
+      </c>
+      <c r="F19" s="22">
+        <f>F4*1000000000/(Population!B122*1000)</f>
+        <v>0.93502497669880824</v>
+      </c>
+      <c r="G19" s="22">
+        <f>G4</f>
+        <v>49</v>
+      </c>
+      <c r="H19" s="22">
+        <f>H4*1000000000/(Population!B122*1000)</f>
+        <v>5.1945832038822681</v>
+      </c>
+      <c r="I19" s="22">
+        <f>I4*1000000/(Population!B122*1000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="H20" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" s="33" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A21" s="63" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" s="66">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="C21" s="66">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="D21" s="66">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="E21" s="66">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="F21" s="66">
+        <v>1.0000000000000001E-9</v>
+      </c>
+      <c r="G21" s="66">
+        <v>1E-3</v>
+      </c>
+      <c r="H21" s="66">
+        <v>1E-3</v>
+      </c>
+      <c r="I21" s="66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A23" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="28">
+        <f>(Capacité!C43/100)*B3</f>
+        <v>2.3996335569770794E-3</v>
+      </c>
+      <c r="C23" s="28">
+        <f>(Capacité!C43/100)*C3</f>
+        <v>1.4765660113611818</v>
+      </c>
+      <c r="D23" s="28">
+        <f>(Capacité!C43/100)*D3</f>
+        <v>6.6445470511253182E-3</v>
+      </c>
+      <c r="E23" s="28">
+        <f>(Capacité!C43/100)*E3</f>
+        <v>3.0058665231281204E-2</v>
+      </c>
+      <c r="F23" s="28">
+        <f>(Capacité!C43/100)*F3</f>
+        <v>2.3730525182590425E-3</v>
+      </c>
+      <c r="G23" s="28">
+        <f>(Capacité!C43/100)*G3</f>
+        <v>2.0882862160679572E-2</v>
+      </c>
+      <c r="H23" s="28">
+        <f>((Capacité!C42/100)*H3)*1000</f>
+        <v>13.743345116682876</v>
+      </c>
+      <c r="I23" s="28">
+        <f>(Capacité!C43/100)*I3</f>
+        <v>3.4277425263741722E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A24" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="28">
+        <f>(Capacité!C43/100)*B4</f>
+        <v>1.11193544619073E-2</v>
+      </c>
+      <c r="C24" s="28">
+        <f>(Capacité!C43/100)*C4</f>
+        <v>2.3730525182590423</v>
+      </c>
+      <c r="D24" s="28">
+        <f>(Capacité!C43/100)*D4</f>
+        <v>7.6992370592404488E-3</v>
+      </c>
+      <c r="E24" s="28">
+        <f>(Capacité!C43/100)*E4</f>
+        <v>3.9023530300259811E-2</v>
+      </c>
+      <c r="F24" s="28">
+        <f>(Capacité!C43/100)*F4</f>
+        <v>4.746105036518085E-3</v>
+      </c>
+      <c r="G24" s="28">
+        <f>(Capacité!C43/100)*G4</f>
+        <v>2.5839905198820682E-2</v>
+      </c>
+      <c r="H24" s="28">
+        <f>((Capacité!C43/100)*H4)*1000</f>
+        <v>26.367250202878246</v>
+      </c>
+      <c r="I24" s="28">
+        <f>(Capacité!C43/100)*I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A25" s="19"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A26" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="21.15234375" customWidth="1"/>
+    <col min="4" max="4" width="14.07421875" customWidth="1"/>
+    <col min="9" max="10" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.84375" style="28" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="18" t="s">
         <v>76</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>197</v>
+        <v>1</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="H1" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="K1" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="I1" s="18" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2">
         <f>(1.33*170+163.83)/74</f>
         <v>5.2693243243243248</v>
       </c>
-      <c r="C2" s="28">
-        <v>1100</v>
-      </c>
-      <c r="D2" s="28">
-        <v>10.6</v>
-      </c>
-      <c r="E2" s="28">
-        <v>43</v>
-      </c>
-      <c r="F2" s="28">
-        <v>4.5</v>
-      </c>
-      <c r="G2" s="28">
+      <c r="C2">
+        <v>2800</v>
+      </c>
+      <c r="D2">
+        <v>12.6</v>
+      </c>
+      <c r="E2">
+        <v>28.5</v>
+      </c>
+      <c r="F2">
+        <v>1.87</v>
+      </c>
+      <c r="G2">
         <v>39.6</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2">
         <v>25</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2">
         <v>3724</v>
       </c>
       <c r="K2" s="28">
-        <f>(0.258-K3)/K3</f>
-        <v>1.7156275560546412</v>
-      </c>
-      <c r="L2" s="28">
+        <v>3724</v>
+      </c>
+      <c r="L2" t="e">
         <f>0.258/K3</f>
-        <v>2.7156275560546415</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3">
         <f>(1.33*1055+163.83)/74</f>
         <v>21.175405405405407</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3">
         <v>4500</v>
       </c>
-      <c r="D3" s="28">
-        <v>14.6</v>
-      </c>
-      <c r="E3" s="28">
-        <v>57</v>
-      </c>
-      <c r="F3" s="28">
-        <v>9</v>
-      </c>
-      <c r="G3" s="28">
+      <c r="D3">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E3">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="F3">
+        <v>17</v>
+      </c>
+      <c r="G3">
         <v>49</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3">
         <v>50</v>
       </c>
-      <c r="K3" s="28">
-        <f>Population!C113*Synthèse!D2/100</f>
-        <v>9.5005664316807653E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="I3">
+        <v>26068</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="16" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>190</v>
+        <v>6</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>77</v>
@@ -1536,19 +2352,15 @@
       <c r="I4" s="15" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K4" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="19"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K5" s="20"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="34" t="s">
         <v>14</v>
       </c>
@@ -1560,725 +2372,9 @@
       <c r="G6" s="35"/>
       <c r="H6" s="35"/>
       <c r="I6" s="35"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="B7" s="29">
-        <v>1E-3</v>
-      </c>
-      <c r="C7" s="28">
-        <v>1</v>
-      </c>
-      <c r="D7" s="29">
-        <v>1E-3</v>
-      </c>
-      <c r="E7" s="29">
-        <v>1E-3</v>
-      </c>
-      <c r="F7" s="29">
-        <v>1E-3</v>
-      </c>
-      <c r="G7" s="28">
-        <v>2.7777800000000001E-4</v>
-      </c>
-      <c r="H7" s="29">
-        <v>1E-3</v>
-      </c>
-      <c r="I7" s="29">
-        <v>1</v>
-      </c>
-      <c r="K7" s="28">
-        <f>269/100 -1</f>
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="48">
-        <f>((Population!C123/100)*B2)/B7</f>
-        <v>37.114258799240247</v>
-      </c>
-      <c r="C8" s="35">
-        <f>(Population!C123/100)*C2</f>
-        <v>7.7478025959996817</v>
-      </c>
-      <c r="D8" s="35">
-        <f>((Population!C123/100)*D2)*1000</f>
-        <v>74.660643197815105</v>
-      </c>
-      <c r="E8" s="35">
-        <f>((Population!C123/100)*E2)*1000</f>
-        <v>302.86864693453305</v>
-      </c>
-      <c r="F8" s="35">
-        <f>((Population!C123/100)*F2)*1000</f>
-        <v>31.695556074544147</v>
-      </c>
-      <c r="G8" s="35">
-        <f>(G2*Population!C115)*0.000277778</f>
-        <v>738.39512671562909</v>
-      </c>
-      <c r="H8" s="35">
-        <f>((Population!C123/100)*H2)*1000</f>
-        <v>176.08642263635642</v>
-      </c>
-      <c r="I8" s="35">
-        <f>(Population!C123/100)*I2</f>
-        <v>26.22983351591165</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="B9" s="35">
-        <f>((Population!C123/100)*B3)*1000</f>
-        <v>149.14805542849609</v>
-      </c>
-      <c r="C9" s="35">
-        <f>(Population!C123/100)*C3</f>
-        <v>31.69555607454415</v>
-      </c>
-      <c r="D9" s="35">
-        <f>((Population!C123/100)*D3)*1000</f>
-        <v>102.83447081963213</v>
-      </c>
-      <c r="E9" s="35">
-        <f>((Population!C123/100)*E3)*1000</f>
-        <v>401.47704361089257</v>
-      </c>
-      <c r="F9" s="35">
-        <f>((Population!C123/100)*F3)*1000</f>
-        <v>63.391112149088293</v>
-      </c>
-      <c r="G9" s="35">
-        <f>(G3*Population!C115)*0.000366668</f>
-        <v>1206.0487944160323</v>
-      </c>
-      <c r="H9" s="35">
-        <f>((Population!C123/100)*H3)*1000</f>
-        <v>352.17284527271283</v>
-      </c>
-      <c r="I9" s="35">
-        <f>(Population!C123/100)*I3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A11" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="G11" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="H11" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="I11" s="35" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="B12" s="29">
-        <v>1</v>
-      </c>
-      <c r="C12" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D12" s="29">
-        <v>1000</v>
-      </c>
-      <c r="E12" s="29">
-        <v>1E-3</v>
-      </c>
-      <c r="F12" s="29">
-        <v>1E-3</v>
-      </c>
-      <c r="G12" s="28">
-        <f>1/0.000277778</f>
-        <v>3599.9971200023037</v>
-      </c>
-      <c r="H12" s="29">
-        <v>1000</v>
-      </c>
-      <c r="I12" s="29">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A13" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16" s="49" t="s">
-        <v>211</v>
-      </c>
-      <c r="B16" s="50">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="C16" s="50">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="D16" s="50">
-        <v>9.9999999999999998E-13</v>
-      </c>
-      <c r="E16" s="50">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F16" s="50">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="G16" s="50">
-        <v>1</v>
-      </c>
-      <c r="H16" s="50">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="I16" s="50">
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A17" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="B17" s="22">
-        <f>B2*1000000000/(Population!B122*1000)</f>
-        <v>0.54743887261886837</v>
-      </c>
-      <c r="C17" s="22">
-        <f>C2*1000000000/(Population!B122*1000)</f>
-        <v>114.28083048540991</v>
-      </c>
-      <c r="D17" s="22">
-        <f>D2*1000000000000/(Population!B122*1000)</f>
-        <v>1101.2516392230409</v>
-      </c>
-      <c r="E17" s="22">
-        <f>E2*1000000000/(Population!B122*1000)</f>
-        <v>4.4673415553387503</v>
-      </c>
-      <c r="F17" s="22">
-        <f>F2*1000000000/(Population!B122*1000)</f>
-        <v>0.46751248834940412</v>
-      </c>
-      <c r="G17" s="22">
-        <f>G2</f>
-        <v>39.6</v>
-      </c>
-      <c r="H17" s="22">
-        <f>H2*1000000000/(Population!B122*1000)</f>
-        <v>2.5972916019411341</v>
-      </c>
-      <c r="I17" s="22">
-        <f>I2*1000000/(Population!B122*1000)</f>
-        <v>0.38689255702515135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A18" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="B18" s="22">
-        <f>B3*1000000000/(Population!B122*1000)</f>
-        <v>2.1999481050863343</v>
-      </c>
-      <c r="C18" s="22">
-        <f>C3*1000000000/(Population!B122*1000)</f>
-        <v>467.51248834940412</v>
-      </c>
-      <c r="D18" s="22">
-        <f>D3*1000000000000/(Population!B122*1000)</f>
-        <v>1516.8182955336224</v>
-      </c>
-      <c r="E18" s="22">
-        <f>E3*1000000000/(Population!B122*1000)</f>
-        <v>5.9218248524257859</v>
-      </c>
-      <c r="F18" s="22">
-        <f>F3*1000000000/(Population!B122*1000)</f>
-        <v>0.93502497669880824</v>
-      </c>
-      <c r="G18" s="22">
-        <f>G3</f>
-        <v>49</v>
-      </c>
-      <c r="H18" s="22">
-        <f>H3*1000000000/(Population!B122*1000)</f>
-        <v>5.1945832038822681</v>
-      </c>
-      <c r="I18" s="22">
-        <f>I3*1000000/(Population!B122*1000)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A19" s="32" t="s">
-        <v>191</v>
-      </c>
-      <c r="B19" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>80</v>
-      </c>
-      <c r="G19" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="I19" s="33" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="B20" s="45">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="C20" s="45">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="D20" s="45">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="E20" s="45">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="F20" s="45">
-        <v>1.0000000000000001E-9</v>
-      </c>
-      <c r="G20" s="45">
-        <v>1E-3</v>
-      </c>
-      <c r="H20" s="45">
-        <v>1E-3</v>
-      </c>
-      <c r="I20" s="45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A22" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="28">
-        <f>(Capacité!C43/100)*B2</f>
-        <v>2.7787518571914371E-3</v>
-      </c>
-      <c r="C22" s="28">
-        <f>(Capacité!C43/100)*C2</f>
-        <v>0.58007950446332146</v>
-      </c>
-      <c r="D22" s="28">
-        <f>(Capacité!C43/100)*D2</f>
-        <v>5.5898570430101885E-3</v>
-      </c>
-      <c r="E22" s="28">
-        <f>(Capacité!C43/100)*E2</f>
-        <v>2.2675835174475294E-2</v>
-      </c>
-      <c r="F22" s="28">
-        <f>(Capacité!C43/100)*F2</f>
-        <v>2.3730525182590425E-3</v>
-      </c>
-      <c r="G22" s="28">
-        <f>(Capacité!C43/100)*G2</f>
-        <v>2.0882862160679572E-2</v>
-      </c>
-      <c r="H22" s="28">
-        <f>((Capacité!C42/100)*H2)*1000</f>
-        <v>13.743345116682876</v>
-      </c>
-      <c r="I22" s="28">
-        <f>(Capacité!C43/100)*I2</f>
-        <v>1.963832795110372</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A23" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="B23" s="28">
-        <f>(Capacité!C43/100)*B3</f>
-        <v>1.1166744249434098E-2</v>
-      </c>
-      <c r="C23" s="28">
-        <f>(Capacité!C43/100)*C3</f>
-        <v>2.3730525182590423</v>
-      </c>
-      <c r="D23" s="28">
-        <f>(Capacité!C43/100)*D3</f>
-        <v>7.6992370592404488E-3</v>
-      </c>
-      <c r="E23" s="28">
-        <f>(Capacité!C43/100)*E3</f>
-        <v>3.0058665231281204E-2</v>
-      </c>
-      <c r="F23" s="28">
-        <f>(Capacité!C43/100)*F3</f>
-        <v>4.746105036518085E-3</v>
-      </c>
-      <c r="G23" s="28">
-        <f>(Capacité!C43/100)*G3</f>
-        <v>2.5839905198820682E-2</v>
-      </c>
-      <c r="H23" s="28">
-        <f>((Capacité!C43/100)*H3)*1000</f>
-        <v>26.367250202878246</v>
-      </c>
-      <c r="I23" s="28">
-        <f>(Capacité!C43/100)*I3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A24" s="19"/>
-    </row>
-    <row r="25" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A25" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="15"/>
-    </row>
-    <row r="26" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A26" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A27" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B27" s="28">
-        <f>B2*Besoins!B5*1000</f>
-        <v>33.599043710798185</v>
-      </c>
-      <c r="C27" s="28" t="e">
-        <f>C2*Besoins!C5</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D27" s="28" t="e">
-        <f>D2*Besoins!D5*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H27" s="28">
-        <f>H2*Besoins!E5*1000</f>
-        <v>183.26764541723307</v>
-      </c>
-      <c r="I27" s="28" t="e">
-        <f>I2*Besoins!G5</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A28" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B28" s="28">
-        <f>B3*Besoins!B5*1000</f>
-        <v>135.02174624662513</v>
-      </c>
-      <c r="C28" s="28" t="e">
-        <f>C3*Besoins!C5</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D28" s="28" t="e">
-        <f>D3*Besoins!D5*1000</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H28" s="28">
-        <f>H3*Besoins!E5*1000</f>
-        <v>366.53529083446614</v>
-      </c>
-      <c r="I28" s="28" t="e">
-        <f>I3*Besoins!G5</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A29" s="19"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="21.1328125" customWidth="1"/>
-    <col min="4" max="4" width="14.06640625" customWidth="1"/>
-    <col min="9" max="10" width="11.86328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="I1" s="18" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2">
-        <f>(1.33*170+163.83)/74</f>
-        <v>5.2693243243243248</v>
-      </c>
-      <c r="C2">
-        <v>2800</v>
-      </c>
-      <c r="D2">
-        <v>12.6</v>
-      </c>
-      <c r="E2">
-        <v>28.5</v>
-      </c>
-      <c r="F2">
-        <v>1.87</v>
-      </c>
-      <c r="G2">
-        <v>39.6</v>
-      </c>
-      <c r="H2">
-        <v>25</v>
-      </c>
-      <c r="I2">
-        <v>3724</v>
-      </c>
-      <c r="K2">
-        <f>(0.258-K3)/K3</f>
-        <v>1.2845755630300952</v>
-      </c>
-      <c r="L2">
-        <f>0.258/K3</f>
-        <v>2.2845755630300952</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3">
-        <f>(1.33*1055+163.83)/74</f>
-        <v>21.175405405405407</v>
-      </c>
-      <c r="C3">
-        <v>4500</v>
-      </c>
-      <c r="D3">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="E3">
-        <v>37.700000000000003</v>
-      </c>
-      <c r="F3">
-        <v>17</v>
-      </c>
-      <c r="G3">
-        <v>49</v>
-      </c>
-      <c r="H3">
-        <v>50</v>
-      </c>
-      <c r="I3">
-        <v>26068</v>
-      </c>
-      <c r="K3">
-        <f>Population!C113*'Synthèse v2'!D2/100</f>
-        <v>0.11293126135771475</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" s="19"/>
-      <c r="K5">
-        <f>269/100 -1</f>
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K6" s="35"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="34" t="s">
         <v>88</v>
       </c>
@@ -2314,8 +2410,11 @@
         <f>(Population!C116/100)*I2</f>
         <v>28.803801226076825</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K7" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="34" t="s">
         <v>101</v>
       </c>
@@ -2352,8 +2451,12 @@
         <v>201.62660858253778</v>
       </c>
       <c r="J8" s="28"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K8" s="35">
+        <f>(Population!E123/100)*K2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="34"/>
       <c r="B9" s="35"/>
       <c r="C9" s="35"/>
@@ -2363,8 +2466,12 @@
       <c r="G9" s="35"/>
       <c r="H9" s="35"/>
       <c r="I9" s="35"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K9" s="35">
+        <f>(Population!E123/100)*K3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="34" t="s">
         <v>86</v>
       </c>
@@ -2392,8 +2499,9 @@
       <c r="I10" s="35" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K10" s="35"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
         <v>83</v>
       </c>
@@ -2422,8 +2530,11 @@
       <c r="I11" s="29">
         <v>10000000000</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="K11" s="35" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="16" t="s">
         <v>85</v>
       </c>
@@ -2451,8 +2562,11 @@
       <c r="I12" s="15" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K12" s="29">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -2462,8 +2576,11 @@
       <c r="G13" s="20"/>
       <c r="H13" s="20"/>
       <c r="I13" s="20"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K13" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="31" t="s">
         <v>90</v>
       </c>
@@ -2475,8 +2592,9 @@
       <c r="G14" s="22"/>
       <c r="H14" s="22"/>
       <c r="I14" s="22"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="31" t="s">
         <v>134</v>
       </c>
@@ -2512,8 +2630,9 @@
         <f>I2*1000000/(Population!B115*1000)</f>
         <v>0.42909555534257776</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K15" s="22"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="31" t="s">
         <v>135</v>
       </c>
@@ -2549,8 +2668,11 @@
         <f>I3*1000000/(Population!B115*1000)</f>
         <v>3.0036688873980446</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="K16" s="49">
+        <v>9.9999999999999995E-7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="32" t="s">
         <v>5</v>
       </c>
@@ -2578,8 +2700,12 @@
       <c r="I17" s="33" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="K17" s="22">
+        <f>K2*1000000/(Population!D122*1000)</f>
+        <v>9.2556771496873207</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="19"/>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -2589,8 +2715,12 @@
       <c r="G18" s="20"/>
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="K18" s="22">
+        <f>K3*1000000/(Population!D122*1000)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="19" t="s">
         <v>16</v>
       </c>
@@ -2626,8 +2756,11 @@
         <f>(Capacité!C43/100)*I2</f>
         <v>1.963832795110372</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="K19" s="33" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
         <v>102</v>
       </c>
@@ -2663,17 +2796,25 @@
         <f>(Capacité!C43/100)*I3</f>
         <v>13.746829565772604</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="K20" s="45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="19"/>
-    </row>
-    <row r="22" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="19" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="15"/>
-    </row>
-    <row r="23" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="K22" s="28">
+        <f>(Capacité!E43/100)*K2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="16" t="s">
         <v>109</v>
       </c>
@@ -2685,8 +2826,12 @@
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
       <c r="I23" s="15"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="K23" s="28">
+        <f>(Capacité!E43/100)*K3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
         <v>108</v>
       </c>
@@ -2714,7 +2859,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
         <v>114</v>
       </c>
@@ -2742,8 +2887,21 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="19"/>
+      <c r="K26" s="15"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K27" s="28">
+        <f>K2*Besoins!I5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="K28" s="28">
+        <f>K3*Besoins!I5</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2753,18 +2911,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0A75E4-DA25-4A08-8974-1A31A91FD529}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.07421875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="11.06640625" style="28"/>
-    <col min="3" max="4" width="12.3984375" style="28" customWidth="1"/>
-    <col min="5" max="5" width="11.9296875" style="28" customWidth="1"/>
-    <col min="6" max="6" width="11.06640625" style="28"/>
-    <col min="7" max="7" width="14.86328125" style="28" customWidth="1"/>
-    <col min="8" max="16384" width="11.06640625" style="28"/>
+    <col min="1" max="1" width="27.69140625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="11.07421875" style="28"/>
+    <col min="3" max="4" width="12.3828125" style="28" customWidth="1"/>
+    <col min="5" max="5" width="11.921875" style="28" customWidth="1"/>
+    <col min="6" max="6" width="11.07421875" style="28"/>
+    <col min="7" max="7" width="14.84375" style="28" customWidth="1"/>
+    <col min="8" max="16384" width="11.07421875" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="23" t="s">
         <v>76</v>
       </c>
@@ -2787,7 +2945,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
         <v>130</v>
       </c>
@@ -2813,7 +2971,7 @@
         <v>4.0776939000000005E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
         <v>131</v>
       </c>
@@ -2839,7 +2997,7 @@
         <v>2.9475940000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
         <v>163</v>
       </c>
@@ -2868,7 +3026,7 @@
         <v>3.5126439500000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
         <v>5</v>
       </c>
@@ -2891,12 +3049,12 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="28" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="28" t="s">
         <v>105</v>
       </c>
@@ -2922,7 +3080,7 @@
         <v>2.7340017428936065E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="28" t="s">
         <v>106</v>
       </c>
@@ -2948,7 +3106,7 @@
         <v>1.9682472147114907E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="28" t="s">
         <v>110</v>
       </c>
@@ -2977,7 +3135,7 @@
         <v>2.3511244788025486E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="28" t="s">
         <v>5</v>
       </c>
@@ -3000,7 +3158,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="30" t="s">
         <v>95</v>
       </c>
@@ -3029,7 +3187,7 @@
         <v>17.921343875225901</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="30" t="s">
         <v>96</v>
       </c>
@@ -3058,7 +3216,7 @@
         <v>12.954588297702438</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="30" t="s">
         <v>164</v>
       </c>
@@ -3087,7 +3245,7 @@
         <v>15.43796608646417</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="30" t="s">
         <v>5</v>
       </c>
@@ -3110,31 +3268,31 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="52"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
       <c r="F18" s="21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="G21" s="28" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="G22" s="28" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="G23" s="28" t="s">
         <v>127</v>
       </c>
@@ -3155,27 +3313,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1104A7-2272-4986-AE6B-8EA45794950A}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="27.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.9296875" customWidth="1"/>
+    <col min="1" max="1" width="27.69140625" customWidth="1"/>
+    <col min="3" max="3" width="11.921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="23" t="s">
         <v>76</v>
       </c>
       <c r="B1" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
         <v>130</v>
       </c>
@@ -3190,7 +3348,7 @@
         <v>26.509803921568629</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
         <v>131</v>
       </c>
@@ -3205,7 +3363,7 @@
         <v>15.600000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
         <v>163</v>
       </c>
@@ -3222,7 +3380,7 @@
         <v>21.054901960784314</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
         <v>5</v>
       </c>
@@ -3236,12 +3394,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>105</v>
       </c>
@@ -3256,7 +3414,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>106</v>
       </c>
@@ -3271,7 +3429,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="28" t="s">
         <v>110</v>
       </c>
@@ -3288,7 +3446,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -3302,7 +3460,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="30" t="s">
         <v>95</v>
       </c>
@@ -3319,7 +3477,7 @@
         <v>494.3108592392208</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="30" t="s">
         <v>96</v>
       </c>
@@ -3336,7 +3494,7 @@
         <v>290.88292870615692</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A15" s="30" t="s">
         <v>164</v>
       </c>
@@ -3353,7 +3511,7 @@
         <v>392.59689397268886</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" s="30" t="s">
         <v>5</v>
       </c>
@@ -3367,14 +3525,14 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="52"/>
+      <c r="C18" s="53"/>
       <c r="D18" s="21" t="s">
         <v>104</v>
       </c>
@@ -3395,132 +3553,132 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE59BEB1-58EA-414F-91E0-ADFFF27E94F9}">
   <dimension ref="A2:U6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.06640625" style="28"/>
+    <col min="1" max="1" width="11.07421875" style="28"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="57" t="s">
+    <row r="2" spans="1:21" ht="16.3" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B2" s="58" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="58" t="s">
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="57" t="s">
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58" t="s">
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="L2" s="58"/>
-      <c r="M2" s="59" t="s">
+      <c r="L2" s="59"/>
+      <c r="M2" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="N2" s="53" t="s">
+      <c r="N2" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="O2" s="57" t="s">
+      <c r="O2" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="58" t="s">
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="S2" s="58"/>
-      <c r="T2" s="60" t="s">
+      <c r="S2" s="59"/>
+      <c r="T2" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="U2" s="56" t="s">
+      <c r="U2" s="57" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="17.649999999999999" x14ac:dyDescent="0.45">
-      <c r="B3" s="54" t="s">
+    <row r="3" spans="1:21" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="B3" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="55" t="s">
         <v>145</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="56" t="s">
         <v>146</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="56" t="s">
         <v>147</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="H3" s="54" t="s">
+      <c r="H3" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="I3" s="54" t="s">
+      <c r="I3" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="J3" s="54" t="s">
+      <c r="J3" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="K3" s="55" t="s">
+      <c r="K3" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="56" t="s">
         <v>153</v>
       </c>
-      <c r="M3" s="59"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="54" t="s">
+      <c r="M3" s="60"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="55" t="s">
         <v>154</v>
       </c>
-      <c r="P3" s="54" t="s">
+      <c r="P3" s="55" t="s">
         <v>155</v>
       </c>
       <c r="Q3" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="R3" s="55" t="s">
+      <c r="R3" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="S3" s="55" t="s">
+      <c r="S3" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="T3" s="60"/>
-      <c r="U3" s="56"/>
-    </row>
-    <row r="4" spans="1:21" ht="38" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="54"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="59"/>
-      <c r="N4" s="53"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
+      <c r="T3" s="61"/>
+      <c r="U3" s="57"/>
+    </row>
+    <row r="4" spans="1:21" ht="38.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="55"/>
+      <c r="P4" s="55"/>
       <c r="Q4" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="56"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="61"/>
+      <c r="U4" s="57"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A5" s="28" t="s">
         <v>160</v>
       </c>
@@ -3586,7 +3744,7 @@
         <v>15.600000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
       <c r="A6" s="28" t="s">
         <v>13</v>
       </c>
@@ -3627,13 +3785,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95CE491-5889-4A7E-A6ED-A3FC6F8FA184}">
   <dimension ref="A1:H127"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" customWidth="1"/>
-    <col min="2" max="2" width="12.86328125" customWidth="1"/>
+    <col min="1" max="1" width="12.3828125" customWidth="1"/>
+    <col min="2" max="2" width="12.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="46" t="s">
         <v>18</v>
       </c>
@@ -3647,7 +3805,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -3661,7 +3819,7 @@
         <v>419997.47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -3675,7 +3833,7 @@
         <v>421419.174</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -3689,7 +3847,7 @@
         <v>422863.59999999992</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -3703,7 +3861,7 @@
         <v>424104.70499999996</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -3717,7 +3875,7 @@
         <v>425188.98800000019</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -3731,7 +3889,7 @@
         <v>425847.82800000004</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -3745,7 +3903,7 @@
         <v>426181.87299999996</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -3759,7 +3917,7 @@
         <v>426651.66799999989</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -3773,7 +3931,7 @@
         <v>426655.42999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -3787,7 +3945,7 @@
         <v>426830.63099999999</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -3801,7 +3959,7 @@
         <v>427627.31800000009</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -3815,7 +3973,7 @@
         <v>428578.28599999996</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -3829,7 +3987,7 @@
         <v>429890.46400000004</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -3843,7 +4001,7 @@
         <v>431461.80999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -3857,7 +4015,7 @@
         <v>433058.58899999998</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -3871,7 +4029,7 @@
         <v>434557.12100000004</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -3885,7 +4043,7 @@
         <v>435683.11500000011</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -3899,7 +4057,7 @@
         <v>436994.47300000006</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -3913,7 +4071,7 @@
         <v>438548.18900000007</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -3927,7 +4085,7 @@
         <v>439690.78899999993</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -3941,7 +4099,7 @@
         <v>440608.95100000006</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -3955,7 +4113,7 @@
         <v>441440.62800000008</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -3969,7 +4127,7 @@
         <v>441999.21399999998</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -3983,7 +4141,7 @@
         <v>442399.391</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -3997,7 +4155,7 @@
         <v>442964.72000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -4011,7 +4169,7 @@
         <v>443910.90800000017</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -4025,7 +4183,7 @@
         <v>444911.48800000001</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -4039,7 +4197,7 @@
         <v>445696.74599999998</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -4053,7 +4211,7 @@
         <v>446503.6480000001</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -4067,7 +4225,7 @@
         <v>447369.19099999999</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -4081,7 +4239,7 @@
         <v>447777.53599999996</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -4095,7 +4253,7 @@
         <v>447705.902</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -4109,7 +4267,7 @@
         <v>449113.45499999996</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -4123,7 +4281,7 @@
         <v>450657.52199999994</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -4137,7 +4295,7 @@
         <v>450259.53600000002</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" s="1">
         <v>2025</v>
       </c>
@@ -4151,7 +4309,7 @@
         <v>448992.58499999996</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" s="1">
         <v>2026</v>
       </c>
@@ -4165,7 +4323,7 @@
         <v>447890.473</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39" s="1">
         <v>2027</v>
       </c>
@@ -4179,7 +4337,7 @@
         <v>447205.74899999995</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40" s="1">
         <v>2028</v>
       </c>
@@ -4193,7 +4351,7 @@
         <v>446459.31699999998</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41" s="1">
         <v>2029</v>
       </c>
@@ -4207,7 +4365,7 @@
         <v>445651.23500000004</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42" s="1">
         <v>2030</v>
       </c>
@@ -4221,7 +4379,7 @@
         <v>444782.38100000005</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43" s="1">
         <v>2031</v>
       </c>
@@ -4235,7 +4393,7 @@
         <v>443853.3349999999</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44" s="1">
         <v>2032</v>
       </c>
@@ -4249,7 +4407,7 @@
         <v>442896.55800000002</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A45" s="1">
         <v>2033</v>
       </c>
@@ -4263,7 +4421,7 @@
         <v>441929.64600000007</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A46" s="1">
         <v>2034</v>
       </c>
@@ -4277,7 +4435,7 @@
         <v>440942.37400000007</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A47" s="1">
         <v>2035</v>
       </c>
@@ -4291,7 +4449,7 @@
         <v>439928.23599999998</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A48" s="1">
         <v>2036</v>
       </c>
@@ -4305,7 +4463,7 @@
         <v>438876.35599999991</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A49" s="1">
         <v>2037</v>
       </c>
@@ -4319,7 +4477,7 @@
         <v>437800.28700000013</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A50" s="1">
         <v>2038</v>
       </c>
@@ -4333,7 +4491,7 @@
         <v>436704.79599999997</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A51" s="1">
         <v>2039</v>
       </c>
@@ -4347,7 +4505,7 @@
         <v>435575.79399999999</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A52" s="1">
         <v>2040</v>
       </c>
@@ -4361,7 +4519,7 @@
         <v>434422.40100000007</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A53" s="1">
         <v>2041</v>
       </c>
@@ -4375,7 +4533,7 @@
         <v>433267.647</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A54" s="1">
         <v>2042</v>
       </c>
@@ -4389,7 +4547,7 @@
         <v>432096.70899999997</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A55" s="1">
         <v>2043</v>
       </c>
@@ -4403,7 +4561,7 @@
         <v>430874.26299999998</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A56" s="1">
         <v>2044</v>
       </c>
@@ -4417,7 +4575,7 @@
         <v>429598.62099999987</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A57" s="1">
         <v>2045</v>
       </c>
@@ -4431,7 +4589,7 @@
         <v>428280.46499999997</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A58" s="1">
         <v>2046</v>
       </c>
@@ -4445,7 +4603,7 @@
         <v>426921.04200000002</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A59" s="1">
         <v>2047</v>
       </c>
@@ -4459,7 +4617,7 @@
         <v>425511.16099999996</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A60" s="1">
         <v>2048</v>
       </c>
@@ -4473,7 +4631,7 @@
         <v>424046.07800000015</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A61" s="1">
         <v>2049</v>
       </c>
@@ -4487,7 +4645,7 @@
         <v>422524.55599999998</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A62" s="1">
         <v>2050</v>
       </c>
@@ -4501,7 +4659,7 @@
         <v>420955.34100000001</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A63" s="1">
         <v>2051</v>
       </c>
@@ -4515,7 +4673,7 @@
         <v>419346.89500000008</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A64" s="1">
         <v>2052</v>
       </c>
@@ -4529,7 +4687,7 @@
         <v>417691.14999999997</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A65" s="1">
         <v>2053</v>
       </c>
@@ -4543,7 +4701,7 @@
         <v>415966.71600000001</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A66" s="1">
         <v>2054</v>
       </c>
@@ -4557,7 +4715,7 @@
         <v>414174.85799999995</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A67" s="1">
         <v>2055</v>
       </c>
@@ -4571,7 +4729,7 @@
         <v>412334.533</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A68" s="1">
         <v>2056</v>
       </c>
@@ -4585,7 +4743,7 @@
         <v>410448.42000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A69" s="1">
         <v>2057</v>
       </c>
@@ -4599,7 +4757,7 @@
         <v>408533.27399999992</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A70" s="1">
         <v>2058</v>
       </c>
@@ -4613,7 +4771,7 @@
         <v>406603.29399999999</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A71" s="1">
         <v>2059</v>
       </c>
@@ -4627,7 +4785,7 @@
         <v>404661.71100000007</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A72" s="1">
         <v>2060</v>
       </c>
@@ -4641,7 +4799,7 @@
         <v>402712.63299999991</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A73" s="1">
         <v>2061</v>
       </c>
@@ -4655,7 +4813,7 @@
         <v>400766.93200000015</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A74" s="1">
         <v>2062</v>
       </c>
@@ -4669,7 +4827,7 @@
         <v>398823.46799999999</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A75" s="1">
         <v>2063</v>
       </c>
@@ -4683,7 +4841,7 @@
         <v>396899.60199999996</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A76" s="1">
         <v>2064</v>
       </c>
@@ -4697,7 +4855,7 @@
         <v>395004.61700000003</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A77" s="1">
         <v>2065</v>
       </c>
@@ -4711,7 +4869,7 @@
         <v>393131.79000000004</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A78" s="1">
         <v>2066</v>
       </c>
@@ -4725,7 +4883,7 @@
         <v>391291.73300000001</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A79" s="1">
         <v>2067</v>
       </c>
@@ -4739,7 +4897,7 @@
         <v>389489.04200000002</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A80" s="1">
         <v>2068</v>
       </c>
@@ -4753,7 +4911,7 @@
         <v>387721.924</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A81" s="1">
         <v>2069</v>
       </c>
@@ -4767,7 +4925,7 @@
         <v>385994.04200000007</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A82" s="1">
         <v>2070</v>
       </c>
@@ -4781,7 +4939,7 @@
         <v>384310.26799999998</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A83" s="1">
         <v>2071</v>
       </c>
@@ -4795,7 +4953,7 @@
         <v>382670.826</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A84" s="1">
         <v>2072</v>
       </c>
@@ -4809,7 +4967,7 @@
         <v>381068.141</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A85" s="1">
         <v>2073</v>
       </c>
@@ -4823,7 +4981,7 @@
         <v>379495.90099999995</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A86" s="1">
         <v>2074</v>
       </c>
@@ -4837,7 +4995,7 @@
         <v>377958.35600000003</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A87" s="1">
         <v>2075</v>
       </c>
@@ -4851,7 +5009,7 @@
         <v>376480.08500000008</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A88" s="1">
         <v>2076</v>
       </c>
@@ -4865,7 +5023,7 @@
         <v>375047.78200000006</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A89" s="1">
         <v>2077</v>
       </c>
@@ -4879,7 +5037,7 @@
         <v>373634.73</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A90" s="1">
         <v>2078</v>
       </c>
@@ -4893,7 +5051,7 @@
         <v>372260.67599999998</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A91" s="1">
         <v>2079</v>
       </c>
@@ -4907,7 +5065,7 @@
         <v>370924.19000000006</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A92" s="1">
         <v>2080</v>
       </c>
@@ -4921,7 +5079,7 @@
         <v>369621.90600000002</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A93" s="1">
         <v>2081</v>
       </c>
@@ -4935,7 +5093,7 @@
         <v>368361.90900000004</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A94" s="1">
         <v>2082</v>
       </c>
@@ -4949,7 +5107,7 @@
         <v>367136.15699999989</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A95" s="1">
         <v>2083</v>
       </c>
@@ -4963,7 +5121,7 @@
         <v>365939.98800000007</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A96" s="1">
         <v>2084</v>
       </c>
@@ -4977,7 +5135,7 @@
         <v>364768.47600000014</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A97" s="1">
         <v>2085</v>
       </c>
@@ -4991,7 +5149,7 @@
         <v>363612.08199999999</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A98" s="1">
         <v>2086</v>
       </c>
@@ -5005,7 +5163,7 @@
         <v>362474.72799999989</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A99" s="1">
         <v>2087</v>
       </c>
@@ -5019,7 +5177,7 @@
         <v>361363.54499999998</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A100" s="1">
         <v>2088</v>
       </c>
@@ -5033,7 +5191,7 @@
         <v>360281.40500000003</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A101" s="1">
         <v>2089</v>
       </c>
@@ -5047,7 +5205,7 @@
         <v>359214.11100000003</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A102" s="1">
         <v>2090</v>
       </c>
@@ -5061,7 +5219,7 @@
         <v>358149.47100000002</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A103" s="1">
         <v>2091</v>
       </c>
@@ -5075,7 +5233,7 @@
         <v>357104.93199999997</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A104" s="1">
         <v>2092</v>
       </c>
@@ -5089,7 +5247,7 @@
         <v>356085.554</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A105" s="1">
         <v>2093</v>
       </c>
@@ -5103,7 +5261,7 @@
         <v>355083.0670000001</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A106" s="1">
         <v>2094</v>
       </c>
@@ -5117,7 +5275,7 @@
         <v>354087.00400000002</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A107" s="1">
         <v>2095</v>
       </c>
@@ -5131,7 +5289,7 @@
         <v>353078.46800000005</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A108" s="1">
         <v>2096</v>
       </c>
@@ -5145,7 +5303,7 @@
         <v>352052.02500000008</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A109" s="1">
         <v>2097</v>
       </c>
@@ -5159,7 +5317,7 @@
         <v>351009.62299999996</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A110" s="1">
         <v>2098</v>
       </c>
@@ -5173,7 +5331,7 @@
         <v>349970.60700000002</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A111" s="1">
         <v>2099</v>
       </c>
@@ -5187,7 +5345,7 @@
         <v>348929.72599999985</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A112" s="1">
         <v>2100</v>
       </c>
@@ -5201,7 +5359,7 @@
         <v>347864.81900000002</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
         <v>167</v>
       </c>
@@ -5217,7 +5375,7 @@
         <v>6.2079223823601231</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
         <v>68</v>
       </c>
@@ -5234,7 +5392,7 @@
         <v>5.9421911649996391</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A115" s="11" t="s">
         <v>189</v>
       </c>
@@ -5251,7 +5409,7 @@
         <v>439497.03716666671</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A116" s="10" t="s">
         <v>21</v>
       </c>
@@ -5268,7 +5426,7 @@
         <v>5.0640769397005476</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A117" s="3" t="s">
         <v>22</v>
       </c>
@@ -5285,7 +5443,7 @@
         <v>403389.38254761917</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
         <v>21</v>
       </c>
@@ -5302,7 +5460,7 @@
         <v>4.2110630256763759</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
         <v>69</v>
       </c>
@@ -5323,9 +5481,9 @@
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
     </row>
-    <row r="120" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A120" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B120" s="4">
         <f>AVERAGE(B31:B62)</f>
@@ -5344,7 +5502,7 @@
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
         <v>21</v>
       </c>
@@ -5361,7 +5519,7 @@
         <v>4.9785141684743905</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A122" s="3" t="s">
         <v>70</v>
       </c>
@@ -5378,7 +5536,7 @@
         <v>402347.65536585363</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
         <v>21</v>
       </c>
@@ -5395,7 +5553,7 @@
         <v>4.1800567453697495</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
         <v>19</v>
       </c>
@@ -5403,9 +5561,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B127" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -5419,14 +5577,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8683F5-D89E-4384-A263-C6122D6DA873}">
   <dimension ref="A1:AK53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" style="28"/>
+    <col min="3" max="3" width="11.84375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.69140625" customWidth="1"/>
+    <col min="9" max="9" width="10.69140625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -5477,7 +5635,7 @@
       <c r="AJ1" s="13"/>
       <c r="AK1" s="13"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>23</v>
       </c>
@@ -5531,7 +5689,7 @@
       <c r="AJ2" s="13"/>
       <c r="AK2" s="13"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>24</v>
       </c>
@@ -5585,7 +5743,7 @@
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>25</v>
       </c>
@@ -5640,7 +5798,7 @@
       <c r="AJ4" s="13"/>
       <c r="AK4" s="13"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>26</v>
       </c>
@@ -5693,7 +5851,7 @@
       <c r="AJ5" s="13"/>
       <c r="AK5" s="13"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>27</v>
       </c>
@@ -5719,7 +5877,7 @@
         <v>14539693914.48213</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>28</v>
       </c>
@@ -5745,7 +5903,7 @@
         <v>14952064687.920418</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
         <v>29</v>
       </c>
@@ -5771,7 +5929,7 @@
         <v>15245174854.3053</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>30</v>
       </c>
@@ -5797,7 +5955,7 @@
         <v>15630580395.880232</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>31</v>
       </c>
@@ -5823,7 +5981,7 @@
         <v>16067461867.683767</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>32</v>
       </c>
@@ -5849,7 +6007,7 @@
         <v>16512311423.171005</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>33</v>
       </c>
@@ -5875,7 +6033,7 @@
         <v>17173198592.745512</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>34</v>
       </c>
@@ -5901,7 +6059,7 @@
         <v>17575027945.751125</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>35</v>
       </c>
@@ -5927,7 +6085,7 @@
         <v>17807088213.890675</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>36</v>
       </c>
@@ -5953,7 +6111,7 @@
         <v>18004403454.357212</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="s">
         <v>37</v>
       </c>
@@ -5979,7 +6137,7 @@
         <v>18502743951.352955</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>38</v>
       </c>
@@ -6005,7 +6163,7 @@
         <v>18893014123.791737</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
         <v>39</v>
       </c>
@@ -6031,7 +6189,7 @@
         <v>19582440522.206104</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19" s="13" t="s">
         <v>40</v>
       </c>
@@ -6057,7 +6215,7 @@
         <v>20221659294.512562</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>41</v>
       </c>
@@ -6083,7 +6241,7 @@
         <v>20401425207.663731</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>42</v>
       </c>
@@ -6109,7 +6267,7 @@
         <v>19535384606.465698</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>43</v>
       </c>
@@ -6136,7 +6294,7 @@
       </c>
       <c r="K22" s="13"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
         <v>44</v>
       </c>
@@ -6162,7 +6320,7 @@
         <v>20396856277.427464</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>45</v>
       </c>
@@ -6188,7 +6346,7 @@
         <v>20238230228.845612</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25" s="13" t="s">
         <v>46</v>
       </c>
@@ -6214,7 +6372,7 @@
         <v>20228258715.518364</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26" s="13" t="s">
         <v>47</v>
       </c>
@@ -6240,7 +6398,7 @@
         <v>20577815766.621822</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27" s="13" t="s">
         <v>48</v>
       </c>
@@ -6266,7 +6424,7 @@
         <v>21081628480.603973</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28" s="13" t="s">
         <v>49</v>
       </c>
@@ -6292,7 +6450,7 @@
         <v>21505364965.621891</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29" s="13" t="s">
         <v>50</v>
       </c>
@@ -6318,7 +6476,7 @@
         <v>22152924720.812515</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30" s="13" t="s">
         <v>51</v>
       </c>
@@ -6344,7 +6502,7 @@
         <v>22640578323.033131</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31" s="13" t="s">
         <v>52</v>
       </c>
@@ -6370,7 +6528,7 @@
         <v>23112148514.524086</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32" s="13" t="s">
         <v>53</v>
       </c>
@@ -6396,7 +6554,7 @@
         <v>21838278294.189957</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" s="13" t="s">
         <v>54</v>
       </c>
@@ -6422,7 +6580,7 @@
         <v>23267260238.964119</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" s="13" t="s">
         <v>55</v>
       </c>
@@ -6448,7 +6606,7 @@
         <v>24152188840.065418</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" s="13" t="s">
         <v>56</v>
       </c>
@@ -6474,7 +6632,7 @@
         <v>24276616351.55632</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A36" s="13" t="s">
         <v>57</v>
       </c>
@@ -6500,13 +6658,13 @@
         <v>24466165583.505955</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A37" s="13"/>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>2015</v>
       </c>
@@ -6526,7 +6684,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A39" s="28" t="s">
         <v>168</v>
       </c>
@@ -6541,15 +6699,15 @@
         <f>D38/B38</f>
         <v>2.6578482824228877</v>
       </c>
-      <c r="K39" s="61" t="s">
+      <c r="K39" s="62" t="s">
         <v>169</v>
       </c>
-      <c r="L39" s="61"/>
-      <c r="M39" s="61"/>
-    </row>
-    <row r="40" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="L39" s="62"/>
+      <c r="M39" s="62"/>
+    </row>
+    <row r="40" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A40" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B40">
         <f>SUM(F2:F36)/SUM(Population!B2:B36)</f>
@@ -6574,7 +6732,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A41" s="3" t="s">
         <v>168</v>
       </c>
@@ -6602,7 +6760,7 @@
         <v>2.3703888007815599</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A42" s="12" t="s">
         <v>67</v>
       </c>
@@ -6631,7 +6789,7 @@
         <v>2.4480223372362699</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A43" s="11" t="s">
         <v>72</v>
       </c>
@@ -6661,7 +6819,7 @@
         <v>2.5245850802099499</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A44" s="3" t="s">
         <v>73</v>
       </c>
@@ -6690,7 +6848,7 @@
         <v>2.5427605678518299</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
       <c r="A45" s="3" t="s">
         <v>71</v>
       </c>
@@ -6719,7 +6877,7 @@
         <v>2.31134286871607</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -6736,31 +6894,31 @@
         <v>2.4394199309591356</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B47" s="21" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B48" s="21" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="B49" s="21" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
         <v>64</v>
       </c>
@@ -6768,11 +6926,11 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A52" s="28"/>
       <c r="B52" s="28"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
         <v>65</v>
       </c>
@@ -6796,13 +6954,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC11EFA9-274E-476D-8BFE-D8769B6BF052}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.69140625" customWidth="1"/>
+    <col min="2" max="2" width="11.61328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B1" s="28" t="s">
         <v>2</v>
       </c>
@@ -6822,7 +6980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="28" t="s">
         <v>113</v>
       </c>
@@ -6851,7 +7009,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="28" t="s">
         <v>112</v>
       </c>
@@ -6880,7 +7038,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -6909,7 +7067,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -6917,7 +7075,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>115</v>
       </c>
@@ -6939,7 +7097,7 @@
         <v>0.74445404791547987</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>116</v>
       </c>
@@ -6957,7 +7115,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>117</v>
       </c>
@@ -6968,7 +7126,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>118</v>
       </c>
@@ -6979,7 +7137,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>119</v>
       </c>
@@ -6990,7 +7148,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>120</v>
       </c>
@@ -7009,114 +7167,114 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE07EBE8-6449-4730-9E28-CE2F7AF6313A}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.06640625" customWidth="1"/>
+    <col min="1" max="1" width="13.07421875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2">
         <f>170/74</f>
         <v>2.2972972972972974</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3">
         <f>1055/74</f>
         <v>14.256756756756756</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" s="35"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" s="35">
         <f>((Population!C116/100)*A2)*1000</f>
         <v>17.76876871873117</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" s="35">
         <f>((Population!C116/100)*A3)*1000</f>
         <v>110.27088822506695</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" s="35"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" s="35" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" s="14">
         <v>1000000000</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="15" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" s="20"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" s="22"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" s="22">
         <f>A2*1000000000/(Population!B115*1000)</f>
         <v>0.264704634686033</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" s="22">
         <f>A3*1000000000/(Population!B115*1000)</f>
         <v>1.6427258211397928</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="33" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" s="20"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19">
         <f>(Capacité!C43/100)*A2</f>
         <v>1.2114682525646763E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20">
         <f>(Capacité!C43/100)*A3</f>
         <v>7.5182294497396079E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="15"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24">
         <f>A2*Besoins!B5*1000</f>
         <v>14.648366196075427</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25" s="28">
         <f>A3*Besoins!B5*1000</f>
         <v>90.906037275644564</v>

--- a/data/seuils.xlsx
+++ b/data/seuils.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\CIRED\PlaneFR\Code\Module_PlaneFR\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DF5D48-A77C-4FFD-9F11-909CC74F3E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821A6BE3-39FF-4922-A0E4-0DFCE10B668C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="8002" windowWidth="14595" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="14595" windowHeight="8746" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Synthèse" sheetId="9" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="228">
   <si>
     <t>N</t>
   </si>
@@ -745,9 +745,6 @@
   </si>
   <si>
     <t>1e12 PDF.m2.yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PDF.m2.yr</t>
   </si>
   <si>
     <t>Lower safe bound</t>
@@ -1158,39 +1155,6 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
@@ -1223,6 +1187,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1509,157 +1506,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C32444-97C3-4A7C-A91C-82059EB528AD}">
   <dimension ref="A1:I26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27" style="28" customWidth="1"/>
-    <col min="2" max="2" width="14.15234375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="11.69140625" style="28" customWidth="1"/>
-    <col min="4" max="4" width="14.07421875" style="28" customWidth="1"/>
-    <col min="5" max="7" width="9.23046875" style="28"/>
-    <col min="8" max="8" width="11.921875" style="28" customWidth="1"/>
-    <col min="9" max="9" width="13.921875" style="28" customWidth="1"/>
-    <col min="10" max="16384" width="9.23046875" style="28"/>
+    <col min="2" max="2" width="14.1328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="28" customWidth="1"/>
+    <col min="4" max="4" width="14.06640625" style="28" customWidth="1"/>
+    <col min="5" max="7" width="9.19921875" style="28"/>
+    <col min="8" max="8" width="11.9296875" style="28" customWidth="1"/>
+    <col min="9" max="9" width="13.9296875" style="28" customWidth="1"/>
+    <col min="10" max="16384" width="9.19921875" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="31.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="79" t="s">
-        <v>217</v>
-      </c>
-      <c r="B1" s="80" t="s">
+    <row r="1" spans="1:9" s="3" customFormat="1" ht="31.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="69" t="s">
         <v>193</v>
       </c>
-      <c r="C1" s="80" t="s">
+      <c r="C1" s="69" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D1" s="69" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="80" t="s">
+      <c r="E1" s="69" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="80" t="s">
+      <c r="F1" s="69" t="s">
         <v>196</v>
       </c>
-      <c r="G1" s="80" t="s">
+      <c r="G1" s="69" t="s">
         <v>200</v>
       </c>
-      <c r="H1" s="80" t="s">
+      <c r="H1" s="69" t="s">
         <v>197</v>
       </c>
-      <c r="I1" s="81" t="s">
+      <c r="I1" s="70" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" s="72" t="s">
-        <v>211</v>
-      </c>
-      <c r="B2" s="73">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2" s="62">
         <f>(1.33*10+163.83)/74</f>
         <v>2.3936486486486488</v>
       </c>
-      <c r="C2" s="73">
+      <c r="C2" s="62">
         <v>1100</v>
       </c>
-      <c r="D2" s="73">
+      <c r="D2" s="62">
         <v>10.6</v>
       </c>
-      <c r="E2" s="73">
+      <c r="E2" s="62">
         <v>34</v>
       </c>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" s="74" t="s">
-        <v>213</v>
-      </c>
-      <c r="B3" s="75">
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" s="63" t="s">
+        <v>212</v>
+      </c>
+      <c r="B3" s="64">
         <f>(1.33*130+163.83)/74</f>
         <v>4.5504054054054057</v>
       </c>
-      <c r="C3" s="75">
+      <c r="C3" s="64">
         <v>2800</v>
       </c>
-      <c r="D3" s="75">
+      <c r="D3" s="64">
         <v>12.6</v>
       </c>
-      <c r="E3" s="75">
+      <c r="E3" s="64">
         <v>57</v>
       </c>
-      <c r="F3" s="75">
+      <c r="F3" s="64">
         <v>4.5</v>
       </c>
-      <c r="G3" s="75">
+      <c r="G3" s="64">
         <v>39.6</v>
       </c>
-      <c r="H3" s="75">
+      <c r="H3" s="64">
         <v>25</v>
       </c>
-      <c r="I3" s="76">
+      <c r="I3" s="65">
         <v>6.5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="74" t="s">
-        <v>212</v>
-      </c>
-      <c r="B4" s="75">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="63" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" s="64">
         <f>(1.33*1050+163.83)/74</f>
         <v>21.085540540540539</v>
       </c>
-      <c r="C4" s="75">
+      <c r="C4" s="64">
         <v>4500</v>
       </c>
-      <c r="D4" s="75">
+      <c r="D4" s="64">
         <v>14.6</v>
       </c>
-      <c r="E4" s="75">
+      <c r="E4" s="64">
         <v>74</v>
       </c>
-      <c r="F4" s="75">
+      <c r="F4" s="64">
         <v>9</v>
       </c>
-      <c r="G4" s="75">
+      <c r="G4" s="64">
         <v>49</v>
       </c>
-      <c r="H4" s="75">
+      <c r="H4" s="64">
         <v>50</v>
       </c>
-      <c r="I4" s="75"/>
-    </row>
-    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="77" t="s">
-        <v>219</v>
-      </c>
-      <c r="B5" s="78" t="s">
+      <c r="I4" s="64"/>
+    </row>
+    <row r="5" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="66" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="67" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="D5" s="78" t="s">
+      <c r="D5" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="78" t="s">
+      <c r="E5" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="78" t="s">
+      <c r="F5" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="78" t="s">
+      <c r="G5" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="78" t="s">
+      <c r="H5" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="78" t="s">
+      <c r="I5" s="67" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="19"/>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
@@ -1670,38 +1667,38 @@
       <c r="H6" s="20"/>
       <c r="I6" s="20"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="63" t="s">
-        <v>225</v>
-      </c>
-      <c r="B7" s="64">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" s="52" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7" s="53">
         <v>1E-3</v>
       </c>
-      <c r="C7" s="65">
+      <c r="C7" s="54">
         <v>1</v>
       </c>
-      <c r="D7" s="64">
+      <c r="D7" s="53">
         <v>1E-3</v>
       </c>
-      <c r="E7" s="64">
+      <c r="E7" s="53">
         <v>1E-3</v>
       </c>
-      <c r="F7" s="64">
+      <c r="F7" s="53">
         <v>1E-3</v>
       </c>
-      <c r="G7" s="65">
+      <c r="G7" s="54">
         <v>2.7777800000000001E-4</v>
       </c>
-      <c r="H7" s="64">
+      <c r="H7" s="53">
         <v>1E-3</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="53">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B8" s="35">
         <f>((Population!C121/100)*B2)*1000</f>
@@ -1736,9 +1733,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="34" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B9" s="48">
         <f>((Population!C123/100)*B3)/B7</f>
@@ -1773,9 +1770,9 @@
         <v>45.782469885452663</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="34" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B10" s="35">
         <f>((Population!C123/100)*B4)*1000</f>
@@ -1810,9 +1807,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="34" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B11" s="35" t="s">
         <v>180</v>
@@ -1839,76 +1836,76 @@
         <v>208</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A12" s="63" t="s">
-        <v>226</v>
-      </c>
-      <c r="B12" s="64">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A12" s="52" t="s">
+        <v>225</v>
+      </c>
+      <c r="B12" s="53">
         <v>1</v>
       </c>
-      <c r="C12" s="64">
+      <c r="C12" s="53">
         <v>1000</v>
       </c>
-      <c r="D12" s="64">
+      <c r="D12" s="53">
         <v>1000</v>
       </c>
-      <c r="E12" s="64">
+      <c r="E12" s="53">
         <v>1E-3</v>
       </c>
-      <c r="F12" s="64">
+      <c r="F12" s="53">
         <v>1E-3</v>
       </c>
-      <c r="G12" s="65">
+      <c r="G12" s="54">
         <f>1/0.000277778</f>
         <v>3599.9971200023037</v>
       </c>
-      <c r="H12" s="64">
+      <c r="H12" s="53">
         <v>1000</v>
       </c>
-      <c r="I12" s="64">
+      <c r="I12" s="53">
         <v>1000000000</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="71" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="69"/>
-      <c r="B13" s="70"/>
-      <c r="C13" s="70"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-    </row>
-    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="67" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" s="68" t="s">
+    <row r="13" spans="1:9" s="60" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="58"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+    </row>
+    <row r="14" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="56" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="57" t="s">
         <v>180</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="68" t="s">
+      <c r="D14" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="68" t="s">
+      <c r="E14" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="68" t="s">
+      <c r="F14" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="68" t="s">
+      <c r="G14" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="H14" s="68" t="s">
+      <c r="H14" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="I14" s="68" t="s">
+      <c r="I14" s="57" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="19"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -1919,38 +1916,38 @@
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A16" s="63" t="s">
-        <v>227</v>
-      </c>
-      <c r="B16" s="64">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="B16" s="53">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="C16" s="64">
+      <c r="C16" s="53">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="D16" s="64">
+      <c r="D16" s="53">
         <v>9.9999999999999998E-13</v>
       </c>
-      <c r="E16" s="64">
+      <c r="E16" s="53">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="F16" s="64">
+      <c r="F16" s="53">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="G16" s="64">
+      <c r="G16" s="53">
         <v>1</v>
       </c>
-      <c r="H16" s="64">
+      <c r="H16" s="53">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="I16" s="64">
+      <c r="I16" s="53">
         <v>9.9999999999999998E-13</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B17" s="22">
         <f>B2*1000000000/(Population!B120*1000)</f>
@@ -1985,9 +1982,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="31" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B18" s="22">
         <f>B3*1000000000/(Population!B122*1000)</f>
@@ -2022,9 +2019,9 @@
         <v>675.29581650469493</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" s="31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B19" s="22">
         <f>B4*1000000000/(Population!B122*1000)</f>
@@ -2059,9 +2056,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A20" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B20" s="33" t="s">
         <v>191</v>
@@ -2085,39 +2082,39 @@
         <v>91</v>
       </c>
       <c r="I20" s="33" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A21" s="63" t="s">
-        <v>228</v>
-      </c>
-      <c r="B21" s="66">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A21" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="B21" s="55">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="C21" s="66">
+      <c r="C21" s="55">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="D21" s="66">
+      <c r="D21" s="55">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="E21" s="66">
+      <c r="E21" s="55">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="F21" s="66">
+      <c r="F21" s="55">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="G21" s="66">
+      <c r="G21" s="55">
         <v>1E-3</v>
       </c>
-      <c r="H21" s="66">
+      <c r="H21" s="55">
         <v>1E-3</v>
       </c>
-      <c r="I21" s="66">
+      <c r="I21" s="55">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="19"/>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
@@ -2128,7 +2125,7 @@
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" s="19" t="s">
         <v>16</v>
       </c>
@@ -2165,7 +2162,7 @@
         <v>3.4277425263741722E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="19" t="s">
         <v>102</v>
       </c>
@@ -2202,10 +2199,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" s="19"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="19"/>
     </row>
   </sheetData>
@@ -2217,15 +2214,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.15234375" customWidth="1"/>
-    <col min="4" max="4" width="14.07421875" customWidth="1"/>
-    <col min="9" max="10" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.84375" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1328125" customWidth="1"/>
+    <col min="4" max="4" width="14.06640625" customWidth="1"/>
+    <col min="9" max="10" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.86328125" style="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="18" t="s">
         <v>76</v>
       </c>
@@ -2257,7 +2254,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" s="19" t="s">
         <v>15</v>
       </c>
@@ -2294,7 +2291,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="19" t="s">
         <v>74</v>
       </c>
@@ -2324,7 +2321,7 @@
         <v>26068</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="16" t="s">
         <v>5</v>
       </c>
@@ -2356,11 +2353,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" s="19"/>
       <c r="K5" s="20"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" s="34" t="s">
         <v>14</v>
       </c>
@@ -2374,7 +2371,7 @@
       <c r="I6" s="35"/>
       <c r="K6" s="35"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" s="34" t="s">
         <v>88</v>
       </c>
@@ -2414,7 +2411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" s="34" t="s">
         <v>101</v>
       </c>
@@ -2456,7 +2453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" s="34"/>
       <c r="B9" s="35"/>
       <c r="C9" s="35"/>
@@ -2471,7 +2468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" s="34" t="s">
         <v>86</v>
       </c>
@@ -2501,7 +2498,7 @@
       </c>
       <c r="K10" s="35"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" s="19" t="s">
         <v>83</v>
       </c>
@@ -2534,7 +2531,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="16" t="s">
         <v>85</v>
       </c>
@@ -2566,7 +2563,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -2580,7 +2577,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" s="31" t="s">
         <v>90</v>
       </c>
@@ -2594,7 +2591,7 @@
       <c r="I14" s="22"/>
       <c r="K14" s="20"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" s="31" t="s">
         <v>134</v>
       </c>
@@ -2632,7 +2629,7 @@
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" s="31" t="s">
         <v>135</v>
       </c>
@@ -2672,7 +2669,7 @@
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" s="32" t="s">
         <v>5</v>
       </c>
@@ -2705,7 +2702,7 @@
         <v>9.2556771496873207</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" s="19"/>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -2720,7 +2717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="19" t="s">
         <v>16</v>
       </c>
@@ -2760,7 +2757,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" s="19" t="s">
         <v>102</v>
       </c>
@@ -2800,11 +2797,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" s="19"/>
       <c r="K21" s="20"/>
     </row>
-    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" s="19" t="s">
         <v>17</v>
       </c>
@@ -2814,7 +2811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="16" t="s">
         <v>109</v>
       </c>
@@ -2831,7 +2828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" s="19" t="s">
         <v>108</v>
       </c>
@@ -2859,7 +2856,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" s="19" t="s">
         <v>114</v>
       </c>
@@ -2887,17 +2884,17 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A26" s="19"/>
       <c r="K26" s="15"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K27" s="28">
         <f>K2*Besoins!I5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="K28" s="28">
         <f>K3*Besoins!I5</f>
         <v>0</v>
@@ -2911,18 +2908,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0A75E4-DA25-4A08-8974-1A31A91FD529}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.07421875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.69140625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="11.07421875" style="28"/>
-    <col min="3" max="4" width="12.3828125" style="28" customWidth="1"/>
-    <col min="5" max="5" width="11.921875" style="28" customWidth="1"/>
-    <col min="6" max="6" width="11.07421875" style="28"/>
-    <col min="7" max="7" width="14.84375" style="28" customWidth="1"/>
-    <col min="8" max="16384" width="11.07421875" style="28"/>
+    <col min="1" max="1" width="27.6640625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="11.06640625" style="28"/>
+    <col min="3" max="4" width="12.3984375" style="28" customWidth="1"/>
+    <col min="5" max="5" width="11.9296875" style="28" customWidth="1"/>
+    <col min="6" max="6" width="11.06640625" style="28"/>
+    <col min="7" max="7" width="14.86328125" style="28" customWidth="1"/>
+    <col min="8" max="16384" width="11.06640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="23" t="s">
         <v>76</v>
       </c>
@@ -2945,7 +2942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="22" t="s">
         <v>130</v>
       </c>
@@ -2971,7 +2968,7 @@
         <v>4.0776939000000005E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="22" t="s">
         <v>131</v>
       </c>
@@ -2997,7 +2994,7 @@
         <v>2.9475940000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="22" t="s">
         <v>163</v>
       </c>
@@ -3026,7 +3023,7 @@
         <v>3.5126439500000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="22" t="s">
         <v>5</v>
       </c>
@@ -3049,12 +3046,12 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="28" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="28" t="s">
         <v>105</v>
       </c>
@@ -3080,7 +3077,7 @@
         <v>2.7340017428936065E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="28" t="s">
         <v>106</v>
       </c>
@@ -3106,7 +3103,7 @@
         <v>1.9682472147114907E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" s="28" t="s">
         <v>110</v>
       </c>
@@ -3135,7 +3132,7 @@
         <v>2.3511244788025486E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" s="28" t="s">
         <v>5</v>
       </c>
@@ -3158,7 +3155,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" s="30" t="s">
         <v>95</v>
       </c>
@@ -3187,7 +3184,7 @@
         <v>17.921343875225901</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" s="30" t="s">
         <v>96</v>
       </c>
@@ -3216,7 +3213,7 @@
         <v>12.954588297702438</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" s="30" t="s">
         <v>164</v>
       </c>
@@ -3245,7 +3242,7 @@
         <v>15.43796608646417</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" s="30" t="s">
         <v>5</v>
       </c>
@@ -3268,31 +3265,31 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
       <c r="F18" s="21" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G21" s="28" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G22" s="28" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="G23" s="28" t="s">
         <v>127</v>
       </c>
@@ -3313,13 +3310,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1104A7-2272-4986-AE6B-8EA45794950A}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.69140625" customWidth="1"/>
-    <col min="3" max="3" width="11.921875" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="23" t="s">
         <v>76</v>
       </c>
@@ -3333,7 +3330,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="22" t="s">
         <v>130</v>
       </c>
@@ -3348,7 +3345,7 @@
         <v>26.509803921568629</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="22" t="s">
         <v>131</v>
       </c>
@@ -3363,7 +3360,7 @@
         <v>15.600000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="22" t="s">
         <v>163</v>
       </c>
@@ -3380,7 +3377,7 @@
         <v>21.054901960784314</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="22" t="s">
         <v>5</v>
       </c>
@@ -3394,12 +3391,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>105</v>
       </c>
@@ -3414,7 +3411,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>106</v>
       </c>
@@ -3429,7 +3426,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="28" t="s">
         <v>110</v>
       </c>
@@ -3446,7 +3443,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -3460,7 +3457,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="30" t="s">
         <v>95</v>
       </c>
@@ -3477,7 +3474,7 @@
         <v>494.3108592392208</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="30" t="s">
         <v>96</v>
       </c>
@@ -3494,7 +3491,7 @@
         <v>290.88292870615692</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" s="28" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="30" t="s">
         <v>164</v>
       </c>
@@ -3511,7 +3508,7 @@
         <v>392.59689397268886</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="30" t="s">
         <v>5</v>
       </c>
@@ -3525,14 +3522,14 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="53"/>
+      <c r="C18" s="72"/>
       <c r="D18" s="21" t="s">
         <v>104</v>
       </c>
@@ -3553,132 +3550,132 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE59BEB1-58EA-414F-91E0-ADFFF27E94F9}">
   <dimension ref="A2:U6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.07421875" style="28"/>
+    <col min="1" max="1" width="11.06640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" ht="16.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="58" t="s">
+    <row r="2" spans="1:21" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="75" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="59" t="s">
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="58" t="s">
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="75" t="s">
         <v>137</v>
       </c>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="59" t="s">
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="76" t="s">
         <v>138</v>
       </c>
-      <c r="L2" s="59"/>
-      <c r="M2" s="60" t="s">
+      <c r="L2" s="76"/>
+      <c r="M2" s="79" t="s">
         <v>139</v>
       </c>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="77" t="s">
         <v>140</v>
       </c>
-      <c r="O2" s="58" t="s">
+      <c r="O2" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="59" t="s">
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="76" t="s">
         <v>142</v>
       </c>
-      <c r="S2" s="59"/>
-      <c r="T2" s="61" t="s">
+      <c r="S2" s="76"/>
+      <c r="T2" s="80" t="s">
         <v>161</v>
       </c>
-      <c r="U2" s="57" t="s">
+      <c r="U2" s="78" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="17.149999999999999" x14ac:dyDescent="0.4">
-      <c r="B3" s="55" t="s">
+    <row r="3" spans="1:21" ht="17.649999999999999" x14ac:dyDescent="0.45">
+      <c r="B3" s="74" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="74" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="74" t="s">
         <v>145</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="73" t="s">
         <v>146</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="73" t="s">
         <v>147</v>
       </c>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="73" t="s">
         <v>148</v>
       </c>
-      <c r="H3" s="55" t="s">
+      <c r="H3" s="74" t="s">
         <v>149</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="I3" s="74" t="s">
         <v>150</v>
       </c>
-      <c r="J3" s="55" t="s">
+      <c r="J3" s="74" t="s">
         <v>151</v>
       </c>
-      <c r="K3" s="56" t="s">
+      <c r="K3" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="L3" s="56" t="s">
+      <c r="L3" s="73" t="s">
         <v>153</v>
       </c>
-      <c r="M3" s="60"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="55" t="s">
+      <c r="M3" s="79"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="74" t="s">
         <v>154</v>
       </c>
-      <c r="P3" s="55" t="s">
+      <c r="P3" s="74" t="s">
         <v>155</v>
       </c>
       <c r="Q3" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="R3" s="56" t="s">
+      <c r="R3" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="S3" s="56" t="s">
+      <c r="S3" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="T3" s="61"/>
-      <c r="U3" s="57"/>
-    </row>
-    <row r="4" spans="1:21" ht="38.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="78"/>
+    </row>
+    <row r="4" spans="1:21" ht="38.200000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="79"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
       <c r="Q4" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="61"/>
-      <c r="U4" s="57"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="78"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>160</v>
       </c>
@@ -3744,24 +3741,13 @@
         <v>15.600000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A6" s="28" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
@@ -3776,6 +3762,17 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T2:T4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -3785,13 +3782,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95CE491-5889-4A7E-A6ED-A3FC6F8FA184}">
   <dimension ref="A1:H127"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.3828125" customWidth="1"/>
-    <col min="2" max="2" width="12.84375" customWidth="1"/>
+    <col min="1" max="1" width="12.3984375" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="48.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="46" t="s">
         <v>18</v>
       </c>
@@ -3805,7 +3802,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -3819,7 +3816,7 @@
         <v>419997.47</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -3833,7 +3830,7 @@
         <v>421419.174</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -3847,7 +3844,7 @@
         <v>422863.59999999992</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -3861,7 +3858,7 @@
         <v>424104.70499999996</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -3875,7 +3872,7 @@
         <v>425188.98800000019</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -3889,7 +3886,7 @@
         <v>425847.82800000004</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -3903,7 +3900,7 @@
         <v>426181.87299999996</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -3917,7 +3914,7 @@
         <v>426651.66799999989</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -3931,7 +3928,7 @@
         <v>426655.42999999993</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -3945,7 +3942,7 @@
         <v>426830.63099999999</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -3959,7 +3956,7 @@
         <v>427627.31800000009</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -3973,7 +3970,7 @@
         <v>428578.28599999996</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -3987,7 +3984,7 @@
         <v>429890.46400000004</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -4001,7 +3998,7 @@
         <v>431461.80999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -4015,7 +4012,7 @@
         <v>433058.58899999998</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -4029,7 +4026,7 @@
         <v>434557.12100000004</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -4043,7 +4040,7 @@
         <v>435683.11500000011</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -4057,7 +4054,7 @@
         <v>436994.47300000006</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -4071,7 +4068,7 @@
         <v>438548.18900000007</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -4085,7 +4082,7 @@
         <v>439690.78899999993</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -4099,7 +4096,7 @@
         <v>440608.95100000006</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -4113,7 +4110,7 @@
         <v>441440.62800000008</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -4127,7 +4124,7 @@
         <v>441999.21399999998</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -4141,7 +4138,7 @@
         <v>442399.391</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -4155,7 +4152,7 @@
         <v>442964.72000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -4169,7 +4166,7 @@
         <v>443910.90800000017</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -4183,7 +4180,7 @@
         <v>444911.48800000001</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -4197,7 +4194,7 @@
         <v>445696.74599999998</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -4211,7 +4208,7 @@
         <v>446503.6480000001</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -4225,7 +4222,7 @@
         <v>447369.19099999999</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -4239,7 +4236,7 @@
         <v>447777.53599999996</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -4253,7 +4250,7 @@
         <v>447705.902</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -4267,7 +4264,7 @@
         <v>449113.45499999996</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -4281,7 +4278,7 @@
         <v>450657.52199999994</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -4295,7 +4292,7 @@
         <v>450259.53600000002</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <v>2025</v>
       </c>
@@ -4309,7 +4306,7 @@
         <v>448992.58499999996</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <v>2026</v>
       </c>
@@ -4323,7 +4320,7 @@
         <v>447890.473</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <v>2027</v>
       </c>
@@ -4337,7 +4334,7 @@
         <v>447205.74899999995</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <v>2028</v>
       </c>
@@ -4351,7 +4348,7 @@
         <v>446459.31699999998</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <v>2029</v>
       </c>
@@ -4365,7 +4362,7 @@
         <v>445651.23500000004</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <v>2030</v>
       </c>
@@ -4379,7 +4376,7 @@
         <v>444782.38100000005</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <v>2031</v>
       </c>
@@ -4393,7 +4390,7 @@
         <v>443853.3349999999</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <v>2032</v>
       </c>
@@ -4407,7 +4404,7 @@
         <v>442896.55800000002</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <v>2033</v>
       </c>
@@ -4421,7 +4418,7 @@
         <v>441929.64600000007</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <v>2034</v>
       </c>
@@ -4435,7 +4432,7 @@
         <v>440942.37400000007</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <v>2035</v>
       </c>
@@ -4449,7 +4446,7 @@
         <v>439928.23599999998</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
         <v>2036</v>
       </c>
@@ -4463,7 +4460,7 @@
         <v>438876.35599999991</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="1">
         <v>2037</v>
       </c>
@@ -4477,7 +4474,7 @@
         <v>437800.28700000013</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
         <v>2038</v>
       </c>
@@ -4491,7 +4488,7 @@
         <v>436704.79599999997</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A51" s="1">
         <v>2039</v>
       </c>
@@ -4505,7 +4502,7 @@
         <v>435575.79399999999</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="1">
         <v>2040</v>
       </c>
@@ -4519,7 +4516,7 @@
         <v>434422.40100000007</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
         <v>2041</v>
       </c>
@@ -4533,7 +4530,7 @@
         <v>433267.647</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="1">
         <v>2042</v>
       </c>
@@ -4547,7 +4544,7 @@
         <v>432096.70899999997</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="1">
         <v>2043</v>
       </c>
@@ -4561,7 +4558,7 @@
         <v>430874.26299999998</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
         <v>2044</v>
       </c>
@@ -4575,7 +4572,7 @@
         <v>429598.62099999987</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A57" s="1">
         <v>2045</v>
       </c>
@@ -4589,7 +4586,7 @@
         <v>428280.46499999997</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="1">
         <v>2046</v>
       </c>
@@ -4603,7 +4600,7 @@
         <v>426921.04200000002</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="1">
         <v>2047</v>
       </c>
@@ -4617,7 +4614,7 @@
         <v>425511.16099999996</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="1">
         <v>2048</v>
       </c>
@@ -4631,7 +4628,7 @@
         <v>424046.07800000015</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="1">
         <v>2049</v>
       </c>
@@ -4645,7 +4642,7 @@
         <v>422524.55599999998</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
         <v>2050</v>
       </c>
@@ -4659,7 +4656,7 @@
         <v>420955.34100000001</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A63" s="1">
         <v>2051</v>
       </c>
@@ -4673,7 +4670,7 @@
         <v>419346.89500000008</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A64" s="1">
         <v>2052</v>
       </c>
@@ -4687,7 +4684,7 @@
         <v>417691.14999999997</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="1">
         <v>2053</v>
       </c>
@@ -4701,7 +4698,7 @@
         <v>415966.71600000001</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="1">
         <v>2054</v>
       </c>
@@ -4715,7 +4712,7 @@
         <v>414174.85799999995</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="1">
         <v>2055</v>
       </c>
@@ -4729,7 +4726,7 @@
         <v>412334.533</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
         <v>2056</v>
       </c>
@@ -4743,7 +4740,7 @@
         <v>410448.42000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" s="1">
         <v>2057</v>
       </c>
@@ -4757,7 +4754,7 @@
         <v>408533.27399999992</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" s="1">
         <v>2058</v>
       </c>
@@ -4771,7 +4768,7 @@
         <v>406603.29399999999</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
         <v>2059</v>
       </c>
@@ -4785,7 +4782,7 @@
         <v>404661.71100000007</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="1">
         <v>2060</v>
       </c>
@@ -4799,7 +4796,7 @@
         <v>402712.63299999991</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="1">
         <v>2061</v>
       </c>
@@ -4813,7 +4810,7 @@
         <v>400766.93200000015</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
         <v>2062</v>
       </c>
@@ -4827,7 +4824,7 @@
         <v>398823.46799999999</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="1">
         <v>2063</v>
       </c>
@@ -4841,7 +4838,7 @@
         <v>396899.60199999996</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" s="1">
         <v>2064</v>
       </c>
@@ -4855,7 +4852,7 @@
         <v>395004.61700000003</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" s="1">
         <v>2065</v>
       </c>
@@ -4869,7 +4866,7 @@
         <v>393131.79000000004</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" s="1">
         <v>2066</v>
       </c>
@@ -4883,7 +4880,7 @@
         <v>391291.73300000001</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" s="1">
         <v>2067</v>
       </c>
@@ -4897,7 +4894,7 @@
         <v>389489.04200000002</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" s="1">
         <v>2068</v>
       </c>
@@ -4911,7 +4908,7 @@
         <v>387721.924</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="1">
         <v>2069</v>
       </c>
@@ -4925,7 +4922,7 @@
         <v>385994.04200000007</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="1">
         <v>2070</v>
       </c>
@@ -4939,7 +4936,7 @@
         <v>384310.26799999998</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" s="1">
         <v>2071</v>
       </c>
@@ -4953,7 +4950,7 @@
         <v>382670.826</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" s="1">
         <v>2072</v>
       </c>
@@ -4967,7 +4964,7 @@
         <v>381068.141</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" s="1">
         <v>2073</v>
       </c>
@@ -4981,7 +4978,7 @@
         <v>379495.90099999995</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" s="1">
         <v>2074</v>
       </c>
@@ -4995,7 +4992,7 @@
         <v>377958.35600000003</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" s="1">
         <v>2075</v>
       </c>
@@ -5009,7 +5006,7 @@
         <v>376480.08500000008</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" s="1">
         <v>2076</v>
       </c>
@@ -5023,7 +5020,7 @@
         <v>375047.78200000006</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" s="1">
         <v>2077</v>
       </c>
@@ -5037,7 +5034,7 @@
         <v>373634.73</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" s="1">
         <v>2078</v>
       </c>
@@ -5051,7 +5048,7 @@
         <v>372260.67599999998</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" s="1">
         <v>2079</v>
       </c>
@@ -5065,7 +5062,7 @@
         <v>370924.19000000006</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" s="1">
         <v>2080</v>
       </c>
@@ -5079,7 +5076,7 @@
         <v>369621.90600000002</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" s="1">
         <v>2081</v>
       </c>
@@ -5093,7 +5090,7 @@
         <v>368361.90900000004</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" s="1">
         <v>2082</v>
       </c>
@@ -5107,7 +5104,7 @@
         <v>367136.15699999989</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" s="1">
         <v>2083</v>
       </c>
@@ -5121,7 +5118,7 @@
         <v>365939.98800000007</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" s="1">
         <v>2084</v>
       </c>
@@ -5135,7 +5132,7 @@
         <v>364768.47600000014</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" s="1">
         <v>2085</v>
       </c>
@@ -5149,7 +5146,7 @@
         <v>363612.08199999999</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" s="1">
         <v>2086</v>
       </c>
@@ -5163,7 +5160,7 @@
         <v>362474.72799999989</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" s="1">
         <v>2087</v>
       </c>
@@ -5177,7 +5174,7 @@
         <v>361363.54499999998</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" s="1">
         <v>2088</v>
       </c>
@@ -5191,7 +5188,7 @@
         <v>360281.40500000003</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" s="1">
         <v>2089</v>
       </c>
@@ -5205,7 +5202,7 @@
         <v>359214.11100000003</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" s="1">
         <v>2090</v>
       </c>
@@ -5219,7 +5216,7 @@
         <v>358149.47100000002</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A103" s="1">
         <v>2091</v>
       </c>
@@ -5233,7 +5230,7 @@
         <v>357104.93199999997</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A104" s="1">
         <v>2092</v>
       </c>
@@ -5247,7 +5244,7 @@
         <v>356085.554</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A105" s="1">
         <v>2093</v>
       </c>
@@ -5261,7 +5258,7 @@
         <v>355083.0670000001</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A106" s="1">
         <v>2094</v>
       </c>
@@ -5275,7 +5272,7 @@
         <v>354087.00400000002</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A107" s="1">
         <v>2095</v>
       </c>
@@ -5289,7 +5286,7 @@
         <v>353078.46800000005</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A108" s="1">
         <v>2096</v>
       </c>
@@ -5303,7 +5300,7 @@
         <v>352052.02500000008</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" s="1">
         <v>2097</v>
       </c>
@@ -5317,7 +5314,7 @@
         <v>351009.62299999996</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" s="1">
         <v>2098</v>
       </c>
@@ -5331,7 +5328,7 @@
         <v>349970.60700000002</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A111" s="1">
         <v>2099</v>
       </c>
@@ -5345,7 +5342,7 @@
         <v>348929.72599999985</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A112" s="1">
         <v>2100</v>
       </c>
@@ -5359,7 +5356,7 @@
         <v>347864.81900000002</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>167</v>
       </c>
@@ -5375,7 +5372,7 @@
         <v>6.2079223823601231</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>68</v>
       </c>
@@ -5392,7 +5389,7 @@
         <v>5.9421911649996391</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A115" s="11" t="s">
         <v>189</v>
       </c>
@@ -5409,7 +5406,7 @@
         <v>439497.03716666671</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116" s="10" t="s">
         <v>21</v>
       </c>
@@ -5426,7 +5423,7 @@
         <v>5.0640769397005476</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A117" s="3" t="s">
         <v>22</v>
       </c>
@@ -5443,7 +5440,7 @@
         <v>403389.38254761917</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>21</v>
       </c>
@@ -5460,7 +5457,7 @@
         <v>4.2110630256763759</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>69</v>
       </c>
@@ -5481,7 +5478,7 @@
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
     </row>
-    <row r="120" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A120" s="3" t="s">
         <v>201</v>
       </c>
@@ -5502,7 +5499,7 @@
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>21</v>
       </c>
@@ -5519,7 +5516,7 @@
         <v>4.9785141684743905</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A122" s="3" t="s">
         <v>70</v>
       </c>
@@ -5536,7 +5533,7 @@
         <v>402347.65536585363</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>21</v>
       </c>
@@ -5553,7 +5550,7 @@
         <v>4.1800567453697495</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>19</v>
       </c>
@@ -5561,7 +5558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B127" t="s">
         <v>192</v>
       </c>
@@ -5577,14 +5574,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8683F5-D89E-4384-A263-C6122D6DA873}">
   <dimension ref="A1:AK53"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="11.84375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.69140625" customWidth="1"/>
-    <col min="9" max="9" width="10.69140625" style="28"/>
+    <col min="3" max="3" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -5635,7 +5632,7 @@
       <c r="AJ1" s="13"/>
       <c r="AK1" s="13"/>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A2" s="13" t="s">
         <v>23</v>
       </c>
@@ -5689,7 +5686,7 @@
       <c r="AJ2" s="13"/>
       <c r="AK2" s="13"/>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A3" s="13" t="s">
         <v>24</v>
       </c>
@@ -5743,7 +5740,7 @@
       <c r="AJ3" s="13"/>
       <c r="AK3" s="13"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A4" s="13" t="s">
         <v>25</v>
       </c>
@@ -5798,7 +5795,7 @@
       <c r="AJ4" s="13"/>
       <c r="AK4" s="13"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A5" s="13" t="s">
         <v>26</v>
       </c>
@@ -5851,7 +5848,7 @@
       <c r="AJ5" s="13"/>
       <c r="AK5" s="13"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A6" s="13" t="s">
         <v>27</v>
       </c>
@@ -5877,7 +5874,7 @@
         <v>14539693914.48213</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A7" s="13" t="s">
         <v>28</v>
       </c>
@@ -5903,7 +5900,7 @@
         <v>14952064687.920418</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A8" s="13" t="s">
         <v>29</v>
       </c>
@@ -5929,7 +5926,7 @@
         <v>15245174854.3053</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A9" s="13" t="s">
         <v>30</v>
       </c>
@@ -5955,7 +5952,7 @@
         <v>15630580395.880232</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A10" s="13" t="s">
         <v>31</v>
       </c>
@@ -5981,7 +5978,7 @@
         <v>16067461867.683767</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A11" s="13" t="s">
         <v>32</v>
       </c>
@@ -6007,7 +6004,7 @@
         <v>16512311423.171005</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A12" s="13" t="s">
         <v>33</v>
       </c>
@@ -6033,7 +6030,7 @@
         <v>17173198592.745512</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A13" s="13" t="s">
         <v>34</v>
       </c>
@@ -6059,7 +6056,7 @@
         <v>17575027945.751125</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A14" s="13" t="s">
         <v>35</v>
       </c>
@@ -6085,7 +6082,7 @@
         <v>17807088213.890675</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A15" s="13" t="s">
         <v>36</v>
       </c>
@@ -6111,7 +6108,7 @@
         <v>18004403454.357212</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.45">
       <c r="A16" s="13" t="s">
         <v>37</v>
       </c>
@@ -6137,7 +6134,7 @@
         <v>18502743951.352955</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" s="13" t="s">
         <v>38</v>
       </c>
@@ -6163,7 +6160,7 @@
         <v>18893014123.791737</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" s="13" t="s">
         <v>39</v>
       </c>
@@ -6189,7 +6186,7 @@
         <v>19582440522.206104</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" s="13" t="s">
         <v>40</v>
       </c>
@@ -6215,7 +6212,7 @@
         <v>20221659294.512562</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" s="13" t="s">
         <v>41</v>
       </c>
@@ -6241,7 +6238,7 @@
         <v>20401425207.663731</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" s="13" t="s">
         <v>42</v>
       </c>
@@ -6267,7 +6264,7 @@
         <v>19535384606.465698</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" s="13" t="s">
         <v>43</v>
       </c>
@@ -6294,7 +6291,7 @@
       </c>
       <c r="K22" s="13"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" s="13" t="s">
         <v>44</v>
       </c>
@@ -6320,7 +6317,7 @@
         <v>20396856277.427464</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" s="13" t="s">
         <v>45</v>
       </c>
@@ -6346,7 +6343,7 @@
         <v>20238230228.845612</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" s="13" t="s">
         <v>46</v>
       </c>
@@ -6372,7 +6369,7 @@
         <v>20228258715.518364</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" s="13" t="s">
         <v>47</v>
       </c>
@@ -6398,7 +6395,7 @@
         <v>20577815766.621822</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" s="13" t="s">
         <v>48</v>
       </c>
@@ -6424,7 +6421,7 @@
         <v>21081628480.603973</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" s="13" t="s">
         <v>49</v>
       </c>
@@ -6450,7 +6447,7 @@
         <v>21505364965.621891</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" s="13" t="s">
         <v>50</v>
       </c>
@@ -6476,7 +6473,7 @@
         <v>22152924720.812515</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" s="13" t="s">
         <v>51</v>
       </c>
@@ -6502,7 +6499,7 @@
         <v>22640578323.033131</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" s="13" t="s">
         <v>52</v>
       </c>
@@ -6528,7 +6525,7 @@
         <v>23112148514.524086</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" s="13" t="s">
         <v>53</v>
       </c>
@@ -6554,7 +6551,7 @@
         <v>21838278294.189957</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A33" s="13" t="s">
         <v>54</v>
       </c>
@@ -6580,7 +6577,7 @@
         <v>23267260238.964119</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A34" s="13" t="s">
         <v>55</v>
       </c>
@@ -6606,7 +6603,7 @@
         <v>24152188840.065418</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A35" s="13" t="s">
         <v>56</v>
       </c>
@@ -6632,7 +6629,7 @@
         <v>24276616351.55632</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A36" s="13" t="s">
         <v>57</v>
       </c>
@@ -6658,13 +6655,13 @@
         <v>24466165583.505955</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A37" s="13"/>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>2015</v>
       </c>
@@ -6684,7 +6681,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A39" s="28" t="s">
         <v>168</v>
       </c>
@@ -6699,13 +6696,13 @@
         <f>D38/B38</f>
         <v>2.6578482824228877</v>
       </c>
-      <c r="K39" s="62" t="s">
+      <c r="K39" s="81" t="s">
         <v>169</v>
       </c>
-      <c r="L39" s="62"/>
-      <c r="M39" s="62"/>
-    </row>
-    <row r="40" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+      <c r="L39" s="81"/>
+      <c r="M39" s="81"/>
+    </row>
+    <row r="40" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A40" s="3" t="s">
         <v>202</v>
       </c>
@@ -6732,7 +6729,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" s="28" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A41" s="3" t="s">
         <v>168</v>
       </c>
@@ -6760,7 +6757,7 @@
         <v>2.3703888007815599</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A42" s="12" t="s">
         <v>67</v>
       </c>
@@ -6789,7 +6786,7 @@
         <v>2.4480223372362699</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A43" s="11" t="s">
         <v>72</v>
       </c>
@@ -6819,7 +6816,7 @@
         <v>2.5245850802099499</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A44" s="3" t="s">
         <v>73</v>
       </c>
@@ -6848,7 +6845,7 @@
         <v>2.5427605678518299</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="29.15" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:13" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
         <v>71</v>
       </c>
@@ -6877,7 +6874,7 @@
         <v>2.31134286871607</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>60</v>
       </c>
@@ -6894,7 +6891,7 @@
         <v>2.4394199309591356</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>203</v>
       </c>
@@ -6902,7 +6899,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>204</v>
       </c>
@@ -6910,7 +6907,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>205</v>
       </c>
@@ -6918,7 +6915,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>64</v>
       </c>
@@ -6926,11 +6923,11 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A52" s="28"/>
       <c r="B52" s="28"/>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>65</v>
       </c>
@@ -6954,13 +6951,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC11EFA9-274E-476D-8BFE-D8769B6BF052}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="28.69140625" customWidth="1"/>
-    <col min="2" max="2" width="11.61328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B1" s="28" t="s">
         <v>2</v>
       </c>
@@ -6980,7 +6977,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="28" t="s">
         <v>113</v>
       </c>
@@ -7009,7 +7006,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="28" t="s">
         <v>112</v>
       </c>
@@ -7038,7 +7035,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>111</v>
       </c>
@@ -7067,7 +7064,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -7075,7 +7072,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>115</v>
       </c>
@@ -7097,7 +7094,7 @@
         <v>0.74445404791547987</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>116</v>
       </c>
@@ -7115,7 +7112,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>117</v>
       </c>
@@ -7126,7 +7123,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>118</v>
       </c>
@@ -7137,7 +7134,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>119</v>
       </c>
@@ -7148,7 +7145,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>120</v>
       </c>
@@ -7167,114 +7164,114 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE07EBE8-6449-4730-9E28-CE2F7AF6313A}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.07421875" customWidth="1"/>
+    <col min="1" max="1" width="13.06640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2">
         <f>170/74</f>
         <v>2.2972972972972974</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3">
         <f>1055/74</f>
         <v>14.256756756756756</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" s="35"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" s="35">
         <f>((Population!C116/100)*A2)*1000</f>
         <v>17.76876871873117</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" s="35">
         <f>((Population!C116/100)*A3)*1000</f>
         <v>110.27088822506695</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" s="35"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" s="35" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" s="14">
         <v>1000000000</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="15" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" s="20"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" s="22"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" s="22">
         <f>A2*1000000000/(Population!B115*1000)</f>
         <v>0.264704634686033</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" s="22">
         <f>A3*1000000000/(Population!B115*1000)</f>
         <v>1.6427258211397928</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" s="33" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" s="20"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19">
         <f>(Capacité!C43/100)*A2</f>
         <v>1.2114682525646763E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20">
         <f>(Capacité!C43/100)*A3</f>
         <v>7.5182294497396079E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="15"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24">
         <f>A2*Besoins!B5*1000</f>
         <v>14.648366196075427</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" s="28">
         <f>A3*Besoins!B5*1000</f>
         <v>90.906037275644564</v>
